--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="FightTypeConquerInfo" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="62">
   <si>
     <t>id</t>
   </si>
@@ -83,6 +83,18 @@
     <t>level_add</t>
   </si>
   <si>
+    <t>drop_crystal</t>
+  </si>
+  <si>
+    <t>reward_crystal</t>
+  </si>
+  <si>
+    <t>reward_equip_rarity</t>
+  </si>
+  <si>
+    <t>reward_equip_attribute_add</t>
+  </si>
+  <si>
     <t>remark</t>
   </si>
   <si>
@@ -150,6 +162,18 @@
   </si>
   <si>
     <t>难度数值加成</t>
+  </si>
+  <si>
+    <t>掉落魔晶</t>
+  </si>
+  <si>
+    <t>奖励-魔晶</t>
+  </si>
+  <si>
+    <t>奖励-装备稀有度</t>
+  </si>
+  <si>
+    <t>奖励-装备属性加成</t>
   </si>
   <si>
     <t>备注</t>
@@ -1159,7 +1183,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S81"/>
+  <dimension ref="A1:W81"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="3" max="3" width="17.125" customWidth="1"/>
@@ -1169,12 +1193,15 @@
     <col min="8" max="8" width="18.25" customWidth="1"/>
     <col min="9" max="16" width="16" customWidth="1"/>
     <col min="17" max="17" width="12.25" customWidth="1"/>
-    <col min="18" max="18" width="12.875" customWidth="1"/>
-    <col min="19" max="19" width="42.875" customWidth="1"/>
-    <col min="20" max="20" width="25.125" customWidth="1"/>
+    <col min="18" max="19" width="12.875" customWidth="1"/>
+    <col min="20" max="20" width="17.375" customWidth="1"/>
+    <col min="21" max="21" width="19.75" customWidth="1"/>
+    <col min="22" max="22" width="29.375" customWidth="1"/>
+    <col min="23" max="23" width="42.875" customWidth="1"/>
+    <col min="24" max="24" width="25.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:23">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1232,126 +1259,162 @@
       <c r="S1" t="s">
         <v>18</v>
       </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:23">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="M2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="N2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="O2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="P2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="Q2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="R2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="S2" t="s">
-        <v>20</v>
+        <v>25</v>
+      </c>
+      <c r="T2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W2" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:19">
+    <row r="3" spans="1:23">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E3" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H3" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I3" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="K3" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="M3" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="N3" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="O3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="P3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="Q3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="R3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="S3" t="s">
-        <v>41</v>
+        <v>45</v>
+      </c>
+      <c r="T3" t="s">
+        <v>46</v>
+      </c>
+      <c r="U3" t="s">
+        <v>47</v>
+      </c>
+      <c r="V3" t="s">
+        <v>48</v>
+      </c>
+      <c r="W3" t="s">
+        <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:19">
+    <row r="4" spans="1:23">
       <c r="A4">
         <v>1000001</v>
       </c>
@@ -1359,16 +1422,16 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D4" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G4" s="1">
         <v>10</v>
@@ -1406,11 +1469,23 @@
       <c r="R4">
         <v>1</v>
       </c>
-      <c r="S4" t="s">
-        <v>44</v>
+      <c r="S4">
+        <v>1</v>
+      </c>
+      <c r="T4">
+        <v>100</v>
+      </c>
+      <c r="U4">
+        <v>1</v>
+      </c>
+      <c r="V4">
+        <v>5</v>
+      </c>
+      <c r="W4" t="s">
+        <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:19">
+    <row r="5" spans="1:23">
       <c r="A5">
         <v>1000002</v>
       </c>
@@ -1418,16 +1493,16 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G5" s="1">
         <v>15</v>
@@ -1465,11 +1540,23 @@
       <c r="R5">
         <v>2</v>
       </c>
-      <c r="S5" t="s">
-        <v>45</v>
+      <c r="S5">
+        <v>1</v>
+      </c>
+      <c r="T5">
+        <v>200</v>
+      </c>
+      <c r="U5">
+        <v>1</v>
+      </c>
+      <c r="V5">
+        <v>10</v>
+      </c>
+      <c r="W5" t="s">
+        <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:19">
+    <row r="6" spans="1:23">
       <c r="A6">
         <v>1000003</v>
       </c>
@@ -1477,16 +1564,16 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G6" s="1">
         <v>20</v>
@@ -1524,11 +1611,23 @@
       <c r="R6">
         <v>3</v>
       </c>
-      <c r="S6" t="s">
-        <v>46</v>
+      <c r="S6">
+        <v>2</v>
+      </c>
+      <c r="T6">
+        <v>300</v>
+      </c>
+      <c r="U6">
+        <v>1</v>
+      </c>
+      <c r="V6">
+        <v>15</v>
+      </c>
+      <c r="W6" t="s">
+        <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:19">
+    <row r="7" spans="1:23">
       <c r="A7">
         <v>1000004</v>
       </c>
@@ -1536,16 +1635,16 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G7" s="1">
         <v>25</v>
@@ -1583,11 +1682,23 @@
       <c r="R7">
         <v>4</v>
       </c>
-      <c r="S7" t="s">
-        <v>47</v>
+      <c r="S7">
+        <v>2</v>
+      </c>
+      <c r="T7">
+        <v>400</v>
+      </c>
+      <c r="U7">
+        <v>1</v>
+      </c>
+      <c r="V7">
+        <v>20</v>
+      </c>
+      <c r="W7" t="s">
+        <v>55</v>
       </c>
     </row>
-    <row r="8" spans="1:19">
+    <row r="8" spans="1:23">
       <c r="A8">
         <v>1000005</v>
       </c>
@@ -1595,16 +1706,16 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G8" s="1">
         <v>30</v>
@@ -1642,11 +1753,23 @@
       <c r="R8">
         <v>5</v>
       </c>
-      <c r="S8" t="s">
-        <v>48</v>
+      <c r="S8">
+        <v>3</v>
+      </c>
+      <c r="T8">
+        <v>500</v>
+      </c>
+      <c r="U8">
+        <v>1</v>
+      </c>
+      <c r="V8">
+        <v>25</v>
+      </c>
+      <c r="W8" t="s">
+        <v>56</v>
       </c>
     </row>
-    <row r="9" spans="1:19">
+    <row r="9" spans="1:23">
       <c r="A9">
         <v>1000006</v>
       </c>
@@ -1654,16 +1777,16 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G9" s="1">
         <v>35</v>
@@ -1701,11 +1824,23 @@
       <c r="R9">
         <v>6</v>
       </c>
-      <c r="S9" t="s">
-        <v>49</v>
+      <c r="S9">
+        <v>3</v>
+      </c>
+      <c r="T9">
+        <v>600</v>
+      </c>
+      <c r="U9">
+        <v>1</v>
+      </c>
+      <c r="V9">
+        <v>30</v>
+      </c>
+      <c r="W9" t="s">
+        <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:19">
+    <row r="10" spans="1:23">
       <c r="A10">
         <v>1000007</v>
       </c>
@@ -1713,16 +1848,16 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D10" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G10" s="1">
         <v>40</v>
@@ -1760,11 +1895,23 @@
       <c r="R10">
         <v>7</v>
       </c>
-      <c r="S10" t="s">
-        <v>50</v>
+      <c r="S10">
+        <v>4</v>
+      </c>
+      <c r="T10">
+        <v>700</v>
+      </c>
+      <c r="U10">
+        <v>1</v>
+      </c>
+      <c r="V10">
+        <v>35</v>
+      </c>
+      <c r="W10" t="s">
+        <v>58</v>
       </c>
     </row>
-    <row r="11" spans="1:19">
+    <row r="11" spans="1:23">
       <c r="A11">
         <v>1000008</v>
       </c>
@@ -1772,16 +1919,16 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D11" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G11" s="1">
         <v>45</v>
@@ -1819,11 +1966,23 @@
       <c r="R11">
         <v>8</v>
       </c>
-      <c r="S11" t="s">
-        <v>51</v>
+      <c r="S11">
+        <v>4</v>
+      </c>
+      <c r="T11">
+        <v>800</v>
+      </c>
+      <c r="U11">
+        <v>1</v>
+      </c>
+      <c r="V11">
+        <v>40</v>
+      </c>
+      <c r="W11" t="s">
+        <v>59</v>
       </c>
     </row>
-    <row r="12" spans="1:19">
+    <row r="12" spans="1:23">
       <c r="A12">
         <v>1000009</v>
       </c>
@@ -1831,16 +1990,16 @@
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D12" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G12" s="1">
         <v>50</v>
@@ -1878,11 +2037,23 @@
       <c r="R12">
         <v>9</v>
       </c>
-      <c r="S12" t="s">
-        <v>52</v>
+      <c r="S12">
+        <v>5</v>
+      </c>
+      <c r="T12">
+        <v>900</v>
+      </c>
+      <c r="U12">
+        <v>1</v>
+      </c>
+      <c r="V12">
+        <v>45</v>
+      </c>
+      <c r="W12" t="s">
+        <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:19">
+    <row r="13" spans="1:23">
       <c r="A13">
         <v>1000010</v>
       </c>
@@ -1890,16 +2061,16 @@
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D13" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G13" s="1">
         <v>55</v>
@@ -1937,8 +2108,20 @@
       <c r="R13">
         <v>10</v>
       </c>
-      <c r="S13" t="s">
-        <v>53</v>
+      <c r="S13">
+        <v>5</v>
+      </c>
+      <c r="T13">
+        <v>1000</v>
+      </c>
+      <c r="U13">
+        <v>1</v>
+      </c>
+      <c r="V13">
+        <v>50</v>
+      </c>
+      <c r="W13" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="19575" windowHeight="11505"/>
   </bookViews>
   <sheets>
     <sheet name="FightTypeConquerInfo" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="64">
   <si>
     <t>id</t>
   </si>
@@ -116,16 +116,16 @@
     <t>世界ID</t>
   </si>
   <si>
-    <t>战斗场景列表</t>
-  </si>
-  <si>
-    <t>boss战斗场景列表</t>
-  </si>
-  <si>
-    <t>敌人列表</t>
-  </si>
-  <si>
-    <t>boss列表</t>
+    <t>战斗场景列表（用&amp;分割）</t>
+  </si>
+  <si>
+    <t>boss战斗场景列表（用&amp;分割）</t>
+  </si>
+  <si>
+    <t>敌人列表（npcInfoId用&amp;分割）（npcInfoId用&amp;分割）</t>
+  </si>
+  <si>
+    <t>boss列表（npcInfoId用&amp;分割）</t>
   </si>
   <si>
     <t>敌人数量</t>
@@ -182,10 +182,16 @@
     <t>1&amp;1</t>
   </si>
   <si>
+    <t>1010010001&amp;1020010001</t>
+  </si>
+  <si>
+    <t>1020020001&amp;1020030001&amp;1010020001</t>
+  </si>
+  <si>
+    <t>剑与魔法-难度1</t>
+  </si>
+  <si>
     <t>1010010001&amp;1010010001</t>
-  </si>
-  <si>
-    <t>剑与魔法-难度1</t>
   </si>
   <si>
     <t>剑与魔法-难度2</t>
@@ -1187,8 +1193,9 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="3" max="3" width="17.125" customWidth="1"/>
-    <col min="4" max="4" width="22.625" customWidth="1"/>
-    <col min="5" max="6" width="23.75" customWidth="1"/>
+    <col min="4" max="4" width="36.5" customWidth="1"/>
+    <col min="5" max="5" width="23.75" customWidth="1"/>
+    <col min="6" max="6" width="32.625" customWidth="1"/>
     <col min="7" max="7" width="10.375" customWidth="1"/>
     <col min="8" max="8" width="18.25" customWidth="1"/>
     <col min="9" max="16" width="16" customWidth="1"/>
@@ -1431,7 +1438,7 @@
         <v>51</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G4" s="1">
         <v>10</v>
@@ -1452,7 +1459,7 @@
         <v>6</v>
       </c>
       <c r="M4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N4">
         <v>3</v>
@@ -1482,7 +1489,7 @@
         <v>5</v>
       </c>
       <c r="W4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:23">
@@ -1499,10 +1506,10 @@
         <v>50</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G5" s="1">
         <v>15</v>
@@ -1553,7 +1560,7 @@
         <v>10</v>
       </c>
       <c r="W5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:23">
@@ -1570,10 +1577,10 @@
         <v>50</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G6" s="1">
         <v>20</v>
@@ -1624,7 +1631,7 @@
         <v>15</v>
       </c>
       <c r="W6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:23">
@@ -1641,10 +1648,10 @@
         <v>50</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G7" s="1">
         <v>25</v>
@@ -1695,7 +1702,7 @@
         <v>20</v>
       </c>
       <c r="W7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:23">
@@ -1712,10 +1719,10 @@
         <v>50</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G8" s="1">
         <v>30</v>
@@ -1766,7 +1773,7 @@
         <v>25</v>
       </c>
       <c r="W8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:23">
@@ -1783,10 +1790,10 @@
         <v>50</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G9" s="1">
         <v>35</v>
@@ -1837,7 +1844,7 @@
         <v>30</v>
       </c>
       <c r="W9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:23">
@@ -1854,10 +1861,10 @@
         <v>50</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G10" s="1">
         <v>40</v>
@@ -1908,7 +1915,7 @@
         <v>35</v>
       </c>
       <c r="W10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:23">
@@ -1925,10 +1932,10 @@
         <v>50</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G11" s="1">
         <v>45</v>
@@ -1979,7 +1986,7 @@
         <v>40</v>
       </c>
       <c r="W11" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:23">
@@ -1996,10 +2003,10 @@
         <v>50</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G12" s="1">
         <v>50</v>
@@ -2050,7 +2057,7 @@
         <v>45</v>
       </c>
       <c r="W12" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:23">
@@ -2067,10 +2074,10 @@
         <v>50</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G13" s="1">
         <v>55</v>
@@ -2121,7 +2128,7 @@
         <v>50</v>
       </c>
       <c r="W13" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="FightTypeConquerInfo" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
   <si>
     <t>id</t>
   </si>
@@ -179,16 +179,22 @@
     <t>备注</t>
   </si>
   <si>
+    <t>99999</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>1010010001</t>
+  </si>
+  <si>
+    <t>1010020001</t>
+  </si>
+  <si>
+    <t>剑与魔法-难度1</t>
+  </si>
+  <si>
     <t>1&amp;1</t>
-  </si>
-  <si>
-    <t>1010010001&amp;1020010001</t>
-  </si>
-  <si>
-    <t>1020020001&amp;1020030001&amp;1010020001</t>
-  </si>
-  <si>
-    <t>剑与魔法-难度1</t>
   </si>
   <si>
     <t>1010010001&amp;1010010001</t>
@@ -236,7 +242,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -244,7 +249,6 @@
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -252,14 +256,12 @@
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -267,7 +269,6 @@
       <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -275,7 +276,6 @@
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -283,7 +283,6 @@
       <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -291,7 +290,6 @@
       <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -299,14 +297,12 @@
       <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -314,7 +310,6 @@
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -322,7 +317,6 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -330,14 +324,12 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -345,42 +337,36 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -689,156 +675,303 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+  <cellXfs count="51">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="2" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="3" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="4" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="5" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="7" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" xfId="8" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="9" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="4" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="10" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="11" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="6" applyFont="1" fillId="0" applyFill="1" borderId="2" applyBorder="1" xfId="12" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="7" applyFont="1" fillId="0" applyFill="1" borderId="2" applyBorder="1" xfId="13" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="8" applyFont="1" fillId="0" applyFill="1" borderId="3" applyBorder="1" xfId="14" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="8" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="15" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="9" applyFont="1" fillId="3" applyFill="1" borderId="4" applyBorder="1" xfId="16" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="10" applyFont="1" fillId="4" applyFill="1" borderId="5" applyBorder="1" xfId="17" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="11" applyFont="1" fillId="4" applyFill="1" borderId="4" applyBorder="1" xfId="18" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="12" applyFont="1" fillId="5" applyFill="1" borderId="6" applyBorder="1" xfId="19" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="13" applyFont="1" fillId="0" applyFill="1" borderId="7" applyBorder="1" xfId="20" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="14" applyFont="1" fillId="0" applyFill="1" borderId="8" applyBorder="1" xfId="21" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="15" applyFont="1" fillId="6" applyFill="1" borderId="0" applyBorder="1" xfId="22" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="16" applyFont="1" fillId="7" applyFill="1" borderId="0" applyBorder="1" xfId="23" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="17" applyFont="1" fillId="8" applyFill="1" borderId="0" applyBorder="1" xfId="24" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="9" applyFill="1" borderId="0" applyBorder="1" xfId="25" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="1" xfId="26" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="11" applyFill="1" borderId="0" applyBorder="1" xfId="27" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="12" applyFill="1" borderId="0" applyBorder="1" xfId="28" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="13" applyFill="1" borderId="0" applyBorder="1" xfId="29" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="14" applyFill="1" borderId="0" applyBorder="1" xfId="30" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="15" applyFill="1" borderId="0" applyBorder="1" xfId="31" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="16" applyFill="1" borderId="0" applyBorder="1" xfId="32" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="17" applyFill="1" borderId="0" applyBorder="1" xfId="33" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="18" applyFill="1" borderId="0" applyBorder="1" xfId="34" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="19" applyFill="1" borderId="0" applyBorder="1" xfId="35" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="20" applyFill="1" borderId="0" applyBorder="1" xfId="36" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="21" applyFill="1" borderId="0" applyBorder="1" xfId="37" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="22" applyFill="1" borderId="0" applyBorder="1" xfId="38" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="23" applyFill="1" borderId="0" applyBorder="1" xfId="39" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="24" applyFill="1" borderId="0" applyBorder="1" xfId="40" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="25" applyFill="1" borderId="0" applyBorder="1" xfId="41" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="26" applyFill="1" borderId="0" applyBorder="1" xfId="42" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="27" applyFill="1" borderId="0" applyBorder="1" xfId="43" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="28" applyFill="1" borderId="0" applyBorder="1" xfId="44" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="29" applyFill="1" borderId="0" applyBorder="1" xfId="45" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="30" applyFill="1" borderId="0" applyBorder="1" xfId="46" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="31" applyFill="1" borderId="0" applyBorder="1" xfId="47" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="32" applyFill="1" borderId="0" applyBorder="1" xfId="48" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1189,946 +1322,946 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W81"/>
+  <dimension ref="A1:W13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="3" max="3" width="17.125" customWidth="1"/>
-    <col min="4" max="4" width="36.5" customWidth="1"/>
-    <col min="5" max="5" width="23.75" customWidth="1"/>
-    <col min="6" max="6" width="32.625" customWidth="1"/>
-    <col min="7" max="7" width="10.375" customWidth="1"/>
-    <col min="8" max="8" width="18.25" customWidth="1"/>
-    <col min="9" max="16" width="16" customWidth="1"/>
-    <col min="17" max="17" width="12.25" customWidth="1"/>
-    <col min="18" max="19" width="12.875" customWidth="1"/>
-    <col min="20" max="20" width="17.375" customWidth="1"/>
-    <col min="21" max="21" width="19.75" customWidth="1"/>
-    <col min="22" max="22" width="29.375" customWidth="1"/>
-    <col min="23" max="23" width="42.875" customWidth="1"/>
-    <col min="24" max="24" width="25.125" customWidth="1"/>
+    <col min="3" max="3" width="17.125" customWidth="1" style="49"/>
+    <col min="4" max="4" width="36.5" customWidth="1" style="49"/>
+    <col min="5" max="5" width="23.75" customWidth="1" style="49"/>
+    <col min="6" max="6" width="32.625" customWidth="1" style="49"/>
+    <col min="7" max="7" width="10.375" customWidth="1" style="49"/>
+    <col min="8" max="8" width="18.25" customWidth="1" style="49"/>
+    <col min="9" max="16" width="16" customWidth="1" style="49"/>
+    <col min="17" max="17" width="12.25" customWidth="1" style="49"/>
+    <col min="18" max="19" width="12.875" customWidth="1" style="49"/>
+    <col min="20" max="20" width="17.375" customWidth="1" style="49"/>
+    <col min="21" max="21" width="19.75" customWidth="1" style="49"/>
+    <col min="22" max="22" width="29.375" customWidth="1" style="49"/>
+    <col min="23" max="23" width="42.875" customWidth="1" style="49"/>
+    <col min="24" max="24" width="25.125" customWidth="1" style="49"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="B1" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
+      <c r="K1" s="49" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+      <c r="W1" s="49" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:23">
-      <c r="A2" t="s">
+    <row r="2">
+      <c r="A2" s="49" t="s">
         <v>23</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="49" t="s">
         <v>23</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="49" t="s">
         <v>24</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="49" t="s">
         <v>24</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="49" t="s">
         <v>24</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="49" t="s">
         <v>24</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="O2" t="s">
+      <c r="O2" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="P2" t="s">
+      <c r="P2" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="Q2" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="R2" t="s">
+      <c r="R2" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="S2" t="s">
+      <c r="S2" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="T2" t="s">
+      <c r="T2" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="U2" t="s">
+      <c r="U2" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="V2" t="s">
+      <c r="V2" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="W2" t="s">
+      <c r="W2" s="49" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:23">
-      <c r="A3" t="s">
+    <row r="3">
+      <c r="A3" s="49" t="s">
         <v>27</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="49" t="s">
         <v>28</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="49" t="s">
         <v>29</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="49" t="s">
         <v>31</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="49" t="s">
         <v>32</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="49" t="s">
         <v>33</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="49" t="s">
         <v>35</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="49" t="s">
         <v>37</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" s="49" t="s">
         <v>38</v>
       </c>
-      <c r="M3" t="s">
+      <c r="M3" s="49" t="s">
         <v>39</v>
       </c>
-      <c r="N3" t="s">
+      <c r="N3" s="49" t="s">
         <v>40</v>
       </c>
-      <c r="O3" t="s">
+      <c r="O3" s="49" t="s">
         <v>41</v>
       </c>
-      <c r="P3" t="s">
+      <c r="P3" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="Q3" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="R3" t="s">
+      <c r="R3" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="S3" t="s">
+      <c r="S3" s="49" t="s">
         <v>45</v>
       </c>
-      <c r="T3" t="s">
+      <c r="T3" s="49" t="s">
         <v>46</v>
       </c>
-      <c r="U3" t="s">
+      <c r="U3" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="V3" t="s">
+      <c r="V3" s="49" t="s">
         <v>48</v>
       </c>
-      <c r="W3" t="s">
+      <c r="W3" s="49" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:23">
-      <c r="A4">
+    <row r="4">
+      <c r="A4" s="49">
         <v>1000001</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B4" s="49">
+        <v>1</v>
+      </c>
+      <c r="C4" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="49" t="s">
+        <v>51</v>
+      </c>
+      <c r="E4" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="F4" s="50" t="s">
+        <v>53</v>
+      </c>
+      <c r="G4" s="50">
+        <v>10</v>
+      </c>
+      <c r="H4" s="50">
+        <v>3</v>
+      </c>
+      <c r="I4" s="50">
+        <v>10</v>
+      </c>
+      <c r="J4" s="50">
+        <v>10</v>
+      </c>
+      <c r="K4" s="49">
+        <v>5</v>
+      </c>
+      <c r="L4" s="49">
+        <v>6</v>
+      </c>
+      <c r="M4" s="49">
+        <v>2</v>
+      </c>
+      <c r="N4" s="49">
+        <v>3</v>
+      </c>
+      <c r="O4" s="49">
+        <v>10</v>
+      </c>
+      <c r="P4" s="49">
+        <v>10</v>
+      </c>
+      <c r="Q4" s="49">
+        <v>1</v>
+      </c>
+      <c r="R4" s="49">
+        <v>1</v>
+      </c>
+      <c r="S4" s="49">
+        <v>1</v>
+      </c>
+      <c r="T4" s="49">
+        <v>100</v>
+      </c>
+      <c r="U4" s="49">
+        <v>1</v>
+      </c>
+      <c r="V4" s="49">
+        <v>5</v>
+      </c>
+      <c r="W4" s="49" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="49">
+        <v>1000002</v>
+      </c>
+      <c r="B5" s="49">
+        <v>1</v>
+      </c>
+      <c r="C5" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5" s="50" t="s">
+        <v>56</v>
+      </c>
+      <c r="F5" s="50" t="s">
+        <v>56</v>
+      </c>
+      <c r="G5" s="50">
+        <v>15</v>
+      </c>
+      <c r="H5" s="50">
+        <v>3</v>
+      </c>
+      <c r="I5" s="50">
+        <v>10</v>
+      </c>
+      <c r="J5" s="50">
+        <v>10</v>
+      </c>
+      <c r="K5" s="49">
+        <v>5</v>
+      </c>
+      <c r="L5" s="49">
+        <v>7</v>
+      </c>
+      <c r="M5" s="49">
+        <v>3</v>
+      </c>
+      <c r="N5" s="49">
+        <v>4</v>
+      </c>
+      <c r="O5" s="49">
+        <v>9</v>
+      </c>
+      <c r="P5" s="49">
+        <v>10</v>
+      </c>
+      <c r="Q5" s="49">
+        <v>2</v>
+      </c>
+      <c r="R5" s="49">
+        <v>2</v>
+      </c>
+      <c r="S5" s="49">
+        <v>1</v>
+      </c>
+      <c r="T5" s="49">
+        <v>200</v>
+      </c>
+      <c r="U5" s="49">
+        <v>1</v>
+      </c>
+      <c r="V5" s="49">
+        <v>10</v>
+      </c>
+      <c r="W5" s="49" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="49">
+        <v>1000003</v>
+      </c>
+      <c r="B6" s="49">
+        <v>1</v>
+      </c>
+      <c r="C6" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" s="50" t="s">
+        <v>56</v>
+      </c>
+      <c r="F6" s="50" t="s">
+        <v>56</v>
+      </c>
+      <c r="G6" s="50">
+        <v>20</v>
+      </c>
+      <c r="H6" s="50">
+        <v>3</v>
+      </c>
+      <c r="I6" s="50">
+        <v>10</v>
+      </c>
+      <c r="J6" s="50">
+        <v>10</v>
+      </c>
+      <c r="K6" s="49">
+        <v>6</v>
+      </c>
+      <c r="L6" s="49">
+        <v>8</v>
+      </c>
+      <c r="M6" s="49">
+        <v>3</v>
+      </c>
+      <c r="N6" s="49">
+        <v>5</v>
+      </c>
+      <c r="O6" s="49">
+        <v>8</v>
+      </c>
+      <c r="P6" s="49">
+        <v>10</v>
+      </c>
+      <c r="Q6" s="49">
+        <v>3</v>
+      </c>
+      <c r="R6" s="49">
+        <v>3</v>
+      </c>
+      <c r="S6" s="49">
+        <v>2</v>
+      </c>
+      <c r="T6" s="49">
+        <v>300</v>
+      </c>
+      <c r="U6" s="49">
+        <v>1</v>
+      </c>
+      <c r="V6" s="49">
+        <v>15</v>
+      </c>
+      <c r="W6" s="49" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="49">
+        <v>1000004</v>
+      </c>
+      <c r="B7" s="49">
+        <v>1</v>
+      </c>
+      <c r="C7" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="E7" s="50" t="s">
+        <v>56</v>
+      </c>
+      <c r="F7" s="50" t="s">
+        <v>56</v>
+      </c>
+      <c r="G7" s="50">
+        <v>25</v>
+      </c>
+      <c r="H7" s="50">
+        <v>3</v>
+      </c>
+      <c r="I7" s="50">
+        <v>10</v>
+      </c>
+      <c r="J7" s="50">
+        <v>10</v>
+      </c>
+      <c r="K7" s="49">
+        <v>6</v>
+      </c>
+      <c r="L7" s="49">
+        <v>9</v>
+      </c>
+      <c r="M7" s="49">
+        <v>3</v>
+      </c>
+      <c r="N7" s="49">
+        <v>6</v>
+      </c>
+      <c r="O7" s="49">
+        <v>7</v>
+      </c>
+      <c r="P7" s="49">
+        <v>10</v>
+      </c>
+      <c r="Q7" s="49">
+        <v>4</v>
+      </c>
+      <c r="R7" s="49">
+        <v>4</v>
+      </c>
+      <c r="S7" s="49">
+        <v>2</v>
+      </c>
+      <c r="T7" s="49">
+        <v>400</v>
+      </c>
+      <c r="U7" s="49">
+        <v>1</v>
+      </c>
+      <c r="V7" s="49">
+        <v>20</v>
+      </c>
+      <c r="W7" s="49" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="49">
+        <v>1000005</v>
+      </c>
+      <c r="B8" s="49">
+        <v>1</v>
+      </c>
+      <c r="C8" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="E8" s="50" t="s">
+        <v>56</v>
+      </c>
+      <c r="F8" s="50" t="s">
+        <v>56</v>
+      </c>
+      <c r="G8" s="50">
+        <v>30</v>
+      </c>
+      <c r="H8" s="50">
+        <v>3</v>
+      </c>
+      <c r="I8" s="50">
+        <v>10</v>
+      </c>
+      <c r="J8" s="50">
+        <v>10</v>
+      </c>
+      <c r="K8" s="49">
+        <v>7</v>
+      </c>
+      <c r="L8" s="49">
+        <v>10</v>
+      </c>
+      <c r="M8" s="49">
+        <v>2</v>
+      </c>
+      <c r="N8" s="49">
+        <v>6</v>
+      </c>
+      <c r="O8" s="49">
+        <v>6</v>
+      </c>
+      <c r="P8" s="49">
+        <v>10</v>
+      </c>
+      <c r="Q8" s="49">
+        <v>5</v>
+      </c>
+      <c r="R8" s="49">
+        <v>5</v>
+      </c>
+      <c r="S8" s="49">
+        <v>3</v>
+      </c>
+      <c r="T8" s="49">
+        <v>500</v>
+      </c>
+      <c r="U8" s="49">
+        <v>1</v>
+      </c>
+      <c r="V8" s="49">
+        <v>25</v>
+      </c>
+      <c r="W8" s="49" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="49">
+        <v>1000006</v>
+      </c>
+      <c r="B9" s="49">
+        <v>1</v>
+      </c>
+      <c r="C9" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="E9" s="50" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" s="50" t="s">
+        <v>56</v>
+      </c>
+      <c r="G9" s="50">
+        <v>35</v>
+      </c>
+      <c r="H9" s="50">
+        <v>3</v>
+      </c>
+      <c r="I9" s="50">
+        <v>10</v>
+      </c>
+      <c r="J9" s="50">
+        <v>10</v>
+      </c>
+      <c r="K9" s="49">
+        <v>8</v>
+      </c>
+      <c r="L9" s="49">
+        <v>11</v>
+      </c>
+      <c r="M9" s="49">
+        <v>1</v>
+      </c>
+      <c r="N9" s="49">
+        <v>6</v>
+      </c>
+      <c r="O9" s="49">
+        <v>5</v>
+      </c>
+      <c r="P9" s="49">
+        <v>10</v>
+      </c>
+      <c r="Q9" s="49">
+        <v>6</v>
+      </c>
+      <c r="R9" s="49">
+        <v>6</v>
+      </c>
+      <c r="S9" s="49">
+        <v>3</v>
+      </c>
+      <c r="T9" s="49">
+        <v>600</v>
+      </c>
+      <c r="U9" s="49">
+        <v>1</v>
+      </c>
+      <c r="V9" s="49">
+        <v>30</v>
+      </c>
+      <c r="W9" s="49" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="49">
+        <v>1000007</v>
+      </c>
+      <c r="B10" s="49">
+        <v>1</v>
+      </c>
+      <c r="C10" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" s="50" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" s="50" t="s">
+        <v>56</v>
+      </c>
+      <c r="G10" s="50">
+        <v>40</v>
+      </c>
+      <c r="H10" s="50">
+        <v>3</v>
+      </c>
+      <c r="I10" s="50">
+        <v>10</v>
+      </c>
+      <c r="J10" s="50">
+        <v>10</v>
+      </c>
+      <c r="K10" s="49">
+        <v>9</v>
+      </c>
+      <c r="L10" s="49">
+        <v>12</v>
+      </c>
+      <c r="M10" s="49">
+        <v>1</v>
+      </c>
+      <c r="N10" s="49">
+        <v>6</v>
+      </c>
+      <c r="O10" s="49">
+        <v>4</v>
+      </c>
+      <c r="P10" s="49">
+        <v>10</v>
+      </c>
+      <c r="Q10" s="49">
+        <v>7</v>
+      </c>
+      <c r="R10" s="49">
+        <v>7</v>
+      </c>
+      <c r="S10" s="49">
+        <v>4</v>
+      </c>
+      <c r="T10" s="49">
+        <v>700</v>
+      </c>
+      <c r="U10" s="49">
+        <v>1</v>
+      </c>
+      <c r="V10" s="49">
+        <v>35</v>
+      </c>
+      <c r="W10" s="49" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="49">
+        <v>1000008</v>
+      </c>
+      <c r="B11" s="49">
+        <v>1</v>
+      </c>
+      <c r="C11" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="E11" s="50" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" s="50" t="s">
+        <v>56</v>
+      </c>
+      <c r="G11" s="50">
+        <v>45</v>
+      </c>
+      <c r="H11" s="50">
+        <v>3</v>
+      </c>
+      <c r="I11" s="50">
+        <v>10</v>
+      </c>
+      <c r="J11" s="50">
+        <v>10</v>
+      </c>
+      <c r="K11" s="49">
+        <v>9</v>
+      </c>
+      <c r="L11" s="49">
+        <v>13</v>
+      </c>
+      <c r="M11" s="49">
+        <v>1</v>
+      </c>
+      <c r="N11" s="49">
+        <v>6</v>
+      </c>
+      <c r="O11" s="49">
+        <v>3</v>
+      </c>
+      <c r="P11" s="49">
+        <v>10</v>
+      </c>
+      <c r="Q11" s="49">
+        <v>8</v>
+      </c>
+      <c r="R11" s="49">
+        <v>8</v>
+      </c>
+      <c r="S11" s="49">
+        <v>4</v>
+      </c>
+      <c r="T11" s="49">
+        <v>800</v>
+      </c>
+      <c r="U11" s="49">
+        <v>1</v>
+      </c>
+      <c r="V11" s="49">
+        <v>40</v>
+      </c>
+      <c r="W11" s="49" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="49">
+        <v>1000009</v>
+      </c>
+      <c r="B12" s="49">
+        <v>1</v>
+      </c>
+      <c r="C12" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="E12" s="50" t="s">
+        <v>56</v>
+      </c>
+      <c r="F12" s="50" t="s">
+        <v>56</v>
+      </c>
+      <c r="G12" s="50">
         <v>50</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="G4" s="1">
-        <v>10</v>
-      </c>
-      <c r="H4" s="1">
+      <c r="H12" s="50">
         <v>3</v>
       </c>
-      <c r="I4" s="1">
-        <v>10</v>
-      </c>
-      <c r="J4" s="1">
-        <v>10</v>
-      </c>
-      <c r="K4">
+      <c r="I12" s="50">
+        <v>10</v>
+      </c>
+      <c r="J12" s="50">
+        <v>10</v>
+      </c>
+      <c r="K12" s="49">
+        <v>10</v>
+      </c>
+      <c r="L12" s="49">
+        <v>14</v>
+      </c>
+      <c r="M12" s="49">
+        <v>1</v>
+      </c>
+      <c r="N12" s="49">
+        <v>6</v>
+      </c>
+      <c r="O12" s="49">
+        <v>2</v>
+      </c>
+      <c r="P12" s="49">
+        <v>10</v>
+      </c>
+      <c r="Q12" s="49">
+        <v>9</v>
+      </c>
+      <c r="R12" s="49">
+        <v>9</v>
+      </c>
+      <c r="S12" s="49">
         <v>5</v>
       </c>
-      <c r="L4">
+      <c r="T12" s="49">
+        <v>900</v>
+      </c>
+      <c r="U12" s="49">
+        <v>1</v>
+      </c>
+      <c r="V12" s="49">
+        <v>45</v>
+      </c>
+      <c r="W12" s="49" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="49">
+        <v>1000010</v>
+      </c>
+      <c r="B13" s="49">
+        <v>1</v>
+      </c>
+      <c r="C13" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="E13" s="50" t="s">
+        <v>56</v>
+      </c>
+      <c r="F13" s="50" t="s">
+        <v>56</v>
+      </c>
+      <c r="G13" s="50">
+        <v>55</v>
+      </c>
+      <c r="H13" s="50">
+        <v>3</v>
+      </c>
+      <c r="I13" s="50">
+        <v>10</v>
+      </c>
+      <c r="J13" s="50">
+        <v>10</v>
+      </c>
+      <c r="K13" s="49">
+        <v>10</v>
+      </c>
+      <c r="L13" s="49">
+        <v>15</v>
+      </c>
+      <c r="M13" s="49">
+        <v>1</v>
+      </c>
+      <c r="N13" s="49">
         <v>6</v>
       </c>
-      <c r="M4">
-        <v>2</v>
-      </c>
-      <c r="N4">
-        <v>3</v>
-      </c>
-      <c r="O4">
-        <v>10</v>
-      </c>
-      <c r="P4">
-        <v>10</v>
-      </c>
-      <c r="Q4">
-        <v>1</v>
-      </c>
-      <c r="R4">
-        <v>1</v>
-      </c>
-      <c r="S4">
-        <v>1</v>
-      </c>
-      <c r="T4">
-        <v>100</v>
-      </c>
-      <c r="U4">
-        <v>1</v>
-      </c>
-      <c r="V4">
+      <c r="O13" s="49">
+        <v>1</v>
+      </c>
+      <c r="P13" s="49">
+        <v>10</v>
+      </c>
+      <c r="Q13" s="49">
+        <v>10</v>
+      </c>
+      <c r="R13" s="49">
+        <v>10</v>
+      </c>
+      <c r="S13" s="49">
         <v>5</v>
       </c>
-      <c r="W4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23">
-      <c r="A5">
-        <v>1000002</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="T13" s="49">
+        <v>1000</v>
+      </c>
+      <c r="U13" s="49">
+        <v>1</v>
+      </c>
+      <c r="V13" s="49">
         <v>50</v>
       </c>
-      <c r="D5" t="s">
-        <v>50</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G5" s="1">
-        <v>15</v>
-      </c>
-      <c r="H5" s="1">
-        <v>3</v>
-      </c>
-      <c r="I5" s="1">
-        <v>10</v>
-      </c>
-      <c r="J5" s="1">
-        <v>10</v>
-      </c>
-      <c r="K5">
-        <v>5</v>
-      </c>
-      <c r="L5">
-        <v>7</v>
-      </c>
-      <c r="M5">
-        <v>3</v>
-      </c>
-      <c r="N5">
-        <v>4</v>
-      </c>
-      <c r="O5">
-        <v>9</v>
-      </c>
-      <c r="P5">
-        <v>10</v>
-      </c>
-      <c r="Q5">
-        <v>2</v>
-      </c>
-      <c r="R5">
-        <v>2</v>
-      </c>
-      <c r="S5">
-        <v>1</v>
-      </c>
-      <c r="T5">
-        <v>200</v>
-      </c>
-      <c r="U5">
-        <v>1</v>
-      </c>
-      <c r="V5">
-        <v>10</v>
-      </c>
-      <c r="W5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23">
-      <c r="A6">
-        <v>1000003</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6" t="s">
-        <v>50</v>
-      </c>
-      <c r="D6" t="s">
-        <v>50</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G6" s="1">
-        <v>20</v>
-      </c>
-      <c r="H6" s="1">
-        <v>3</v>
-      </c>
-      <c r="I6" s="1">
-        <v>10</v>
-      </c>
-      <c r="J6" s="1">
-        <v>10</v>
-      </c>
-      <c r="K6">
-        <v>6</v>
-      </c>
-      <c r="L6">
-        <v>8</v>
-      </c>
-      <c r="M6">
-        <v>3</v>
-      </c>
-      <c r="N6">
-        <v>5</v>
-      </c>
-      <c r="O6">
-        <v>8</v>
-      </c>
-      <c r="P6">
-        <v>10</v>
-      </c>
-      <c r="Q6">
-        <v>3</v>
-      </c>
-      <c r="R6">
-        <v>3</v>
-      </c>
-      <c r="S6">
-        <v>2</v>
-      </c>
-      <c r="T6">
-        <v>300</v>
-      </c>
-      <c r="U6">
-        <v>1</v>
-      </c>
-      <c r="V6">
-        <v>15</v>
-      </c>
-      <c r="W6" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23">
-      <c r="A7">
-        <v>1000004</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7" t="s">
-        <v>50</v>
-      </c>
-      <c r="D7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G7" s="1">
-        <v>25</v>
-      </c>
-      <c r="H7" s="1">
-        <v>3</v>
-      </c>
-      <c r="I7" s="1">
-        <v>10</v>
-      </c>
-      <c r="J7" s="1">
-        <v>10</v>
-      </c>
-      <c r="K7">
-        <v>6</v>
-      </c>
-      <c r="L7">
-        <v>9</v>
-      </c>
-      <c r="M7">
-        <v>3</v>
-      </c>
-      <c r="N7">
-        <v>6</v>
-      </c>
-      <c r="O7">
-        <v>7</v>
-      </c>
-      <c r="P7">
-        <v>10</v>
-      </c>
-      <c r="Q7">
-        <v>4</v>
-      </c>
-      <c r="R7">
-        <v>4</v>
-      </c>
-      <c r="S7">
-        <v>2</v>
-      </c>
-      <c r="T7">
-        <v>400</v>
-      </c>
-      <c r="U7">
-        <v>1</v>
-      </c>
-      <c r="V7">
-        <v>20</v>
-      </c>
-      <c r="W7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23">
-      <c r="A8">
-        <v>1000005</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8" t="s">
-        <v>50</v>
-      </c>
-      <c r="D8" t="s">
-        <v>50</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G8" s="1">
-        <v>30</v>
-      </c>
-      <c r="H8" s="1">
-        <v>3</v>
-      </c>
-      <c r="I8" s="1">
-        <v>10</v>
-      </c>
-      <c r="J8" s="1">
-        <v>10</v>
-      </c>
-      <c r="K8">
-        <v>7</v>
-      </c>
-      <c r="L8">
-        <v>10</v>
-      </c>
-      <c r="M8">
-        <v>2</v>
-      </c>
-      <c r="N8">
-        <v>6</v>
-      </c>
-      <c r="O8">
-        <v>6</v>
-      </c>
-      <c r="P8">
-        <v>10</v>
-      </c>
-      <c r="Q8">
-        <v>5</v>
-      </c>
-      <c r="R8">
-        <v>5</v>
-      </c>
-      <c r="S8">
-        <v>3</v>
-      </c>
-      <c r="T8">
-        <v>500</v>
-      </c>
-      <c r="U8">
-        <v>1</v>
-      </c>
-      <c r="V8">
-        <v>25</v>
-      </c>
-      <c r="W8" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23">
-      <c r="A9">
-        <v>1000006</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9" t="s">
-        <v>50</v>
-      </c>
-      <c r="D9" t="s">
-        <v>50</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G9" s="1">
-        <v>35</v>
-      </c>
-      <c r="H9" s="1">
-        <v>3</v>
-      </c>
-      <c r="I9" s="1">
-        <v>10</v>
-      </c>
-      <c r="J9" s="1">
-        <v>10</v>
-      </c>
-      <c r="K9">
-        <v>8</v>
-      </c>
-      <c r="L9">
-        <v>11</v>
-      </c>
-      <c r="M9">
-        <v>1</v>
-      </c>
-      <c r="N9">
-        <v>6</v>
-      </c>
-      <c r="O9">
-        <v>5</v>
-      </c>
-      <c r="P9">
-        <v>10</v>
-      </c>
-      <c r="Q9">
-        <v>6</v>
-      </c>
-      <c r="R9">
-        <v>6</v>
-      </c>
-      <c r="S9">
-        <v>3</v>
-      </c>
-      <c r="T9">
-        <v>600</v>
-      </c>
-      <c r="U9">
-        <v>1</v>
-      </c>
-      <c r="V9">
-        <v>30</v>
-      </c>
-      <c r="W9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23">
-      <c r="A10">
-        <v>1000007</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D10" t="s">
-        <v>50</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G10" s="1">
-        <v>40</v>
-      </c>
-      <c r="H10" s="1">
-        <v>3</v>
-      </c>
-      <c r="I10" s="1">
-        <v>10</v>
-      </c>
-      <c r="J10" s="1">
-        <v>10</v>
-      </c>
-      <c r="K10">
-        <v>9</v>
-      </c>
-      <c r="L10">
-        <v>12</v>
-      </c>
-      <c r="M10">
-        <v>1</v>
-      </c>
-      <c r="N10">
-        <v>6</v>
-      </c>
-      <c r="O10">
-        <v>4</v>
-      </c>
-      <c r="P10">
-        <v>10</v>
-      </c>
-      <c r="Q10">
-        <v>7</v>
-      </c>
-      <c r="R10">
-        <v>7</v>
-      </c>
-      <c r="S10">
-        <v>4</v>
-      </c>
-      <c r="T10">
-        <v>700</v>
-      </c>
-      <c r="U10">
-        <v>1</v>
-      </c>
-      <c r="V10">
-        <v>35</v>
-      </c>
-      <c r="W10" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:23">
-      <c r="A11">
-        <v>1000008</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11" t="s">
-        <v>50</v>
-      </c>
-      <c r="D11" t="s">
-        <v>50</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G11" s="1">
-        <v>45</v>
-      </c>
-      <c r="H11" s="1">
-        <v>3</v>
-      </c>
-      <c r="I11" s="1">
-        <v>10</v>
-      </c>
-      <c r="J11" s="1">
-        <v>10</v>
-      </c>
-      <c r="K11">
-        <v>9</v>
-      </c>
-      <c r="L11">
-        <v>13</v>
-      </c>
-      <c r="M11">
-        <v>1</v>
-      </c>
-      <c r="N11">
-        <v>6</v>
-      </c>
-      <c r="O11">
-        <v>3</v>
-      </c>
-      <c r="P11">
-        <v>10</v>
-      </c>
-      <c r="Q11">
-        <v>8</v>
-      </c>
-      <c r="R11">
-        <v>8</v>
-      </c>
-      <c r="S11">
-        <v>4</v>
-      </c>
-      <c r="T11">
-        <v>800</v>
-      </c>
-      <c r="U11">
-        <v>1</v>
-      </c>
-      <c r="V11">
-        <v>40</v>
-      </c>
-      <c r="W11" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23">
-      <c r="A12">
-        <v>1000009</v>
-      </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12" t="s">
-        <v>50</v>
-      </c>
-      <c r="D12" t="s">
-        <v>50</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G12" s="1">
-        <v>50</v>
-      </c>
-      <c r="H12" s="1">
-        <v>3</v>
-      </c>
-      <c r="I12" s="1">
-        <v>10</v>
-      </c>
-      <c r="J12" s="1">
-        <v>10</v>
-      </c>
-      <c r="K12">
-        <v>10</v>
-      </c>
-      <c r="L12">
-        <v>14</v>
-      </c>
-      <c r="M12">
-        <v>1</v>
-      </c>
-      <c r="N12">
-        <v>6</v>
-      </c>
-      <c r="O12">
-        <v>2</v>
-      </c>
-      <c r="P12">
-        <v>10</v>
-      </c>
-      <c r="Q12">
-        <v>9</v>
-      </c>
-      <c r="R12">
-        <v>9</v>
-      </c>
-      <c r="S12">
-        <v>5</v>
-      </c>
-      <c r="T12">
-        <v>900</v>
-      </c>
-      <c r="U12">
-        <v>1</v>
-      </c>
-      <c r="V12">
-        <v>45</v>
-      </c>
-      <c r="W12" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="13" spans="1:23">
-      <c r="A13">
-        <v>1000010</v>
-      </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13" t="s">
-        <v>50</v>
-      </c>
-      <c r="D13" t="s">
-        <v>50</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G13" s="1">
-        <v>55</v>
-      </c>
-      <c r="H13" s="1">
-        <v>3</v>
-      </c>
-      <c r="I13" s="1">
-        <v>10</v>
-      </c>
-      <c r="J13" s="1">
-        <v>10</v>
-      </c>
-      <c r="K13">
-        <v>10</v>
-      </c>
-      <c r="L13">
-        <v>15</v>
-      </c>
-      <c r="M13">
-        <v>1</v>
-      </c>
-      <c r="N13">
-        <v>6</v>
-      </c>
-      <c r="O13">
-        <v>1</v>
-      </c>
-      <c r="P13">
-        <v>10</v>
-      </c>
-      <c r="Q13">
-        <v>10</v>
-      </c>
-      <c r="R13">
-        <v>10</v>
-      </c>
-      <c r="S13">
-        <v>5</v>
-      </c>
-      <c r="T13">
-        <v>1000</v>
-      </c>
-      <c r="U13">
-        <v>1</v>
-      </c>
-      <c r="V13">
-        <v>50</v>
-      </c>
-      <c r="W13" t="s">
-        <v>63</v>
+      <c r="W13" s="49" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
@@ -1,33 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19575" windowHeight="11505"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="19575" windowHeight="11505" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="FightTypeConquerInfo" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
   <si>
     <t>id</t>
   </si>
@@ -47,16 +33,16 @@
     <t>enemy_boss_ids</t>
   </si>
   <si>
-    <t>enemy_num</t>
-  </si>
-  <si>
     <t>attack_start_num</t>
   </si>
   <si>
-    <t>attack_wave_min</t>
-  </si>
-  <si>
-    <t>attack_wave_max</t>
+    <t>attack_show_time</t>
+  </si>
+  <si>
+    <t>attack_num_addrate</t>
+  </si>
+  <si>
+    <t>attack_num_add</t>
   </si>
   <si>
     <t>fight_num_min</t>
@@ -128,16 +114,16 @@
     <t>boss列表（npcInfoId用&amp;分割）</t>
   </si>
   <si>
-    <t>敌人数量</t>
-  </si>
-  <si>
-    <t>起始敌人数量</t>
-  </si>
-  <si>
-    <t>最小进攻次数</t>
-  </si>
-  <si>
-    <t>最大进攻次数</t>
+    <t>第一关敌人数量</t>
+  </si>
+  <si>
+    <t>进攻时间(秒)</t>
+  </si>
+  <si>
+    <t>每关敌人倍数</t>
+  </si>
+  <si>
+    <t>每关增加敌人数量</t>
   </si>
   <si>
     <t>关卡次数-最小</t>
@@ -189,6 +175,18 @@
   </si>
   <si>
     <t>1010020001</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>2</t>
   </si>
   <si>
     <t>剑与魔法-难度1</t>
@@ -230,12 +228,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="166" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="167" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -672,22 +670,22 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="19" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
@@ -696,7 +694,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
@@ -820,160 +818,161 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" applyNumberFormat="1" fontId="19" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" applyNumberFormat="1" fontId="19" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="2" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" applyNumberFormat="1" fontId="19" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="3" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" applyNumberFormat="1" fontId="19" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="4" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" applyNumberFormat="1" fontId="19" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="5" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="7" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" xfId="8" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="9" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="4" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="10" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="11" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="6" applyFont="1" fillId="0" applyFill="1" borderId="2" applyBorder="1" xfId="12" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="7" applyFont="1" fillId="0" applyFill="1" borderId="2" applyBorder="1" xfId="13" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="8" applyFont="1" fillId="0" applyFill="1" borderId="3" applyBorder="1" xfId="14" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="8" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="15" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="9" applyFont="1" fillId="3" applyFill="1" borderId="4" applyBorder="1" xfId="16" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="10" applyFont="1" fillId="4" applyFill="1" borderId="5" applyBorder="1" xfId="17" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="11" applyFont="1" fillId="4" applyFill="1" borderId="4" applyBorder="1" xfId="18" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="12" applyFont="1" fillId="5" applyFill="1" borderId="6" applyBorder="1" xfId="19" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="13" applyFont="1" fillId="0" applyFill="1" borderId="7" applyBorder="1" xfId="20" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="14" applyFont="1" fillId="0" applyFill="1" borderId="8" applyBorder="1" xfId="21" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="15" applyFont="1" fillId="6" applyFill="1" borderId="0" applyBorder="1" xfId="22" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="16" applyFont="1" fillId="7" applyFill="1" borderId="0" applyBorder="1" xfId="23" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="17" applyFont="1" fillId="8" applyFill="1" borderId="0" applyBorder="1" xfId="24" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="9" applyFill="1" borderId="0" applyBorder="1" xfId="25" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="1" xfId="26" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="11" applyFill="1" borderId="0" applyBorder="1" xfId="27" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="12" applyFill="1" borderId="0" applyBorder="1" xfId="28" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="13" applyFill="1" borderId="0" applyBorder="1" xfId="29" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="14" applyFill="1" borderId="0" applyBorder="1" xfId="30" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="15" applyFill="1" borderId="0" applyBorder="1" xfId="31" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="16" applyFill="1" borderId="0" applyBorder="1" xfId="32" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="17" applyFill="1" borderId="0" applyBorder="1" xfId="33" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="18" applyFill="1" borderId="0" applyBorder="1" xfId="34" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="19" applyFill="1" borderId="0" applyBorder="1" xfId="35" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="20" applyFill="1" borderId="0" applyBorder="1" xfId="36" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="21" applyFill="1" borderId="0" applyBorder="1" xfId="37" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="22" applyFill="1" borderId="0" applyBorder="1" xfId="38" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="23" applyFill="1" borderId="0" applyBorder="1" xfId="39" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="24" applyFill="1" borderId="0" applyBorder="1" xfId="40" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="25" applyFill="1" borderId="0" applyBorder="1" xfId="41" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="26" applyFill="1" borderId="0" applyBorder="1" xfId="42" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="27" applyFill="1" borderId="0" applyBorder="1" xfId="43" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="28" applyFill="1" borderId="0" applyBorder="1" xfId="44" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="29" applyFill="1" borderId="0" applyBorder="1" xfId="45" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="30" applyFill="1" borderId="0" applyBorder="1" xfId="46" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="31" applyFill="1" borderId="0" applyBorder="1" xfId="47" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="32" applyFill="1" borderId="0" applyBorder="1" xfId="48" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="2" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="3" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="4" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="5" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="7" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" xfId="8" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="9" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="4" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="10" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="11" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="6" applyFont="1" fillId="0" applyFill="1" borderId="2" applyBorder="1" xfId="12" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="7" applyFont="1" fillId="0" applyFill="1" borderId="2" applyBorder="1" xfId="13" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="8" applyFont="1" fillId="0" applyFill="1" borderId="3" applyBorder="1" xfId="14" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="8" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="15" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="9" applyFont="1" fillId="3" applyFill="1" borderId="4" applyBorder="1" xfId="16" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="10" applyFont="1" fillId="4" applyFill="1" borderId="5" applyBorder="1" xfId="17" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="11" applyFont="1" fillId="4" applyFill="1" borderId="4" applyBorder="1" xfId="18" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="12" applyFont="1" fillId="5" applyFill="1" borderId="6" applyBorder="1" xfId="19" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="13" applyFont="1" fillId="0" applyFill="1" borderId="7" applyBorder="1" xfId="20" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="14" applyFont="1" fillId="0" applyFill="1" borderId="8" applyBorder="1" xfId="21" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="15" applyFont="1" fillId="6" applyFill="1" borderId="0" applyBorder="1" xfId="22" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="16" applyFont="1" fillId="7" applyFill="1" borderId="0" applyBorder="1" xfId="23" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="17" applyFont="1" fillId="8" applyFill="1" borderId="0" applyBorder="1" xfId="24" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="9" applyFill="1" borderId="0" applyBorder="1" xfId="25" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="1" xfId="26" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="11" applyFill="1" borderId="0" applyBorder="1" xfId="27" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="12" applyFill="1" borderId="0" applyBorder="1" xfId="28" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="13" applyFill="1" borderId="0" applyBorder="1" xfId="29" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="14" applyFill="1" borderId="0" applyBorder="1" xfId="30" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="15" applyFill="1" borderId="0" applyBorder="1" xfId="31" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="16" applyFill="1" borderId="0" applyBorder="1" xfId="32" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="17" applyFill="1" borderId="0" applyBorder="1" xfId="33" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="18" applyFill="1" borderId="0" applyBorder="1" xfId="34" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="19" applyFill="1" borderId="0" applyBorder="1" xfId="35" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="20" applyFill="1" borderId="0" applyBorder="1" xfId="36" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="21" applyFill="1" borderId="0" applyBorder="1" xfId="37" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="22" applyFill="1" borderId="0" applyBorder="1" xfId="38" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="23" applyFill="1" borderId="0" applyBorder="1" xfId="39" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="24" applyFill="1" borderId="0" applyBorder="1" xfId="40" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="25" applyFill="1" borderId="0" applyBorder="1" xfId="41" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="26" applyFill="1" borderId="0" applyBorder="1" xfId="42" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="27" applyFill="1" borderId="0" applyBorder="1" xfId="43" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="28" applyFill="1" borderId="0" applyBorder="1" xfId="44" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="29" applyFill="1" borderId="0" applyBorder="1" xfId="45" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="30" applyFill="1" borderId="0" applyBorder="1" xfId="46" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="31" applyFill="1" borderId="0" applyBorder="1" xfId="47" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="32" applyFill="1" borderId="0" applyBorder="1" xfId="48" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1027,11 +1026,74 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1320,251 +1382,254 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:W13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="3" max="3" width="17.125" customWidth="1" style="49"/>
-    <col min="4" max="4" width="36.5" customWidth="1" style="49"/>
-    <col min="5" max="5" width="23.75" customWidth="1" style="49"/>
-    <col min="6" max="6" width="32.625" customWidth="1" style="49"/>
-    <col min="7" max="7" width="10.375" customWidth="1" style="49"/>
-    <col min="8" max="8" width="18.25" customWidth="1" style="49"/>
-    <col min="9" max="16" width="16" customWidth="1" style="49"/>
-    <col min="17" max="17" width="12.25" customWidth="1" style="49"/>
-    <col min="18" max="19" width="12.875" customWidth="1" style="49"/>
-    <col min="20" max="20" width="17.375" customWidth="1" style="49"/>
-    <col min="21" max="21" width="19.75" customWidth="1" style="49"/>
-    <col min="22" max="22" width="29.375" customWidth="1" style="49"/>
-    <col min="23" max="23" width="42.875" customWidth="1" style="49"/>
-    <col min="24" max="24" width="25.125" customWidth="1" style="49"/>
+    <col min="3" max="3" width="17.125" customWidth="1" style="50"/>
+    <col min="4" max="4" width="36.5" customWidth="1" style="50"/>
+    <col min="5" max="5" width="23.75" customWidth="1" style="50"/>
+    <col min="6" max="6" width="32.625" customWidth="1" style="50"/>
+    <col min="7" max="7" width="10.375" customWidth="1" style="50"/>
+    <col min="8" max="8" width="18.25" customWidth="1" style="50"/>
+    <col min="9" max="16" width="16" customWidth="1" style="50"/>
+    <col min="17" max="17" width="12.25" customWidth="1" style="50"/>
+    <col min="18" max="19" width="12.875" customWidth="1" style="50"/>
+    <col min="20" max="20" width="17.375" customWidth="1" style="50"/>
+    <col min="21" max="21" width="19.75" customWidth="1" style="50"/>
+    <col min="22" max="22" width="29.375" customWidth="1" style="50"/>
+    <col min="23" max="23" width="42.875" customWidth="1" style="50"/>
+    <col min="24" max="24" width="25.125" customWidth="1" style="50"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="49" t="s">
+      <c r="B1" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="49" t="s">
+      <c r="D1" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="49" t="s">
+      <c r="E1" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="49" t="s">
+      <c r="F1" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="49" t="s">
+      <c r="G1" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="49" t="s">
+      <c r="H1" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="49" t="s">
+      <c r="I1" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="49" t="s">
+      <c r="J1" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="49" t="s">
+      <c r="K1" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="49" t="s">
+      <c r="L1" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="49" t="s">
+      <c r="M1" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="49" t="s">
+      <c r="N1" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="49" t="s">
+      <c r="O1" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="49" t="s">
+      <c r="P1" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="49" t="s">
+      <c r="Q1" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="49" t="s">
+      <c r="R1" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="49" t="s">
+      <c r="S1" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="49" t="s">
+      <c r="T1" s="50" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="49" t="s">
+      <c r="U1" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="49" t="s">
+      <c r="V1" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="49" t="s">
+      <c r="W1" s="50" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="49" t="s">
+      <c r="C2" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="49" t="s">
+      <c r="D2" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="49" t="s">
+      <c r="E2" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="49" t="s">
+      <c r="F2" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="49" t="s">
+      <c r="G2" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="H2" s="49" t="s">
+      <c r="H2" s="50" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" s="50" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="49" t="s">
+      <c r="K2" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="49" t="s">
+      <c r="L2" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="K2" s="49" t="s">
+      <c r="M2" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="L2" s="49" t="s">
+      <c r="N2" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="49" t="s">
+      <c r="O2" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="N2" s="49" t="s">
+      <c r="P2" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="O2" s="49" t="s">
+      <c r="Q2" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="P2" s="49" t="s">
+      <c r="R2" s="50" t="s">
+        <v>26</v>
+      </c>
+      <c r="S2" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="Q2" s="49" t="s">
+      <c r="T2" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="R2" s="49" t="s">
-        <v>26</v>
-      </c>
-      <c r="S2" s="49" t="s">
+      <c r="U2" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="T2" s="49" t="s">
+      <c r="V2" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="U2" s="49" t="s">
-        <v>25</v>
-      </c>
-      <c r="V2" s="49" t="s">
-        <v>25</v>
-      </c>
-      <c r="W2" s="49" t="s">
+      <c r="W2" s="50" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="49" t="s">
+      <c r="B3" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="49" t="s">
+      <c r="C3" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="49" t="s">
+      <c r="D3" s="50" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="49" t="s">
+      <c r="E3" s="50" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="49" t="s">
+      <c r="F3" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="G3" s="49" t="s">
+      <c r="G3" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="H3" s="49" t="s">
+      <c r="H3" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="I3" s="49" t="s">
+      <c r="I3" s="50" t="s">
         <v>35</v>
       </c>
-      <c r="J3" s="49" t="s">
+      <c r="J3" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="K3" s="49" t="s">
+      <c r="K3" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="L3" s="49" t="s">
+      <c r="L3" s="50" t="s">
         <v>38</v>
       </c>
-      <c r="M3" s="49" t="s">
+      <c r="M3" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="N3" s="49" t="s">
+      <c r="N3" s="50" t="s">
         <v>40</v>
       </c>
-      <c r="O3" s="49" t="s">
+      <c r="O3" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="P3" s="49" t="s">
+      <c r="P3" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="Q3" s="49" t="s">
+      <c r="Q3" s="50" t="s">
         <v>43</v>
       </c>
-      <c r="R3" s="49" t="s">
+      <c r="R3" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="S3" s="49" t="s">
+      <c r="S3" s="50" t="s">
         <v>45</v>
       </c>
-      <c r="T3" s="49" t="s">
+      <c r="T3" s="50" t="s">
         <v>46</v>
       </c>
-      <c r="U3" s="49" t="s">
+      <c r="U3" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="V3" s="49" t="s">
+      <c r="V3" s="50" t="s">
         <v>48</v>
       </c>
-      <c r="W3" s="49" t="s">
+      <c r="W3" s="50" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="49">
+      <c r="A4" s="50">
         <v>1000001</v>
       </c>
-      <c r="B4" s="49">
-        <v>1</v>
-      </c>
-      <c r="C4" s="49" t="s">
+      <c r="B4" s="50">
+        <v>1</v>
+      </c>
+      <c r="C4" s="50" t="s">
         <v>50</v>
       </c>
-      <c r="D4" s="49" t="s">
+      <c r="D4" s="50" t="s">
         <v>51</v>
       </c>
       <c r="E4" s="50" t="s">
@@ -1573,720 +1638,720 @@
       <c r="F4" s="50" t="s">
         <v>53</v>
       </c>
-      <c r="G4" s="50">
+      <c r="G4" s="50" t="s">
+        <v>54</v>
+      </c>
+      <c r="H4" s="50" t="s">
+        <v>55</v>
+      </c>
+      <c r="I4" s="50">
+        <v>1</v>
+      </c>
+      <c r="J4" s="50" t="s">
+        <v>56</v>
+      </c>
+      <c r="K4" s="50">
+        <v>5</v>
+      </c>
+      <c r="L4" s="50">
+        <v>6</v>
+      </c>
+      <c r="M4" s="50">
+        <v>2</v>
+      </c>
+      <c r="N4" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="O4" s="50">
         <v>10</v>
       </c>
-      <c r="H4" s="50">
-        <v>3</v>
-      </c>
-      <c r="I4" s="50">
+      <c r="P4" s="50">
         <v>10</v>
       </c>
-      <c r="J4" s="50">
-        <v>10</v>
-      </c>
-      <c r="K4" s="49">
+      <c r="Q4" s="50">
+        <v>1</v>
+      </c>
+      <c r="R4" s="50">
+        <v>1</v>
+      </c>
+      <c r="S4" s="50">
+        <v>1</v>
+      </c>
+      <c r="T4" s="50">
+        <v>100</v>
+      </c>
+      <c r="U4" s="50">
+        <v>1</v>
+      </c>
+      <c r="V4" s="50">
         <v>5</v>
       </c>
-      <c r="L4" s="49">
-        <v>6</v>
-      </c>
-      <c r="M4" s="49">
-        <v>2</v>
-      </c>
-      <c r="N4" s="49">
-        <v>3</v>
-      </c>
-      <c r="O4" s="49">
-        <v>10</v>
-      </c>
-      <c r="P4" s="49">
-        <v>10</v>
-      </c>
-      <c r="Q4" s="49">
-        <v>1</v>
-      </c>
-      <c r="R4" s="49">
-        <v>1</v>
-      </c>
-      <c r="S4" s="49">
-        <v>1</v>
-      </c>
-      <c r="T4" s="49">
-        <v>100</v>
-      </c>
-      <c r="U4" s="49">
-        <v>1</v>
-      </c>
-      <c r="V4" s="49">
-        <v>5</v>
-      </c>
-      <c r="W4" s="49" t="s">
-        <v>54</v>
+      <c r="W4" s="50" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="49">
+      <c r="A5" s="50">
         <v>1000002</v>
       </c>
-      <c r="B5" s="49">
-        <v>1</v>
-      </c>
-      <c r="C5" s="49" t="s">
-        <v>55</v>
-      </c>
-      <c r="D5" s="49" t="s">
-        <v>55</v>
+      <c r="B5" s="50">
+        <v>1</v>
+      </c>
+      <c r="C5" s="50" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" s="50" t="s">
+        <v>59</v>
       </c>
       <c r="E5" s="50" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F5" s="50" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G5" s="50">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H5" s="50">
+        <v>5</v>
+      </c>
+      <c r="I5" s="50">
+        <v>1</v>
+      </c>
+      <c r="J5" s="50">
+        <v>2</v>
+      </c>
+      <c r="K5" s="50">
+        <v>5</v>
+      </c>
+      <c r="L5" s="50">
+        <v>7</v>
+      </c>
+      <c r="M5" s="50">
         <v>3</v>
       </c>
-      <c r="I5" s="50">
+      <c r="N5" s="50">
+        <v>4</v>
+      </c>
+      <c r="O5" s="50">
+        <v>9</v>
+      </c>
+      <c r="P5" s="50">
         <v>10</v>
       </c>
-      <c r="J5" s="50">
+      <c r="Q5" s="50">
+        <v>2</v>
+      </c>
+      <c r="R5" s="50">
+        <v>2</v>
+      </c>
+      <c r="S5" s="50">
+        <v>1</v>
+      </c>
+      <c r="T5" s="50">
+        <v>200</v>
+      </c>
+      <c r="U5" s="50">
+        <v>1</v>
+      </c>
+      <c r="V5" s="50">
         <v>10</v>
       </c>
-      <c r="K5" s="49">
-        <v>5</v>
-      </c>
-      <c r="L5" s="49">
-        <v>7</v>
-      </c>
-      <c r="M5" s="49">
-        <v>3</v>
-      </c>
-      <c r="N5" s="49">
-        <v>4</v>
-      </c>
-      <c r="O5" s="49">
-        <v>9</v>
-      </c>
-      <c r="P5" s="49">
-        <v>10</v>
-      </c>
-      <c r="Q5" s="49">
-        <v>2</v>
-      </c>
-      <c r="R5" s="49">
-        <v>2</v>
-      </c>
-      <c r="S5" s="49">
-        <v>1</v>
-      </c>
-      <c r="T5" s="49">
-        <v>200</v>
-      </c>
-      <c r="U5" s="49">
-        <v>1</v>
-      </c>
-      <c r="V5" s="49">
-        <v>10</v>
-      </c>
-      <c r="W5" s="49" t="s">
-        <v>57</v>
+      <c r="W5" s="50" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="49">
+      <c r="A6" s="50">
         <v>1000003</v>
       </c>
-      <c r="B6" s="49">
-        <v>1</v>
-      </c>
-      <c r="C6" s="49" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" s="49" t="s">
-        <v>55</v>
+      <c r="B6" s="50">
+        <v>1</v>
+      </c>
+      <c r="C6" s="50" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" s="50" t="s">
+        <v>59</v>
       </c>
       <c r="E6" s="50" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F6" s="50" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G6" s="50">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="H6" s="50">
+        <v>5</v>
+      </c>
+      <c r="I6" s="50">
+        <v>1</v>
+      </c>
+      <c r="J6" s="50">
+        <v>2</v>
+      </c>
+      <c r="K6" s="50">
+        <v>6</v>
+      </c>
+      <c r="L6" s="50">
+        <v>8</v>
+      </c>
+      <c r="M6" s="50">
         <v>3</v>
       </c>
-      <c r="I6" s="50">
+      <c r="N6" s="50">
+        <v>5</v>
+      </c>
+      <c r="O6" s="50">
+        <v>8</v>
+      </c>
+      <c r="P6" s="50">
         <v>10</v>
       </c>
-      <c r="J6" s="50">
-        <v>10</v>
-      </c>
-      <c r="K6" s="49">
-        <v>6</v>
-      </c>
-      <c r="L6" s="49">
-        <v>8</v>
-      </c>
-      <c r="M6" s="49">
+      <c r="Q6" s="50">
         <v>3</v>
       </c>
-      <c r="N6" s="49">
-        <v>5</v>
-      </c>
-      <c r="O6" s="49">
-        <v>8</v>
-      </c>
-      <c r="P6" s="49">
-        <v>10</v>
-      </c>
-      <c r="Q6" s="49">
+      <c r="R6" s="50">
         <v>3</v>
       </c>
-      <c r="R6" s="49">
-        <v>3</v>
-      </c>
-      <c r="S6" s="49">
+      <c r="S6" s="50">
         <v>2</v>
       </c>
-      <c r="T6" s="49">
+      <c r="T6" s="50">
         <v>300</v>
       </c>
-      <c r="U6" s="49">
-        <v>1</v>
-      </c>
-      <c r="V6" s="49">
+      <c r="U6" s="50">
+        <v>1</v>
+      </c>
+      <c r="V6" s="50">
         <v>15</v>
       </c>
-      <c r="W6" s="49" t="s">
-        <v>58</v>
+      <c r="W6" s="50" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="49">
+      <c r="A7" s="50">
         <v>1000004</v>
       </c>
-      <c r="B7" s="49">
-        <v>1</v>
-      </c>
-      <c r="C7" s="49" t="s">
-        <v>55</v>
-      </c>
-      <c r="D7" s="49" t="s">
-        <v>55</v>
+      <c r="B7" s="50">
+        <v>1</v>
+      </c>
+      <c r="C7" s="50" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" s="50" t="s">
+        <v>59</v>
       </c>
       <c r="E7" s="50" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F7" s="50" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G7" s="50">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="H7" s="50">
+        <v>5</v>
+      </c>
+      <c r="I7" s="50">
+        <v>1</v>
+      </c>
+      <c r="J7" s="50">
+        <v>2</v>
+      </c>
+      <c r="K7" s="50">
+        <v>6</v>
+      </c>
+      <c r="L7" s="50">
+        <v>9</v>
+      </c>
+      <c r="M7" s="50">
         <v>3</v>
       </c>
-      <c r="I7" s="50">
+      <c r="N7" s="50">
+        <v>6</v>
+      </c>
+      <c r="O7" s="50">
+        <v>7</v>
+      </c>
+      <c r="P7" s="50">
         <v>10</v>
       </c>
-      <c r="J7" s="50">
-        <v>10</v>
-      </c>
-      <c r="K7" s="49">
-        <v>6</v>
-      </c>
-      <c r="L7" s="49">
-        <v>9</v>
-      </c>
-      <c r="M7" s="49">
-        <v>3</v>
-      </c>
-      <c r="N7" s="49">
-        <v>6</v>
-      </c>
-      <c r="O7" s="49">
-        <v>7</v>
-      </c>
-      <c r="P7" s="49">
-        <v>10</v>
-      </c>
-      <c r="Q7" s="49">
+      <c r="Q7" s="50">
         <v>4</v>
       </c>
-      <c r="R7" s="49">
+      <c r="R7" s="50">
         <v>4</v>
       </c>
-      <c r="S7" s="49">
+      <c r="S7" s="50">
         <v>2</v>
       </c>
-      <c r="T7" s="49">
+      <c r="T7" s="50">
         <v>400</v>
       </c>
-      <c r="U7" s="49">
-        <v>1</v>
-      </c>
-      <c r="V7" s="49">
+      <c r="U7" s="50">
+        <v>1</v>
+      </c>
+      <c r="V7" s="50">
         <v>20</v>
       </c>
-      <c r="W7" s="49" t="s">
-        <v>59</v>
+      <c r="W7" s="50" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="49">
+      <c r="A8" s="50">
         <v>1000005</v>
       </c>
-      <c r="B8" s="49">
-        <v>1</v>
-      </c>
-      <c r="C8" s="49" t="s">
-        <v>55</v>
-      </c>
-      <c r="D8" s="49" t="s">
-        <v>55</v>
+      <c r="B8" s="50">
+        <v>1</v>
+      </c>
+      <c r="C8" s="50" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" s="50" t="s">
+        <v>59</v>
       </c>
       <c r="E8" s="50" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F8" s="50" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G8" s="50">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="H8" s="50">
+        <v>5</v>
+      </c>
+      <c r="I8" s="50">
+        <v>1</v>
+      </c>
+      <c r="J8" s="50">
+        <v>2</v>
+      </c>
+      <c r="K8" s="50">
+        <v>7</v>
+      </c>
+      <c r="L8" s="50">
+        <v>10</v>
+      </c>
+      <c r="M8" s="50">
+        <v>2</v>
+      </c>
+      <c r="N8" s="50">
+        <v>6</v>
+      </c>
+      <c r="O8" s="50">
+        <v>6</v>
+      </c>
+      <c r="P8" s="50">
+        <v>10</v>
+      </c>
+      <c r="Q8" s="50">
+        <v>5</v>
+      </c>
+      <c r="R8" s="50">
+        <v>5</v>
+      </c>
+      <c r="S8" s="50">
         <v>3</v>
       </c>
-      <c r="I8" s="50">
-        <v>10</v>
-      </c>
-      <c r="J8" s="50">
-        <v>10</v>
-      </c>
-      <c r="K8" s="49">
-        <v>7</v>
-      </c>
-      <c r="L8" s="49">
-        <v>10</v>
-      </c>
-      <c r="M8" s="49">
-        <v>2</v>
-      </c>
-      <c r="N8" s="49">
-        <v>6</v>
-      </c>
-      <c r="O8" s="49">
-        <v>6</v>
-      </c>
-      <c r="P8" s="49">
-        <v>10</v>
-      </c>
-      <c r="Q8" s="49">
-        <v>5</v>
-      </c>
-      <c r="R8" s="49">
-        <v>5</v>
-      </c>
-      <c r="S8" s="49">
-        <v>3</v>
-      </c>
-      <c r="T8" s="49">
+      <c r="T8" s="50">
         <v>500</v>
       </c>
-      <c r="U8" s="49">
-        <v>1</v>
-      </c>
-      <c r="V8" s="49">
+      <c r="U8" s="50">
+        <v>1</v>
+      </c>
+      <c r="V8" s="50">
         <v>25</v>
       </c>
-      <c r="W8" s="49" t="s">
-        <v>60</v>
+      <c r="W8" s="50" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="49">
+      <c r="A9" s="50">
         <v>1000006</v>
       </c>
-      <c r="B9" s="49">
-        <v>1</v>
-      </c>
-      <c r="C9" s="49" t="s">
-        <v>55</v>
-      </c>
-      <c r="D9" s="49" t="s">
-        <v>55</v>
+      <c r="B9" s="50">
+        <v>1</v>
+      </c>
+      <c r="C9" s="50" t="s">
+        <v>59</v>
+      </c>
+      <c r="D9" s="50" t="s">
+        <v>59</v>
       </c>
       <c r="E9" s="50" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F9" s="50" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G9" s="50">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="H9" s="50">
+        <v>5</v>
+      </c>
+      <c r="I9" s="50">
+        <v>1</v>
+      </c>
+      <c r="J9" s="50">
+        <v>2</v>
+      </c>
+      <c r="K9" s="50">
+        <v>8</v>
+      </c>
+      <c r="L9" s="50">
+        <v>11</v>
+      </c>
+      <c r="M9" s="50">
+        <v>1</v>
+      </c>
+      <c r="N9" s="50">
+        <v>6</v>
+      </c>
+      <c r="O9" s="50">
+        <v>5</v>
+      </c>
+      <c r="P9" s="50">
+        <v>10</v>
+      </c>
+      <c r="Q9" s="50">
+        <v>6</v>
+      </c>
+      <c r="R9" s="50">
+        <v>6</v>
+      </c>
+      <c r="S9" s="50">
         <v>3</v>
       </c>
-      <c r="I9" s="50">
-        <v>10</v>
-      </c>
-      <c r="J9" s="50">
-        <v>10</v>
-      </c>
-      <c r="K9" s="49">
-        <v>8</v>
-      </c>
-      <c r="L9" s="49">
-        <v>11</v>
-      </c>
-      <c r="M9" s="49">
-        <v>1</v>
-      </c>
-      <c r="N9" s="49">
-        <v>6</v>
-      </c>
-      <c r="O9" s="49">
-        <v>5</v>
-      </c>
-      <c r="P9" s="49">
-        <v>10</v>
-      </c>
-      <c r="Q9" s="49">
-        <v>6</v>
-      </c>
-      <c r="R9" s="49">
-        <v>6</v>
-      </c>
-      <c r="S9" s="49">
-        <v>3</v>
-      </c>
-      <c r="T9" s="49">
+      <c r="T9" s="50">
         <v>600</v>
       </c>
-      <c r="U9" s="49">
-        <v>1</v>
-      </c>
-      <c r="V9" s="49">
+      <c r="U9" s="50">
+        <v>1</v>
+      </c>
+      <c r="V9" s="50">
         <v>30</v>
       </c>
-      <c r="W9" s="49" t="s">
-        <v>61</v>
+      <c r="W9" s="50" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="49">
+      <c r="A10" s="50">
         <v>1000007</v>
       </c>
-      <c r="B10" s="49">
-        <v>1</v>
-      </c>
-      <c r="C10" s="49" t="s">
-        <v>55</v>
-      </c>
-      <c r="D10" s="49" t="s">
-        <v>55</v>
+      <c r="B10" s="50">
+        <v>1</v>
+      </c>
+      <c r="C10" s="50" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" s="50" t="s">
+        <v>59</v>
       </c>
       <c r="E10" s="50" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F10" s="50" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G10" s="50">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="H10" s="50">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I10" s="50">
+        <v>1</v>
+      </c>
+      <c r="J10" s="50">
+        <v>2</v>
+      </c>
+      <c r="K10" s="50">
+        <v>9</v>
+      </c>
+      <c r="L10" s="50">
+        <v>12</v>
+      </c>
+      <c r="M10" s="50">
+        <v>1</v>
+      </c>
+      <c r="N10" s="50">
+        <v>6</v>
+      </c>
+      <c r="O10" s="50">
+        <v>4</v>
+      </c>
+      <c r="P10" s="50">
         <v>10</v>
       </c>
-      <c r="J10" s="50">
-        <v>10</v>
-      </c>
-      <c r="K10" s="49">
-        <v>9</v>
-      </c>
-      <c r="L10" s="49">
-        <v>12</v>
-      </c>
-      <c r="M10" s="49">
-        <v>1</v>
-      </c>
-      <c r="N10" s="49">
-        <v>6</v>
-      </c>
-      <c r="O10" s="49">
+      <c r="Q10" s="50">
+        <v>7</v>
+      </c>
+      <c r="R10" s="50">
+        <v>7</v>
+      </c>
+      <c r="S10" s="50">
         <v>4</v>
       </c>
-      <c r="P10" s="49">
-        <v>10</v>
-      </c>
-      <c r="Q10" s="49">
-        <v>7</v>
-      </c>
-      <c r="R10" s="49">
-        <v>7</v>
-      </c>
-      <c r="S10" s="49">
-        <v>4</v>
-      </c>
-      <c r="T10" s="49">
+      <c r="T10" s="50">
         <v>700</v>
       </c>
-      <c r="U10" s="49">
-        <v>1</v>
-      </c>
-      <c r="V10" s="49">
+      <c r="U10" s="50">
+        <v>1</v>
+      </c>
+      <c r="V10" s="50">
         <v>35</v>
       </c>
-      <c r="W10" s="49" t="s">
-        <v>62</v>
+      <c r="W10" s="50" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="49">
+      <c r="A11" s="50">
         <v>1000008</v>
       </c>
-      <c r="B11" s="49">
-        <v>1</v>
-      </c>
-      <c r="C11" s="49" t="s">
-        <v>55</v>
-      </c>
-      <c r="D11" s="49" t="s">
-        <v>55</v>
+      <c r="B11" s="50">
+        <v>1</v>
+      </c>
+      <c r="C11" s="50" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" s="50" t="s">
+        <v>59</v>
       </c>
       <c r="E11" s="50" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F11" s="50" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G11" s="50">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="H11" s="50">
+        <v>5</v>
+      </c>
+      <c r="I11" s="50">
+        <v>1</v>
+      </c>
+      <c r="J11" s="50">
+        <v>2</v>
+      </c>
+      <c r="K11" s="50">
+        <v>9</v>
+      </c>
+      <c r="L11" s="50">
+        <v>13</v>
+      </c>
+      <c r="M11" s="50">
+        <v>1</v>
+      </c>
+      <c r="N11" s="50">
+        <v>6</v>
+      </c>
+      <c r="O11" s="50">
         <v>3</v>
       </c>
-      <c r="I11" s="50">
+      <c r="P11" s="50">
         <v>10</v>
       </c>
-      <c r="J11" s="50">
-        <v>10</v>
-      </c>
-      <c r="K11" s="49">
-        <v>9</v>
-      </c>
-      <c r="L11" s="49">
-        <v>13</v>
-      </c>
-      <c r="M11" s="49">
-        <v>1</v>
-      </c>
-      <c r="N11" s="49">
-        <v>6</v>
-      </c>
-      <c r="O11" s="49">
-        <v>3</v>
-      </c>
-      <c r="P11" s="49">
-        <v>10</v>
-      </c>
-      <c r="Q11" s="49">
+      <c r="Q11" s="50">
         <v>8</v>
       </c>
-      <c r="R11" s="49">
+      <c r="R11" s="50">
         <v>8</v>
       </c>
-      <c r="S11" s="49">
+      <c r="S11" s="50">
         <v>4</v>
       </c>
-      <c r="T11" s="49">
+      <c r="T11" s="50">
         <v>800</v>
       </c>
-      <c r="U11" s="49">
-        <v>1</v>
-      </c>
-      <c r="V11" s="49">
+      <c r="U11" s="50">
+        <v>1</v>
+      </c>
+      <c r="V11" s="50">
         <v>40</v>
       </c>
-      <c r="W11" s="49" t="s">
-        <v>63</v>
+      <c r="W11" s="50" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="49">
+      <c r="A12" s="50">
         <v>1000009</v>
       </c>
-      <c r="B12" s="49">
-        <v>1</v>
-      </c>
-      <c r="C12" s="49" t="s">
-        <v>55</v>
-      </c>
-      <c r="D12" s="49" t="s">
-        <v>55</v>
+      <c r="B12" s="50">
+        <v>1</v>
+      </c>
+      <c r="C12" s="50" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" s="50" t="s">
+        <v>59</v>
       </c>
       <c r="E12" s="50" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F12" s="50" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G12" s="50">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="H12" s="50">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I12" s="50">
+        <v>1</v>
+      </c>
+      <c r="J12" s="50">
+        <v>2</v>
+      </c>
+      <c r="K12" s="50">
         <v>10</v>
       </c>
-      <c r="J12" s="50">
+      <c r="L12" s="50">
+        <v>14</v>
+      </c>
+      <c r="M12" s="50">
+        <v>1</v>
+      </c>
+      <c r="N12" s="50">
+        <v>6</v>
+      </c>
+      <c r="O12" s="50">
+        <v>2</v>
+      </c>
+      <c r="P12" s="50">
         <v>10</v>
       </c>
-      <c r="K12" s="49">
-        <v>10</v>
-      </c>
-      <c r="L12" s="49">
-        <v>14</v>
-      </c>
-      <c r="M12" s="49">
-        <v>1</v>
-      </c>
-      <c r="N12" s="49">
-        <v>6</v>
-      </c>
-      <c r="O12" s="49">
-        <v>2</v>
-      </c>
-      <c r="P12" s="49">
-        <v>10</v>
-      </c>
-      <c r="Q12" s="49">
+      <c r="Q12" s="50">
         <v>9</v>
       </c>
-      <c r="R12" s="49">
+      <c r="R12" s="50">
         <v>9</v>
       </c>
-      <c r="S12" s="49">
+      <c r="S12" s="50">
         <v>5</v>
       </c>
-      <c r="T12" s="49">
+      <c r="T12" s="50">
         <v>900</v>
       </c>
-      <c r="U12" s="49">
-        <v>1</v>
-      </c>
-      <c r="V12" s="49">
+      <c r="U12" s="50">
+        <v>1</v>
+      </c>
+      <c r="V12" s="50">
         <v>45</v>
       </c>
-      <c r="W12" s="49" t="s">
-        <v>64</v>
+      <c r="W12" s="50" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="49">
+      <c r="A13" s="50">
         <v>1000010</v>
       </c>
-      <c r="B13" s="49">
-        <v>1</v>
-      </c>
-      <c r="C13" s="49" t="s">
-        <v>55</v>
-      </c>
-      <c r="D13" s="49" t="s">
-        <v>55</v>
+      <c r="B13" s="50">
+        <v>1</v>
+      </c>
+      <c r="C13" s="50" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" s="50" t="s">
+        <v>59</v>
       </c>
       <c r="E13" s="50" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F13" s="50" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G13" s="50">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="H13" s="50">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I13" s="50">
+        <v>1</v>
+      </c>
+      <c r="J13" s="50">
+        <v>2</v>
+      </c>
+      <c r="K13" s="50">
         <v>10</v>
       </c>
-      <c r="J13" s="50">
+      <c r="L13" s="50">
+        <v>15</v>
+      </c>
+      <c r="M13" s="50">
+        <v>1</v>
+      </c>
+      <c r="N13" s="50">
+        <v>6</v>
+      </c>
+      <c r="O13" s="50">
+        <v>1</v>
+      </c>
+      <c r="P13" s="50">
         <v>10</v>
       </c>
-      <c r="K13" s="49">
+      <c r="Q13" s="50">
         <v>10</v>
       </c>
-      <c r="L13" s="49">
-        <v>15</v>
-      </c>
-      <c r="M13" s="49">
-        <v>1</v>
-      </c>
-      <c r="N13" s="49">
-        <v>6</v>
-      </c>
-      <c r="O13" s="49">
-        <v>1</v>
-      </c>
-      <c r="P13" s="49">
+      <c r="R13" s="50">
         <v>10</v>
       </c>
-      <c r="Q13" s="49">
-        <v>10</v>
-      </c>
-      <c r="R13" s="49">
-        <v>10</v>
-      </c>
-      <c r="S13" s="49">
+      <c r="S13" s="50">
         <v>5</v>
       </c>
-      <c r="T13" s="49">
+      <c r="T13" s="50">
         <v>1000</v>
       </c>
-      <c r="U13" s="49">
-        <v>1</v>
-      </c>
-      <c r="V13" s="49">
+      <c r="U13" s="50">
+        <v>1</v>
+      </c>
+      <c r="V13" s="50">
         <v>50</v>
       </c>
-      <c r="W13" s="49" t="s">
-        <v>65</v>
+      <c r="W13" s="50" t="s">
+        <v>69</v>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1"/>
-    <row r="32" ht="15" customHeight="1"/>
-    <row r="33" ht="15" customHeight="1"/>
-    <row r="34" ht="15" customHeight="1"/>
-    <row r="35" ht="15" customHeight="1"/>
-    <row r="36" ht="15" customHeight="1"/>
-    <row r="37" ht="15" customHeight="1"/>
-    <row r="38" ht="15" customHeight="1"/>
-    <row r="39" ht="15" customHeight="1"/>
-    <row r="40" ht="15" customHeight="1"/>
-    <row r="41" ht="15" customHeight="1"/>
-    <row r="73" ht="12" customHeight="1"/>
-    <row r="74" ht="12" customHeight="1"/>
-    <row r="75" ht="12" customHeight="1"/>
-    <row r="76" ht="12" customHeight="1"/>
-    <row r="77" ht="12" customHeight="1"/>
-    <row r="78" ht="12" customHeight="1"/>
-    <row r="79" ht="12" customHeight="1"/>
-    <row r="80" ht="12" customHeight="1"/>
-    <row r="81" ht="12" customHeight="1"/>
+    <row r="31" ht="15" customHeight="1" s="51" customFormat="1"/>
+    <row r="32" ht="15" customHeight="1" s="51" customFormat="1"/>
+    <row r="33" ht="15" customHeight="1" s="51" customFormat="1"/>
+    <row r="34" ht="15" customHeight="1" s="51" customFormat="1"/>
+    <row r="35" ht="15" customHeight="1" s="51" customFormat="1"/>
+    <row r="36" ht="15" customHeight="1" s="51" customFormat="1"/>
+    <row r="37" ht="15" customHeight="1" s="51" customFormat="1"/>
+    <row r="38" ht="15" customHeight="1" s="51" customFormat="1"/>
+    <row r="39" ht="15" customHeight="1" s="51" customFormat="1"/>
+    <row r="40" ht="15" customHeight="1" s="51" customFormat="1"/>
+    <row r="41" ht="15" customHeight="1" s="51" customFormat="1"/>
+    <row r="73" ht="12" customHeight="1" s="51" customFormat="1"/>
+    <row r="74" ht="12" customHeight="1" s="51" customFormat="1"/>
+    <row r="75" ht="12" customHeight="1" s="51" customFormat="1"/>
+    <row r="76" ht="12" customHeight="1" s="51" customFormat="1"/>
+    <row r="77" ht="12" customHeight="1" s="51" customFormat="1"/>
+    <row r="78" ht="12" customHeight="1" s="51" customFormat="1"/>
+    <row r="79" ht="12" customHeight="1" s="51" customFormat="1"/>
+    <row r="80" ht="12" customHeight="1" s="51" customFormat="1"/>
+    <row r="81" ht="12" customHeight="1" s="51" customFormat="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
@@ -177,13 +177,13 @@
     <t>1010020001</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
     <t>10</t>
   </si>
   <si>
-    <t>3</t>
+    <t>60</t>
+  </si>
+  <si>
+    <t>5</t>
   </si>
   <si>
     <t>2</t>
@@ -966,7 +966,7 @@
     <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="32" applyFill="1" borderId="0" applyBorder="1" xfId="48" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="19575" windowHeight="11505" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="FightTypeConquerInfo" sheetId="1" state="visible" r:id="rId1"/>
@@ -16,15 +16,17 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="20">
+  <fonts count="19">
     <font>
       <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="134"/>
       <color rgb="FF0000FF"/>
       <sz val="11"/>
       <u val="single"/>
@@ -32,6 +34,7 @@
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="134"/>
       <color rgb="FF800080"/>
       <sz val="11"/>
       <u val="single"/>
@@ -39,12 +42,14 @@
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="134"/>
       <color rgb="FFFF0000"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="134"/>
       <b val="1"/>
       <color theme="3"/>
       <sz val="18"/>
@@ -52,6 +57,7 @@
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="134"/>
       <i val="1"/>
       <color rgb="FF7F7F7F"/>
       <sz val="11"/>
@@ -59,6 +65,7 @@
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="134"/>
       <b val="1"/>
       <color theme="3"/>
       <sz val="15"/>
@@ -66,6 +73,7 @@
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="134"/>
       <b val="1"/>
       <color theme="3"/>
       <sz val="13"/>
@@ -73,6 +81,7 @@
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="134"/>
       <b val="1"/>
       <color theme="3"/>
       <sz val="11"/>
@@ -80,12 +89,14 @@
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="134"/>
       <color rgb="FF3F3F76"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="134"/>
       <b val="1"/>
       <color rgb="FF3F3F3F"/>
       <sz val="11"/>
@@ -93,6 +104,7 @@
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="134"/>
       <b val="1"/>
       <color rgb="FFFA7D00"/>
       <sz val="11"/>
@@ -100,6 +112,7 @@
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="134"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
@@ -107,12 +120,14 @@
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="134"/>
       <color rgb="FFFA7D00"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="134"/>
       <b val="1"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -120,31 +135,29 @@
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="134"/>
       <color rgb="FF006100"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="134"/>
       <color rgb="FF9C0006"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="134"/>
       <color rgb="FF9C6500"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="134"/>
       <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
@@ -451,22 +464,22 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="19" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="19" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
@@ -475,7 +488,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
@@ -529,10 +542,10 @@
     <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
@@ -541,10 +554,10 @@
     <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
@@ -553,10 +566,10 @@
     <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
@@ -565,10 +578,10 @@
     <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
@@ -577,10 +590,10 @@
     <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
@@ -589,167 +602,17 @@
     <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="52">
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="11">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="12">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="13">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="14">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="15">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="16">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="17">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="18">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="19">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="20">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="21">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="22">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="23">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="24">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="25">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="26">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="27">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="28">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="29">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="30">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="31">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="32">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="33">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="34">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="35">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="36">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="37">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="38">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="41">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="43">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="44">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="45">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="46">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="47">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="48">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1168,1304 +1031,1337 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y13"/>
+  <dimension ref="A1:X13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="17.125" customWidth="1" style="50" min="3" max="3"/>
-    <col width="36.5" customWidth="1" style="50" min="4" max="4"/>
-    <col width="23.75" customWidth="1" style="50" min="5" max="5"/>
-    <col width="32.625" customWidth="1" style="50" min="6" max="6"/>
-    <col width="10.375" customWidth="1" style="50" min="7" max="7"/>
-    <col width="18.25" customWidth="1" style="50" min="8" max="8"/>
-    <col width="16" customWidth="1" style="50" min="9" max="16"/>
-    <col width="12.25" customWidth="1" style="50" min="17" max="17"/>
-    <col width="12.875" customWidth="1" style="50" min="18" max="19"/>
-    <col width="17.375" customWidth="1" style="50" min="20" max="20"/>
-    <col width="19.75" customWidth="1" style="50" min="21" max="21"/>
-    <col width="29.375" customWidth="1" style="50" min="22" max="22"/>
-    <col width="42.875" customWidth="1" style="50" min="23" max="23"/>
-    <col width="25.125" customWidth="1" style="50" min="24" max="24"/>
+    <col width="17.125" customWidth="1" style="1" min="3" max="3"/>
+    <col width="36.5" customWidth="1" style="1" min="4" max="4"/>
+    <col width="23.75" customWidth="1" style="1" min="5" max="5"/>
+    <col width="18.375" customWidth="1" style="1" min="6" max="6"/>
+    <col width="31.875" customWidth="1" style="1" min="7" max="7"/>
+    <col width="18.25" customWidth="1" style="1" min="8" max="8"/>
+    <col width="16" customWidth="1" style="1" min="9" max="16"/>
+    <col width="12.25" customWidth="1" style="1" min="17" max="17"/>
+    <col width="12.875" customWidth="1" style="1" min="18" max="19"/>
+    <col width="17.375" customWidth="1" style="1" min="20" max="20"/>
+    <col width="19.75" customWidth="1" style="1" min="21" max="21"/>
+    <col width="29.375" customWidth="1" style="1" min="22" max="22"/>
+    <col width="42.875" customWidth="1" style="1" min="23" max="23"/>
+    <col width="25.125" customWidth="1" style="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="50" t="inlineStr">
+      <c r="A1" s="0" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" s="50" t="inlineStr">
+      <c r="B1" s="0" t="inlineStr">
         <is>
           <t>world_id</t>
         </is>
       </c>
-      <c r="C1" s="50" t="inlineStr">
+      <c r="C1" s="0" t="inlineStr">
         <is>
           <t>fight_scene_ids</t>
         </is>
       </c>
-      <c r="D1" s="50" t="inlineStr">
+      <c r="D1" s="0" t="inlineStr">
         <is>
           <t>fight_scene_boss_ids</t>
         </is>
       </c>
-      <c r="E1" s="50" t="inlineStr">
+      <c r="E1" s="0" t="inlineStr">
         <is>
           <t>enemy_ids</t>
         </is>
       </c>
-      <c r="F1" s="50" t="inlineStr">
+      <c r="F1" s="0" t="inlineStr">
         <is>
           <t>enemy_boss_ids</t>
         </is>
       </c>
-      <c r="G1" s="50" t="inlineStr">
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>attack_boss_num</t>
+        </is>
+      </c>
+      <c r="H1" s="0" t="inlineStr">
         <is>
           <t>attack_start_num</t>
         </is>
       </c>
-      <c r="H1" s="50" t="inlineStr">
+      <c r="I1" s="0" t="inlineStr">
         <is>
           <t>attack_show_time</t>
         </is>
       </c>
-      <c r="I1" s="50" t="inlineStr">
+      <c r="J1" s="0" t="inlineStr">
         <is>
           <t>attack_num_addrate</t>
         </is>
       </c>
-      <c r="J1" s="50" t="inlineStr">
+      <c r="K1" s="0" t="inlineStr">
         <is>
           <t>attack_num_add</t>
         </is>
       </c>
-      <c r="K1" s="50" t="inlineStr">
-        <is>
-          <t>fight_num_min</t>
-        </is>
-      </c>
-      <c r="L1" s="50" t="inlineStr">
-        <is>
-          <t>fight_num_max</t>
-        </is>
-      </c>
-      <c r="M1" s="50" t="inlineStr">
-        <is>
-          <t>road_num_min</t>
-        </is>
-      </c>
-      <c r="N1" s="50" t="inlineStr">
-        <is>
-          <t>road_num_max</t>
-        </is>
-      </c>
-      <c r="O1" s="50" t="inlineStr">
-        <is>
-          <t>road_length_min</t>
-        </is>
-      </c>
-      <c r="P1" s="50" t="inlineStr">
-        <is>
-          <t>road_length_max</t>
-        </is>
-      </c>
-      <c r="Q1" s="50" t="inlineStr">
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>attack_intensity_addrate</t>
+        </is>
+      </c>
+      <c r="M1" s="0" t="inlineStr">
+        <is>
+          <t>fight_num</t>
+        </is>
+      </c>
+      <c r="N1" s="0" t="inlineStr">
+        <is>
+          <t>road_num</t>
+        </is>
+      </c>
+      <c r="O1" s="0" t="inlineStr">
+        <is>
+          <t>road_length</t>
+        </is>
+      </c>
+      <c r="P1" s="0" t="inlineStr">
         <is>
           <t>level</t>
         </is>
       </c>
-      <c r="R1" s="50" t="inlineStr">
+      <c r="Q1" s="0" t="inlineStr">
         <is>
           <t>level_add</t>
         </is>
       </c>
-      <c r="S1" s="50" t="inlineStr">
+      <c r="R1" s="0" t="inlineStr">
         <is>
           <t>drop_crystal</t>
         </is>
       </c>
-      <c r="T1" s="50" t="inlineStr">
+      <c r="S1" s="0" t="inlineStr">
         <is>
           <t>reward_crystal</t>
         </is>
       </c>
-      <c r="U1" s="50" t="inlineStr">
+      <c r="T1" s="0" t="inlineStr">
         <is>
           <t>reward_equip_rarity</t>
         </is>
       </c>
-      <c r="V1" s="50" t="inlineStr">
+      <c r="U1" s="0" t="inlineStr">
         <is>
           <t>reward_equip_attribute_add</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="V1" s="0" t="inlineStr">
         <is>
           <t>reward_exp</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="W1" s="0" t="inlineStr">
         <is>
           <t>reward_exp_boss</t>
         </is>
       </c>
-      <c r="Y1" s="50" t="inlineStr">
+      <c r="X1" s="0" t="inlineStr">
         <is>
           <t>remark</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="50" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
         <is>
           <t>long</t>
         </is>
       </c>
-      <c r="B2" s="50" t="inlineStr">
+      <c r="B2" s="0" t="inlineStr">
         <is>
           <t>long</t>
         </is>
       </c>
-      <c r="C2" s="50" t="inlineStr">
+      <c r="C2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D2" s="50" t="inlineStr">
+      <c r="D2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E2" s="50" t="inlineStr">
+      <c r="E2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F2" s="50" t="inlineStr">
+      <c r="F2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="G2" s="50" t="inlineStr">
+      <c r="G2" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H2" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="H2" s="50" t="inlineStr">
+      <c r="I2" s="0" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="I2" s="50" t="inlineStr">
+      <c r="J2" s="0" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="J2" s="50" t="inlineStr">
+      <c r="K2" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="K2" s="50" t="inlineStr">
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="M2" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N2" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="O2" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="P2" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="L2" s="50" t="inlineStr">
+      <c r="Q2" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="R2" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="M2" s="50" t="inlineStr">
+      <c r="S2" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="N2" s="50" t="inlineStr">
+      <c r="T2" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="O2" s="50" t="inlineStr">
+      <c r="U2" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="P2" s="50" t="inlineStr">
+      <c r="V2" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="Q2" s="50" t="inlineStr">
+      <c r="W2" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="R2" s="50" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="S2" s="50" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="T2" s="50" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="U2" s="50" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="V2" s="50" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="Y2" s="50" t="inlineStr">
+      <c r="X2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="50" t="inlineStr">
-        <is>
-          <t>序号</t>
-        </is>
-      </c>
-      <c r="B3" s="50" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>编号</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
         <is>
           <t>世界ID</t>
         </is>
       </c>
-      <c r="C3" s="50" t="inlineStr">
+      <c r="C3" s="0" t="inlineStr">
         <is>
           <t>战斗场景列表（用&amp;分割）</t>
         </is>
       </c>
-      <c r="D3" s="50" t="inlineStr">
+      <c r="D3" s="0" t="inlineStr">
         <is>
           <t>boss战斗场景列表（用&amp;分割）</t>
         </is>
       </c>
-      <c r="E3" s="50" t="inlineStr">
-        <is>
-          <t>敌人列表（npcInfoId用&amp;分割）（npcInfoId用&amp;分割）</t>
-        </is>
-      </c>
-      <c r="F3" s="50" t="inlineStr">
+      <c r="E3" s="0" t="inlineStr">
+        <is>
+          <t>敌人列表（npcInfoId用&amp;分割）</t>
+        </is>
+      </c>
+      <c r="F3" s="0" t="inlineStr">
         <is>
           <t>boss列表（npcInfoId用&amp;分割）</t>
         </is>
       </c>
-      <c r="G3" s="50" t="inlineStr">
+      <c r="G3" s="0" t="inlineStr">
+        <is>
+          <t>boss数量(单个数x或范围x-y)</t>
+        </is>
+      </c>
+      <c r="H3" s="0" t="inlineStr">
         <is>
           <t>第一关敌人数量</t>
         </is>
       </c>
-      <c r="H3" s="50" t="inlineStr">
+      <c r="I3" s="0" t="inlineStr">
         <is>
           <t>进攻时间(秒)</t>
         </is>
       </c>
-      <c r="I3" s="50" t="inlineStr">
+      <c r="J3" s="0" t="inlineStr">
         <is>
           <t>每关敌人倍数</t>
         </is>
       </c>
-      <c r="J3" s="50" t="inlineStr">
+      <c r="K3" s="0" t="inlineStr">
         <is>
           <t>每关增加敌人数量</t>
         </is>
       </c>
-      <c r="K3" s="50" t="inlineStr">
-        <is>
-          <t>关卡次数-最小</t>
-        </is>
-      </c>
-      <c r="L3" s="50" t="inlineStr">
-        <is>
-          <t>关卡次数-最大</t>
-        </is>
-      </c>
-      <c r="M3" s="50" t="inlineStr">
-        <is>
-          <t>道路数量-最小</t>
-        </is>
-      </c>
-      <c r="N3" s="50" t="inlineStr">
-        <is>
-          <t>道路数量-最大</t>
-        </is>
-      </c>
-      <c r="O3" s="50" t="inlineStr">
-        <is>
-          <t>道路长度-最小</t>
-        </is>
-      </c>
-      <c r="P3" s="50" t="inlineStr">
-        <is>
-          <t>道路长度-最大</t>
-        </is>
-      </c>
-      <c r="Q3" s="50" t="inlineStr">
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>普通敌人每关强度倍率(默认1,如1.1则每关HP/护甲/攻击力×1.1)</t>
+        </is>
+      </c>
+      <c r="M3" s="0" t="inlineStr">
+        <is>
+          <t>关卡次数(单个数x或范围x-y)</t>
+        </is>
+      </c>
+      <c r="N3" s="0" t="inlineStr">
+        <is>
+          <t>道路数量(单个数x或范围x-y)</t>
+        </is>
+      </c>
+      <c r="O3" s="0" t="inlineStr">
+        <is>
+          <t>道路长度(单个数x或范围x-y)</t>
+        </is>
+      </c>
+      <c r="P3" s="0" t="inlineStr">
         <is>
           <t>难度</t>
         </is>
       </c>
-      <c r="R3" s="50" t="inlineStr">
+      <c r="Q3" s="0" t="inlineStr">
         <is>
           <t>难度数值加成</t>
         </is>
       </c>
-      <c r="S3" s="50" t="inlineStr">
+      <c r="R3" s="0" t="inlineStr">
         <is>
           <t>掉落魔晶</t>
         </is>
       </c>
-      <c r="T3" s="50" t="inlineStr">
+      <c r="S3" s="0" t="inlineStr">
         <is>
           <t>奖励-魔晶</t>
         </is>
       </c>
-      <c r="U3" s="50" t="inlineStr">
+      <c r="T3" s="0" t="inlineStr">
         <is>
           <t>奖励-装备稀有度</t>
         </is>
       </c>
-      <c r="V3" s="50" t="inlineStr">
+      <c r="U3" s="0" t="inlineStr">
         <is>
           <t>奖励-装备属性加成</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="V3" s="0" t="inlineStr">
         <is>
           <t>奖励-普通关卡经验</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" s="0" t="inlineStr">
         <is>
           <t>奖励-BOSS关卡经验</t>
         </is>
       </c>
-      <c r="Y3" s="50" t="inlineStr">
+      <c r="X3" s="0" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="50" t="n">
+      <c r="A4" s="0" t="n">
         <v>1000001</v>
       </c>
-      <c r="B4" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="50" t="inlineStr">
+      <c r="B4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
         <is>
           <t>99999</t>
         </is>
       </c>
-      <c r="D4" s="50" t="inlineStr">
+      <c r="D4" s="0" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E4" s="50" t="inlineStr">
+      <c r="E4" s="0" t="inlineStr">
         <is>
           <t>1010010001</t>
         </is>
       </c>
-      <c r="F4" s="50" t="inlineStr">
+      <c r="F4" s="0" t="inlineStr">
         <is>
           <t>1010020001</t>
         </is>
       </c>
-      <c r="G4" s="50" t="inlineStr">
+      <c r="G4" s="0" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="0" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H4" s="50" t="inlineStr">
+      <c r="I4" s="0" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="I4" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" s="50" t="inlineStr">
+      <c r="J4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" s="0" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="K4" s="50" t="n">
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" s="0" t="inlineStr">
+        <is>
+          <t>5-6</t>
+        </is>
+      </c>
+      <c r="N4" s="0" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O4" s="0" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="T4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="L4" s="50" t="n">
-        <v>6</v>
-      </c>
-      <c r="M4" s="50" t="n">
-        <v>2</v>
-      </c>
-      <c r="N4" s="50" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O4" s="50" t="n">
+      <c r="V4" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="P4" s="50" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q4" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="R4" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="T4" s="50" t="n">
-        <v>100</v>
-      </c>
-      <c r="U4" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="V4" s="50" t="n">
-        <v>5</v>
-      </c>
-      <c r="W4" t="n">
-        <v>10</v>
-      </c>
-      <c r="X4" t="n">
+      <c r="W4" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="Y4" s="50" t="inlineStr">
+      <c r="X4" s="0" t="inlineStr">
         <is>
           <t>剑与魔法-难度1</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="50" t="n">
+      <c r="A5" s="0" t="n">
         <v>1000002</v>
       </c>
-      <c r="B5" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="50" t="inlineStr">
+      <c r="B5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>1&amp;1</t>
         </is>
       </c>
-      <c r="D5" s="50" t="inlineStr">
+      <c r="D5" s="0" t="inlineStr">
         <is>
           <t>1&amp;1</t>
         </is>
       </c>
-      <c r="E5" s="50" t="inlineStr">
+      <c r="E5" s="0" t="inlineStr">
         <is>
           <t>1010010001&amp;1010010001</t>
         </is>
       </c>
-      <c r="F5" s="50" t="inlineStr">
+      <c r="F5" s="0" t="inlineStr">
         <is>
           <t>1010010001&amp;1010010001</t>
         </is>
       </c>
-      <c r="G5" s="50" t="n">
+      <c r="G5" s="0" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H5" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="H5" s="50" t="n">
+      <c r="I5" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="I5" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" s="50" t="n">
+      <c r="J5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="K5" s="50" t="n">
-        <v>5</v>
-      </c>
-      <c r="L5" s="50" t="n">
-        <v>7</v>
-      </c>
-      <c r="M5" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="N5" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="O5" s="50" t="n">
-        <v>9</v>
-      </c>
-      <c r="P5" s="50" t="n">
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="0" t="inlineStr">
+        <is>
+          <t>5-7</t>
+        </is>
+      </c>
+      <c r="N5" s="0" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
+      </c>
+      <c r="O5" s="0" t="inlineStr">
+        <is>
+          <t>9-10</t>
+        </is>
+      </c>
+      <c r="P5" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q5" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="R5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="T5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="Q5" s="50" t="n">
-        <v>2</v>
-      </c>
-      <c r="R5" s="50" t="n">
-        <v>2</v>
-      </c>
-      <c r="S5" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" s="50" t="n">
-        <v>200</v>
-      </c>
-      <c r="U5" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" s="50" t="n">
-        <v>10</v>
-      </c>
-      <c r="W5" t="n">
+      <c r="V5" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="X5" t="n">
+      <c r="W5" s="0" t="n">
         <v>100</v>
       </c>
-      <c r="Y5" s="50" t="inlineStr">
+      <c r="X5" s="0" t="inlineStr">
         <is>
           <t>剑与魔法-难度2</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="50" t="n">
+      <c r="A6" s="0" t="n">
         <v>1000003</v>
       </c>
-      <c r="B6" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="50" t="inlineStr">
+      <c r="B6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
         <is>
           <t>1&amp;1</t>
         </is>
       </c>
-      <c r="D6" s="50" t="inlineStr">
+      <c r="D6" s="0" t="inlineStr">
         <is>
           <t>1&amp;1</t>
         </is>
       </c>
-      <c r="E6" s="50" t="inlineStr">
+      <c r="E6" s="0" t="inlineStr">
         <is>
           <t>1010010001&amp;1010010001</t>
         </is>
       </c>
-      <c r="F6" s="50" t="inlineStr">
+      <c r="F6" s="0" t="inlineStr">
         <is>
           <t>1010010001&amp;1010010001</t>
         </is>
       </c>
-      <c r="G6" s="50" t="n">
+      <c r="G6" s="0" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H6" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="H6" s="50" t="n">
+      <c r="I6" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="I6" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" s="50" t="n">
+      <c r="J6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="K6" s="50" t="n">
-        <v>6</v>
-      </c>
-      <c r="L6" s="50" t="n">
-        <v>8</v>
-      </c>
-      <c r="M6" s="50" t="n">
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" s="0" t="inlineStr">
+        <is>
+          <t>6-8</t>
+        </is>
+      </c>
+      <c r="N6" s="0" t="inlineStr">
+        <is>
+          <t>3-5</t>
+        </is>
+      </c>
+      <c r="O6" s="0" t="inlineStr">
+        <is>
+          <t>8-10</t>
+        </is>
+      </c>
+      <c r="P6" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="N6" s="50" t="n">
-        <v>5</v>
-      </c>
-      <c r="O6" s="50" t="n">
-        <v>8</v>
-      </c>
-      <c r="P6" s="50" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q6" s="50" t="n">
+      <c r="Q6" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="R6" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="S6" s="50" t="n">
+      <c r="R6" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="T6" s="50" t="n">
+      <c r="S6" s="0" t="n">
         <v>300</v>
       </c>
-      <c r="U6" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" s="50" t="n">
+      <c r="T6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" s="0" t="n">
         <v>15</v>
       </c>
-      <c r="W6" t="n">
+      <c r="V6" s="0" t="n">
         <v>30</v>
       </c>
-      <c r="X6" t="n">
+      <c r="W6" s="0" t="n">
         <v>150</v>
       </c>
-      <c r="Y6" s="50" t="inlineStr">
+      <c r="X6" s="0" t="inlineStr">
         <is>
           <t>剑与魔法-难度3</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="50" t="n">
+      <c r="A7" s="0" t="n">
         <v>1000004</v>
       </c>
-      <c r="B7" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="50" t="inlineStr">
+      <c r="B7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
         <is>
           <t>1&amp;1</t>
         </is>
       </c>
-      <c r="D7" s="50" t="inlineStr">
+      <c r="D7" s="0" t="inlineStr">
         <is>
           <t>1&amp;1</t>
         </is>
       </c>
-      <c r="E7" s="50" t="inlineStr">
+      <c r="E7" s="0" t="inlineStr">
         <is>
           <t>1010010001&amp;1010010001</t>
         </is>
       </c>
-      <c r="F7" s="50" t="inlineStr">
+      <c r="F7" s="0" t="inlineStr">
         <is>
           <t>1010010001&amp;1010010001</t>
         </is>
       </c>
-      <c r="G7" s="50" t="n">
+      <c r="G7" s="0" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="H7" s="50" t="n">
+      <c r="I7" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="I7" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" s="50" t="n">
+      <c r="J7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="K7" s="50" t="n">
-        <v>6</v>
-      </c>
-      <c r="L7" s="50" t="n">
-        <v>9</v>
-      </c>
-      <c r="M7" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="N7" s="50" t="n">
-        <v>6</v>
-      </c>
-      <c r="O7" s="50" t="n">
-        <v>7</v>
-      </c>
-      <c r="P7" s="50" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q7" s="50" t="n">
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" s="0" t="inlineStr">
+        <is>
+          <t>6-9</t>
+        </is>
+      </c>
+      <c r="N7" s="0" t="inlineStr">
+        <is>
+          <t>3-6</t>
+        </is>
+      </c>
+      <c r="O7" s="0" t="inlineStr">
+        <is>
+          <t>7-10</t>
+        </is>
+      </c>
+      <c r="P7" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="R7" s="50" t="n">
+      <c r="Q7" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="S7" s="50" t="n">
+      <c r="R7" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="T7" s="50" t="n">
+      <c r="S7" s="0" t="n">
         <v>400</v>
       </c>
-      <c r="U7" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" s="50" t="n">
+      <c r="T7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="W7" t="n">
+      <c r="V7" s="0" t="n">
         <v>40</v>
       </c>
-      <c r="X7" t="n">
+      <c r="W7" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="Y7" s="50" t="inlineStr">
+      <c r="X7" s="0" t="inlineStr">
         <is>
           <t>剑与魔法-难度4</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="50" t="n">
+      <c r="A8" s="0" t="n">
         <v>1000005</v>
       </c>
-      <c r="B8" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="50" t="inlineStr">
+      <c r="B8" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
         <is>
           <t>1&amp;1</t>
         </is>
       </c>
-      <c r="D8" s="50" t="inlineStr">
+      <c r="D8" s="0" t="inlineStr">
         <is>
           <t>1&amp;1</t>
         </is>
       </c>
-      <c r="E8" s="50" t="inlineStr">
+      <c r="E8" s="0" t="inlineStr">
         <is>
           <t>1010010001&amp;1010010001</t>
         </is>
       </c>
-      <c r="F8" s="50" t="inlineStr">
+      <c r="F8" s="0" t="inlineStr">
         <is>
           <t>1010010001&amp;1010010001</t>
         </is>
       </c>
-      <c r="G8" s="50" t="n">
+      <c r="G8" s="0" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="H8" s="50" t="n">
+      <c r="I8" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="I8" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" s="50" t="n">
+      <c r="J8" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="K8" s="50" t="n">
-        <v>7</v>
-      </c>
-      <c r="L8" s="50" t="n">
-        <v>10</v>
-      </c>
-      <c r="M8" s="50" t="n">
-        <v>2</v>
-      </c>
-      <c r="N8" s="50" t="n">
-        <v>6</v>
-      </c>
-      <c r="O8" s="50" t="n">
-        <v>6</v>
-      </c>
-      <c r="P8" s="50" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q8" s="50" t="n">
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" s="0" t="inlineStr">
+        <is>
+          <t>7-10</t>
+        </is>
+      </c>
+      <c r="N8" s="0" t="inlineStr">
+        <is>
+          <t>2-6</t>
+        </is>
+      </c>
+      <c r="O8" s="0" t="inlineStr">
+        <is>
+          <t>6-10</t>
+        </is>
+      </c>
+      <c r="P8" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="R8" s="50" t="n">
+      <c r="Q8" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="S8" s="50" t="n">
+      <c r="R8" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="T8" s="50" t="n">
+      <c r="S8" s="0" t="n">
         <v>500</v>
       </c>
-      <c r="U8" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="V8" s="50" t="n">
+      <c r="T8" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" s="0" t="n">
         <v>25</v>
       </c>
-      <c r="W8" t="n">
+      <c r="V8" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="X8" t="n">
+      <c r="W8" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="Y8" s="50" t="inlineStr">
+      <c r="X8" s="0" t="inlineStr">
         <is>
           <t>剑与魔法-难度5</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="50" t="n">
+      <c r="A9" s="0" t="n">
         <v>1000006</v>
       </c>
-      <c r="B9" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="50" t="inlineStr">
+      <c r="B9" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
         <is>
           <t>1&amp;1</t>
         </is>
       </c>
-      <c r="D9" s="50" t="inlineStr">
+      <c r="D9" s="0" t="inlineStr">
         <is>
           <t>1&amp;1</t>
         </is>
       </c>
-      <c r="E9" s="50" t="inlineStr">
+      <c r="E9" s="0" t="inlineStr">
         <is>
           <t>1010010001&amp;1010010001</t>
         </is>
       </c>
-      <c r="F9" s="50" t="inlineStr">
+      <c r="F9" s="0" t="inlineStr">
         <is>
           <t>1010010001&amp;1010010001</t>
         </is>
       </c>
-      <c r="G9" s="50" t="n">
+      <c r="G9" s="0" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H9" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="H9" s="50" t="n">
+      <c r="I9" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="I9" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" s="50" t="n">
+      <c r="J9" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="K9" s="50" t="n">
-        <v>8</v>
-      </c>
-      <c r="L9" s="50" t="n">
-        <v>11</v>
-      </c>
-      <c r="M9" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" s="50" t="n">
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="0" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="N9" s="0" t="inlineStr">
+        <is>
+          <t>1-6</t>
+        </is>
+      </c>
+      <c r="O9" s="0" t="inlineStr">
+        <is>
+          <t>5-10</t>
+        </is>
+      </c>
+      <c r="P9" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="O9" s="50" t="n">
-        <v>5</v>
-      </c>
-      <c r="P9" s="50" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q9" s="50" t="n">
+      <c r="Q9" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="R9" s="50" t="n">
-        <v>6</v>
-      </c>
-      <c r="S9" s="50" t="n">
+      <c r="R9" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="T9" s="50" t="n">
+      <c r="S9" s="0" t="n">
         <v>600</v>
       </c>
-      <c r="U9" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="V9" s="50" t="n">
+      <c r="T9" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" s="0" t="n">
         <v>30</v>
       </c>
-      <c r="W9" t="n">
+      <c r="V9" s="0" t="n">
         <v>60</v>
       </c>
-      <c r="X9" t="n">
+      <c r="W9" s="0" t="n">
         <v>300</v>
       </c>
-      <c r="Y9" s="50" t="inlineStr">
+      <c r="X9" s="0" t="inlineStr">
         <is>
           <t>剑与魔法-难度6</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="50" t="n">
+      <c r="A10" s="0" t="n">
         <v>1000007</v>
       </c>
-      <c r="B10" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" s="50" t="inlineStr">
+      <c r="B10" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
         <is>
           <t>1&amp;1</t>
         </is>
       </c>
-      <c r="D10" s="50" t="inlineStr">
+      <c r="D10" s="0" t="inlineStr">
         <is>
           <t>1&amp;1</t>
         </is>
       </c>
-      <c r="E10" s="50" t="inlineStr">
+      <c r="E10" s="0" t="inlineStr">
         <is>
           <t>1010010001&amp;1010010001</t>
         </is>
       </c>
-      <c r="F10" s="50" t="inlineStr">
+      <c r="F10" s="0" t="inlineStr">
         <is>
           <t>1010010001&amp;1010010001</t>
         </is>
       </c>
-      <c r="G10" s="50" t="n">
+      <c r="G10" s="0" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="H10" s="50" t="n">
+      <c r="I10" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="I10" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="50" t="n">
+      <c r="J10" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="K10" s="50" t="n">
-        <v>9</v>
-      </c>
-      <c r="L10" s="50" t="n">
-        <v>12</v>
-      </c>
-      <c r="M10" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" s="50" t="n">
-        <v>6</v>
-      </c>
-      <c r="O10" s="50" t="n">
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="0" t="inlineStr">
+        <is>
+          <t>9-12</t>
+        </is>
+      </c>
+      <c r="N10" s="0" t="inlineStr">
+        <is>
+          <t>1-6</t>
+        </is>
+      </c>
+      <c r="O10" s="0" t="inlineStr">
+        <is>
+          <t>4-10</t>
+        </is>
+      </c>
+      <c r="P10" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q10" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="R10" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="P10" s="50" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q10" s="50" t="n">
-        <v>7</v>
-      </c>
-      <c r="R10" s="50" t="n">
-        <v>7</v>
-      </c>
-      <c r="S10" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="T10" s="50" t="n">
+      <c r="S10" s="0" t="n">
         <v>700</v>
       </c>
-      <c r="U10" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="V10" s="50" t="n">
+      <c r="T10" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" s="0" t="n">
         <v>35</v>
       </c>
-      <c r="W10" t="n">
+      <c r="V10" s="0" t="n">
         <v>70</v>
       </c>
-      <c r="X10" t="n">
+      <c r="W10" s="0" t="n">
         <v>350</v>
       </c>
-      <c r="Y10" s="50" t="inlineStr">
+      <c r="X10" s="0" t="inlineStr">
         <is>
           <t>剑与魔法-难度7</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="50" t="n">
+      <c r="A11" s="0" t="n">
         <v>1000008</v>
       </c>
-      <c r="B11" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="50" t="inlineStr">
+      <c r="B11" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
         <is>
           <t>1&amp;1</t>
         </is>
       </c>
-      <c r="D11" s="50" t="inlineStr">
+      <c r="D11" s="0" t="inlineStr">
         <is>
           <t>1&amp;1</t>
         </is>
       </c>
-      <c r="E11" s="50" t="inlineStr">
+      <c r="E11" s="0" t="inlineStr">
         <is>
           <t>1010010001&amp;1010010001</t>
         </is>
       </c>
-      <c r="F11" s="50" t="inlineStr">
+      <c r="F11" s="0" t="inlineStr">
         <is>
           <t>1010010001&amp;1010010001</t>
         </is>
       </c>
-      <c r="G11" s="50" t="n">
+      <c r="G11" s="0" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H11" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="H11" s="50" t="n">
+      <c r="I11" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="I11" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" s="50" t="n">
+      <c r="J11" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="K11" s="50" t="n">
-        <v>9</v>
-      </c>
-      <c r="L11" s="50" t="n">
-        <v>13</v>
-      </c>
-      <c r="M11" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" s="50" t="n">
-        <v>6</v>
-      </c>
-      <c r="O11" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="P11" s="50" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q11" s="50" t="n">
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="0" t="inlineStr">
+        <is>
+          <t>9-13</t>
+        </is>
+      </c>
+      <c r="N11" s="0" t="inlineStr">
+        <is>
+          <t>1-6</t>
+        </is>
+      </c>
+      <c r="O11" s="0" t="inlineStr">
+        <is>
+          <t>3-10</t>
+        </is>
+      </c>
+      <c r="P11" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="R11" s="50" t="n">
+      <c r="Q11" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="S11" s="50" t="n">
+      <c r="R11" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="T11" s="50" t="n">
+      <c r="S11" s="0" t="n">
         <v>800</v>
       </c>
-      <c r="U11" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="V11" s="50" t="n">
+      <c r="T11" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" s="0" t="n">
         <v>40</v>
       </c>
-      <c r="W11" t="n">
+      <c r="V11" s="0" t="n">
         <v>80</v>
       </c>
-      <c r="X11" t="n">
+      <c r="W11" s="0" t="n">
         <v>400</v>
       </c>
-      <c r="Y11" s="50" t="inlineStr">
+      <c r="X11" s="0" t="inlineStr">
         <is>
           <t>剑与魔法-难度8</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="50" t="n">
+      <c r="A12" s="0" t="n">
         <v>1000009</v>
       </c>
-      <c r="B12" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="50" t="inlineStr">
+      <c r="B12" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
         <is>
           <t>1&amp;1</t>
         </is>
       </c>
-      <c r="D12" s="50" t="inlineStr">
+      <c r="D12" s="0" t="inlineStr">
         <is>
           <t>1&amp;1</t>
         </is>
       </c>
-      <c r="E12" s="50" t="inlineStr">
+      <c r="E12" s="0" t="inlineStr">
         <is>
           <t>1010010001&amp;1010010001</t>
         </is>
       </c>
-      <c r="F12" s="50" t="inlineStr">
+      <c r="F12" s="0" t="inlineStr">
         <is>
           <t>1010010001&amp;1010010001</t>
         </is>
       </c>
-      <c r="G12" s="50" t="n">
+      <c r="G12" s="0" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H12" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="H12" s="50" t="n">
+      <c r="I12" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="I12" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" s="50" t="n">
+      <c r="J12" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="K12" s="50" t="n">
-        <v>10</v>
-      </c>
-      <c r="L12" s="50" t="n">
-        <v>14</v>
-      </c>
-      <c r="M12" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" s="50" t="n">
-        <v>6</v>
-      </c>
-      <c r="O12" s="50" t="n">
-        <v>2</v>
-      </c>
-      <c r="P12" s="50" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q12" s="50" t="n">
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="0" t="inlineStr">
+        <is>
+          <t>10-14</t>
+        </is>
+      </c>
+      <c r="N12" s="0" t="inlineStr">
+        <is>
+          <t>1-6</t>
+        </is>
+      </c>
+      <c r="O12" s="0" t="inlineStr">
+        <is>
+          <t>2-10</t>
+        </is>
+      </c>
+      <c r="P12" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="R12" s="50" t="n">
+      <c r="Q12" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="S12" s="50" t="n">
+      <c r="R12" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="T12" s="50" t="n">
+      <c r="S12" s="0" t="n">
         <v>900</v>
       </c>
-      <c r="U12" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="V12" s="50" t="n">
+      <c r="T12" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" s="0" t="n">
         <v>45</v>
       </c>
-      <c r="W12" t="n">
+      <c r="V12" s="0" t="n">
         <v>90</v>
       </c>
-      <c r="X12" t="n">
+      <c r="W12" s="0" t="n">
         <v>450</v>
       </c>
-      <c r="Y12" s="50" t="inlineStr">
+      <c r="X12" s="0" t="inlineStr">
         <is>
           <t>剑与魔法-难度9</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="50" t="n">
+      <c r="A13" s="0" t="n">
         <v>1000010</v>
       </c>
-      <c r="B13" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="50" t="inlineStr">
+      <c r="B13" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
         <is>
           <t>1&amp;1</t>
         </is>
       </c>
-      <c r="D13" s="50" t="inlineStr">
+      <c r="D13" s="0" t="inlineStr">
         <is>
           <t>1&amp;1</t>
         </is>
       </c>
-      <c r="E13" s="50" t="inlineStr">
+      <c r="E13" s="0" t="inlineStr">
         <is>
           <t>1010010001&amp;1010010001</t>
         </is>
       </c>
-      <c r="F13" s="50" t="inlineStr">
+      <c r="F13" s="0" t="inlineStr">
         <is>
           <t>1010010001&amp;1010010001</t>
         </is>
       </c>
-      <c r="G13" s="50" t="n">
+      <c r="G13" s="0" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="H13" s="50" t="n">
+      <c r="I13" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="I13" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" s="50" t="n">
+      <c r="J13" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="K13" s="50" t="n">
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" s="0" t="inlineStr">
+        <is>
+          <t>10-15</t>
+        </is>
+      </c>
+      <c r="N13" s="0" t="inlineStr">
+        <is>
+          <t>1-6</t>
+        </is>
+      </c>
+      <c r="O13" s="0" t="inlineStr">
+        <is>
+          <t>1-10</t>
+        </is>
+      </c>
+      <c r="P13" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="L13" s="50" t="n">
-        <v>15</v>
-      </c>
-      <c r="M13" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" s="50" t="n">
-        <v>6</v>
-      </c>
-      <c r="O13" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="P13" s="50" t="n">
+      <c r="Q13" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="Q13" s="50" t="n">
-        <v>10</v>
-      </c>
-      <c r="R13" s="50" t="n">
-        <v>10</v>
-      </c>
-      <c r="S13" s="50" t="n">
+      <c r="R13" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="T13" s="50" t="n">
+      <c r="S13" s="0" t="n">
         <v>1000</v>
       </c>
-      <c r="U13" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="V13" s="50" t="n">
+      <c r="T13" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="W13" t="n">
+      <c r="V13" s="0" t="n">
         <v>100</v>
       </c>
-      <c r="X13" t="n">
+      <c r="W13" s="0" t="n">
         <v>500</v>
       </c>
-      <c r="Y13" s="50" t="inlineStr">
+      <c r="X13" s="0" t="inlineStr">
         <is>
           <t>剑与魔法-难度10</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" s="51"/>
-    <row r="32" ht="15" customHeight="1" s="51"/>
-    <row r="33" ht="15" customHeight="1" s="51"/>
-    <row r="34" ht="15" customHeight="1" s="51"/>
-    <row r="35" ht="15" customHeight="1" s="51"/>
-    <row r="36" ht="15" customHeight="1" s="51"/>
-    <row r="37" ht="15" customHeight="1" s="51"/>
-    <row r="38" ht="15" customHeight="1" s="51"/>
-    <row r="39" ht="15" customHeight="1" s="51"/>
-    <row r="40" ht="15" customHeight="1" s="51"/>
-    <row r="41" ht="15" customHeight="1" s="51"/>
-    <row r="73" ht="12" customHeight="1" s="51"/>
-    <row r="74" ht="12" customHeight="1" s="51"/>
-    <row r="75" ht="12" customHeight="1" s="51"/>
-    <row r="76" ht="12" customHeight="1" s="51"/>
-    <row r="77" ht="12" customHeight="1" s="51"/>
-    <row r="78" ht="12" customHeight="1" s="51"/>
-    <row r="79" ht="12" customHeight="1" s="51"/>
-    <row r="80" ht="12" customHeight="1" s="51"/>
-    <row r="81" ht="12" customHeight="1" s="51"/>
+    <row r="31" ht="15" customHeight="1" s="1"/>
+    <row r="32" ht="15" customHeight="1" s="1"/>
+    <row r="33" ht="15" customHeight="1" s="1"/>
+    <row r="34" ht="15" customHeight="1" s="1"/>
+    <row r="35" ht="15" customHeight="1" s="1"/>
+    <row r="36" ht="15" customHeight="1" s="1"/>
+    <row r="37" ht="15" customHeight="1" s="1"/>
+    <row r="38" ht="15" customHeight="1" s="1"/>
+    <row r="39" ht="15" customHeight="1" s="1"/>
+    <row r="40" ht="15" customHeight="1" s="1"/>
+    <row r="41" ht="15" customHeight="1" s="1"/>
+    <row r="73" ht="12" customHeight="1" s="1"/>
+    <row r="74" ht="12" customHeight="1" s="1"/>
+    <row r="75" ht="12" customHeight="1" s="1"/>
+    <row r="76" ht="12" customHeight="1" s="1"/>
+    <row r="77" ht="12" customHeight="1" s="1"/>
+    <row r="78" ht="12" customHeight="1" s="1"/>
+    <row r="79" ht="12" customHeight="1" s="1"/>
+    <row r="80" ht="12" customHeight="1" s="1"/>
+    <row r="81" ht="12" customHeight="1" s="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
@@ -183,19 +183,19 @@
     <t>1010020001</t>
   </si>
   <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>5-6</t>
+  </si>
+  <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>5-6</t>
   </si>
   <si>
     <t>剑与魔法-难度1</t>
@@ -882,7 +882,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1028,6 +1028,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="32" applyFill="1" borderId="0" applyBorder="1" xfId="48" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
@@ -1451,1004 +1454,1004 @@
   <dimension ref="A1:X13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="3" max="3" width="17.125" customWidth="1" style="50"/>
-    <col min="4" max="4" width="36.5" customWidth="1" style="50"/>
-    <col min="5" max="5" width="23.75" customWidth="1" style="50"/>
-    <col min="6" max="6" width="18.375" customWidth="1" style="50"/>
-    <col min="7" max="7" width="31.875" customWidth="1" style="50"/>
-    <col min="8" max="8" width="18.25" customWidth="1" style="50"/>
-    <col min="9" max="16" width="16" customWidth="1" style="50"/>
-    <col min="17" max="17" width="12.25" customWidth="1" style="50"/>
-    <col min="18" max="19" width="12.875" customWidth="1" style="50"/>
-    <col min="20" max="20" width="17.375" customWidth="1" style="50"/>
-    <col min="21" max="21" width="19.75" customWidth="1" style="50"/>
-    <col min="22" max="22" width="29.375" customWidth="1" style="50"/>
-    <col min="23" max="23" width="42.875" customWidth="1" style="50"/>
-    <col min="24" max="24" width="25.125" customWidth="1" style="50"/>
+    <col min="3" max="3" width="17.125" customWidth="1" style="51"/>
+    <col min="4" max="4" width="36.5" customWidth="1" style="51"/>
+    <col min="5" max="5" width="23.75" customWidth="1" style="51"/>
+    <col min="6" max="6" width="18.375" customWidth="1" style="51"/>
+    <col min="7" max="7" width="31.875" customWidth="1" style="51"/>
+    <col min="8" max="8" width="18.25" customWidth="1" style="51"/>
+    <col min="9" max="16" width="16" customWidth="1" style="51"/>
+    <col min="17" max="17" width="12.25" customWidth="1" style="51"/>
+    <col min="18" max="19" width="12.875" customWidth="1" style="51"/>
+    <col min="20" max="20" width="17.375" customWidth="1" style="51"/>
+    <col min="21" max="21" width="19.75" customWidth="1" style="51"/>
+    <col min="22" max="22" width="29.375" customWidth="1" style="51"/>
+    <col min="23" max="23" width="42.875" customWidth="1" style="51"/>
+    <col min="24" max="24" width="25.125" customWidth="1" style="51"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="50" t="s">
+      <c r="B1" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="50" t="s">
+      <c r="D1" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="50" t="s">
+      <c r="E1" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="50" t="s">
+      <c r="F1" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="50" t="s">
+      <c r="G1" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="50" t="s">
+      <c r="H1" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="50" t="s">
+      <c r="I1" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="50" t="s">
+      <c r="J1" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="50" t="s">
+      <c r="K1" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="50" t="s">
+      <c r="L1" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="50" t="s">
+      <c r="M1" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="50" t="s">
+      <c r="N1" s="51" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="50" t="s">
+      <c r="O1" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="50" t="s">
+      <c r="P1" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="50" t="s">
+      <c r="Q1" s="51" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="50" t="s">
+      <c r="R1" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="50" t="s">
+      <c r="S1" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="50" t="s">
+      <c r="T1" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="50" t="s">
+      <c r="U1" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="50" t="s">
+      <c r="V1" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="50" t="s">
+      <c r="W1" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="50" t="s">
+      <c r="X1" s="51" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="50" t="s">
+      <c r="C2" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="50" t="s">
+      <c r="D2" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="50" t="s">
+      <c r="E2" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="50" t="s">
+      <c r="F2" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="50" t="s">
+      <c r="G2" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="H2" s="50" t="s">
+      <c r="H2" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="50" t="s">
+      <c r="I2" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="J2" s="50" t="s">
+      <c r="J2" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="K2" s="50" t="s">
+      <c r="K2" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="50" t="s">
+      <c r="L2" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="M2" s="50" t="s">
+      <c r="M2" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="N2" s="50" t="s">
+      <c r="N2" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="O2" s="50" t="s">
+      <c r="O2" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="P2" s="50" t="s">
+      <c r="P2" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="Q2" s="50" t="s">
+      <c r="Q2" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="R2" s="50" t="s">
+      <c r="R2" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="S2" s="50" t="s">
+      <c r="S2" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="T2" s="50" t="s">
+      <c r="T2" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="U2" s="50" t="s">
+      <c r="U2" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="V2" s="50" t="s">
+      <c r="V2" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="W2" s="50" t="s">
+      <c r="W2" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="X2" s="50" t="s">
+      <c r="X2" s="51" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="49" t="s">
+      <c r="B3" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="50" t="s">
+      <c r="C3" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="50" t="s">
+      <c r="D3" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="50" t="s">
+      <c r="E3" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="50" t="s">
+      <c r="F3" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="G3" s="50" t="s">
+      <c r="G3" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="H3" s="50" t="s">
+      <c r="H3" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="I3" s="50" t="s">
+      <c r="I3" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J3" s="50" t="s">
+      <c r="J3" s="51" t="s">
         <v>37</v>
       </c>
-      <c r="K3" s="50" t="s">
+      <c r="K3" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="L3" s="50" t="s">
+      <c r="L3" s="51" t="s">
         <v>39</v>
       </c>
-      <c r="M3" s="50" t="s">
+      <c r="M3" s="51" t="s">
         <v>40</v>
       </c>
-      <c r="N3" s="50" t="s">
+      <c r="N3" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="O3" s="50" t="s">
+      <c r="O3" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="P3" s="50" t="s">
+      <c r="P3" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="Q3" s="50" t="s">
+      <c r="Q3" s="51" t="s">
         <v>44</v>
       </c>
-      <c r="R3" s="50" t="s">
+      <c r="R3" s="51" t="s">
         <v>45</v>
       </c>
-      <c r="S3" s="50" t="s">
+      <c r="S3" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="T3" s="50" t="s">
+      <c r="T3" s="51" t="s">
         <v>47</v>
       </c>
-      <c r="U3" s="50" t="s">
+      <c r="U3" s="51" t="s">
         <v>48</v>
       </c>
-      <c r="V3" s="50" t="s">
+      <c r="V3" s="51" t="s">
         <v>49</v>
       </c>
-      <c r="W3" s="50" t="s">
+      <c r="W3" s="51" t="s">
         <v>50</v>
       </c>
-      <c r="X3" s="50" t="s">
+      <c r="X3" s="51" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="49">
+      <c r="A4" s="50">
         <v>1000001</v>
       </c>
-      <c r="B4" s="49">
-        <v>1</v>
-      </c>
-      <c r="C4" s="50" t="s">
+      <c r="B4" s="50">
+        <v>1</v>
+      </c>
+      <c r="C4" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="D4" s="50" t="s">
+      <c r="D4" s="51" t="s">
         <v>53</v>
       </c>
-      <c r="E4" s="50" t="s">
+      <c r="E4" s="51" t="s">
         <v>54</v>
       </c>
-      <c r="F4" s="50" t="s">
+      <c r="F4" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="G4" s="50" t="s">
+      <c r="G4" s="51" t="s">
+        <v>53</v>
+      </c>
+      <c r="H4" s="51" t="s">
         <v>56</v>
       </c>
-      <c r="H4" s="50" t="s">
+      <c r="I4" s="51" t="s">
         <v>57</v>
       </c>
-      <c r="I4" s="50" t="s">
+      <c r="J4" s="51">
+        <v>1</v>
+      </c>
+      <c r="K4" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="J4" s="50">
-        <v>1</v>
-      </c>
-      <c r="K4" s="50" t="s">
+      <c r="L4" s="51">
+        <v>1</v>
+      </c>
+      <c r="M4" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="L4" s="50">
-        <v>1</v>
-      </c>
-      <c r="M4" s="50" t="s">
+      <c r="N4" s="51" t="s">
         <v>60</v>
       </c>
-      <c r="N4" s="50" t="s">
+      <c r="O4" s="51" t="s">
         <v>56</v>
       </c>
-      <c r="O4" s="50" t="s">
-        <v>57</v>
-      </c>
-      <c r="P4" s="50">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="50">
-        <v>1</v>
-      </c>
-      <c r="R4" s="50">
-        <v>1</v>
-      </c>
-      <c r="S4" s="50">
+      <c r="P4" s="51">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="51">
+        <v>1</v>
+      </c>
+      <c r="R4" s="51">
+        <v>1</v>
+      </c>
+      <c r="S4" s="51">
         <v>100</v>
       </c>
-      <c r="T4" s="50">
-        <v>1</v>
-      </c>
-      <c r="U4" s="50">
+      <c r="T4" s="51">
+        <v>1</v>
+      </c>
+      <c r="U4" s="51">
         <v>5</v>
       </c>
-      <c r="V4" s="50">
+      <c r="V4" s="51">
         <v>10</v>
       </c>
-      <c r="W4" s="50">
+      <c r="W4" s="51">
         <v>50</v>
       </c>
-      <c r="X4" s="50" t="s">
+      <c r="X4" s="51" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="49">
+      <c r="A5" s="50">
         <v>1000002</v>
       </c>
-      <c r="B5" s="49">
-        <v>1</v>
-      </c>
-      <c r="C5" s="50" t="s">
+      <c r="B5" s="50">
+        <v>1</v>
+      </c>
+      <c r="C5" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="D5" s="50" t="s">
+      <c r="D5" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="E5" s="50" t="s">
+      <c r="E5" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="F5" s="50" t="s">
+      <c r="F5" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="G5" s="50" t="s">
-        <v>56</v>
-      </c>
-      <c r="H5" s="50">
+      <c r="G5" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="H5" s="51">
         <v>3</v>
       </c>
-      <c r="I5" s="50">
+      <c r="I5" s="51">
         <v>5</v>
       </c>
-      <c r="J5" s="50">
-        <v>1</v>
-      </c>
-      <c r="K5" s="50">
+      <c r="J5" s="51">
+        <v>1</v>
+      </c>
+      <c r="K5" s="51">
         <v>2</v>
       </c>
-      <c r="L5" s="50">
-        <v>1</v>
-      </c>
-      <c r="M5" s="50" t="s">
+      <c r="L5" s="51">
+        <v>1</v>
+      </c>
+      <c r="M5" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="N5" s="50" t="s">
+      <c r="N5" s="51" t="s">
         <v>65</v>
       </c>
-      <c r="O5" s="50" t="s">
+      <c r="O5" s="51" t="s">
         <v>66</v>
       </c>
-      <c r="P5" s="50">
+      <c r="P5" s="51">
         <v>2</v>
       </c>
-      <c r="Q5" s="50">
+      <c r="Q5" s="51">
         <v>2</v>
       </c>
-      <c r="R5" s="50">
-        <v>1</v>
-      </c>
-      <c r="S5" s="50">
+      <c r="R5" s="51">
+        <v>1</v>
+      </c>
+      <c r="S5" s="51">
         <v>200</v>
       </c>
-      <c r="T5" s="50">
-        <v>1</v>
-      </c>
-      <c r="U5" s="50">
+      <c r="T5" s="51">
+        <v>1</v>
+      </c>
+      <c r="U5" s="51">
         <v>10</v>
       </c>
-      <c r="V5" s="50">
+      <c r="V5" s="51">
         <v>20</v>
       </c>
-      <c r="W5" s="50">
+      <c r="W5" s="51">
         <v>100</v>
       </c>
-      <c r="X5" s="50" t="s">
+      <c r="X5" s="51" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="49">
+      <c r="A6" s="50">
         <v>1000003</v>
       </c>
-      <c r="B6" s="49">
-        <v>1</v>
-      </c>
-      <c r="C6" s="50" t="s">
+      <c r="B6" s="50">
+        <v>1</v>
+      </c>
+      <c r="C6" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="D6" s="50" t="s">
+      <c r="D6" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="E6" s="50" t="s">
+      <c r="E6" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="F6" s="50" t="s">
+      <c r="F6" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="G6" s="50" t="s">
-        <v>56</v>
-      </c>
-      <c r="H6" s="50">
+      <c r="G6" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="H6" s="51">
         <v>3</v>
       </c>
-      <c r="I6" s="50">
+      <c r="I6" s="51">
         <v>5</v>
       </c>
-      <c r="J6" s="50">
-        <v>1</v>
-      </c>
-      <c r="K6" s="50">
+      <c r="J6" s="51">
+        <v>1</v>
+      </c>
+      <c r="K6" s="51">
         <v>2</v>
       </c>
-      <c r="L6" s="50">
-        <v>1</v>
-      </c>
-      <c r="M6" s="50" t="s">
+      <c r="L6" s="51">
+        <v>1</v>
+      </c>
+      <c r="M6" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="N6" s="50" t="s">
+      <c r="N6" s="51" t="s">
         <v>69</v>
       </c>
-      <c r="O6" s="50" t="s">
+      <c r="O6" s="51" t="s">
         <v>70</v>
       </c>
-      <c r="P6" s="50">
+      <c r="P6" s="51">
         <v>3</v>
       </c>
-      <c r="Q6" s="50">
+      <c r="Q6" s="51">
         <v>3</v>
       </c>
-      <c r="R6" s="50">
+      <c r="R6" s="51">
         <v>2</v>
       </c>
-      <c r="S6" s="50">
+      <c r="S6" s="51">
         <v>300</v>
       </c>
-      <c r="T6" s="50">
-        <v>1</v>
-      </c>
-      <c r="U6" s="50">
+      <c r="T6" s="51">
+        <v>1</v>
+      </c>
+      <c r="U6" s="51">
         <v>15</v>
       </c>
-      <c r="V6" s="50">
+      <c r="V6" s="51">
         <v>30</v>
       </c>
-      <c r="W6" s="50">
+      <c r="W6" s="51">
         <v>150</v>
       </c>
-      <c r="X6" s="50" t="s">
+      <c r="X6" s="51" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="49">
+      <c r="A7" s="50">
         <v>1000004</v>
       </c>
-      <c r="B7" s="49">
-        <v>1</v>
-      </c>
-      <c r="C7" s="50" t="s">
+      <c r="B7" s="50">
+        <v>1</v>
+      </c>
+      <c r="C7" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="D7" s="50" t="s">
+      <c r="D7" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="E7" s="50" t="s">
+      <c r="E7" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="F7" s="50" t="s">
+      <c r="F7" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="G7" s="50" t="s">
-        <v>56</v>
-      </c>
-      <c r="H7" s="50">
+      <c r="G7" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="H7" s="51">
         <v>3</v>
       </c>
-      <c r="I7" s="50">
+      <c r="I7" s="51">
         <v>5</v>
       </c>
-      <c r="J7" s="50">
-        <v>1</v>
-      </c>
-      <c r="K7" s="50">
+      <c r="J7" s="51">
+        <v>1</v>
+      </c>
+      <c r="K7" s="51">
         <v>2</v>
       </c>
-      <c r="L7" s="50">
-        <v>1</v>
-      </c>
-      <c r="M7" s="50" t="s">
+      <c r="L7" s="51">
+        <v>1</v>
+      </c>
+      <c r="M7" s="51" t="s">
         <v>72</v>
       </c>
-      <c r="N7" s="50" t="s">
+      <c r="N7" s="51" t="s">
         <v>73</v>
       </c>
-      <c r="O7" s="50" t="s">
+      <c r="O7" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="P7" s="50">
+      <c r="P7" s="51">
         <v>4</v>
       </c>
-      <c r="Q7" s="50">
+      <c r="Q7" s="51">
         <v>4</v>
       </c>
-      <c r="R7" s="50">
+      <c r="R7" s="51">
         <v>2</v>
       </c>
-      <c r="S7" s="50">
+      <c r="S7" s="51">
         <v>400</v>
       </c>
-      <c r="T7" s="50">
-        <v>1</v>
-      </c>
-      <c r="U7" s="50">
+      <c r="T7" s="51">
+        <v>1</v>
+      </c>
+      <c r="U7" s="51">
         <v>20</v>
       </c>
-      <c r="V7" s="50">
+      <c r="V7" s="51">
         <v>40</v>
       </c>
-      <c r="W7" s="50">
+      <c r="W7" s="51">
         <v>200</v>
       </c>
-      <c r="X7" s="50" t="s">
+      <c r="X7" s="51" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="49">
+      <c r="A8" s="50">
         <v>1000005</v>
       </c>
-      <c r="B8" s="49">
-        <v>1</v>
-      </c>
-      <c r="C8" s="50" t="s">
+      <c r="B8" s="50">
+        <v>1</v>
+      </c>
+      <c r="C8" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="D8" s="50" t="s">
+      <c r="D8" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="E8" s="50" t="s">
+      <c r="E8" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="F8" s="50" t="s">
+      <c r="F8" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="G8" s="50" t="s">
-        <v>56</v>
-      </c>
-      <c r="H8" s="50">
+      <c r="G8" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="H8" s="51">
         <v>3</v>
       </c>
-      <c r="I8" s="50">
+      <c r="I8" s="51">
         <v>5</v>
       </c>
-      <c r="J8" s="50">
-        <v>1</v>
-      </c>
-      <c r="K8" s="50">
+      <c r="J8" s="51">
+        <v>1</v>
+      </c>
+      <c r="K8" s="51">
         <v>2</v>
       </c>
-      <c r="L8" s="50">
-        <v>1</v>
-      </c>
-      <c r="M8" s="50" t="s">
+      <c r="L8" s="51">
+        <v>1</v>
+      </c>
+      <c r="M8" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="N8" s="50" t="s">
+      <c r="N8" s="51" t="s">
         <v>76</v>
       </c>
-      <c r="O8" s="50" t="s">
+      <c r="O8" s="51" t="s">
         <v>77</v>
       </c>
-      <c r="P8" s="50">
+      <c r="P8" s="51">
         <v>5</v>
       </c>
-      <c r="Q8" s="50">
+      <c r="Q8" s="51">
         <v>5</v>
       </c>
-      <c r="R8" s="50">
+      <c r="R8" s="51">
         <v>3</v>
       </c>
-      <c r="S8" s="50">
+      <c r="S8" s="51">
         <v>500</v>
       </c>
-      <c r="T8" s="50">
-        <v>1</v>
-      </c>
-      <c r="U8" s="50">
+      <c r="T8" s="51">
+        <v>1</v>
+      </c>
+      <c r="U8" s="51">
         <v>25</v>
       </c>
-      <c r="V8" s="50">
+      <c r="V8" s="51">
         <v>50</v>
       </c>
-      <c r="W8" s="50">
+      <c r="W8" s="51">
         <v>250</v>
       </c>
-      <c r="X8" s="50" t="s">
+      <c r="X8" s="51" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="49">
+      <c r="A9" s="50">
         <v>1000006</v>
       </c>
-      <c r="B9" s="49">
-        <v>1</v>
-      </c>
-      <c r="C9" s="50" t="s">
+      <c r="B9" s="50">
+        <v>1</v>
+      </c>
+      <c r="C9" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="D9" s="50" t="s">
+      <c r="D9" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="E9" s="50" t="s">
+      <c r="E9" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="F9" s="50" t="s">
+      <c r="F9" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="G9" s="50" t="s">
-        <v>56</v>
-      </c>
-      <c r="H9" s="50">
+      <c r="G9" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="H9" s="51">
         <v>3</v>
       </c>
-      <c r="I9" s="50">
+      <c r="I9" s="51">
         <v>5</v>
       </c>
-      <c r="J9" s="50">
-        <v>1</v>
-      </c>
-      <c r="K9" s="50">
+      <c r="J9" s="51">
+        <v>1</v>
+      </c>
+      <c r="K9" s="51">
         <v>2</v>
       </c>
-      <c r="L9" s="50">
-        <v>1</v>
-      </c>
-      <c r="M9" s="50" t="s">
+      <c r="L9" s="51">
+        <v>1</v>
+      </c>
+      <c r="M9" s="51" t="s">
         <v>79</v>
       </c>
-      <c r="N9" s="50" t="s">
+      <c r="N9" s="51" t="s">
         <v>80</v>
       </c>
-      <c r="O9" s="50" t="s">
+      <c r="O9" s="51" t="s">
         <v>81</v>
       </c>
-      <c r="P9" s="50">
+      <c r="P9" s="51">
         <v>6</v>
       </c>
-      <c r="Q9" s="50">
+      <c r="Q9" s="51">
         <v>6</v>
       </c>
-      <c r="R9" s="50">
+      <c r="R9" s="51">
         <v>3</v>
       </c>
-      <c r="S9" s="50">
+      <c r="S9" s="51">
         <v>600</v>
       </c>
-      <c r="T9" s="50">
-        <v>1</v>
-      </c>
-      <c r="U9" s="50">
+      <c r="T9" s="51">
+        <v>1</v>
+      </c>
+      <c r="U9" s="51">
         <v>30</v>
       </c>
-      <c r="V9" s="50">
+      <c r="V9" s="51">
         <v>60</v>
       </c>
-      <c r="W9" s="50">
+      <c r="W9" s="51">
         <v>300</v>
       </c>
-      <c r="X9" s="50" t="s">
+      <c r="X9" s="51" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="49">
+      <c r="A10" s="50">
         <v>1000007</v>
       </c>
-      <c r="B10" s="49">
-        <v>1</v>
-      </c>
-      <c r="C10" s="50" t="s">
+      <c r="B10" s="50">
+        <v>1</v>
+      </c>
+      <c r="C10" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="D10" s="50" t="s">
+      <c r="D10" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="E10" s="50" t="s">
+      <c r="E10" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="F10" s="50" t="s">
+      <c r="F10" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="G10" s="50" t="s">
-        <v>56</v>
-      </c>
-      <c r="H10" s="50">
+      <c r="G10" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="H10" s="51">
         <v>3</v>
       </c>
-      <c r="I10" s="50">
+      <c r="I10" s="51">
         <v>5</v>
       </c>
-      <c r="J10" s="50">
-        <v>1</v>
-      </c>
-      <c r="K10" s="50">
+      <c r="J10" s="51">
+        <v>1</v>
+      </c>
+      <c r="K10" s="51">
         <v>2</v>
       </c>
-      <c r="L10" s="50">
-        <v>1</v>
-      </c>
-      <c r="M10" s="50" t="s">
+      <c r="L10" s="51">
+        <v>1</v>
+      </c>
+      <c r="M10" s="51" t="s">
         <v>83</v>
       </c>
-      <c r="N10" s="50" t="s">
+      <c r="N10" s="51" t="s">
         <v>80</v>
       </c>
-      <c r="O10" s="50" t="s">
+      <c r="O10" s="51" t="s">
         <v>84</v>
       </c>
-      <c r="P10" s="50">
+      <c r="P10" s="51">
         <v>7</v>
       </c>
-      <c r="Q10" s="50">
+      <c r="Q10" s="51">
         <v>7</v>
       </c>
-      <c r="R10" s="50">
+      <c r="R10" s="51">
         <v>4</v>
       </c>
-      <c r="S10" s="50">
+      <c r="S10" s="51">
         <v>700</v>
       </c>
-      <c r="T10" s="50">
-        <v>1</v>
-      </c>
-      <c r="U10" s="50">
+      <c r="T10" s="51">
+        <v>1</v>
+      </c>
+      <c r="U10" s="51">
         <v>35</v>
       </c>
-      <c r="V10" s="50">
+      <c r="V10" s="51">
         <v>70</v>
       </c>
-      <c r="W10" s="50">
+      <c r="W10" s="51">
         <v>350</v>
       </c>
-      <c r="X10" s="50" t="s">
+      <c r="X10" s="51" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="49">
+      <c r="A11" s="50">
         <v>1000008</v>
       </c>
-      <c r="B11" s="49">
-        <v>1</v>
-      </c>
-      <c r="C11" s="50" t="s">
+      <c r="B11" s="50">
+        <v>1</v>
+      </c>
+      <c r="C11" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="50" t="s">
+      <c r="D11" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="E11" s="50" t="s">
+      <c r="E11" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="F11" s="50" t="s">
+      <c r="F11" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="G11" s="50" t="s">
-        <v>56</v>
-      </c>
-      <c r="H11" s="50">
+      <c r="G11" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="H11" s="51">
         <v>3</v>
       </c>
-      <c r="I11" s="50">
+      <c r="I11" s="51">
         <v>5</v>
       </c>
-      <c r="J11" s="50">
-        <v>1</v>
-      </c>
-      <c r="K11" s="50">
+      <c r="J11" s="51">
+        <v>1</v>
+      </c>
+      <c r="K11" s="51">
         <v>2</v>
       </c>
-      <c r="L11" s="50">
-        <v>1</v>
-      </c>
-      <c r="M11" s="50" t="s">
+      <c r="L11" s="51">
+        <v>1</v>
+      </c>
+      <c r="M11" s="51" t="s">
         <v>86</v>
       </c>
-      <c r="N11" s="50" t="s">
+      <c r="N11" s="51" t="s">
         <v>80</v>
       </c>
-      <c r="O11" s="50" t="s">
+      <c r="O11" s="51" t="s">
         <v>87</v>
       </c>
-      <c r="P11" s="50">
+      <c r="P11" s="51">
         <v>8</v>
       </c>
-      <c r="Q11" s="50">
+      <c r="Q11" s="51">
         <v>8</v>
       </c>
-      <c r="R11" s="50">
+      <c r="R11" s="51">
         <v>4</v>
       </c>
-      <c r="S11" s="50">
+      <c r="S11" s="51">
         <v>800</v>
       </c>
-      <c r="T11" s="50">
-        <v>1</v>
-      </c>
-      <c r="U11" s="50">
+      <c r="T11" s="51">
+        <v>1</v>
+      </c>
+      <c r="U11" s="51">
         <v>40</v>
       </c>
-      <c r="V11" s="50">
+      <c r="V11" s="51">
         <v>80</v>
       </c>
-      <c r="W11" s="50">
+      <c r="W11" s="51">
         <v>400</v>
       </c>
-      <c r="X11" s="50" t="s">
+      <c r="X11" s="51" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="49">
+      <c r="A12" s="50">
         <v>1000009</v>
       </c>
-      <c r="B12" s="49">
-        <v>1</v>
-      </c>
-      <c r="C12" s="50" t="s">
+      <c r="B12" s="50">
+        <v>1</v>
+      </c>
+      <c r="C12" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="D12" s="50" t="s">
+      <c r="D12" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="E12" s="50" t="s">
+      <c r="E12" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="50" t="s">
+      <c r="F12" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="G12" s="50" t="s">
-        <v>56</v>
-      </c>
-      <c r="H12" s="50">
+      <c r="G12" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="H12" s="51">
         <v>3</v>
       </c>
-      <c r="I12" s="50">
+      <c r="I12" s="51">
         <v>5</v>
       </c>
-      <c r="J12" s="50">
-        <v>1</v>
-      </c>
-      <c r="K12" s="50">
+      <c r="J12" s="51">
+        <v>1</v>
+      </c>
+      <c r="K12" s="51">
         <v>2</v>
       </c>
-      <c r="L12" s="50">
-        <v>1</v>
-      </c>
-      <c r="M12" s="50" t="s">
+      <c r="L12" s="51">
+        <v>1</v>
+      </c>
+      <c r="M12" s="51" t="s">
         <v>89</v>
       </c>
-      <c r="N12" s="50" t="s">
+      <c r="N12" s="51" t="s">
         <v>80</v>
       </c>
-      <c r="O12" s="50" t="s">
+      <c r="O12" s="51" t="s">
         <v>90</v>
       </c>
-      <c r="P12" s="50">
+      <c r="P12" s="51">
         <v>9</v>
       </c>
-      <c r="Q12" s="50">
+      <c r="Q12" s="51">
         <v>9</v>
       </c>
-      <c r="R12" s="50">
+      <c r="R12" s="51">
         <v>5</v>
       </c>
-      <c r="S12" s="50">
+      <c r="S12" s="51">
         <v>900</v>
       </c>
-      <c r="T12" s="50">
-        <v>1</v>
-      </c>
-      <c r="U12" s="50">
+      <c r="T12" s="51">
+        <v>1</v>
+      </c>
+      <c r="U12" s="51">
         <v>45</v>
       </c>
-      <c r="V12" s="50">
+      <c r="V12" s="51">
         <v>90</v>
       </c>
-      <c r="W12" s="50">
+      <c r="W12" s="51">
         <v>450</v>
       </c>
-      <c r="X12" s="50" t="s">
+      <c r="X12" s="51" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="49">
+      <c r="A13" s="50">
         <v>1000010</v>
       </c>
-      <c r="B13" s="49">
-        <v>1</v>
-      </c>
-      <c r="C13" s="50" t="s">
+      <c r="B13" s="50">
+        <v>1</v>
+      </c>
+      <c r="C13" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="D13" s="50" t="s">
+      <c r="D13" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="E13" s="50" t="s">
+      <c r="E13" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="F13" s="50" t="s">
+      <c r="F13" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="G13" s="50" t="s">
-        <v>56</v>
-      </c>
-      <c r="H13" s="50">
+      <c r="G13" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="H13" s="51">
         <v>3</v>
       </c>
-      <c r="I13" s="50">
+      <c r="I13" s="51">
         <v>5</v>
       </c>
-      <c r="J13" s="50">
-        <v>1</v>
-      </c>
-      <c r="K13" s="50">
+      <c r="J13" s="51">
+        <v>1</v>
+      </c>
+      <c r="K13" s="51">
         <v>2</v>
       </c>
-      <c r="L13" s="50">
-        <v>1</v>
-      </c>
-      <c r="M13" s="50" t="s">
+      <c r="L13" s="51">
+        <v>1</v>
+      </c>
+      <c r="M13" s="51" t="s">
         <v>92</v>
       </c>
-      <c r="N13" s="50" t="s">
+      <c r="N13" s="51" t="s">
         <v>80</v>
       </c>
-      <c r="O13" s="50" t="s">
+      <c r="O13" s="51" t="s">
         <v>93</v>
       </c>
-      <c r="P13" s="50">
+      <c r="P13" s="51">
         <v>10</v>
       </c>
-      <c r="Q13" s="50">
+      <c r="Q13" s="51">
         <v>10</v>
       </c>
-      <c r="R13" s="50">
+      <c r="R13" s="51">
         <v>5</v>
       </c>
-      <c r="S13" s="50">
+      <c r="S13" s="51">
         <v>1000</v>
       </c>
-      <c r="T13" s="50">
-        <v>1</v>
-      </c>
-      <c r="U13" s="50">
+      <c r="T13" s="51">
+        <v>1</v>
+      </c>
+      <c r="U13" s="51">
         <v>50</v>
       </c>
-      <c r="V13" s="50">
+      <c r="V13" s="51">
         <v>100</v>
       </c>
-      <c r="W13" s="50">
+      <c r="W13" s="51">
         <v>500</v>
       </c>
-      <c r="X13" s="50" t="s">
+      <c r="X13" s="51" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" s="50" customFormat="1"/>
-    <row r="32" ht="15" customHeight="1" s="50" customFormat="1"/>
-    <row r="33" ht="15" customHeight="1" s="50" customFormat="1"/>
-    <row r="34" ht="15" customHeight="1" s="50" customFormat="1"/>
-    <row r="35" ht="15" customHeight="1" s="50" customFormat="1"/>
-    <row r="36" ht="15" customHeight="1" s="50" customFormat="1"/>
-    <row r="37" ht="15" customHeight="1" s="50" customFormat="1"/>
-    <row r="38" ht="15" customHeight="1" s="50" customFormat="1"/>
-    <row r="39" ht="15" customHeight="1" s="50" customFormat="1"/>
-    <row r="40" ht="15" customHeight="1" s="50" customFormat="1"/>
-    <row r="41" ht="15" customHeight="1" s="50" customFormat="1"/>
-    <row r="73" ht="12" customHeight="1" s="50" customFormat="1"/>
-    <row r="74" ht="12" customHeight="1" s="50" customFormat="1"/>
-    <row r="75" ht="12" customHeight="1" s="50" customFormat="1"/>
-    <row r="76" ht="12" customHeight="1" s="50" customFormat="1"/>
-    <row r="77" ht="12" customHeight="1" s="50" customFormat="1"/>
-    <row r="78" ht="12" customHeight="1" s="50" customFormat="1"/>
-    <row r="79" ht="12" customHeight="1" s="50" customFormat="1"/>
-    <row r="80" ht="12" customHeight="1" s="50" customFormat="1"/>
-    <row r="81" ht="12" customHeight="1" s="50" customFormat="1"/>
+    <row r="31" ht="15" customHeight="1" s="51" customFormat="1"/>
+    <row r="32" ht="15" customHeight="1" s="51" customFormat="1"/>
+    <row r="33" ht="15" customHeight="1" s="51" customFormat="1"/>
+    <row r="34" ht="15" customHeight="1" s="51" customFormat="1"/>
+    <row r="35" ht="15" customHeight="1" s="51" customFormat="1"/>
+    <row r="36" ht="15" customHeight="1" s="51" customFormat="1"/>
+    <row r="37" ht="15" customHeight="1" s="51" customFormat="1"/>
+    <row r="38" ht="15" customHeight="1" s="51" customFormat="1"/>
+    <row r="39" ht="15" customHeight="1" s="51" customFormat="1"/>
+    <row r="40" ht="15" customHeight="1" s="51" customFormat="1"/>
+    <row r="41" ht="15" customHeight="1" s="51" customFormat="1"/>
+    <row r="73" ht="12" customHeight="1" s="51" customFormat="1"/>
+    <row r="74" ht="12" customHeight="1" s="51" customFormat="1"/>
+    <row r="75" ht="12" customHeight="1" s="51" customFormat="1"/>
+    <row r="76" ht="12" customHeight="1" s="51" customFormat="1"/>
+    <row r="77" ht="12" customHeight="1" s="51" customFormat="1"/>
+    <row r="78" ht="12" customHeight="1" s="51" customFormat="1"/>
+    <row r="79" ht="12" customHeight="1" s="51" customFormat="1"/>
+    <row r="80" ht="12" customHeight="1" s="51" customFormat="1"/>
+    <row r="81" ht="12" customHeight="1" s="51" customFormat="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
@@ -1,19 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="FightTypeConquerInfo" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="95">
   <si>
     <t>id</t>
   </si>
@@ -303,13 +317,19 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
   <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -317,6 +337,7 @@
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -324,12 +345,14 @@
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -337,6 +360,7 @@
       <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -344,6 +368,7 @@
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -351,6 +376,7 @@
       <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -358,6 +384,7 @@
       <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -365,12 +392,14 @@
       <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -378,6 +407,7 @@
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -385,6 +415,7 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -392,12 +423,14 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -405,30 +438,35 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -882,161 +920,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="52">
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="2" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="3" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="4" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="5" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="7" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" xfId="8" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="9" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="4" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="10" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="11" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="6" applyFont="1" fillId="0" applyFill="1" borderId="2" applyBorder="1" xfId="12" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="7" applyFont="1" fillId="0" applyFill="1" borderId="2" applyBorder="1" xfId="13" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="8" applyFont="1" fillId="0" applyFill="1" borderId="3" applyBorder="1" xfId="14" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="8" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="15" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="9" applyFont="1" fillId="3" applyFill="1" borderId="4" applyBorder="1" xfId="16" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="10" applyFont="1" fillId="4" applyFill="1" borderId="5" applyBorder="1" xfId="17" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="11" applyFont="1" fillId="4" applyFill="1" borderId="4" applyBorder="1" xfId="18" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="12" applyFont="1" fillId="5" applyFill="1" borderId="6" applyBorder="1" xfId="19" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="13" applyFont="1" fillId="0" applyFill="1" borderId="7" applyBorder="1" xfId="20" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="14" applyFont="1" fillId="0" applyFill="1" borderId="8" applyBorder="1" xfId="21" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="15" applyFont="1" fillId="6" applyFill="1" borderId="0" applyBorder="1" xfId="22" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="16" applyFont="1" fillId="7" applyFill="1" borderId="0" applyBorder="1" xfId="23" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="17" applyFont="1" fillId="8" applyFill="1" borderId="0" applyBorder="1" xfId="24" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="9" applyFill="1" borderId="0" applyBorder="1" xfId="25" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="1" xfId="26" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="11" applyFill="1" borderId="0" applyBorder="1" xfId="27" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="12" applyFill="1" borderId="0" applyBorder="1" xfId="28" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="13" applyFill="1" borderId="0" applyBorder="1" xfId="29" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="14" applyFill="1" borderId="0" applyBorder="1" xfId="30" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="15" applyFill="1" borderId="0" applyBorder="1" xfId="31" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="16" applyFill="1" borderId="0" applyBorder="1" xfId="32" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="17" applyFill="1" borderId="0" applyBorder="1" xfId="33" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="18" applyFill="1" borderId="0" applyBorder="1" xfId="34" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="19" applyFill="1" borderId="0" applyBorder="1" xfId="35" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="20" applyFill="1" borderId="0" applyBorder="1" xfId="36" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="21" applyFill="1" borderId="0" applyBorder="1" xfId="37" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="22" applyFill="1" borderId="0" applyBorder="1" xfId="38" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="23" applyFill="1" borderId="0" applyBorder="1" xfId="39" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="24" applyFill="1" borderId="0" applyBorder="1" xfId="40" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="25" applyFill="1" borderId="0" applyBorder="1" xfId="41" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="26" applyFill="1" borderId="0" applyBorder="1" xfId="42" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="27" applyFill="1" borderId="0" applyBorder="1" xfId="43" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="28" applyFill="1" borderId="0" applyBorder="1" xfId="44" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="29" applyFill="1" borderId="0" applyBorder="1" xfId="45" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="30" applyFill="1" borderId="0" applyBorder="1" xfId="46" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="31" applyFill="1" borderId="0" applyBorder="1" xfId="47" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="32" applyFill="1" borderId="0" applyBorder="1" xfId="48" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1090,74 +978,11 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1446,1015 +1271,1012 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:X13"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:X81"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="3" max="3" width="17.125" customWidth="1" style="51"/>
-    <col min="4" max="4" width="36.5" customWidth="1" style="51"/>
-    <col min="5" max="5" width="23.75" customWidth="1" style="51"/>
-    <col min="6" max="6" width="18.375" customWidth="1" style="51"/>
-    <col min="7" max="7" width="31.875" customWidth="1" style="51"/>
-    <col min="8" max="8" width="18.25" customWidth="1" style="51"/>
-    <col min="9" max="16" width="16" customWidth="1" style="51"/>
-    <col min="17" max="17" width="12.25" customWidth="1" style="51"/>
-    <col min="18" max="19" width="12.875" customWidth="1" style="51"/>
-    <col min="20" max="20" width="17.375" customWidth="1" style="51"/>
-    <col min="21" max="21" width="19.75" customWidth="1" style="51"/>
-    <col min="22" max="22" width="29.375" customWidth="1" style="51"/>
-    <col min="23" max="23" width="42.875" customWidth="1" style="51"/>
-    <col min="24" max="24" width="25.125" customWidth="1" style="51"/>
+    <col min="3" max="3" width="17.125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="36.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="23.75" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18.375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="31.875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.25" style="1" customWidth="1"/>
+    <col min="9" max="16" width="16" style="1" customWidth="1"/>
+    <col min="17" max="17" width="12.25" style="1" customWidth="1"/>
+    <col min="18" max="19" width="12.875" style="1" customWidth="1"/>
+    <col min="20" max="20" width="17.375" style="1" customWidth="1"/>
+    <col min="21" max="21" width="36.875" style="1" customWidth="1"/>
+    <col min="22" max="22" width="29.375" style="1" customWidth="1"/>
+    <col min="23" max="23" width="42.875" style="1" customWidth="1"/>
+    <col min="24" max="24" width="25.125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="50" t="s">
+    <row r="1" spans="1:24">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="51" t="s">
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="51" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="51" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="51" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="51" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="51" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="51" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="51" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="51" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="51" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="51" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="51" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="51" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="51" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="51" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="51" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="51" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="51" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="51" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="51" t="s">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="51" t="s">
+      <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="51" t="s">
+      <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="50" t="s">
+    <row r="2" spans="1:24">
+      <c r="A2" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="50" t="s">
+      <c r="B2" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="51" t="s">
+      <c r="C2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="51" t="s">
+      <c r="D2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="51" t="s">
+      <c r="E2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="51" t="s">
+      <c r="F2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="51" t="s">
+      <c r="G2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H2" s="51" t="s">
+      <c r="H2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="51" t="s">
+      <c r="I2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="J2" s="51" t="s">
+      <c r="J2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="K2" s="51" t="s">
+      <c r="K2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="51" t="s">
+      <c r="L2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="M2" s="51" t="s">
+      <c r="M2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="N2" s="51" t="s">
+      <c r="N2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="O2" s="51" t="s">
+      <c r="O2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="P2" s="51" t="s">
+      <c r="P2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Q2" s="51" t="s">
+      <c r="Q2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="R2" s="51" t="s">
+      <c r="R2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="S2" s="51" t="s">
+      <c r="S2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="T2" s="51" t="s">
+      <c r="T2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="U2" s="51" t="s">
+      <c r="U2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="V2" s="51" t="s">
+      <c r="V2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="W2" s="51" t="s">
+      <c r="W2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="X2" s="51" t="s">
+      <c r="X2" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="50" t="s">
+    <row r="3" spans="1:24">
+      <c r="A3" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="50" t="s">
+      <c r="B3" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="51" t="s">
+      <c r="C3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="51" t="s">
+      <c r="D3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="51" t="s">
+      <c r="E3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="51" t="s">
+      <c r="F3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G3" s="51" t="s">
+      <c r="G3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H3" s="51" t="s">
+      <c r="H3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="I3" s="51" t="s">
+      <c r="I3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="J3" s="51" t="s">
+      <c r="J3" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="K3" s="51" t="s">
+      <c r="K3" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="L3" s="51" t="s">
+      <c r="L3" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="M3" s="51" t="s">
+      <c r="M3" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="N3" s="51" t="s">
+      <c r="N3" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="O3" s="51" t="s">
+      <c r="O3" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="P3" s="51" t="s">
+      <c r="P3" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="Q3" s="51" t="s">
+      <c r="Q3" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="R3" s="51" t="s">
+      <c r="R3" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="S3" s="51" t="s">
+      <c r="S3" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="T3" s="51" t="s">
+      <c r="T3" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="U3" s="51" t="s">
+      <c r="U3" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="V3" s="51" t="s">
+      <c r="V3" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="W3" s="51" t="s">
+      <c r="W3" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="X3" s="51" t="s">
+      <c r="X3" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="50">
+    <row r="4" spans="1:24">
+      <c r="A4">
         <v>1000001</v>
       </c>
-      <c r="B4" s="50">
-        <v>1</v>
-      </c>
-      <c r="C4" s="51" t="s">
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D4" s="51" t="s">
+      <c r="D4" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E4" s="51" t="s">
+      <c r="E4" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F4" s="51" t="s">
+      <c r="F4" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G4" s="51" t="s">
+      <c r="G4" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="H4" s="51" t="s">
+      <c r="H4" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="I4" s="51" t="s">
+      <c r="I4" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="J4" s="51">
-        <v>1</v>
-      </c>
-      <c r="K4" s="51" t="s">
+      <c r="J4" s="1">
+        <v>1</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="L4" s="51">
-        <v>1</v>
-      </c>
-      <c r="M4" s="51" t="s">
+      <c r="L4" s="1">
+        <v>1</v>
+      </c>
+      <c r="M4" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="N4" s="51" t="s">
+      <c r="N4" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="O4" s="51" t="s">
+      <c r="O4" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="P4" s="51">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="51">
-        <v>1</v>
-      </c>
-      <c r="R4" s="51">
-        <v>1</v>
-      </c>
-      <c r="S4" s="51">
+      <c r="P4" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>1</v>
+      </c>
+      <c r="R4" s="1">
+        <v>1</v>
+      </c>
+      <c r="S4" s="1">
         <v>100</v>
       </c>
-      <c r="T4" s="51">
-        <v>1</v>
-      </c>
-      <c r="U4" s="51">
+      <c r="T4" s="1">
+        <v>1</v>
+      </c>
+      <c r="U4" s="1">
         <v>5</v>
       </c>
-      <c r="V4" s="51">
+      <c r="V4" s="1">
         <v>10</v>
       </c>
-      <c r="W4" s="51">
+      <c r="W4" s="1">
         <v>50</v>
       </c>
-      <c r="X4" s="51" t="s">
+      <c r="X4" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="50">
+    <row r="5" spans="1:24">
+      <c r="A5">
         <v>1000002</v>
       </c>
-      <c r="B5" s="50">
-        <v>1</v>
-      </c>
-      <c r="C5" s="51" t="s">
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D5" s="51" t="s">
+      <c r="D5" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E5" s="51" t="s">
+      <c r="E5" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F5" s="51" t="s">
+      <c r="F5" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="G5" s="51" t="s">
+      <c r="G5" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="H5" s="51">
+      <c r="H5" s="1">
         <v>3</v>
       </c>
-      <c r="I5" s="51">
+      <c r="I5" s="1">
         <v>5</v>
       </c>
-      <c r="J5" s="51">
-        <v>1</v>
-      </c>
-      <c r="K5" s="51">
+      <c r="J5" s="1">
+        <v>1</v>
+      </c>
+      <c r="K5" s="1">
         <v>2</v>
       </c>
-      <c r="L5" s="51">
-        <v>1</v>
-      </c>
-      <c r="M5" s="51" t="s">
+      <c r="L5" s="1">
+        <v>1</v>
+      </c>
+      <c r="M5" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="N5" s="51" t="s">
+      <c r="N5" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="O5" s="51" t="s">
+      <c r="O5" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="P5" s="51">
+      <c r="P5" s="1">
         <v>2</v>
       </c>
-      <c r="Q5" s="51">
+      <c r="Q5" s="1">
         <v>2</v>
       </c>
-      <c r="R5" s="51">
-        <v>1</v>
-      </c>
-      <c r="S5" s="51">
+      <c r="R5" s="1">
+        <v>1</v>
+      </c>
+      <c r="S5" s="1">
         <v>200</v>
       </c>
-      <c r="T5" s="51">
-        <v>1</v>
-      </c>
-      <c r="U5" s="51">
+      <c r="T5" s="1">
+        <v>1</v>
+      </c>
+      <c r="U5" s="1">
+        <v>5</v>
+      </c>
+      <c r="V5" s="1">
+        <v>20</v>
+      </c>
+      <c r="W5" s="1">
+        <v>100</v>
+      </c>
+      <c r="X5" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24">
+      <c r="A6">
+        <v>1000003</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H6" s="1">
+        <v>3</v>
+      </c>
+      <c r="I6" s="1">
+        <v>5</v>
+      </c>
+      <c r="J6" s="1">
+        <v>1</v>
+      </c>
+      <c r="K6" s="1">
+        <v>2</v>
+      </c>
+      <c r="L6" s="1">
+        <v>1</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="P6" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>3</v>
+      </c>
+      <c r="R6" s="1">
+        <v>2</v>
+      </c>
+      <c r="S6" s="1">
+        <v>300</v>
+      </c>
+      <c r="T6" s="1">
+        <v>2</v>
+      </c>
+      <c r="U6" s="1">
         <v>10</v>
       </c>
-      <c r="V5" s="51">
+      <c r="V6" s="1">
+        <v>30</v>
+      </c>
+      <c r="W6" s="1">
+        <v>150</v>
+      </c>
+      <c r="X6" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24">
+      <c r="A7">
+        <v>1000004</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H7" s="1">
+        <v>3</v>
+      </c>
+      <c r="I7" s="1">
+        <v>5</v>
+      </c>
+      <c r="J7" s="1">
+        <v>1</v>
+      </c>
+      <c r="K7" s="1">
+        <v>2</v>
+      </c>
+      <c r="L7" s="1">
+        <v>1</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="P7" s="1">
+        <v>4</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>4</v>
+      </c>
+      <c r="R7" s="1">
+        <v>2</v>
+      </c>
+      <c r="S7" s="1">
+        <v>400</v>
+      </c>
+      <c r="T7" s="1">
+        <v>2</v>
+      </c>
+      <c r="U7" s="1">
+        <v>10</v>
+      </c>
+      <c r="V7" s="1">
+        <v>40</v>
+      </c>
+      <c r="W7" s="1">
+        <v>200</v>
+      </c>
+      <c r="X7" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24">
+      <c r="A8">
+        <v>1000005</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H8" s="1">
+        <v>3</v>
+      </c>
+      <c r="I8" s="1">
+        <v>5</v>
+      </c>
+      <c r="J8" s="1">
+        <v>1</v>
+      </c>
+      <c r="K8" s="1">
+        <v>2</v>
+      </c>
+      <c r="L8" s="1">
+        <v>1</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="P8" s="1">
+        <v>5</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>5</v>
+      </c>
+      <c r="R8" s="1">
+        <v>3</v>
+      </c>
+      <c r="S8" s="1">
+        <v>500</v>
+      </c>
+      <c r="T8" s="1">
+        <v>3</v>
+      </c>
+      <c r="U8" s="1">
+        <v>15</v>
+      </c>
+      <c r="V8" s="1">
+        <v>50</v>
+      </c>
+      <c r="W8" s="1">
+        <v>250</v>
+      </c>
+      <c r="X8" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24">
+      <c r="A9">
+        <v>1000006</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H9" s="1">
+        <v>3</v>
+      </c>
+      <c r="I9" s="1">
+        <v>5</v>
+      </c>
+      <c r="J9" s="1">
+        <v>1</v>
+      </c>
+      <c r="K9" s="1">
+        <v>2</v>
+      </c>
+      <c r="L9" s="1">
+        <v>1</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="P9" s="1">
+        <v>6</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>6</v>
+      </c>
+      <c r="R9" s="1">
+        <v>3</v>
+      </c>
+      <c r="S9" s="1">
+        <v>600</v>
+      </c>
+      <c r="T9" s="1">
+        <v>3</v>
+      </c>
+      <c r="U9" s="1">
+        <v>15</v>
+      </c>
+      <c r="V9" s="1">
+        <v>60</v>
+      </c>
+      <c r="W9" s="1">
+        <v>300</v>
+      </c>
+      <c r="X9" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24">
+      <c r="A10">
+        <v>1000007</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H10" s="1">
+        <v>3</v>
+      </c>
+      <c r="I10" s="1">
+        <v>5</v>
+      </c>
+      <c r="J10" s="1">
+        <v>1</v>
+      </c>
+      <c r="K10" s="1">
+        <v>2</v>
+      </c>
+      <c r="L10" s="1">
+        <v>1</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="P10" s="1">
+        <v>7</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>7</v>
+      </c>
+      <c r="R10" s="1">
+        <v>4</v>
+      </c>
+      <c r="S10" s="1">
+        <v>700</v>
+      </c>
+      <c r="T10" s="1">
+        <v>4</v>
+      </c>
+      <c r="U10" s="1">
         <v>20</v>
       </c>
-      <c r="W5" s="51">
+      <c r="V10" s="1">
+        <v>70</v>
+      </c>
+      <c r="W10" s="1">
+        <v>350</v>
+      </c>
+      <c r="X10" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24">
+      <c r="A11">
+        <v>1000008</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H11" s="1">
+        <v>3</v>
+      </c>
+      <c r="I11" s="1">
+        <v>5</v>
+      </c>
+      <c r="J11" s="1">
+        <v>1</v>
+      </c>
+      <c r="K11" s="1">
+        <v>2</v>
+      </c>
+      <c r="L11" s="1">
+        <v>1</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="P11" s="1">
+        <v>8</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>8</v>
+      </c>
+      <c r="R11" s="1">
+        <v>4</v>
+      </c>
+      <c r="S11" s="1">
+        <v>800</v>
+      </c>
+      <c r="T11" s="1">
+        <v>4</v>
+      </c>
+      <c r="U11" s="1">
+        <v>20</v>
+      </c>
+      <c r="V11" s="1">
+        <v>80</v>
+      </c>
+      <c r="W11" s="1">
+        <v>400</v>
+      </c>
+      <c r="X11" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24">
+      <c r="A12">
+        <v>1000009</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H12" s="1">
+        <v>3</v>
+      </c>
+      <c r="I12" s="1">
+        <v>5</v>
+      </c>
+      <c r="J12" s="1">
+        <v>1</v>
+      </c>
+      <c r="K12" s="1">
+        <v>2</v>
+      </c>
+      <c r="L12" s="1">
+        <v>1</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="P12" s="1">
+        <v>9</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>9</v>
+      </c>
+      <c r="R12" s="1">
+        <v>5</v>
+      </c>
+      <c r="S12" s="1">
+        <v>900</v>
+      </c>
+      <c r="T12" s="1">
+        <v>5</v>
+      </c>
+      <c r="U12" s="1">
+        <v>25</v>
+      </c>
+      <c r="V12" s="1">
+        <v>90</v>
+      </c>
+      <c r="W12" s="1">
+        <v>450</v>
+      </c>
+      <c r="X12" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24">
+      <c r="A13">
+        <v>1000010</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H13" s="1">
+        <v>3</v>
+      </c>
+      <c r="I13" s="1">
+        <v>5</v>
+      </c>
+      <c r="J13" s="1">
+        <v>1</v>
+      </c>
+      <c r="K13" s="1">
+        <v>2</v>
+      </c>
+      <c r="L13" s="1">
+        <v>1</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="P13" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>10</v>
+      </c>
+      <c r="R13" s="1">
+        <v>5</v>
+      </c>
+      <c r="S13" s="1">
+        <v>1000</v>
+      </c>
+      <c r="T13" s="1">
+        <v>5</v>
+      </c>
+      <c r="U13" s="1">
+        <v>25</v>
+      </c>
+      <c r="V13" s="1">
         <v>100</v>
       </c>
-      <c r="X5" s="51" t="s">
-        <v>67</v>
+      <c r="W13" s="1">
+        <v>500</v>
+      </c>
+      <c r="X13" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="50">
-        <v>1000003</v>
-      </c>
-      <c r="B6" s="50">
-        <v>1</v>
-      </c>
-      <c r="C6" s="51" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" s="51" t="s">
-        <v>62</v>
-      </c>
-      <c r="E6" s="51" t="s">
-        <v>63</v>
-      </c>
-      <c r="F6" s="51" t="s">
-        <v>63</v>
-      </c>
-      <c r="G6" s="51" t="s">
-        <v>60</v>
-      </c>
-      <c r="H6" s="51">
-        <v>3</v>
-      </c>
-      <c r="I6" s="51">
-        <v>5</v>
-      </c>
-      <c r="J6" s="51">
-        <v>1</v>
-      </c>
-      <c r="K6" s="51">
-        <v>2</v>
-      </c>
-      <c r="L6" s="51">
-        <v>1</v>
-      </c>
-      <c r="M6" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="N6" s="51" t="s">
-        <v>69</v>
-      </c>
-      <c r="O6" s="51" t="s">
-        <v>70</v>
-      </c>
-      <c r="P6" s="51">
-        <v>3</v>
-      </c>
-      <c r="Q6" s="51">
-        <v>3</v>
-      </c>
-      <c r="R6" s="51">
-        <v>2</v>
-      </c>
-      <c r="S6" s="51">
-        <v>300</v>
-      </c>
-      <c r="T6" s="51">
-        <v>1</v>
-      </c>
-      <c r="U6" s="51">
-        <v>15</v>
-      </c>
-      <c r="V6" s="51">
-        <v>30</v>
-      </c>
-      <c r="W6" s="51">
-        <v>150</v>
-      </c>
-      <c r="X6" s="51" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="50">
-        <v>1000004</v>
-      </c>
-      <c r="B7" s="50">
-        <v>1</v>
-      </c>
-      <c r="C7" s="51" t="s">
-        <v>62</v>
-      </c>
-      <c r="D7" s="51" t="s">
-        <v>62</v>
-      </c>
-      <c r="E7" s="51" t="s">
-        <v>63</v>
-      </c>
-      <c r="F7" s="51" t="s">
-        <v>63</v>
-      </c>
-      <c r="G7" s="51" t="s">
-        <v>60</v>
-      </c>
-      <c r="H7" s="51">
-        <v>3</v>
-      </c>
-      <c r="I7" s="51">
-        <v>5</v>
-      </c>
-      <c r="J7" s="51">
-        <v>1</v>
-      </c>
-      <c r="K7" s="51">
-        <v>2</v>
-      </c>
-      <c r="L7" s="51">
-        <v>1</v>
-      </c>
-      <c r="M7" s="51" t="s">
-        <v>72</v>
-      </c>
-      <c r="N7" s="51" t="s">
-        <v>73</v>
-      </c>
-      <c r="O7" s="51" t="s">
-        <v>74</v>
-      </c>
-      <c r="P7" s="51">
-        <v>4</v>
-      </c>
-      <c r="Q7" s="51">
-        <v>4</v>
-      </c>
-      <c r="R7" s="51">
-        <v>2</v>
-      </c>
-      <c r="S7" s="51">
-        <v>400</v>
-      </c>
-      <c r="T7" s="51">
-        <v>1</v>
-      </c>
-      <c r="U7" s="51">
-        <v>20</v>
-      </c>
-      <c r="V7" s="51">
-        <v>40</v>
-      </c>
-      <c r="W7" s="51">
-        <v>200</v>
-      </c>
-      <c r="X7" s="51" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="50">
-        <v>1000005</v>
-      </c>
-      <c r="B8" s="50">
-        <v>1</v>
-      </c>
-      <c r="C8" s="51" t="s">
-        <v>62</v>
-      </c>
-      <c r="D8" s="51" t="s">
-        <v>62</v>
-      </c>
-      <c r="E8" s="51" t="s">
-        <v>63</v>
-      </c>
-      <c r="F8" s="51" t="s">
-        <v>63</v>
-      </c>
-      <c r="G8" s="51" t="s">
-        <v>60</v>
-      </c>
-      <c r="H8" s="51">
-        <v>3</v>
-      </c>
-      <c r="I8" s="51">
-        <v>5</v>
-      </c>
-      <c r="J8" s="51">
-        <v>1</v>
-      </c>
-      <c r="K8" s="51">
-        <v>2</v>
-      </c>
-      <c r="L8" s="51">
-        <v>1</v>
-      </c>
-      <c r="M8" s="51" t="s">
-        <v>74</v>
-      </c>
-      <c r="N8" s="51" t="s">
-        <v>76</v>
-      </c>
-      <c r="O8" s="51" t="s">
-        <v>77</v>
-      </c>
-      <c r="P8" s="51">
-        <v>5</v>
-      </c>
-      <c r="Q8" s="51">
-        <v>5</v>
-      </c>
-      <c r="R8" s="51">
-        <v>3</v>
-      </c>
-      <c r="S8" s="51">
-        <v>500</v>
-      </c>
-      <c r="T8" s="51">
-        <v>1</v>
-      </c>
-      <c r="U8" s="51">
-        <v>25</v>
-      </c>
-      <c r="V8" s="51">
-        <v>50</v>
-      </c>
-      <c r="W8" s="51">
-        <v>250</v>
-      </c>
-      <c r="X8" s="51" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="50">
-        <v>1000006</v>
-      </c>
-      <c r="B9" s="50">
-        <v>1</v>
-      </c>
-      <c r="C9" s="51" t="s">
-        <v>62</v>
-      </c>
-      <c r="D9" s="51" t="s">
-        <v>62</v>
-      </c>
-      <c r="E9" s="51" t="s">
-        <v>63</v>
-      </c>
-      <c r="F9" s="51" t="s">
-        <v>63</v>
-      </c>
-      <c r="G9" s="51" t="s">
-        <v>60</v>
-      </c>
-      <c r="H9" s="51">
-        <v>3</v>
-      </c>
-      <c r="I9" s="51">
-        <v>5</v>
-      </c>
-      <c r="J9" s="51">
-        <v>1</v>
-      </c>
-      <c r="K9" s="51">
-        <v>2</v>
-      </c>
-      <c r="L9" s="51">
-        <v>1</v>
-      </c>
-      <c r="M9" s="51" t="s">
-        <v>79</v>
-      </c>
-      <c r="N9" s="51" t="s">
-        <v>80</v>
-      </c>
-      <c r="O9" s="51" t="s">
-        <v>81</v>
-      </c>
-      <c r="P9" s="51">
-        <v>6</v>
-      </c>
-      <c r="Q9" s="51">
-        <v>6</v>
-      </c>
-      <c r="R9" s="51">
-        <v>3</v>
-      </c>
-      <c r="S9" s="51">
-        <v>600</v>
-      </c>
-      <c r="T9" s="51">
-        <v>1</v>
-      </c>
-      <c r="U9" s="51">
-        <v>30</v>
-      </c>
-      <c r="V9" s="51">
-        <v>60</v>
-      </c>
-      <c r="W9" s="51">
-        <v>300</v>
-      </c>
-      <c r="X9" s="51" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="50">
-        <v>1000007</v>
-      </c>
-      <c r="B10" s="50">
-        <v>1</v>
-      </c>
-      <c r="C10" s="51" t="s">
-        <v>62</v>
-      </c>
-      <c r="D10" s="51" t="s">
-        <v>62</v>
-      </c>
-      <c r="E10" s="51" t="s">
-        <v>63</v>
-      </c>
-      <c r="F10" s="51" t="s">
-        <v>63</v>
-      </c>
-      <c r="G10" s="51" t="s">
-        <v>60</v>
-      </c>
-      <c r="H10" s="51">
-        <v>3</v>
-      </c>
-      <c r="I10" s="51">
-        <v>5</v>
-      </c>
-      <c r="J10" s="51">
-        <v>1</v>
-      </c>
-      <c r="K10" s="51">
-        <v>2</v>
-      </c>
-      <c r="L10" s="51">
-        <v>1</v>
-      </c>
-      <c r="M10" s="51" t="s">
-        <v>83</v>
-      </c>
-      <c r="N10" s="51" t="s">
-        <v>80</v>
-      </c>
-      <c r="O10" s="51" t="s">
-        <v>84</v>
-      </c>
-      <c r="P10" s="51">
-        <v>7</v>
-      </c>
-      <c r="Q10" s="51">
-        <v>7</v>
-      </c>
-      <c r="R10" s="51">
-        <v>4</v>
-      </c>
-      <c r="S10" s="51">
-        <v>700</v>
-      </c>
-      <c r="T10" s="51">
-        <v>1</v>
-      </c>
-      <c r="U10" s="51">
-        <v>35</v>
-      </c>
-      <c r="V10" s="51">
-        <v>70</v>
-      </c>
-      <c r="W10" s="51">
-        <v>350</v>
-      </c>
-      <c r="X10" s="51" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="50">
-        <v>1000008</v>
-      </c>
-      <c r="B11" s="50">
-        <v>1</v>
-      </c>
-      <c r="C11" s="51" t="s">
-        <v>62</v>
-      </c>
-      <c r="D11" s="51" t="s">
-        <v>62</v>
-      </c>
-      <c r="E11" s="51" t="s">
-        <v>63</v>
-      </c>
-      <c r="F11" s="51" t="s">
-        <v>63</v>
-      </c>
-      <c r="G11" s="51" t="s">
-        <v>60</v>
-      </c>
-      <c r="H11" s="51">
-        <v>3</v>
-      </c>
-      <c r="I11" s="51">
-        <v>5</v>
-      </c>
-      <c r="J11" s="51">
-        <v>1</v>
-      </c>
-      <c r="K11" s="51">
-        <v>2</v>
-      </c>
-      <c r="L11" s="51">
-        <v>1</v>
-      </c>
-      <c r="M11" s="51" t="s">
-        <v>86</v>
-      </c>
-      <c r="N11" s="51" t="s">
-        <v>80</v>
-      </c>
-      <c r="O11" s="51" t="s">
-        <v>87</v>
-      </c>
-      <c r="P11" s="51">
-        <v>8</v>
-      </c>
-      <c r="Q11" s="51">
-        <v>8</v>
-      </c>
-      <c r="R11" s="51">
-        <v>4</v>
-      </c>
-      <c r="S11" s="51">
-        <v>800</v>
-      </c>
-      <c r="T11" s="51">
-        <v>1</v>
-      </c>
-      <c r="U11" s="51">
-        <v>40</v>
-      </c>
-      <c r="V11" s="51">
-        <v>80</v>
-      </c>
-      <c r="W11" s="51">
-        <v>400</v>
-      </c>
-      <c r="X11" s="51" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="50">
-        <v>1000009</v>
-      </c>
-      <c r="B12" s="50">
-        <v>1</v>
-      </c>
-      <c r="C12" s="51" t="s">
-        <v>62</v>
-      </c>
-      <c r="D12" s="51" t="s">
-        <v>62</v>
-      </c>
-      <c r="E12" s="51" t="s">
-        <v>63</v>
-      </c>
-      <c r="F12" s="51" t="s">
-        <v>63</v>
-      </c>
-      <c r="G12" s="51" t="s">
-        <v>60</v>
-      </c>
-      <c r="H12" s="51">
-        <v>3</v>
-      </c>
-      <c r="I12" s="51">
-        <v>5</v>
-      </c>
-      <c r="J12" s="51">
-        <v>1</v>
-      </c>
-      <c r="K12" s="51">
-        <v>2</v>
-      </c>
-      <c r="L12" s="51">
-        <v>1</v>
-      </c>
-      <c r="M12" s="51" t="s">
-        <v>89</v>
-      </c>
-      <c r="N12" s="51" t="s">
-        <v>80</v>
-      </c>
-      <c r="O12" s="51" t="s">
-        <v>90</v>
-      </c>
-      <c r="P12" s="51">
-        <v>9</v>
-      </c>
-      <c r="Q12" s="51">
-        <v>9</v>
-      </c>
-      <c r="R12" s="51">
-        <v>5</v>
-      </c>
-      <c r="S12" s="51">
-        <v>900</v>
-      </c>
-      <c r="T12" s="51">
-        <v>1</v>
-      </c>
-      <c r="U12" s="51">
-        <v>45</v>
-      </c>
-      <c r="V12" s="51">
-        <v>90</v>
-      </c>
-      <c r="W12" s="51">
-        <v>450</v>
-      </c>
-      <c r="X12" s="51" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="50">
-        <v>1000010</v>
-      </c>
-      <c r="B13" s="50">
-        <v>1</v>
-      </c>
-      <c r="C13" s="51" t="s">
-        <v>62</v>
-      </c>
-      <c r="D13" s="51" t="s">
-        <v>62</v>
-      </c>
-      <c r="E13" s="51" t="s">
-        <v>63</v>
-      </c>
-      <c r="F13" s="51" t="s">
-        <v>63</v>
-      </c>
-      <c r="G13" s="51" t="s">
-        <v>60</v>
-      </c>
-      <c r="H13" s="51">
-        <v>3</v>
-      </c>
-      <c r="I13" s="51">
-        <v>5</v>
-      </c>
-      <c r="J13" s="51">
-        <v>1</v>
-      </c>
-      <c r="K13" s="51">
-        <v>2</v>
-      </c>
-      <c r="L13" s="51">
-        <v>1</v>
-      </c>
-      <c r="M13" s="51" t="s">
-        <v>92</v>
-      </c>
-      <c r="N13" s="51" t="s">
-        <v>80</v>
-      </c>
-      <c r="O13" s="51" t="s">
-        <v>93</v>
-      </c>
-      <c r="P13" s="51">
-        <v>10</v>
-      </c>
-      <c r="Q13" s="51">
-        <v>10</v>
-      </c>
-      <c r="R13" s="51">
-        <v>5</v>
-      </c>
-      <c r="S13" s="51">
-        <v>1000</v>
-      </c>
-      <c r="T13" s="51">
-        <v>1</v>
-      </c>
-      <c r="U13" s="51">
-        <v>50</v>
-      </c>
-      <c r="V13" s="51">
-        <v>100</v>
-      </c>
-      <c r="W13" s="51">
-        <v>500</v>
-      </c>
-      <c r="X13" s="51" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="32" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="33" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="34" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="35" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="36" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="37" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="38" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="39" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="40" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="41" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="73" ht="12" customHeight="1" s="51" customFormat="1"/>
-    <row r="74" ht="12" customHeight="1" s="51" customFormat="1"/>
-    <row r="75" ht="12" customHeight="1" s="51" customFormat="1"/>
-    <row r="76" ht="12" customHeight="1" s="51" customFormat="1"/>
-    <row r="77" ht="12" customHeight="1" s="51" customFormat="1"/>
-    <row r="78" ht="12" customHeight="1" s="51" customFormat="1"/>
-    <row r="79" ht="12" customHeight="1" s="51" customFormat="1"/>
-    <row r="80" ht="12" customHeight="1" s="51" customFormat="1"/>
-    <row r="81" ht="12" customHeight="1" s="51" customFormat="1"/>
+    <row r="31" s="1" customFormat="1" ht="15" customHeight="1"/>
+    <row r="32" s="1" customFormat="1" ht="15" customHeight="1"/>
+    <row r="33" s="1" customFormat="1" ht="15" customHeight="1"/>
+    <row r="34" s="1" customFormat="1" ht="15" customHeight="1"/>
+    <row r="35" s="1" customFormat="1" ht="15" customHeight="1"/>
+    <row r="36" s="1" customFormat="1" ht="15" customHeight="1"/>
+    <row r="37" s="1" customFormat="1" ht="15" customHeight="1"/>
+    <row r="38" s="1" customFormat="1" ht="15" customHeight="1"/>
+    <row r="39" s="1" customFormat="1" ht="15" customHeight="1"/>
+    <row r="40" s="1" customFormat="1" ht="15" customHeight="1"/>
+    <row r="41" s="1" customFormat="1" ht="15" customHeight="1"/>
+    <row r="73" s="1" customFormat="1" ht="12" customHeight="1"/>
+    <row r="74" s="1" customFormat="1" ht="12" customHeight="1"/>
+    <row r="75" s="1" customFormat="1" ht="12" customHeight="1"/>
+    <row r="76" s="1" customFormat="1" ht="12" customHeight="1"/>
+    <row r="77" s="1" customFormat="1" ht="12" customHeight="1"/>
+    <row r="78" s="1" customFormat="1" ht="12" customHeight="1"/>
+    <row r="79" s="1" customFormat="1" ht="12" customHeight="1"/>
+    <row r="80" s="1" customFormat="1" ht="12" customHeight="1"/>
+    <row r="81" s="1" customFormat="1" ht="12" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
@@ -1031,7 +1031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y13"/>
+  <dimension ref="A1:X13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="17.125" customWidth="1" style="1" min="3" max="3"/>
@@ -1061,117 +1061,112 @@
           <t>world_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="0" t="inlineStr">
         <is>
           <t>fight_scene_ids</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="0" t="inlineStr">
         <is>
           <t>fight_scene_boss_ids</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="0" t="inlineStr">
         <is>
           <t>enemy_ids</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="0" t="inlineStr">
         <is>
           <t>enemy_boss_ids</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="0" t="inlineStr">
         <is>
           <t>attack_boss_num</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="0" t="inlineStr">
         <is>
           <t>attack_start_num</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="0" t="inlineStr">
         <is>
           <t>attack_show_time</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="0" t="inlineStr">
         <is>
           <t>attack_num_addrate</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="0" t="inlineStr">
         <is>
           <t>attack_num_add</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="0" t="inlineStr">
         <is>
           <t>attack_intensity_addrate</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="0" t="inlineStr">
         <is>
           <t>fight_num</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="0" t="inlineStr">
         <is>
           <t>road_num</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="0" t="inlineStr">
         <is>
           <t>road_length</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="0" t="inlineStr">
         <is>
           <t>level</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="0" t="inlineStr">
         <is>
           <t>level_add</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="0" t="inlineStr">
         <is>
           <t>drop_crystal</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="0" t="inlineStr">
         <is>
           <t>reward_crystal</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="0" t="inlineStr">
         <is>
           <t>reward_equip_rarity</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>reward_equip_attribute_add</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
+      <c r="U1" s="0" t="inlineStr">
         <is>
           <t>reward_exp</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="V1" s="0" t="inlineStr">
         <is>
           <t>reward_exp_boss</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="W1" s="0" t="inlineStr">
         <is>
           <t>remark</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="X1" s="0" t="inlineStr">
         <is>
           <t>bg_color</t>
         </is>
@@ -1188,117 +1183,112 @@
           <t>long</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="0" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="0" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" s="0" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P2" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Q2" s="0" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="R2" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S2" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T2" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V2" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="X2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -1315,117 +1305,112 @@
           <t>世界ID</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="0" t="inlineStr">
         <is>
           <t>战斗场景列表（用&amp;分割）</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="0" t="inlineStr">
         <is>
           <t>boss战斗场景列表（用&amp;分割）</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="0" t="inlineStr">
         <is>
           <t>敌人列表（npcInfoId用&amp;分割）</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="0" t="inlineStr">
         <is>
           <t>boss列表（npcInfoId用&amp;分割）</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="0" t="inlineStr">
         <is>
           <t>boss数量(单个数x或范围x-y)</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="0" t="inlineStr">
         <is>
           <t>第一关敌人数量</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="0" t="inlineStr">
         <is>
           <t>进攻时间(秒)</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="0" t="inlineStr">
         <is>
           <t>每关敌人倍数</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="0" t="inlineStr">
         <is>
           <t>每关增加敌人数量</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" s="0" t="inlineStr">
         <is>
           <t>普通敌人每关强度倍率(默认1,如1.1则每关HP/护甲/攻击力×1.1)</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" s="0" t="inlineStr">
         <is>
           <t>关卡次数(单个数x或范围x-y)</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="0" t="inlineStr">
         <is>
           <t>道路数量(单个数x或范围x-y)</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O3" s="0" t="inlineStr">
         <is>
           <t>道路长度(单个数x或范围x-y)</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P3" s="0" t="inlineStr">
         <is>
           <t>难度</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Q3" s="0" t="inlineStr">
         <is>
           <t>难度数值加成</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="R3" s="0" t="inlineStr">
         <is>
           <t>掉落魔晶</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S3" s="0" t="inlineStr">
         <is>
           <t>奖励-魔晶</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T3" s="0" t="inlineStr">
         <is>
           <t>奖励-装备稀有度</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>奖励-装备属性加成</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
+      <c r="U3" s="0" t="inlineStr">
         <is>
           <t>奖励-普通关卡经验</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="V3" s="0" t="inlineStr">
         <is>
           <t>奖励-BOSS关卡经验</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" s="0" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="X3" s="0" t="inlineStr">
         <is>
           <t>背景色(由易到难)</t>
         </is>
@@ -1438,97 +1423,94 @@
       <c r="B4" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="0" t="inlineStr">
         <is>
           <t>99999</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="0" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="0" t="inlineStr">
         <is>
           <t>1010010001</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="0" t="inlineStr">
         <is>
           <t>1010020001</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="0" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="0" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="0" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="inlineStr">
+      <c r="J4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" s="0" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="L4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" t="inlineStr">
+      <c r="L4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" s="0" t="inlineStr">
         <is>
           <t>5-6</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N4" s="0" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O4" s="0" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" t="n">
+      <c r="P4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" s="0" t="n">
         <v>100</v>
       </c>
-      <c r="T4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U4" t="n">
-        <v>5</v>
-      </c>
-      <c r="V4" t="n">
+      <c r="T4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="W4" t="n">
+      <c r="V4" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" s="0" t="inlineStr">
         <is>
           <t>剑与魔法-难度1</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="X4" s="0" t="inlineStr">
         <is>
           <t>#2ECC71</t>
         </is>
@@ -1541,91 +1523,88 @@
       <c r="B5" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>1&amp;1</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="0" t="inlineStr">
         <is>
           <t>1&amp;1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="0" t="inlineStr">
         <is>
           <t>1010010001&amp;1010010001</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="0" t="inlineStr">
         <is>
           <t>1010010001&amp;1010010001</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="0" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
+      <c r="J5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="inlineStr">
+      <c r="L5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="0" t="inlineStr">
         <is>
           <t>5-7</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N5" s="0" t="inlineStr">
         <is>
           <t>3-4</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O5" s="0" t="inlineStr">
         <is>
           <t>9-10</t>
         </is>
       </c>
-      <c r="P5" t="n">
+      <c r="P5" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q5" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="R5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>5</v>
-      </c>
-      <c r="V5" t="n">
+      <c r="T5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="W5" t="n">
+      <c r="V5" s="0" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" s="0" t="inlineStr">
         <is>
           <t>剑与魔法-难度2</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="X5" s="0" t="inlineStr">
         <is>
           <t>#82C91E</t>
         </is>
@@ -1638,91 +1617,88 @@
       <c r="B6" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="0" t="inlineStr">
         <is>
           <t>1&amp;1</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="0" t="inlineStr">
         <is>
           <t>1&amp;1</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="0" t="inlineStr">
         <is>
           <t>1010010001&amp;1010010001</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="0" t="inlineStr">
         <is>
           <t>1010010001&amp;1010010001</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="0" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
+      <c r="J6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="inlineStr">
+      <c r="L6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" s="0" t="inlineStr">
         <is>
           <t>6-8</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N6" s="0" t="inlineStr">
         <is>
           <t>3-5</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="O6" s="0" t="inlineStr">
         <is>
           <t>8-10</t>
         </is>
       </c>
-      <c r="P6" t="n">
+      <c r="P6" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="Q6" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="R6" t="n">
+      <c r="R6" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="S6" t="n">
+      <c r="S6" s="0" t="n">
         <v>300</v>
       </c>
-      <c r="T6" t="n">
+      <c r="T6" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="U6" t="n">
-        <v>10</v>
-      </c>
-      <c r="V6" t="n">
+      <c r="U6" s="0" t="n">
         <v>30</v>
       </c>
-      <c r="W6" t="n">
+      <c r="V6" s="0" t="n">
         <v>150</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" s="0" t="inlineStr">
         <is>
           <t>剑与魔法-难度3</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="X6" s="0" t="inlineStr">
         <is>
           <t>#C0CA33</t>
         </is>
@@ -1735,91 +1711,88 @@
       <c r="B7" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="0" t="inlineStr">
         <is>
           <t>1&amp;1</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="0" t="inlineStr">
         <is>
           <t>1&amp;1</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="0" t="inlineStr">
         <is>
           <t>1010010001&amp;1010010001</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="0" t="inlineStr">
         <is>
           <t>1010010001&amp;1010010001</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="0" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
+      <c r="J7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="inlineStr">
+      <c r="L7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" s="0" t="inlineStr">
         <is>
           <t>6-9</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N7" s="0" t="inlineStr">
         <is>
           <t>3-6</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="O7" s="0" t="inlineStr">
         <is>
           <t>7-10</t>
         </is>
       </c>
-      <c r="P7" t="n">
+      <c r="P7" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="Q7" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="R7" t="n">
+      <c r="R7" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="S7" t="n">
+      <c r="S7" s="0" t="n">
         <v>400</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T7" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="U7" t="n">
-        <v>10</v>
-      </c>
-      <c r="V7" t="n">
+      <c r="U7" s="0" t="n">
         <v>40</v>
       </c>
-      <c r="W7" t="n">
+      <c r="V7" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" s="0" t="inlineStr">
         <is>
           <t>剑与魔法-难度4</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="X7" s="0" t="inlineStr">
         <is>
           <t>#FBC02D</t>
         </is>
@@ -1832,91 +1805,88 @@
       <c r="B8" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="0" t="inlineStr">
         <is>
           <t>1&amp;1</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="0" t="inlineStr">
         <is>
           <t>1&amp;1</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="0" t="inlineStr">
         <is>
           <t>1010010001&amp;1010010001</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="0" t="inlineStr">
         <is>
           <t>1010010001&amp;1010010001</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="0" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
+      <c r="J8" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="inlineStr">
+      <c r="L8" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" s="0" t="inlineStr">
         <is>
           <t>7-10</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N8" s="0" t="inlineStr">
         <is>
           <t>2-6</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="O8" s="0" t="inlineStr">
         <is>
           <t>6-10</t>
         </is>
       </c>
-      <c r="P8" t="n">
+      <c r="P8" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="Q8" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="R8" t="n">
+      <c r="R8" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="S8" t="n">
+      <c r="S8" s="0" t="n">
         <v>500</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T8" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="U8" t="n">
-        <v>15</v>
-      </c>
-      <c r="V8" t="n">
+      <c r="U8" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="W8" t="n">
+      <c r="V8" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" s="0" t="inlineStr">
         <is>
           <t>剑与魔法-难度5</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="X8" s="0" t="inlineStr">
         <is>
           <t>#FB8C00</t>
         </is>
@@ -1929,91 +1899,88 @@
       <c r="B9" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="0" t="inlineStr">
         <is>
           <t>1&amp;1</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="0" t="inlineStr">
         <is>
           <t>1&amp;1</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="0" t="inlineStr">
         <is>
           <t>1010010001&amp;1010010001</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="0" t="inlineStr">
         <is>
           <t>1010010001&amp;1010010001</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="0" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
+      <c r="J9" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="inlineStr">
+      <c r="L9" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="0" t="inlineStr">
         <is>
           <t>8-11</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N9" s="0" t="inlineStr">
         <is>
           <t>1-6</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="O9" s="0" t="inlineStr">
         <is>
           <t>5-10</t>
         </is>
       </c>
-      <c r="P9" t="n">
+      <c r="P9" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="Q9" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="R9" t="n">
+      <c r="R9" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="S9" t="n">
+      <c r="S9" s="0" t="n">
         <v>600</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T9" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="U9" t="n">
-        <v>15</v>
-      </c>
-      <c r="V9" t="n">
+      <c r="U9" s="0" t="n">
         <v>60</v>
       </c>
-      <c r="W9" t="n">
+      <c r="V9" s="0" t="n">
         <v>300</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" s="0" t="inlineStr">
         <is>
           <t>剑与魔法-难度6</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="X9" s="0" t="inlineStr">
         <is>
           <t>#F4511E</t>
         </is>
@@ -2026,91 +1993,88 @@
       <c r="B10" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="0" t="inlineStr">
         <is>
           <t>1&amp;1</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="0" t="inlineStr">
         <is>
           <t>1&amp;1</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="0" t="inlineStr">
         <is>
           <t>1010010001&amp;1010010001</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="0" t="inlineStr">
         <is>
           <t>1010010001&amp;1010010001</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="0" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
+      <c r="J10" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="inlineStr">
+      <c r="L10" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="0" t="inlineStr">
         <is>
           <t>9-12</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N10" s="0" t="inlineStr">
         <is>
           <t>1-6</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="O10" s="0" t="inlineStr">
         <is>
           <t>4-10</t>
         </is>
       </c>
-      <c r="P10" t="n">
+      <c r="P10" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="Q10" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="R10" t="n">
+      <c r="R10" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="S10" t="n">
+      <c r="S10" s="0" t="n">
         <v>700</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T10" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="U10" t="n">
-        <v>20</v>
-      </c>
-      <c r="V10" t="n">
+      <c r="U10" s="0" t="n">
         <v>70</v>
       </c>
-      <c r="W10" t="n">
+      <c r="V10" s="0" t="n">
         <v>350</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" s="0" t="inlineStr">
         <is>
           <t>剑与魔法-难度7</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="X10" s="0" t="inlineStr">
         <is>
           <t>#E53935</t>
         </is>
@@ -2123,91 +2087,88 @@
       <c r="B11" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="0" t="inlineStr">
         <is>
           <t>1&amp;1</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="0" t="inlineStr">
         <is>
           <t>1&amp;1</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="0" t="inlineStr">
         <is>
           <t>1010010001&amp;1010010001</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="0" t="inlineStr">
         <is>
           <t>1010010001&amp;1010010001</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="0" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H11" t="n">
+      <c r="H11" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
+      <c r="J11" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="inlineStr">
+      <c r="L11" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="0" t="inlineStr">
         <is>
           <t>9-13</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N11" s="0" t="inlineStr">
         <is>
           <t>1-6</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="O11" s="0" t="inlineStr">
         <is>
           <t>3-10</t>
         </is>
       </c>
-      <c r="P11" t="n">
+      <c r="P11" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q11" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R11" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="S11" t="n">
+      <c r="S11" s="0" t="n">
         <v>800</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T11" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="U11" t="n">
-        <v>20</v>
-      </c>
-      <c r="V11" t="n">
+      <c r="U11" s="0" t="n">
         <v>80</v>
       </c>
-      <c r="W11" t="n">
+      <c r="V11" s="0" t="n">
         <v>400</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" s="0" t="inlineStr">
         <is>
           <t>剑与魔法-难度8</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="X11" s="0" t="inlineStr">
         <is>
           <t>#C2185B</t>
         </is>
@@ -2220,91 +2181,88 @@
       <c r="B12" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="0" t="inlineStr">
         <is>
           <t>1&amp;1</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="0" t="inlineStr">
         <is>
           <t>1&amp;1</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="0" t="inlineStr">
         <is>
           <t>1010010001&amp;1010010001</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="0" t="inlineStr">
         <is>
           <t>1010010001&amp;1010010001</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="0" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H12" t="n">
+      <c r="H12" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
+      <c r="J12" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="inlineStr">
+      <c r="L12" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="0" t="inlineStr">
         <is>
           <t>10-14</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="N12" s="0" t="inlineStr">
         <is>
           <t>1-6</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="O12" s="0" t="inlineStr">
         <is>
           <t>2-10</t>
         </is>
       </c>
-      <c r="P12" t="n">
+      <c r="P12" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="Q12" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="R12" t="n">
+      <c r="R12" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="S12" t="n">
+      <c r="S12" s="0" t="n">
         <v>900</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T12" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="U12" t="n">
-        <v>25</v>
-      </c>
-      <c r="V12" t="n">
+      <c r="U12" s="0" t="n">
         <v>90</v>
       </c>
-      <c r="W12" t="n">
+      <c r="V12" s="0" t="n">
         <v>450</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" s="0" t="inlineStr">
         <is>
           <t>剑与魔法-难度9</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="X12" s="0" t="inlineStr">
         <is>
           <t>#8E24AA</t>
         </is>
@@ -2317,91 +2275,88 @@
       <c r="B13" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="0" t="inlineStr">
         <is>
           <t>1&amp;1</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="0" t="inlineStr">
         <is>
           <t>1&amp;1</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="0" t="inlineStr">
         <is>
           <t>1010010001&amp;1010010001</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="0" t="inlineStr">
         <is>
           <t>1010010001&amp;1010010001</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="0" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H13" t="n">
+      <c r="H13" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
+      <c r="J13" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="inlineStr">
+      <c r="L13" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" s="0" t="inlineStr">
         <is>
           <t>10-15</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="N13" s="0" t="inlineStr">
         <is>
           <t>1-6</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="O13" s="0" t="inlineStr">
         <is>
           <t>1-10</t>
         </is>
       </c>
-      <c r="P13" t="n">
+      <c r="P13" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="Q13" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="R13" t="n">
+      <c r="R13" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="S13" t="n">
+      <c r="S13" s="0" t="n">
         <v>1000</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T13" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="U13" t="n">
-        <v>25</v>
-      </c>
-      <c r="V13" t="n">
+      <c r="U13" s="0" t="n">
         <v>100</v>
       </c>
-      <c r="W13" t="n">
+      <c r="V13" s="0" t="n">
         <v>500</v>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" s="0" t="inlineStr">
         <is>
           <t>剑与魔法-难度10</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="X13" s="0" t="inlineStr">
         <is>
           <t>#4A148C</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="FightTypeConquerInfo" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="103">
   <si>
     <t>id</t>
   </si>
@@ -35,6 +35,9 @@
     <t>world_id</t>
   </si>
   <si>
+    <t>level</t>
+  </si>
+  <si>
     <t>fight_scene_ids</t>
   </si>
   <si>
@@ -74,12 +77,6 @@
     <t>road_length</t>
   </si>
   <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>level_add</t>
-  </si>
-  <si>
     <t>drop_crystal</t>
   </si>
   <si>
@@ -104,12 +101,12 @@
     <t>long</t>
   </si>
   <si>
+    <t>int</t>
+  </si>
+  <si>
     <t>string</t>
   </si>
   <si>
-    <t>int</t>
-  </si>
-  <si>
     <t>float</t>
   </si>
   <si>
@@ -119,6 +116,9 @@
     <t>世界ID</t>
   </si>
   <si>
+    <t>难度</t>
+  </si>
+  <si>
     <t>战斗场景列表（用&amp;分割）</t>
   </si>
   <si>
@@ -146,7 +146,7 @@
     <t>每关增加敌人数量</t>
   </si>
   <si>
-    <t>普通敌人每关强度倍率(默认1,如1.1则每关HP/护甲/攻击力×1.1)</t>
+    <t>每关强度倍率(默认1,如1.1则每关HP/护甲/攻击力×1.1,含BOSS)</t>
   </si>
   <si>
     <t>关卡次数(单个数x或范围x-y)</t>
@@ -158,12 +158,6 @@
     <t>道路长度(单个数x或范围x-y)</t>
   </si>
   <si>
-    <t>难度</t>
-  </si>
-  <si>
-    <t>难度数值加成</t>
-  </si>
-  <si>
     <t>掉落魔晶</t>
   </si>
   <si>
@@ -185,9 +179,6 @@
     <t>背景色(由易到难)</t>
   </si>
   <si>
-    <t>99999</t>
-  </si>
-  <si>
     <t>1010010001</t>
   </si>
   <si>
@@ -206,70 +197,73 @@
     <t>5</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>剑与魔法-难度1</t>
+  </si>
+  <si>
+    <t>#2ECC71</t>
+  </si>
+  <si>
+    <t>1&amp;1</t>
+  </si>
+  <si>
+    <t>99999&amp;99999</t>
+  </si>
+  <si>
+    <t>1010010001&amp;1020010001</t>
+  </si>
+  <si>
+    <t>1010020001&amp;1020020001&amp;1020030001</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>9-10</t>
+  </si>
+  <si>
+    <t>剑与魔法-难度2</t>
+  </si>
+  <si>
+    <t>#82C91E</t>
+  </si>
+  <si>
+    <t>1010010001&amp;1010010001</t>
+  </si>
+  <si>
+    <t>6-8</t>
+  </si>
+  <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t>8-10</t>
+  </si>
+  <si>
+    <t>剑与魔法-难度3</t>
+  </si>
+  <si>
+    <t>#C0CA33</t>
+  </si>
+  <si>
+    <t>6-9</t>
+  </si>
+  <si>
+    <t>4-5</t>
+  </si>
+  <si>
+    <t>7-10</t>
+  </si>
+  <si>
+    <t>剑与魔法-难度4</t>
+  </si>
+  <si>
+    <t>#FBC02D</t>
+  </si>
+  <si>
     <t>5-6</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>剑与魔法-难度1</t>
-  </si>
-  <si>
-    <t>#2ECC71</t>
-  </si>
-  <si>
-    <t>1&amp;1</t>
-  </si>
-  <si>
-    <t>1010010001&amp;1010010001</t>
-  </si>
-  <si>
-    <t>5-7</t>
-  </si>
-  <si>
-    <t>3-4</t>
-  </si>
-  <si>
-    <t>9-10</t>
-  </si>
-  <si>
-    <t>剑与魔法-难度2</t>
-  </si>
-  <si>
-    <t>#82C91E</t>
-  </si>
-  <si>
-    <t>6-8</t>
-  </si>
-  <si>
-    <t>3-5</t>
-  </si>
-  <si>
-    <t>8-10</t>
-  </si>
-  <si>
-    <t>剑与魔法-难度3</t>
-  </si>
-  <si>
-    <t>#C0CA33</t>
-  </si>
-  <si>
-    <t>6-9</t>
-  </si>
-  <si>
-    <t>3-6</t>
-  </si>
-  <si>
-    <t>7-10</t>
-  </si>
-  <si>
-    <t>剑与魔法-难度4</t>
-  </si>
-  <si>
-    <t>#FBC02D</t>
-  </si>
-  <si>
-    <t>2-6</t>
   </si>
   <si>
     <t>6-10</t>
@@ -950,11 +944,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1303,16 +1301,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:X81"/>
+  <dimension ref="A1:W81"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="3" max="3" width="17.125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="36.5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="23.75" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18.375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="31.875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="18.25" style="1" customWidth="1"/>
-    <col min="9" max="16" width="16" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="36.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="23.75" style="1" customWidth="1"/>
+    <col min="7" max="7" width="18.375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="31.875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.25" style="1" customWidth="1"/>
+    <col min="10" max="16" width="16" style="1" customWidth="1"/>
     <col min="17" max="17" width="12.25" style="1" customWidth="1"/>
     <col min="18" max="19" width="12.875" style="1" customWidth="1"/>
     <col min="20" max="20" width="17.375" style="1" customWidth="1"/>
@@ -1322,7 +1321,7 @@
     <col min="24" max="24" width="25.125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:23">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1392,19 +1391,16 @@
       <c r="W1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" t="s">
+    </row>
+    <row r="2" spans="1:23">
+      <c r="A2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:24">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
         <v>24</v>
-      </c>
-      <c r="B2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" t="s">
-        <v>25</v>
       </c>
       <c r="D2" t="s">
         <v>25</v>
@@ -1419,22 +1415,22 @@
         <v>25</v>
       </c>
       <c r="H2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" t="s">
         <v>26</v>
-      </c>
-      <c r="I2" t="s">
-        <v>27</v>
-      </c>
-      <c r="J2" t="s">
-        <v>27</v>
       </c>
       <c r="K2" t="s">
         <v>26</v>
       </c>
       <c r="L2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="M2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N2" t="s">
         <v>25</v>
@@ -1443,108 +1439,102 @@
         <v>25</v>
       </c>
       <c r="P2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="R2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="S2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="T2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="U2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="V2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W2" t="s">
         <v>25</v>
       </c>
-      <c r="X2" t="s">
-        <v>25</v>
-      </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:23">
       <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s">
         <v>28</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>29</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>30</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>31</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>32</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>33</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>34</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>35</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>36</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>37</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>38</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>39</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>40</v>
       </c>
-      <c r="N3" t="s">
+      <c r="O3" t="s">
         <v>41</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>42</v>
       </c>
-      <c r="P3" t="s">
+      <c r="Q3" t="s">
         <v>43</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="R3" t="s">
         <v>44</v>
       </c>
-      <c r="R3" t="s">
+      <c r="S3" t="s">
         <v>45</v>
       </c>
-      <c r="S3" t="s">
+      <c r="T3" t="s">
         <v>46</v>
       </c>
-      <c r="T3" t="s">
+      <c r="U3" t="s">
         <v>47</v>
       </c>
-      <c r="U3" t="s">
+      <c r="V3" t="s">
         <v>48</v>
       </c>
-      <c r="V3" t="s">
+      <c r="W3" t="s">
         <v>49</v>
       </c>
-      <c r="W3" t="s">
-        <v>50</v>
-      </c>
-      <c r="X3" t="s">
-        <v>51</v>
-      </c>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:23">
       <c r="A4">
         <v>1000001</v>
       </c>
@@ -1554,734 +1544,704 @@
       <c r="C4">
         <v>1</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>99999</v>
+      </c>
+      <c r="F4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H4" t="s">
         <v>52</v>
       </c>
-      <c r="E4" t="s">
+      <c r="I4" t="s">
         <v>53</v>
       </c>
-      <c r="F4" t="s">
+      <c r="J4" t="s">
         <v>54</v>
       </c>
-      <c r="G4" t="s">
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4" t="s">
         <v>55</v>
       </c>
-      <c r="H4" t="s">
-        <v>56</v>
-      </c>
-      <c r="I4" t="s">
-        <v>57</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4" t="s">
-        <v>58</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4" t="s">
-        <v>59</v>
-      </c>
-      <c r="N4" t="s">
-        <v>60</v>
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>5</v>
       </c>
       <c r="O4" t="s">
         <v>56</v>
       </c>
-      <c r="P4">
-        <v>1</v>
+      <c r="P4" t="s">
+        <v>53</v>
       </c>
       <c r="Q4">
         <v>1</v>
       </c>
       <c r="R4">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="S4">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="T4">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="U4">
-        <v>10</v>
-      </c>
-      <c r="V4">
         <v>50</v>
       </c>
+      <c r="V4" t="s">
+        <v>57</v>
+      </c>
       <c r="W4" t="s">
-        <v>61</v>
-      </c>
-      <c r="X4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:23">
       <c r="A5">
         <v>1000002</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" t="s">
+        <v>61</v>
+      </c>
+      <c r="G5" t="s">
+        <v>62</v>
+      </c>
+      <c r="H5" t="s">
+        <v>56</v>
+      </c>
+      <c r="I5">
+        <v>20</v>
+      </c>
+      <c r="J5">
+        <v>60</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>10</v>
+      </c>
+      <c r="M5">
+        <v>1.5</v>
+      </c>
+      <c r="N5" t="s">
         <v>63</v>
       </c>
-      <c r="D5" t="s">
-        <v>63</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="O5">
+        <v>3</v>
+      </c>
+      <c r="P5" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F5" t="s">
-        <v>64</v>
-      </c>
-      <c r="G5" t="s">
-        <v>60</v>
-      </c>
-      <c r="H5">
-        <v>3</v>
-      </c>
-      <c r="I5">
-        <v>5</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5" t="s">
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5">
+        <v>200</v>
+      </c>
+      <c r="S5">
+        <v>1</v>
+      </c>
+      <c r="T5">
+        <v>20</v>
+      </c>
+      <c r="U5">
+        <v>100</v>
+      </c>
+      <c r="V5" t="s">
         <v>65</v>
       </c>
-      <c r="N5" t="s">
+      <c r="W5" t="s">
         <v>66</v>
       </c>
-      <c r="O5" t="s">
-        <v>67</v>
-      </c>
-      <c r="P5">
-        <v>2</v>
-      </c>
-      <c r="Q5">
-        <v>2</v>
-      </c>
-      <c r="R5">
-        <v>1</v>
-      </c>
-      <c r="S5">
-        <v>200</v>
-      </c>
-      <c r="T5">
-        <v>1</v>
-      </c>
-      <c r="U5">
-        <v>20</v>
-      </c>
-      <c r="V5">
-        <v>100</v>
-      </c>
-      <c r="W5" t="s">
-        <v>68</v>
-      </c>
-      <c r="X5" t="s">
-        <v>69</v>
-      </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:23">
       <c r="A6">
         <v>1000003</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
-      <c r="C6" t="s">
-        <v>63</v>
+      <c r="C6">
+        <v>3</v>
       </c>
       <c r="D6" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E6" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F6" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G6" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="H6">
         <v>3</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>15</v>
+      </c>
+      <c r="M6">
         <v>2</v>
       </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-      <c r="M6" t="s">
+      <c r="N6" t="s">
+        <v>68</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="P6" t="s">
         <v>70</v>
       </c>
-      <c r="N6" t="s">
+      <c r="Q6">
+        <v>2</v>
+      </c>
+      <c r="R6">
+        <v>300</v>
+      </c>
+      <c r="S6">
+        <v>2</v>
+      </c>
+      <c r="T6">
+        <v>30</v>
+      </c>
+      <c r="U6">
+        <v>150</v>
+      </c>
+      <c r="V6" t="s">
         <v>71</v>
       </c>
-      <c r="O6" t="s">
+      <c r="W6" t="s">
         <v>72</v>
       </c>
-      <c r="P6">
-        <v>3</v>
-      </c>
-      <c r="Q6">
-        <v>3</v>
-      </c>
-      <c r="R6">
-        <v>2</v>
-      </c>
-      <c r="S6">
-        <v>300</v>
-      </c>
-      <c r="T6">
-        <v>2</v>
-      </c>
-      <c r="U6">
-        <v>30</v>
-      </c>
-      <c r="V6">
-        <v>150</v>
-      </c>
-      <c r="W6" t="s">
-        <v>73</v>
-      </c>
-      <c r="X6" t="s">
-        <v>74</v>
-      </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:23">
       <c r="A7">
         <v>1000004</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
-      <c r="C7" t="s">
-        <v>63</v>
+      <c r="C7">
+        <v>4</v>
       </c>
       <c r="D7" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E7" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F7" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H7">
+        <v>4</v>
+      </c>
+      <c r="I7">
+        <v>40</v>
+      </c>
+      <c r="J7">
         <v>60</v>
       </c>
-      <c r="H7">
-        <v>3</v>
-      </c>
-      <c r="I7">
-        <v>5</v>
-      </c>
-      <c r="J7">
-        <v>1</v>
-      </c>
       <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
         <v>2</v>
       </c>
-      <c r="L7">
-        <v>1</v>
-      </c>
-      <c r="M7" t="s">
+      <c r="M7">
+        <v>2.5</v>
+      </c>
+      <c r="N7" t="s">
+        <v>73</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="P7" t="s">
         <v>75</v>
       </c>
-      <c r="N7" t="s">
+      <c r="Q7">
+        <v>2</v>
+      </c>
+      <c r="R7">
+        <v>400</v>
+      </c>
+      <c r="S7">
+        <v>2</v>
+      </c>
+      <c r="T7">
+        <v>40</v>
+      </c>
+      <c r="U7">
+        <v>200</v>
+      </c>
+      <c r="V7" t="s">
         <v>76</v>
       </c>
-      <c r="O7" t="s">
+      <c r="W7" t="s">
         <v>77</v>
       </c>
-      <c r="P7">
-        <v>4</v>
-      </c>
-      <c r="Q7">
-        <v>4</v>
-      </c>
-      <c r="R7">
-        <v>2</v>
-      </c>
-      <c r="S7">
-        <v>400</v>
-      </c>
-      <c r="T7">
-        <v>2</v>
-      </c>
-      <c r="U7">
-        <v>40</v>
-      </c>
-      <c r="V7">
-        <v>200</v>
-      </c>
-      <c r="W7" t="s">
-        <v>78</v>
-      </c>
-      <c r="X7" t="s">
-        <v>79</v>
-      </c>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:23">
       <c r="A8">
         <v>1000005</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
-      <c r="C8" t="s">
-        <v>63</v>
+      <c r="C8">
+        <v>5</v>
       </c>
       <c r="D8" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E8" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H8">
+        <v>5</v>
+      </c>
+      <c r="I8">
+        <v>50</v>
+      </c>
+      <c r="J8">
         <v>60</v>
       </c>
-      <c r="H8">
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>2</v>
+      </c>
+      <c r="M8">
         <v>3</v>
       </c>
-      <c r="I8">
-        <v>5</v>
-      </c>
-      <c r="J8">
-        <v>1</v>
-      </c>
-      <c r="K8">
-        <v>2</v>
-      </c>
-      <c r="L8">
-        <v>1</v>
-      </c>
-      <c r="M8" t="s">
-        <v>77</v>
-      </c>
       <c r="N8" t="s">
+        <v>75</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="P8" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q8">
+        <v>3</v>
+      </c>
+      <c r="R8">
+        <v>500</v>
+      </c>
+      <c r="S8">
+        <v>3</v>
+      </c>
+      <c r="T8">
+        <v>50</v>
+      </c>
+      <c r="U8">
+        <v>250</v>
+      </c>
+      <c r="V8" t="s">
         <v>80</v>
       </c>
-      <c r="O8" t="s">
+      <c r="W8" t="s">
         <v>81</v>
       </c>
-      <c r="P8">
-        <v>5</v>
-      </c>
-      <c r="Q8">
-        <v>5</v>
-      </c>
-      <c r="R8">
-        <v>3</v>
-      </c>
-      <c r="S8">
-        <v>500</v>
-      </c>
-      <c r="T8">
-        <v>3</v>
-      </c>
-      <c r="U8">
-        <v>50</v>
-      </c>
-      <c r="V8">
-        <v>250</v>
-      </c>
-      <c r="W8" t="s">
-        <v>82</v>
-      </c>
-      <c r="X8" t="s">
-        <v>83</v>
-      </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:23">
       <c r="A9">
         <v>1000006</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
-      <c r="C9" t="s">
-        <v>63</v>
+      <c r="C9">
+        <v>6</v>
       </c>
       <c r="D9" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E9" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G9" t="s">
+        <v>67</v>
+      </c>
+      <c r="H9">
+        <v>6</v>
+      </c>
+      <c r="I9">
         <v>60</v>
       </c>
-      <c r="H9">
+      <c r="J9">
+        <v>60</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>2</v>
+      </c>
+      <c r="M9">
+        <v>3.5</v>
+      </c>
+      <c r="N9" t="s">
+        <v>82</v>
+      </c>
+      <c r="O9" t="s">
+        <v>83</v>
+      </c>
+      <c r="P9" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q9">
         <v>3</v>
       </c>
-      <c r="I9">
-        <v>5</v>
-      </c>
-      <c r="J9">
-        <v>1</v>
-      </c>
-      <c r="K9">
-        <v>2</v>
-      </c>
-      <c r="L9">
-        <v>1</v>
-      </c>
-      <c r="M9" t="s">
-        <v>84</v>
-      </c>
-      <c r="N9" t="s">
+      <c r="R9">
+        <v>600</v>
+      </c>
+      <c r="S9">
+        <v>3</v>
+      </c>
+      <c r="T9">
+        <v>60</v>
+      </c>
+      <c r="U9">
+        <v>300</v>
+      </c>
+      <c r="V9" t="s">
         <v>85</v>
       </c>
-      <c r="O9" t="s">
+      <c r="W9" t="s">
         <v>86</v>
       </c>
-      <c r="P9">
-        <v>6</v>
-      </c>
-      <c r="Q9">
-        <v>6</v>
-      </c>
-      <c r="R9">
-        <v>3</v>
-      </c>
-      <c r="S9">
-        <v>600</v>
-      </c>
-      <c r="T9">
-        <v>3</v>
-      </c>
-      <c r="U9">
-        <v>60</v>
-      </c>
-      <c r="V9">
-        <v>300</v>
-      </c>
-      <c r="W9" t="s">
-        <v>87</v>
-      </c>
-      <c r="X9" t="s">
-        <v>88</v>
-      </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:23">
       <c r="A10">
         <v>1000007</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
-      <c r="C10" t="s">
-        <v>63</v>
+      <c r="C10">
+        <v>7</v>
       </c>
       <c r="D10" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E10" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F10" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G10" t="s">
+        <v>67</v>
+      </c>
+      <c r="H10">
+        <v>7</v>
+      </c>
+      <c r="I10">
+        <v>70</v>
+      </c>
+      <c r="J10">
         <v>60</v>
       </c>
-      <c r="H10">
-        <v>3</v>
-      </c>
-      <c r="I10">
-        <v>5</v>
-      </c>
-      <c r="J10">
-        <v>1</v>
-      </c>
       <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
         <v>2</v>
       </c>
-      <c r="L10">
-        <v>1</v>
-      </c>
-      <c r="M10" t="s">
+      <c r="M10">
+        <v>4</v>
+      </c>
+      <c r="N10" t="s">
+        <v>87</v>
+      </c>
+      <c r="O10" t="s">
+        <v>83</v>
+      </c>
+      <c r="P10" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q10">
+        <v>4</v>
+      </c>
+      <c r="R10">
+        <v>700</v>
+      </c>
+      <c r="S10">
+        <v>4</v>
+      </c>
+      <c r="T10">
+        <v>70</v>
+      </c>
+      <c r="U10">
+        <v>350</v>
+      </c>
+      <c r="V10" t="s">
         <v>89</v>
       </c>
-      <c r="N10" t="s">
-        <v>85</v>
-      </c>
-      <c r="O10" t="s">
+      <c r="W10" t="s">
         <v>90</v>
       </c>
-      <c r="P10">
-        <v>7</v>
-      </c>
-      <c r="Q10">
-        <v>7</v>
-      </c>
-      <c r="R10">
-        <v>4</v>
-      </c>
-      <c r="S10">
-        <v>700</v>
-      </c>
-      <c r="T10">
-        <v>4</v>
-      </c>
-      <c r="U10">
-        <v>70</v>
-      </c>
-      <c r="V10">
-        <v>350</v>
-      </c>
-      <c r="W10" t="s">
-        <v>91</v>
-      </c>
-      <c r="X10" t="s">
-        <v>92</v>
-      </c>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:23">
       <c r="A11">
         <v>1000008</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
-      <c r="C11" t="s">
-        <v>63</v>
+      <c r="C11">
+        <v>8</v>
       </c>
       <c r="D11" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E11" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F11" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G11" t="s">
+        <v>67</v>
+      </c>
+      <c r="H11">
+        <v>8</v>
+      </c>
+      <c r="I11">
+        <v>80</v>
+      </c>
+      <c r="J11">
         <v>60</v>
       </c>
-      <c r="H11">
-        <v>3</v>
-      </c>
-      <c r="I11">
-        <v>5</v>
-      </c>
-      <c r="J11">
-        <v>1</v>
-      </c>
       <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
         <v>2</v>
       </c>
-      <c r="L11">
-        <v>1</v>
-      </c>
-      <c r="M11" t="s">
+      <c r="M11">
+        <v>4.5</v>
+      </c>
+      <c r="N11" t="s">
+        <v>91</v>
+      </c>
+      <c r="O11" t="s">
+        <v>83</v>
+      </c>
+      <c r="P11" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q11">
+        <v>4</v>
+      </c>
+      <c r="R11">
+        <v>800</v>
+      </c>
+      <c r="S11">
+        <v>4</v>
+      </c>
+      <c r="T11">
+        <v>80</v>
+      </c>
+      <c r="U11">
+        <v>400</v>
+      </c>
+      <c r="V11" t="s">
         <v>93</v>
       </c>
-      <c r="N11" t="s">
-        <v>85</v>
-      </c>
-      <c r="O11" t="s">
+      <c r="W11" t="s">
         <v>94</v>
       </c>
-      <c r="P11">
-        <v>8</v>
-      </c>
-      <c r="Q11">
-        <v>8</v>
-      </c>
-      <c r="R11">
-        <v>4</v>
-      </c>
-      <c r="S11">
-        <v>800</v>
-      </c>
-      <c r="T11">
-        <v>4</v>
-      </c>
-      <c r="U11">
-        <v>80</v>
-      </c>
-      <c r="V11">
-        <v>400</v>
-      </c>
-      <c r="W11" t="s">
-        <v>95</v>
-      </c>
-      <c r="X11" t="s">
-        <v>96</v>
-      </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:23">
       <c r="A12">
         <v>1000009</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
-      <c r="C12" t="s">
-        <v>63</v>
+      <c r="C12">
+        <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E12" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F12" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G12" t="s">
+        <v>67</v>
+      </c>
+      <c r="H12">
+        <v>9</v>
+      </c>
+      <c r="I12">
+        <v>90</v>
+      </c>
+      <c r="J12">
         <v>60</v>
       </c>
-      <c r="H12">
-        <v>3</v>
-      </c>
-      <c r="I12">
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>2</v>
+      </c>
+      <c r="M12">
         <v>5</v>
       </c>
-      <c r="J12">
-        <v>1</v>
-      </c>
-      <c r="K12">
-        <v>2</v>
-      </c>
-      <c r="L12">
-        <v>1</v>
-      </c>
-      <c r="M12" t="s">
+      <c r="N12" t="s">
+        <v>95</v>
+      </c>
+      <c r="O12" t="s">
+        <v>83</v>
+      </c>
+      <c r="P12" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q12">
+        <v>5</v>
+      </c>
+      <c r="R12">
+        <v>900</v>
+      </c>
+      <c r="S12">
+        <v>5</v>
+      </c>
+      <c r="T12">
+        <v>90</v>
+      </c>
+      <c r="U12">
+        <v>450</v>
+      </c>
+      <c r="V12" t="s">
         <v>97</v>
       </c>
-      <c r="N12" t="s">
-        <v>85</v>
-      </c>
-      <c r="O12" t="s">
+      <c r="W12" t="s">
         <v>98</v>
       </c>
-      <c r="P12">
-        <v>9</v>
-      </c>
-      <c r="Q12">
-        <v>9</v>
-      </c>
-      <c r="R12">
-        <v>5</v>
-      </c>
-      <c r="S12">
-        <v>900</v>
-      </c>
-      <c r="T12">
-        <v>5</v>
-      </c>
-      <c r="U12">
-        <v>90</v>
-      </c>
-      <c r="V12">
-        <v>450</v>
-      </c>
-      <c r="W12" t="s">
-        <v>99</v>
-      </c>
-      <c r="X12" t="s">
-        <v>100</v>
-      </c>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:23">
       <c r="A13">
         <v>1000010</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
-      <c r="C13" t="s">
-        <v>63</v>
+      <c r="C13">
+        <v>10</v>
       </c>
       <c r="D13" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E13" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F13" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G13" t="s">
+        <v>67</v>
+      </c>
+      <c r="H13">
+        <v>10</v>
+      </c>
+      <c r="I13">
+        <v>100</v>
+      </c>
+      <c r="J13">
         <v>60</v>
       </c>
-      <c r="H13">
-        <v>3</v>
-      </c>
-      <c r="I13">
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>2</v>
+      </c>
+      <c r="M13">
+        <v>5.5</v>
+      </c>
+      <c r="N13" t="s">
+        <v>99</v>
+      </c>
+      <c r="O13" t="s">
+        <v>83</v>
+      </c>
+      <c r="P13" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q13">
         <v>5</v>
       </c>
-      <c r="J13">
-        <v>1</v>
-      </c>
-      <c r="K13">
-        <v>2</v>
-      </c>
-      <c r="L13">
-        <v>1</v>
-      </c>
-      <c r="M13" t="s">
+      <c r="R13">
+        <v>1000</v>
+      </c>
+      <c r="S13">
+        <v>5</v>
+      </c>
+      <c r="T13">
+        <v>100</v>
+      </c>
+      <c r="U13">
+        <v>500</v>
+      </c>
+      <c r="V13" t="s">
         <v>101</v>
       </c>
-      <c r="N13" t="s">
-        <v>85</v>
-      </c>
-      <c r="O13" t="s">
+      <c r="W13" t="s">
         <v>102</v>
-      </c>
-      <c r="P13">
-        <v>10</v>
-      </c>
-      <c r="Q13">
-        <v>10</v>
-      </c>
-      <c r="R13">
-        <v>5</v>
-      </c>
-      <c r="S13">
-        <v>1000</v>
-      </c>
-      <c r="T13">
-        <v>5</v>
-      </c>
-      <c r="U13">
-        <v>100</v>
-      </c>
-      <c r="V13">
-        <v>500</v>
-      </c>
-      <c r="W13" t="s">
-        <v>103</v>
-      </c>
-      <c r="X13" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="FightTypeConquerInfo" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="104">
   <si>
     <t>id</t>
   </si>
@@ -203,25 +203,22 @@
     <t>60</t>
   </si>
   <si>
-    <t>5</t>
+    <t>剑与魔法-难度1</t>
+  </si>
+  <si>
+    <t>#2ECC71</t>
+  </si>
+  <si>
+    <t>1&amp;2</t>
+  </si>
+  <si>
+    <t>1010010001&amp;1020010001</t>
+  </si>
+  <si>
+    <t>1010020001&amp;1020020001&amp;1020030001</t>
   </si>
   <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>剑与魔法-难度1</t>
-  </si>
-  <si>
-    <t>#2ECC71</t>
-  </si>
-  <si>
-    <t>1&amp;2</t>
-  </si>
-  <si>
-    <t>1010010001&amp;1020010001</t>
-  </si>
-  <si>
-    <t>1010020001&amp;1020020001&amp;1020030001</t>
   </si>
   <si>
     <t>6</t>
@@ -1319,7 +1316,8 @@
     <col min="9" max="9" width="18.25" style="1" customWidth="1"/>
     <col min="10" max="16" width="16" style="1" customWidth="1"/>
     <col min="17" max="17" width="12.25" style="1" customWidth="1"/>
-    <col min="18" max="19" width="12.875" style="1" customWidth="1"/>
+    <col min="18" max="18" width="12.875" style="1" customWidth="1"/>
+    <col min="19" max="19" width="27.125" style="1" customWidth="1"/>
     <col min="20" max="20" width="17.375" style="1" customWidth="1"/>
     <col min="21" max="21" width="36.875" style="1" customWidth="1"/>
     <col min="22" max="22" width="29.375" style="1" customWidth="1"/>
@@ -1583,8 +1581,8 @@
       <c r="K4" s="1">
         <v>1</v>
       </c>
-      <c r="L4" s="1" t="s">
-        <v>58</v>
+      <c r="L4" s="1">
+        <v>5</v>
       </c>
       <c r="M4" s="1">
         <v>1</v>
@@ -1592,11 +1590,11 @@
       <c r="N4" s="1">
         <v>5</v>
       </c>
-      <c r="O4" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>56</v>
+      <c r="O4" s="1">
+        <v>2</v>
+      </c>
+      <c r="P4" s="1">
+        <v>10</v>
       </c>
       <c r="Q4" s="1">
         <v>1</v>
@@ -1617,10 +1615,10 @@
         <v>1</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:24">
@@ -1634,19 +1632,19 @@
         <v>2</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F5" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>59</v>
       </c>
       <c r="I5" s="1">
         <v>20</v>
@@ -1664,16 +1662,16 @@
         <v>1.5</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O5" s="1">
         <v>3</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q5" s="1" t="s">
-        <v>59</v>
+        <v>65</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>2</v>
       </c>
       <c r="R5" s="1">
         <v>200</v>
@@ -1691,10 +1689,10 @@
         <v>2</v>
       </c>
       <c r="W5" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="X5" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="X5" s="1" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:24">
@@ -1708,16 +1706,16 @@
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H6" s="1">
         <v>3</v>
@@ -1738,13 +1736,13 @@
         <v>2</v>
       </c>
       <c r="N6" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="O6" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="O6" s="3" t="s">
+      <c r="P6" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="Q6" s="1">
         <v>3</v>
@@ -1765,10 +1763,10 @@
         <v>3</v>
       </c>
       <c r="W6" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="X6" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="X6" s="1" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:24">
@@ -1782,16 +1780,16 @@
         <v>4</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H7" s="1">
         <v>4</v>
@@ -1812,13 +1810,13 @@
         <v>2.5</v>
       </c>
       <c r="N7" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="O7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="O7" s="3" t="s">
+      <c r="P7" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="P7" s="1" t="s">
-        <v>77</v>
       </c>
       <c r="Q7" s="1">
         <v>4</v>
@@ -1839,10 +1837,10 @@
         <v>4</v>
       </c>
       <c r="W7" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="X7" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="X7" s="1" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:24">
@@ -1856,16 +1854,16 @@
         <v>5</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H8" s="1">
         <v>5</v>
@@ -1886,13 +1884,13 @@
         <v>3</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O8" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="P8" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="P8" s="1" t="s">
-        <v>81</v>
       </c>
       <c r="Q8" s="1">
         <v>5</v>
@@ -1901,7 +1899,7 @@
         <v>500</v>
       </c>
       <c r="S8" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T8" s="1">
         <v>50</v>
@@ -1913,10 +1911,10 @@
         <v>5</v>
       </c>
       <c r="W8" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="X8" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="X8" s="1" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:24">
@@ -1930,16 +1928,16 @@
         <v>6</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H9" s="1">
         <v>6</v>
@@ -1960,13 +1958,13 @@
         <v>3.5</v>
       </c>
       <c r="N9" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="O9" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="O9" s="1" t="s">
+      <c r="P9" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="P9" s="1" t="s">
-        <v>86</v>
       </c>
       <c r="Q9" s="1">
         <v>6</v>
@@ -1987,10 +1985,10 @@
         <v>6</v>
       </c>
       <c r="W9" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="X9" s="1" t="s">
         <v>87</v>
-      </c>
-      <c r="X9" s="1" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:24">
@@ -2004,16 +2002,16 @@
         <v>7</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H10" s="1">
         <v>7</v>
@@ -2034,13 +2032,13 @@
         <v>4</v>
       </c>
       <c r="N10" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="P10" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="O10" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="P10" s="1" t="s">
-        <v>90</v>
       </c>
       <c r="Q10" s="1">
         <v>7</v>
@@ -2049,7 +2047,7 @@
         <v>700</v>
       </c>
       <c r="S10" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T10" s="1">
         <v>70</v>
@@ -2061,10 +2059,10 @@
         <v>7</v>
       </c>
       <c r="W10" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="X10" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="X10" s="1" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:24">
@@ -2078,16 +2076,16 @@
         <v>8</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H11" s="1">
         <v>8</v>
@@ -2108,13 +2106,13 @@
         <v>4.5</v>
       </c>
       <c r="N11" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="P11" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="O11" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="P11" s="1" t="s">
-        <v>94</v>
       </c>
       <c r="Q11" s="1">
         <v>8</v>
@@ -2123,7 +2121,7 @@
         <v>800</v>
       </c>
       <c r="S11" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T11" s="1">
         <v>80</v>
@@ -2135,10 +2133,10 @@
         <v>8</v>
       </c>
       <c r="W11" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="X11" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="X11" s="1" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:24">
@@ -2152,16 +2150,16 @@
         <v>9</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H12" s="1">
         <v>9</v>
@@ -2182,13 +2180,13 @@
         <v>5</v>
       </c>
       <c r="N12" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="P12" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="O12" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="P12" s="1" t="s">
-        <v>98</v>
       </c>
       <c r="Q12" s="1">
         <v>9</v>
@@ -2197,7 +2195,7 @@
         <v>900</v>
       </c>
       <c r="S12" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T12" s="1">
         <v>90</v>
@@ -2209,10 +2207,10 @@
         <v>9</v>
       </c>
       <c r="W12" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="X12" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="X12" s="1" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:24">
@@ -2226,16 +2224,16 @@
         <v>10</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H13" s="1">
         <v>10</v>
@@ -2256,13 +2254,13 @@
         <v>5.5</v>
       </c>
       <c r="N13" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="P13" s="1" t="s">
         <v>101</v>
-      </c>
-      <c r="O13" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="P13" s="1" t="s">
-        <v>102</v>
       </c>
       <c r="Q13" s="1">
         <v>10</v>
@@ -2271,7 +2269,7 @@
         <v>1000</v>
       </c>
       <c r="S13" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T13" s="1">
         <v>100</v>
@@ -2283,10 +2281,10 @@
         <v>10</v>
       </c>
       <c r="W13" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="X13" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="X13" s="1" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" ht="15" customHeight="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="FightTypeConquerInfo" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="107">
   <si>
     <t>id</t>
   </si>
@@ -233,22 +233,31 @@
     <t>#82C91E</t>
   </si>
   <si>
+    <t>1010010001&amp;1020010001&amp;1030010001&amp;1030020001</t>
+  </si>
+  <si>
+    <t>1020020001&amp;1020030001&amp;1031010001&amp;1031020001</t>
+  </si>
+  <si>
+    <t>6-7</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>8-10</t>
+  </si>
+  <si>
+    <t>300</t>
+  </si>
+  <si>
+    <t>剑与魔法-难度3</t>
+  </si>
+  <si>
+    <t>#C0CA33</t>
+  </si>
+  <si>
     <t>1010010001&amp;1010010001</t>
-  </si>
-  <si>
-    <t>6-8</t>
-  </si>
-  <si>
-    <t>3-4</t>
-  </si>
-  <si>
-    <t>8-10</t>
-  </si>
-  <si>
-    <t>剑与魔法-难度3</t>
-  </si>
-  <si>
-    <t>#C0CA33</t>
   </si>
   <si>
     <t>6-9</t>
@@ -356,7 +365,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -364,7 +372,6 @@
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -372,14 +379,12 @@
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -387,7 +392,6 @@
       <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -395,7 +399,6 @@
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -403,7 +406,6 @@
       <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -411,7 +413,6 @@
       <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -419,14 +420,12 @@
       <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -434,7 +433,6 @@
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -442,7 +440,6 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -450,14 +447,12 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -465,35 +460,30 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -947,13 +937,163 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+  <cellXfs count="54">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="2" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="3" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="4" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="5" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="7" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" xfId="8" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="9" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="4" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="10" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="11" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="6" applyFont="1" fillId="0" applyFill="1" borderId="2" applyBorder="1" xfId="12" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="7" applyFont="1" fillId="0" applyFill="1" borderId="2" applyBorder="1" xfId="13" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="8" applyFont="1" fillId="0" applyFill="1" borderId="3" applyBorder="1" xfId="14" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="8" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="15" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="9" applyFont="1" fillId="3" applyFill="1" borderId="4" applyBorder="1" xfId="16" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="10" applyFont="1" fillId="4" applyFill="1" borderId="5" applyBorder="1" xfId="17" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="11" applyFont="1" fillId="4" applyFill="1" borderId="4" applyBorder="1" xfId="18" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="12" applyFont="1" fillId="5" applyFill="1" borderId="6" applyBorder="1" xfId="19" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="13" applyFont="1" fillId="0" applyFill="1" borderId="7" applyBorder="1" xfId="20" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="14" applyFont="1" fillId="0" applyFill="1" borderId="8" applyBorder="1" xfId="21" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="15" applyFont="1" fillId="6" applyFill="1" borderId="0" applyBorder="1" xfId="22" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="16" applyFont="1" fillId="7" applyFill="1" borderId="0" applyBorder="1" xfId="23" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="17" applyFont="1" fillId="8" applyFill="1" borderId="0" applyBorder="1" xfId="24" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="9" applyFill="1" borderId="0" applyBorder="1" xfId="25" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="1" xfId="26" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="11" applyFill="1" borderId="0" applyBorder="1" xfId="27" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="12" applyFill="1" borderId="0" applyBorder="1" xfId="28" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="13" applyFill="1" borderId="0" applyBorder="1" xfId="29" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="14" applyFill="1" borderId="0" applyBorder="1" xfId="30" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="15" applyFill="1" borderId="0" applyBorder="1" xfId="31" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="16" applyFill="1" borderId="0" applyBorder="1" xfId="32" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="17" applyFill="1" borderId="0" applyBorder="1" xfId="33" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="18" applyFill="1" borderId="0" applyBorder="1" xfId="34" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="19" applyFill="1" borderId="0" applyBorder="1" xfId="35" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="20" applyFill="1" borderId="0" applyBorder="1" xfId="36" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="21" applyFill="1" borderId="0" applyBorder="1" xfId="37" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="22" applyFill="1" borderId="0" applyBorder="1" xfId="38" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="23" applyFill="1" borderId="0" applyBorder="1" xfId="39" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="24" applyFill="1" borderId="0" applyBorder="1" xfId="40" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="25" applyFill="1" borderId="0" applyBorder="1" xfId="41" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="26" applyFill="1" borderId="0" applyBorder="1" xfId="42" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="27" applyFill="1" borderId="0" applyBorder="1" xfId="43" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="28" applyFill="1" borderId="0" applyBorder="1" xfId="44" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="29" applyFill="1" borderId="0" applyBorder="1" xfId="45" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="30" applyFill="1" borderId="0" applyBorder="1" xfId="46" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="31" applyFill="1" borderId="0" applyBorder="1" xfId="47" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="32" applyFill="1" borderId="0" applyBorder="1" xfId="48" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="49" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="49" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1304,1009 +1444,1009 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:X81"/>
+  <dimension ref="A1:X13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="3" max="3" width="16" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="36.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="23.75" style="1" customWidth="1"/>
-    <col min="7" max="7" width="18.375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="31.875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="18.25" style="1" customWidth="1"/>
-    <col min="10" max="16" width="16" style="1" customWidth="1"/>
-    <col min="17" max="17" width="12.25" style="1" customWidth="1"/>
-    <col min="18" max="18" width="12.875" style="1" customWidth="1"/>
-    <col min="19" max="19" width="27.125" style="1" customWidth="1"/>
-    <col min="20" max="20" width="17.375" style="1" customWidth="1"/>
-    <col min="21" max="21" width="36.875" style="1" customWidth="1"/>
-    <col min="22" max="22" width="29.375" style="1" customWidth="1"/>
-    <col min="23" max="23" width="42.875" style="1" customWidth="1"/>
-    <col min="24" max="24" width="25.125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1" style="51"/>
+    <col min="4" max="4" width="17.125" customWidth="1" style="51"/>
+    <col min="5" max="5" width="36.5" customWidth="1" style="51"/>
+    <col min="6" max="6" width="23.75" customWidth="1" style="51"/>
+    <col min="7" max="7" width="18.375" customWidth="1" style="51"/>
+    <col min="8" max="8" width="31.875" customWidth="1" style="51"/>
+    <col min="9" max="9" width="18.25" customWidth="1" style="51"/>
+    <col min="10" max="16" width="16" customWidth="1" style="51"/>
+    <col min="17" max="17" width="12.25" customWidth="1" style="51"/>
+    <col min="18" max="18" width="12.875" customWidth="1" style="51"/>
+    <col min="19" max="19" width="27.125" customWidth="1" style="51"/>
+    <col min="20" max="20" width="17.375" customWidth="1" style="51"/>
+    <col min="21" max="21" width="36.875" customWidth="1" style="51"/>
+    <col min="22" max="22" width="29.375" customWidth="1" style="51"/>
+    <col min="23" max="23" width="42.875" customWidth="1" style="51"/>
+    <col min="24" max="24" width="25.125" customWidth="1" style="51"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="51" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="51" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" s="51" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
-      <c r="A2" t="s">
+    <row r="2">
+      <c r="A2" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="N2" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="O2" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="P2" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="Q2" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="R2" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="S2" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="T2" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="U2" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="V2" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="W2" s="1" t="s">
+      <c r="W2" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="X2" s="1" t="s">
+      <c r="X2" s="51" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
-      <c r="A3" t="s">
+    <row r="3">
+      <c r="A3" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="51" t="s">
         <v>37</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="L3" s="51" t="s">
         <v>39</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="M3" s="51" t="s">
         <v>40</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="N3" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="O3" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="P3" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="Q3" s="1" t="s">
+      <c r="Q3" s="51" t="s">
         <v>44</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="R3" s="51" t="s">
         <v>45</v>
       </c>
-      <c r="S3" s="1" t="s">
+      <c r="S3" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="T3" s="1" t="s">
+      <c r="T3" s="51" t="s">
         <v>47</v>
       </c>
-      <c r="U3" s="1" t="s">
+      <c r="U3" s="51" t="s">
         <v>48</v>
       </c>
-      <c r="V3" s="1" t="s">
+      <c r="V3" s="51" t="s">
         <v>49</v>
       </c>
-      <c r="W3" s="1" t="s">
+      <c r="W3" s="51" t="s">
         <v>50</v>
       </c>
-      <c r="X3" s="1" t="s">
+      <c r="X3" s="51" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:24">
-      <c r="A4">
+    <row r="4">
+      <c r="A4" s="50">
         <v>1000001</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1">
-        <v>1</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="B4" s="50">
+        <v>1</v>
+      </c>
+      <c r="C4" s="51">
+        <v>1</v>
+      </c>
+      <c r="D4" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="51" t="s">
         <v>53</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="51" t="s">
         <v>54</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" s="51" t="s">
         <v>56</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="J4" s="51" t="s">
         <v>57</v>
       </c>
-      <c r="K4" s="1">
-        <v>1</v>
-      </c>
-      <c r="L4" s="1">
+      <c r="K4" s="51">
+        <v>1</v>
+      </c>
+      <c r="L4" s="51">
         <v>5</v>
       </c>
-      <c r="M4" s="1">
-        <v>1</v>
-      </c>
-      <c r="N4" s="1">
+      <c r="M4" s="51">
+        <v>1</v>
+      </c>
+      <c r="N4" s="51">
         <v>5</v>
       </c>
-      <c r="O4" s="1">
+      <c r="O4" s="51">
         <v>2</v>
       </c>
-      <c r="P4" s="1">
+      <c r="P4" s="51">
         <v>10</v>
       </c>
-      <c r="Q4" s="1">
-        <v>1</v>
-      </c>
-      <c r="R4" s="1">
+      <c r="Q4" s="51">
+        <v>1</v>
+      </c>
+      <c r="R4" s="51">
         <v>100</v>
       </c>
-      <c r="S4" s="1">
-        <v>1</v>
-      </c>
-      <c r="T4" s="1">
+      <c r="S4" s="51">
+        <v>1</v>
+      </c>
+      <c r="T4" s="51">
         <v>10</v>
       </c>
-      <c r="U4" s="1">
+      <c r="U4" s="51">
         <v>50</v>
       </c>
-      <c r="V4" s="1">
-        <v>1</v>
-      </c>
-      <c r="W4" s="1" t="s">
+      <c r="V4" s="51">
+        <v>1</v>
+      </c>
+      <c r="W4" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="X4" s="1" t="s">
+      <c r="X4" s="51" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:24">
-      <c r="A5">
+    <row r="5">
+      <c r="A5" s="50">
         <v>1000002</v>
       </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5" s="1">
+      <c r="B5" s="50">
+        <v>1</v>
+      </c>
+      <c r="C5" s="51">
         <v>2</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="51" t="s">
         <v>60</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="51" t="s">
         <v>53</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="51" t="s">
         <v>61</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="I5" s="1">
+      <c r="I5" s="51">
         <v>20</v>
       </c>
-      <c r="J5" s="1">
+      <c r="J5" s="51">
         <v>60</v>
       </c>
-      <c r="K5" s="1">
-        <v>1</v>
-      </c>
-      <c r="L5" s="1">
+      <c r="K5" s="51">
+        <v>1</v>
+      </c>
+      <c r="L5" s="51">
         <v>10</v>
       </c>
-      <c r="M5" s="1">
+      <c r="M5" s="51">
         <v>1.5</v>
       </c>
-      <c r="N5" s="1" t="s">
+      <c r="N5" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="O5" s="1">
+      <c r="O5" s="51">
         <v>3</v>
       </c>
-      <c r="P5" s="2" t="s">
+      <c r="P5" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="Q5" s="1">
+      <c r="Q5" s="51">
         <v>2</v>
       </c>
-      <c r="R5" s="1">
+      <c r="R5" s="51">
         <v>200</v>
       </c>
-      <c r="S5" s="1">
-        <v>1</v>
-      </c>
-      <c r="T5" s="1">
+      <c r="S5" s="51">
+        <v>1</v>
+      </c>
+      <c r="T5" s="51">
         <v>20</v>
       </c>
-      <c r="U5" s="1">
+      <c r="U5" s="51">
         <v>100</v>
       </c>
-      <c r="V5" s="1">
+      <c r="V5" s="51">
         <v>2</v>
       </c>
-      <c r="W5" s="1" t="s">
+      <c r="W5" s="51" t="s">
         <v>66</v>
       </c>
-      <c r="X5" s="1" t="s">
+      <c r="X5" s="51" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="6" spans="1:24">
-      <c r="A6">
+    <row r="6">
+      <c r="A6" s="50">
         <v>1000003</v>
       </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6" s="1">
+      <c r="B6" s="50">
+        <v>1</v>
+      </c>
+      <c r="C6" s="51">
         <v>3</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="51" t="s">
         <v>60</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="51" t="s">
         <v>53</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="H6" s="1">
+      <c r="G6" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="H6" s="51">
         <v>3</v>
       </c>
-      <c r="I6" s="1">
+      <c r="I6" s="51">
         <v>30</v>
       </c>
-      <c r="J6" s="1">
+      <c r="J6" s="51">
         <v>60</v>
       </c>
-      <c r="K6" s="1">
-        <v>1</v>
-      </c>
-      <c r="L6" s="1">
+      <c r="K6" s="51">
+        <v>1</v>
+      </c>
+      <c r="L6" s="51">
         <v>15</v>
       </c>
-      <c r="M6" s="1">
+      <c r="M6" s="51">
         <v>2</v>
       </c>
-      <c r="N6" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="O6" s="3" t="s">
+      <c r="N6" s="51" t="s">
         <v>70</v>
       </c>
-      <c r="P6" s="1" t="s">
+      <c r="O6" s="53" t="s">
         <v>71</v>
       </c>
-      <c r="Q6" s="1">
+      <c r="P6" s="51" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q6" s="51">
         <v>3</v>
       </c>
-      <c r="R6" s="1">
+      <c r="R6" s="51" t="s">
+        <v>73</v>
+      </c>
+      <c r="S6" s="51">
+        <v>2</v>
+      </c>
+      <c r="T6" s="51">
+        <v>30</v>
+      </c>
+      <c r="U6" s="51">
+        <v>150</v>
+      </c>
+      <c r="V6" s="51">
+        <v>3</v>
+      </c>
+      <c r="W6" s="51" t="s">
+        <v>74</v>
+      </c>
+      <c r="X6" s="51" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="50">
+        <v>1000004</v>
+      </c>
+      <c r="B7" s="50">
+        <v>1</v>
+      </c>
+      <c r="C7" s="51">
+        <v>4</v>
+      </c>
+      <c r="D7" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="E7" s="51" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7" s="51" t="s">
+        <v>76</v>
+      </c>
+      <c r="G7" s="51" t="s">
+        <v>76</v>
+      </c>
+      <c r="H7" s="51">
+        <v>4</v>
+      </c>
+      <c r="I7" s="51">
+        <v>40</v>
+      </c>
+      <c r="J7" s="51">
+        <v>60</v>
+      </c>
+      <c r="K7" s="51">
+        <v>1</v>
+      </c>
+      <c r="L7" s="51">
+        <v>2</v>
+      </c>
+      <c r="M7" s="51">
+        <v>2.5</v>
+      </c>
+      <c r="N7" s="51" t="s">
+        <v>77</v>
+      </c>
+      <c r="O7" s="53" t="s">
+        <v>78</v>
+      </c>
+      <c r="P7" s="51" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q7" s="51">
+        <v>4</v>
+      </c>
+      <c r="R7" s="51">
+        <v>400</v>
+      </c>
+      <c r="S7" s="51">
+        <v>2</v>
+      </c>
+      <c r="T7" s="51">
+        <v>40</v>
+      </c>
+      <c r="U7" s="51">
+        <v>200</v>
+      </c>
+      <c r="V7" s="51">
+        <v>4</v>
+      </c>
+      <c r="W7" s="51" t="s">
+        <v>80</v>
+      </c>
+      <c r="X7" s="51" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="50">
+        <v>1000005</v>
+      </c>
+      <c r="B8" s="50">
+        <v>1</v>
+      </c>
+      <c r="C8" s="51">
+        <v>5</v>
+      </c>
+      <c r="D8" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="E8" s="51" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="51" t="s">
+        <v>76</v>
+      </c>
+      <c r="G8" s="51" t="s">
+        <v>76</v>
+      </c>
+      <c r="H8" s="51">
+        <v>5</v>
+      </c>
+      <c r="I8" s="51">
+        <v>50</v>
+      </c>
+      <c r="J8" s="51">
+        <v>60</v>
+      </c>
+      <c r="K8" s="51">
+        <v>1</v>
+      </c>
+      <c r="L8" s="51">
+        <v>2</v>
+      </c>
+      <c r="M8" s="51">
+        <v>3</v>
+      </c>
+      <c r="N8" s="51" t="s">
+        <v>79</v>
+      </c>
+      <c r="O8" s="53" t="s">
+        <v>82</v>
+      </c>
+      <c r="P8" s="51" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q8" s="51">
+        <v>5</v>
+      </c>
+      <c r="R8" s="51">
+        <v>500</v>
+      </c>
+      <c r="S8" s="51">
+        <v>2</v>
+      </c>
+      <c r="T8" s="51">
+        <v>50</v>
+      </c>
+      <c r="U8" s="51">
+        <v>250</v>
+      </c>
+      <c r="V8" s="51">
+        <v>5</v>
+      </c>
+      <c r="W8" s="51" t="s">
+        <v>84</v>
+      </c>
+      <c r="X8" s="51" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="50">
+        <v>1000006</v>
+      </c>
+      <c r="B9" s="50">
+        <v>1</v>
+      </c>
+      <c r="C9" s="51">
+        <v>6</v>
+      </c>
+      <c r="D9" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="E9" s="51" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9" s="51" t="s">
+        <v>76</v>
+      </c>
+      <c r="G9" s="51" t="s">
+        <v>76</v>
+      </c>
+      <c r="H9" s="51">
+        <v>6</v>
+      </c>
+      <c r="I9" s="51">
+        <v>60</v>
+      </c>
+      <c r="J9" s="51">
+        <v>60</v>
+      </c>
+      <c r="K9" s="51">
+        <v>1</v>
+      </c>
+      <c r="L9" s="51">
+        <v>2</v>
+      </c>
+      <c r="M9" s="51">
+        <v>3.5</v>
+      </c>
+      <c r="N9" s="51" t="s">
+        <v>86</v>
+      </c>
+      <c r="O9" s="51" t="s">
+        <v>87</v>
+      </c>
+      <c r="P9" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q9" s="51">
+        <v>6</v>
+      </c>
+      <c r="R9" s="51">
+        <v>600</v>
+      </c>
+      <c r="S9" s="51">
+        <v>3</v>
+      </c>
+      <c r="T9" s="51">
+        <v>60</v>
+      </c>
+      <c r="U9" s="51">
         <v>300</v>
       </c>
-      <c r="S6" s="1">
+      <c r="V9" s="51">
+        <v>6</v>
+      </c>
+      <c r="W9" s="51" t="s">
+        <v>89</v>
+      </c>
+      <c r="X9" s="51" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="50">
+        <v>1000007</v>
+      </c>
+      <c r="B10" s="50">
+        <v>1</v>
+      </c>
+      <c r="C10" s="51">
+        <v>7</v>
+      </c>
+      <c r="D10" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="E10" s="51" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" s="51" t="s">
+        <v>76</v>
+      </c>
+      <c r="G10" s="51" t="s">
+        <v>76</v>
+      </c>
+      <c r="H10" s="51">
+        <v>7</v>
+      </c>
+      <c r="I10" s="51">
+        <v>70</v>
+      </c>
+      <c r="J10" s="51">
+        <v>60</v>
+      </c>
+      <c r="K10" s="51">
+        <v>1</v>
+      </c>
+      <c r="L10" s="51">
         <v>2</v>
       </c>
-      <c r="T6" s="1">
-        <v>30</v>
-      </c>
-      <c r="U6" s="1">
-        <v>150</v>
-      </c>
-      <c r="V6" s="1">
+      <c r="M10" s="51">
+        <v>4</v>
+      </c>
+      <c r="N10" s="51" t="s">
+        <v>91</v>
+      </c>
+      <c r="O10" s="51" t="s">
+        <v>87</v>
+      </c>
+      <c r="P10" s="51" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q10" s="51">
+        <v>7</v>
+      </c>
+      <c r="R10" s="51">
+        <v>700</v>
+      </c>
+      <c r="S10" s="51">
         <v>3</v>
       </c>
-      <c r="W6" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="X6" s="1" t="s">
-        <v>73</v>
+      <c r="T10" s="51">
+        <v>70</v>
+      </c>
+      <c r="U10" s="51">
+        <v>350</v>
+      </c>
+      <c r="V10" s="51">
+        <v>7</v>
+      </c>
+      <c r="W10" s="51" t="s">
+        <v>93</v>
+      </c>
+      <c r="X10" s="51" t="s">
+        <v>94</v>
       </c>
     </row>
-    <row r="7" spans="1:24">
-      <c r="A7">
-        <v>1000004</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7" s="1">
+    <row r="11">
+      <c r="A11" s="50">
+        <v>1000008</v>
+      </c>
+      <c r="B11" s="50">
+        <v>1</v>
+      </c>
+      <c r="C11" s="51">
+        <v>8</v>
+      </c>
+      <c r="D11" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="E11" s="51" t="s">
+        <v>53</v>
+      </c>
+      <c r="F11" s="51" t="s">
+        <v>76</v>
+      </c>
+      <c r="G11" s="51" t="s">
+        <v>76</v>
+      </c>
+      <c r="H11" s="51">
+        <v>8</v>
+      </c>
+      <c r="I11" s="51">
+        <v>80</v>
+      </c>
+      <c r="J11" s="51">
+        <v>60</v>
+      </c>
+      <c r="K11" s="51">
+        <v>1</v>
+      </c>
+      <c r="L11" s="51">
+        <v>2</v>
+      </c>
+      <c r="M11" s="51">
+        <v>4.5</v>
+      </c>
+      <c r="N11" s="51" t="s">
+        <v>95</v>
+      </c>
+      <c r="O11" s="51" t="s">
+        <v>87</v>
+      </c>
+      <c r="P11" s="51" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q11" s="51">
+        <v>8</v>
+      </c>
+      <c r="R11" s="51">
+        <v>800</v>
+      </c>
+      <c r="S11" s="51">
+        <v>3</v>
+      </c>
+      <c r="T11" s="51">
+        <v>80</v>
+      </c>
+      <c r="U11" s="51">
+        <v>400</v>
+      </c>
+      <c r="V11" s="51">
+        <v>8</v>
+      </c>
+      <c r="W11" s="51" t="s">
+        <v>97</v>
+      </c>
+      <c r="X11" s="51" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="50">
+        <v>1000009</v>
+      </c>
+      <c r="B12" s="50">
+        <v>1</v>
+      </c>
+      <c r="C12" s="51">
+        <v>9</v>
+      </c>
+      <c r="D12" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="E12" s="51" t="s">
+        <v>53</v>
+      </c>
+      <c r="F12" s="51" t="s">
+        <v>76</v>
+      </c>
+      <c r="G12" s="51" t="s">
+        <v>76</v>
+      </c>
+      <c r="H12" s="51">
+        <v>9</v>
+      </c>
+      <c r="I12" s="51">
+        <v>90</v>
+      </c>
+      <c r="J12" s="51">
+        <v>60</v>
+      </c>
+      <c r="K12" s="51">
+        <v>1</v>
+      </c>
+      <c r="L12" s="51">
+        <v>2</v>
+      </c>
+      <c r="M12" s="51">
+        <v>5</v>
+      </c>
+      <c r="N12" s="51" t="s">
+        <v>99</v>
+      </c>
+      <c r="O12" s="51" t="s">
+        <v>87</v>
+      </c>
+      <c r="P12" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q12" s="51">
+        <v>9</v>
+      </c>
+      <c r="R12" s="51">
+        <v>900</v>
+      </c>
+      <c r="S12" s="51">
         <v>4</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="T12" s="51">
+        <v>90</v>
+      </c>
+      <c r="U12" s="51">
+        <v>450</v>
+      </c>
+      <c r="V12" s="51">
+        <v>9</v>
+      </c>
+      <c r="W12" s="51" t="s">
+        <v>101</v>
+      </c>
+      <c r="X12" s="51" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="50">
+        <v>1000010</v>
+      </c>
+      <c r="B13" s="50">
+        <v>1</v>
+      </c>
+      <c r="C13" s="51">
+        <v>10</v>
+      </c>
+      <c r="D13" s="51" t="s">
         <v>60</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E13" s="51" t="s">
         <v>53</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="H7" s="1">
+      <c r="F13" s="51" t="s">
+        <v>76</v>
+      </c>
+      <c r="G13" s="51" t="s">
+        <v>76</v>
+      </c>
+      <c r="H13" s="51">
+        <v>10</v>
+      </c>
+      <c r="I13" s="51">
+        <v>100</v>
+      </c>
+      <c r="J13" s="51">
+        <v>60</v>
+      </c>
+      <c r="K13" s="51">
+        <v>1</v>
+      </c>
+      <c r="L13" s="51">
+        <v>2</v>
+      </c>
+      <c r="M13" s="51">
+        <v>5.5</v>
+      </c>
+      <c r="N13" s="51" t="s">
+        <v>103</v>
+      </c>
+      <c r="O13" s="51" t="s">
+        <v>87</v>
+      </c>
+      <c r="P13" s="51" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q13" s="51">
+        <v>10</v>
+      </c>
+      <c r="R13" s="51">
+        <v>1000</v>
+      </c>
+      <c r="S13" s="51">
         <v>4</v>
       </c>
-      <c r="I7" s="1">
-        <v>40</v>
-      </c>
-      <c r="J7" s="1">
-        <v>60</v>
-      </c>
-      <c r="K7" s="1">
-        <v>1</v>
-      </c>
-      <c r="L7" s="1">
-        <v>2</v>
-      </c>
-      <c r="M7" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="O7" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="P7" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q7" s="1">
-        <v>4</v>
-      </c>
-      <c r="R7" s="1">
-        <v>400</v>
-      </c>
-      <c r="S7" s="1">
-        <v>2</v>
-      </c>
-      <c r="T7" s="1">
-        <v>40</v>
-      </c>
-      <c r="U7" s="1">
-        <v>200</v>
-      </c>
-      <c r="V7" s="1">
-        <v>4</v>
-      </c>
-      <c r="W7" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="X7" s="1" t="s">
-        <v>78</v>
+      <c r="T13" s="51">
+        <v>100</v>
+      </c>
+      <c r="U13" s="51">
+        <v>500</v>
+      </c>
+      <c r="V13" s="51">
+        <v>10</v>
+      </c>
+      <c r="W13" s="51" t="s">
+        <v>105</v>
+      </c>
+      <c r="X13" s="51" t="s">
+        <v>106</v>
       </c>
     </row>
-    <row r="8" spans="1:24">
-      <c r="A8">
-        <v>1000005</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8" s="1">
-        <v>5</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="H8" s="1">
-        <v>5</v>
-      </c>
-      <c r="I8" s="1">
-        <v>50</v>
-      </c>
-      <c r="J8" s="1">
-        <v>60</v>
-      </c>
-      <c r="K8" s="1">
-        <v>1</v>
-      </c>
-      <c r="L8" s="1">
-        <v>2</v>
-      </c>
-      <c r="M8" s="1">
-        <v>3</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="P8" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q8" s="1">
-        <v>5</v>
-      </c>
-      <c r="R8" s="1">
-        <v>500</v>
-      </c>
-      <c r="S8" s="1">
-        <v>2</v>
-      </c>
-      <c r="T8" s="1">
-        <v>50</v>
-      </c>
-      <c r="U8" s="1">
-        <v>250</v>
-      </c>
-      <c r="V8" s="1">
-        <v>5</v>
-      </c>
-      <c r="W8" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="X8" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24">
-      <c r="A9">
-        <v>1000006</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9" s="1">
-        <v>6</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="H9" s="1">
-        <v>6</v>
-      </c>
-      <c r="I9" s="1">
-        <v>60</v>
-      </c>
-      <c r="J9" s="1">
-        <v>60</v>
-      </c>
-      <c r="K9" s="1">
-        <v>1</v>
-      </c>
-      <c r="L9" s="1">
-        <v>2</v>
-      </c>
-      <c r="M9" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="O9" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="P9" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q9" s="1">
-        <v>6</v>
-      </c>
-      <c r="R9" s="1">
-        <v>600</v>
-      </c>
-      <c r="S9" s="1">
-        <v>3</v>
-      </c>
-      <c r="T9" s="1">
-        <v>60</v>
-      </c>
-      <c r="U9" s="1">
-        <v>300</v>
-      </c>
-      <c r="V9" s="1">
-        <v>6</v>
-      </c>
-      <c r="W9" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="X9" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24">
-      <c r="A10">
-        <v>1000007</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10" s="1">
-        <v>7</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="H10" s="1">
-        <v>7</v>
-      </c>
-      <c r="I10" s="1">
-        <v>70</v>
-      </c>
-      <c r="J10" s="1">
-        <v>60</v>
-      </c>
-      <c r="K10" s="1">
-        <v>1</v>
-      </c>
-      <c r="L10" s="1">
-        <v>2</v>
-      </c>
-      <c r="M10" s="1">
-        <v>4</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="O10" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="P10" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="Q10" s="1">
-        <v>7</v>
-      </c>
-      <c r="R10" s="1">
-        <v>700</v>
-      </c>
-      <c r="S10" s="1">
-        <v>3</v>
-      </c>
-      <c r="T10" s="1">
-        <v>70</v>
-      </c>
-      <c r="U10" s="1">
-        <v>350</v>
-      </c>
-      <c r="V10" s="1">
-        <v>7</v>
-      </c>
-      <c r="W10" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="X10" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24">
-      <c r="A11">
-        <v>1000008</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11" s="1">
-        <v>8</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="H11" s="1">
-        <v>8</v>
-      </c>
-      <c r="I11" s="1">
-        <v>80</v>
-      </c>
-      <c r="J11" s="1">
-        <v>60</v>
-      </c>
-      <c r="K11" s="1">
-        <v>1</v>
-      </c>
-      <c r="L11" s="1">
-        <v>2</v>
-      </c>
-      <c r="M11" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="O11" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="P11" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="Q11" s="1">
-        <v>8</v>
-      </c>
-      <c r="R11" s="1">
-        <v>800</v>
-      </c>
-      <c r="S11" s="1">
-        <v>3</v>
-      </c>
-      <c r="T11" s="1">
-        <v>80</v>
-      </c>
-      <c r="U11" s="1">
-        <v>400</v>
-      </c>
-      <c r="V11" s="1">
-        <v>8</v>
-      </c>
-      <c r="W11" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="X11" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24">
-      <c r="A12">
-        <v>1000009</v>
-      </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12" s="1">
-        <v>9</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="H12" s="1">
-        <v>9</v>
-      </c>
-      <c r="I12" s="1">
-        <v>90</v>
-      </c>
-      <c r="J12" s="1">
-        <v>60</v>
-      </c>
-      <c r="K12" s="1">
-        <v>1</v>
-      </c>
-      <c r="L12" s="1">
-        <v>2</v>
-      </c>
-      <c r="M12" s="1">
-        <v>5</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="O12" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="P12" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q12" s="1">
-        <v>9</v>
-      </c>
-      <c r="R12" s="1">
-        <v>900</v>
-      </c>
-      <c r="S12" s="1">
-        <v>4</v>
-      </c>
-      <c r="T12" s="1">
-        <v>90</v>
-      </c>
-      <c r="U12" s="1">
-        <v>450</v>
-      </c>
-      <c r="V12" s="1">
-        <v>9</v>
-      </c>
-      <c r="W12" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="X12" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24">
-      <c r="A13">
-        <v>1000010</v>
-      </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13" s="1">
-        <v>10</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="H13" s="1">
-        <v>10</v>
-      </c>
-      <c r="I13" s="1">
-        <v>100</v>
-      </c>
-      <c r="J13" s="1">
-        <v>60</v>
-      </c>
-      <c r="K13" s="1">
-        <v>1</v>
-      </c>
-      <c r="L13" s="1">
-        <v>2</v>
-      </c>
-      <c r="M13" s="1">
-        <v>5.5</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="O13" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="P13" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="Q13" s="1">
-        <v>10</v>
-      </c>
-      <c r="R13" s="1">
-        <v>1000</v>
-      </c>
-      <c r="S13" s="1">
-        <v>4</v>
-      </c>
-      <c r="T13" s="1">
-        <v>100</v>
-      </c>
-      <c r="U13" s="1">
-        <v>500</v>
-      </c>
-      <c r="V13" s="1">
-        <v>10</v>
-      </c>
-      <c r="W13" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="X13" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="31" s="1" customFormat="1" ht="15" customHeight="1"/>
-    <row r="32" s="1" customFormat="1" ht="15" customHeight="1"/>
-    <row r="33" s="1" customFormat="1" ht="15" customHeight="1"/>
-    <row r="34" s="1" customFormat="1" ht="15" customHeight="1"/>
-    <row r="35" s="1" customFormat="1" ht="15" customHeight="1"/>
-    <row r="36" s="1" customFormat="1" ht="15" customHeight="1"/>
-    <row r="37" s="1" customFormat="1" ht="15" customHeight="1"/>
-    <row r="38" s="1" customFormat="1" ht="15" customHeight="1"/>
-    <row r="39" s="1" customFormat="1" ht="15" customHeight="1"/>
-    <row r="40" s="1" customFormat="1" ht="15" customHeight="1"/>
-    <row r="41" s="1" customFormat="1" ht="15" customHeight="1"/>
-    <row r="73" s="1" customFormat="1" ht="12" customHeight="1"/>
-    <row r="74" s="1" customFormat="1" ht="12" customHeight="1"/>
-    <row r="75" s="1" customFormat="1" ht="12" customHeight="1"/>
-    <row r="76" s="1" customFormat="1" ht="12" customHeight="1"/>
-    <row r="77" s="1" customFormat="1" ht="12" customHeight="1"/>
-    <row r="78" s="1" customFormat="1" ht="12" customHeight="1"/>
-    <row r="79" s="1" customFormat="1" ht="12" customHeight="1"/>
-    <row r="80" s="1" customFormat="1" ht="12" customHeight="1"/>
-    <row r="81" s="1" customFormat="1" ht="12" customHeight="1"/>
+    <row r="31" ht="15" customHeight="1" s="51" customFormat="1"/>
+    <row r="32" ht="15" customHeight="1" s="51" customFormat="1"/>
+    <row r="33" ht="15" customHeight="1" s="51" customFormat="1"/>
+    <row r="34" ht="15" customHeight="1" s="51" customFormat="1"/>
+    <row r="35" ht="15" customHeight="1" s="51" customFormat="1"/>
+    <row r="36" ht="15" customHeight="1" s="51" customFormat="1"/>
+    <row r="37" ht="15" customHeight="1" s="51" customFormat="1"/>
+    <row r="38" ht="15" customHeight="1" s="51" customFormat="1"/>
+    <row r="39" ht="15" customHeight="1" s="51" customFormat="1"/>
+    <row r="40" ht="15" customHeight="1" s="51" customFormat="1"/>
+    <row r="41" ht="15" customHeight="1" s="51" customFormat="1"/>
+    <row r="73" ht="12" customHeight="1" s="51" customFormat="1"/>
+    <row r="74" ht="12" customHeight="1" s="51" customFormat="1"/>
+    <row r="75" ht="12" customHeight="1" s="51" customFormat="1"/>
+    <row r="76" ht="12" customHeight="1" s="51" customFormat="1"/>
+    <row r="77" ht="12" customHeight="1" s="51" customFormat="1"/>
+    <row r="78" ht="12" customHeight="1" s="51" customFormat="1"/>
+    <row r="79" ht="12" customHeight="1" s="51" customFormat="1"/>
+    <row r="80" ht="12" customHeight="1" s="51" customFormat="1"/>
+    <row r="81" ht="12" customHeight="1" s="51" customFormat="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="108">
   <si>
     <t>id</t>
   </si>
@@ -219,6 +219,9 @@
   </si>
   <si>
     <t>2</t>
+  </si>
+  <si>
+    <t>7</t>
   </si>
   <si>
     <t>6</t>
@@ -1795,20 +1798,20 @@
       <c r="K5" s="51">
         <v>1</v>
       </c>
-      <c r="L5" s="51">
-        <v>10</v>
+      <c r="L5" s="51" t="s">
+        <v>64</v>
       </c>
       <c r="M5" s="51">
         <v>1.5</v>
       </c>
       <c r="N5" s="51" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O5" s="51">
         <v>3</v>
       </c>
       <c r="P5" s="52" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q5" s="51">
         <v>2</v>
@@ -1829,10 +1832,10 @@
         <v>2</v>
       </c>
       <c r="W5" s="51" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="X5" s="51" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6">
@@ -1852,10 +1855,10 @@
         <v>53</v>
       </c>
       <c r="F6" s="51" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G6" s="51" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H6" s="51">
         <v>3</v>
@@ -1876,19 +1879,19 @@
         <v>2</v>
       </c>
       <c r="N6" s="51" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="O6" s="53" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P6" s="51" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q6" s="51">
         <v>3</v>
       </c>
       <c r="R6" s="51" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="S6" s="51">
         <v>2</v>
@@ -1903,10 +1906,10 @@
         <v>3</v>
       </c>
       <c r="W6" s="51" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="X6" s="51" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7">
@@ -1926,10 +1929,10 @@
         <v>53</v>
       </c>
       <c r="F7" s="51" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G7" s="51" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H7" s="51">
         <v>4</v>
@@ -1950,13 +1953,13 @@
         <v>2.5</v>
       </c>
       <c r="N7" s="51" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O7" s="53" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P7" s="51" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q7" s="51">
         <v>4</v>
@@ -1977,10 +1980,10 @@
         <v>4</v>
       </c>
       <c r="W7" s="51" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="X7" s="51" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8">
@@ -2000,10 +2003,10 @@
         <v>53</v>
       </c>
       <c r="F8" s="51" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G8" s="51" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H8" s="51">
         <v>5</v>
@@ -2024,13 +2027,13 @@
         <v>3</v>
       </c>
       <c r="N8" s="51" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O8" s="53" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P8" s="51" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q8" s="51">
         <v>5</v>
@@ -2051,10 +2054,10 @@
         <v>5</v>
       </c>
       <c r="W8" s="51" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X8" s="51" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9">
@@ -2074,10 +2077,10 @@
         <v>53</v>
       </c>
       <c r="F9" s="51" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G9" s="51" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H9" s="51">
         <v>6</v>
@@ -2098,13 +2101,13 @@
         <v>3.5</v>
       </c>
       <c r="N9" s="51" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O9" s="51" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P9" s="51" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q9" s="51">
         <v>6</v>
@@ -2125,10 +2128,10 @@
         <v>6</v>
       </c>
       <c r="W9" s="51" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="X9" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10">
@@ -2148,10 +2151,10 @@
         <v>53</v>
       </c>
       <c r="F10" s="51" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G10" s="51" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H10" s="51">
         <v>7</v>
@@ -2172,13 +2175,13 @@
         <v>4</v>
       </c>
       <c r="N10" s="51" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O10" s="51" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P10" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q10" s="51">
         <v>7</v>
@@ -2199,10 +2202,10 @@
         <v>7</v>
       </c>
       <c r="W10" s="51" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="X10" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11">
@@ -2222,10 +2225,10 @@
         <v>53</v>
       </c>
       <c r="F11" s="51" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G11" s="51" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H11" s="51">
         <v>8</v>
@@ -2246,13 +2249,13 @@
         <v>4.5</v>
       </c>
       <c r="N11" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O11" s="51" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P11" s="51" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q11" s="51">
         <v>8</v>
@@ -2273,10 +2276,10 @@
         <v>8</v>
       </c>
       <c r="W11" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="X11" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12">
@@ -2296,10 +2299,10 @@
         <v>53</v>
       </c>
       <c r="F12" s="51" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G12" s="51" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H12" s="51">
         <v>9</v>
@@ -2320,13 +2323,13 @@
         <v>5</v>
       </c>
       <c r="N12" s="51" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O12" s="51" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P12" s="51" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q12" s="51">
         <v>9</v>
@@ -2347,10 +2350,10 @@
         <v>9</v>
       </c>
       <c r="W12" s="51" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="X12" s="51" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13">
@@ -2370,10 +2373,10 @@
         <v>53</v>
       </c>
       <c r="F13" s="51" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G13" s="51" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H13" s="51">
         <v>10</v>
@@ -2394,13 +2397,13 @@
         <v>5.5</v>
       </c>
       <c r="N13" s="51" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O13" s="51" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P13" s="51" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q13" s="51">
         <v>10</v>
@@ -2421,10 +2424,10 @@
         <v>10</v>
       </c>
       <c r="W13" s="51" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="X13" s="51" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="51" customFormat="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="109">
   <si>
     <t>id</t>
   </si>
@@ -221,7 +221,10 @@
     <t>2</t>
   </si>
   <si>
-    <t>7</t>
+    <t>8</t>
+  </si>
+  <si>
+    <t>1.25</t>
   </si>
   <si>
     <t>6</t>
@@ -1801,17 +1804,17 @@
       <c r="L5" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="M5" s="51">
-        <v>1.5</v>
+      <c r="M5" s="51" t="s">
+        <v>65</v>
       </c>
       <c r="N5" s="51" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O5" s="51">
         <v>3</v>
       </c>
       <c r="P5" s="52" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q5" s="51">
         <v>2</v>
@@ -1832,10 +1835,10 @@
         <v>2</v>
       </c>
       <c r="W5" s="51" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="X5" s="51" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6">
@@ -1855,10 +1858,10 @@
         <v>53</v>
       </c>
       <c r="F6" s="51" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G6" s="51" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H6" s="51">
         <v>3</v>
@@ -1879,19 +1882,19 @@
         <v>2</v>
       </c>
       <c r="N6" s="51" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="O6" s="53" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="P6" s="51" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q6" s="51">
         <v>3</v>
       </c>
       <c r="R6" s="51" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="S6" s="51">
         <v>2</v>
@@ -1906,10 +1909,10 @@
         <v>3</v>
       </c>
       <c r="W6" s="51" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="X6" s="51" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7">
@@ -1929,10 +1932,10 @@
         <v>53</v>
       </c>
       <c r="F7" s="51" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G7" s="51" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H7" s="51">
         <v>4</v>
@@ -1953,13 +1956,13 @@
         <v>2.5</v>
       </c>
       <c r="N7" s="51" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O7" s="53" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P7" s="51" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Q7" s="51">
         <v>4</v>
@@ -1980,10 +1983,10 @@
         <v>4</v>
       </c>
       <c r="W7" s="51" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X7" s="51" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8">
@@ -2003,10 +2006,10 @@
         <v>53</v>
       </c>
       <c r="F8" s="51" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G8" s="51" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H8" s="51">
         <v>5</v>
@@ -2027,13 +2030,13 @@
         <v>3</v>
       </c>
       <c r="N8" s="51" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O8" s="53" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P8" s="51" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q8" s="51">
         <v>5</v>
@@ -2054,10 +2057,10 @@
         <v>5</v>
       </c>
       <c r="W8" s="51" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="X8" s="51" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9">
@@ -2077,10 +2080,10 @@
         <v>53</v>
       </c>
       <c r="F9" s="51" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G9" s="51" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H9" s="51">
         <v>6</v>
@@ -2101,13 +2104,13 @@
         <v>3.5</v>
       </c>
       <c r="N9" s="51" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O9" s="51" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P9" s="51" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q9" s="51">
         <v>6</v>
@@ -2128,10 +2131,10 @@
         <v>6</v>
       </c>
       <c r="W9" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="X9" s="51" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10">
@@ -2151,10 +2154,10 @@
         <v>53</v>
       </c>
       <c r="F10" s="51" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G10" s="51" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H10" s="51">
         <v>7</v>
@@ -2175,13 +2178,13 @@
         <v>4</v>
       </c>
       <c r="N10" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O10" s="51" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P10" s="51" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q10" s="51">
         <v>7</v>
@@ -2202,10 +2205,10 @@
         <v>7</v>
       </c>
       <c r="W10" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="X10" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11">
@@ -2225,10 +2228,10 @@
         <v>53</v>
       </c>
       <c r="F11" s="51" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G11" s="51" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H11" s="51">
         <v>8</v>
@@ -2249,13 +2252,13 @@
         <v>4.5</v>
       </c>
       <c r="N11" s="51" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O11" s="51" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P11" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q11" s="51">
         <v>8</v>
@@ -2276,10 +2279,10 @@
         <v>8</v>
       </c>
       <c r="W11" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="X11" s="51" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
@@ -2299,10 +2302,10 @@
         <v>53</v>
       </c>
       <c r="F12" s="51" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G12" s="51" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H12" s="51">
         <v>9</v>
@@ -2323,13 +2326,13 @@
         <v>5</v>
       </c>
       <c r="N12" s="51" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O12" s="51" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P12" s="51" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q12" s="51">
         <v>9</v>
@@ -2350,10 +2353,10 @@
         <v>9</v>
       </c>
       <c r="W12" s="51" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="X12" s="51" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13">
@@ -2373,10 +2376,10 @@
         <v>53</v>
       </c>
       <c r="F13" s="51" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G13" s="51" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H13" s="51">
         <v>10</v>
@@ -2397,13 +2400,13 @@
         <v>5.5</v>
       </c>
       <c r="N13" s="51" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O13" s="51" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P13" s="51" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q13" s="51">
         <v>10</v>
@@ -2424,10 +2427,10 @@
         <v>10</v>
       </c>
       <c r="W13" s="51" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="X13" s="51" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="51" customFormat="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
@@ -1,33 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="FightTypeConquerInfo" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="113">
   <si>
     <t>id</t>
   </si>
@@ -68,6 +54,9 @@
     <t>attack_intensity_addrate</t>
   </si>
   <si>
+    <t>attack_intensity_baserate</t>
+  </si>
+  <si>
     <t>fight_num</t>
   </si>
   <si>
@@ -152,6 +141,9 @@
     <t>每关强度倍率(默认1,如1.1则每关HP/护甲/攻击力×1.1,含BOSS)</t>
   </si>
   <si>
+    <t>基础强度倍率(默认1,该难度所有关卡敌人HP/护甲/攻击力×该值;0或不配按1处理)</t>
+  </si>
+  <si>
     <t>关卡次数(单个数x或范围x-y)</t>
   </si>
   <si>
@@ -203,6 +195,9 @@
     <t>60</t>
   </si>
   <si>
+    <t>7</t>
+  </si>
+  <si>
     <t>剑与魔法-难度1</t>
   </si>
   <si>
@@ -221,10 +216,13 @@
     <t>2</t>
   </si>
   <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>1.25</t>
+    <t>12</t>
+  </si>
+  <si>
+    <t>1.1</t>
+  </si>
+  <si>
+    <t>1.5</t>
   </si>
   <si>
     <t>6</t>
@@ -359,12 +357,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="166" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="167" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="19">
     <font>
@@ -1155,11 +1153,74 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1448,10 +1509,13 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:X13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Y13"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="3" max="3" width="16" customWidth="1" style="51"/>
     <col min="4" max="4" width="17.125" customWidth="1" style="51"/>
@@ -1544,153 +1608,162 @@
       <c r="X1" s="51" t="s">
         <v>23</v>
       </c>
+      <c r="Y1" s="49" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="50" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B2" s="50" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C2" s="51" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="51" t="s">
+      <c r="J2" s="51" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2" s="51" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="51" t="s">
+      <c r="M2" s="51" t="s">
+        <v>28</v>
+      </c>
+      <c r="N2" s="51" t="s">
+        <v>28</v>
+      </c>
+      <c r="O2" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="P2" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q2" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="R2" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="51" t="s">
+      <c r="S2" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="51" t="s">
+      <c r="T2" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="51" t="s">
-        <v>25</v>
-      </c>
-      <c r="J2" s="51" t="s">
-        <v>27</v>
-      </c>
-      <c r="K2" s="51" t="s">
-        <v>27</v>
-      </c>
-      <c r="L2" s="51" t="s">
-        <v>25</v>
-      </c>
-      <c r="M2" s="51" t="s">
-        <v>27</v>
-      </c>
-      <c r="N2" s="51" t="s">
+      <c r="U2" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="O2" s="51" t="s">
+      <c r="V2" s="51" t="s">
         <v>26</v>
-      </c>
-      <c r="P2" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q2" s="51" t="s">
-        <v>25</v>
-      </c>
-      <c r="R2" s="51" t="s">
-        <v>25</v>
-      </c>
-      <c r="S2" s="51" t="s">
-        <v>25</v>
-      </c>
-      <c r="T2" s="51" t="s">
-        <v>25</v>
-      </c>
-      <c r="U2" s="51" t="s">
-        <v>25</v>
-      </c>
-      <c r="V2" s="51" t="s">
-        <v>25</v>
       </c>
       <c r="W2" s="51" t="s">
         <v>26</v>
       </c>
       <c r="X2" s="51" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="Y2" s="49" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="50" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B3" s="50" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C3" s="51" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D3" s="51" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E3" s="51" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F3" s="51" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G3" s="51" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H3" s="51" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I3" s="51" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J3" s="51" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K3" s="51" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L3" s="51" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M3" s="51" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N3" s="51" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O3" s="51" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P3" s="51" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q3" s="51" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="R3" s="51" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="S3" s="51" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T3" s="51" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U3" s="51" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="V3" s="51" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="W3" s="51" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="X3" s="51" t="s">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="Y3" s="49" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="4">
@@ -1704,67 +1777,70 @@
         <v>1</v>
       </c>
       <c r="D4" s="51" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E4" s="51" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F4" s="51" t="s">
+        <v>56</v>
+      </c>
+      <c r="G4" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="H4" s="51" t="s">
         <v>54</v>
       </c>
-      <c r="G4" s="51" t="s">
-        <v>55</v>
-      </c>
-      <c r="H4" s="51" t="s">
-        <v>52</v>
-      </c>
       <c r="I4" s="51" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J4" s="51" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K4" s="51">
         <v>1</v>
       </c>
-      <c r="L4" s="51">
+      <c r="L4" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="M4" s="51">
+        <v>1</v>
+      </c>
+      <c r="N4" s="51">
+        <v>1</v>
+      </c>
+      <c r="O4" s="51">
         <v>5</v>
       </c>
-      <c r="M4" s="51">
-        <v>1</v>
-      </c>
-      <c r="N4" s="51">
-        <v>5</v>
-      </c>
-      <c r="O4" s="51">
+      <c r="P4" s="51">
         <v>2</v>
       </c>
-      <c r="P4" s="51">
+      <c r="Q4" s="51">
         <v>10</v>
       </c>
-      <c r="Q4" s="51">
-        <v>1</v>
-      </c>
       <c r="R4" s="51">
+        <v>1</v>
+      </c>
+      <c r="S4" s="51">
         <v>100</v>
       </c>
-      <c r="S4" s="51">
-        <v>1</v>
-      </c>
       <c r="T4" s="51">
+        <v>1</v>
+      </c>
+      <c r="U4" s="51">
         <v>10</v>
       </c>
-      <c r="U4" s="51">
+      <c r="V4" s="51">
         <v>50</v>
       </c>
-      <c r="V4" s="51">
-        <v>1</v>
-      </c>
-      <c r="W4" s="51" t="s">
-        <v>58</v>
+      <c r="W4" s="51">
+        <v>1</v>
       </c>
       <c r="X4" s="51" t="s">
-        <v>59</v>
+        <v>61</v>
+      </c>
+      <c r="Y4" s="49" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="5">
@@ -1778,19 +1854,19 @@
         <v>2</v>
       </c>
       <c r="D5" s="51" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E5" s="51" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F5" s="51" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G5" s="51" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="H5" s="51" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="I5" s="51">
         <v>20</v>
@@ -1802,43 +1878,46 @@
         <v>1</v>
       </c>
       <c r="L5" s="51" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="M5" s="51" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="N5" s="51" t="s">
-        <v>66</v>
-      </c>
-      <c r="O5" s="51">
+        <v>69</v>
+      </c>
+      <c r="O5" s="51" t="s">
+        <v>70</v>
+      </c>
+      <c r="P5" s="51">
         <v>3</v>
       </c>
-      <c r="P5" s="52" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q5" s="51">
+      <c r="Q5" s="52" t="s">
+        <v>71</v>
+      </c>
+      <c r="R5" s="51">
         <v>2</v>
       </c>
-      <c r="R5" s="51">
+      <c r="S5" s="51">
         <v>200</v>
       </c>
-      <c r="S5" s="51">
-        <v>1</v>
-      </c>
       <c r="T5" s="51">
+        <v>1</v>
+      </c>
+      <c r="U5" s="51">
         <v>20</v>
       </c>
-      <c r="U5" s="51">
+      <c r="V5" s="51">
         <v>100</v>
       </c>
-      <c r="V5" s="51">
+      <c r="W5" s="51">
         <v>2</v>
       </c>
-      <c r="W5" s="51" t="s">
-        <v>68</v>
-      </c>
       <c r="X5" s="51" t="s">
-        <v>69</v>
+        <v>72</v>
+      </c>
+      <c r="Y5" s="49" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="6">
@@ -1852,16 +1931,16 @@
         <v>3</v>
       </c>
       <c r="D6" s="51" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E6" s="51" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F6" s="51" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G6" s="51" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="H6" s="51">
         <v>3</v>
@@ -1881,38 +1960,41 @@
       <c r="M6" s="51">
         <v>2</v>
       </c>
-      <c r="N6" s="51" t="s">
-        <v>72</v>
-      </c>
-      <c r="O6" s="53" t="s">
-        <v>73</v>
-      </c>
-      <c r="P6" s="51" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q6" s="51">
+      <c r="N6" s="51">
+        <v>1</v>
+      </c>
+      <c r="O6" s="51" t="s">
+        <v>76</v>
+      </c>
+      <c r="P6" s="53" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q6" s="51" t="s">
+        <v>78</v>
+      </c>
+      <c r="R6" s="51">
         <v>3</v>
       </c>
-      <c r="R6" s="51" t="s">
-        <v>75</v>
-      </c>
-      <c r="S6" s="51">
+      <c r="S6" s="51" t="s">
+        <v>79</v>
+      </c>
+      <c r="T6" s="51">
         <v>2</v>
       </c>
-      <c r="T6" s="51">
+      <c r="U6" s="51">
         <v>30</v>
       </c>
-      <c r="U6" s="51">
+      <c r="V6" s="51">
         <v>150</v>
       </c>
-      <c r="V6" s="51">
+      <c r="W6" s="51">
         <v>3</v>
       </c>
-      <c r="W6" s="51" t="s">
-        <v>76</v>
-      </c>
       <c r="X6" s="51" t="s">
-        <v>77</v>
+        <v>80</v>
+      </c>
+      <c r="Y6" s="49" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="7">
@@ -1926,16 +2008,16 @@
         <v>4</v>
       </c>
       <c r="D7" s="51" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E7" s="51" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F7" s="51" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G7" s="51" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H7" s="51">
         <v>4</v>
@@ -1955,38 +2037,41 @@
       <c r="M7" s="51">
         <v>2.5</v>
       </c>
-      <c r="N7" s="51" t="s">
-        <v>79</v>
-      </c>
-      <c r="O7" s="53" t="s">
-        <v>80</v>
-      </c>
-      <c r="P7" s="51" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q7" s="51">
+      <c r="N7" s="51">
+        <v>1</v>
+      </c>
+      <c r="O7" s="51" t="s">
+        <v>83</v>
+      </c>
+      <c r="P7" s="53" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q7" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="R7" s="51">
         <v>4</v>
       </c>
-      <c r="R7" s="51">
+      <c r="S7" s="51">
         <v>400</v>
       </c>
-      <c r="S7" s="51">
+      <c r="T7" s="51">
         <v>2</v>
       </c>
-      <c r="T7" s="51">
+      <c r="U7" s="51">
         <v>40</v>
       </c>
-      <c r="U7" s="51">
+      <c r="V7" s="51">
         <v>200</v>
       </c>
-      <c r="V7" s="51">
+      <c r="W7" s="51">
         <v>4</v>
       </c>
-      <c r="W7" s="51" t="s">
-        <v>82</v>
-      </c>
       <c r="X7" s="51" t="s">
-        <v>83</v>
+        <v>86</v>
+      </c>
+      <c r="Y7" s="49" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="8">
@@ -2000,16 +2085,16 @@
         <v>5</v>
       </c>
       <c r="D8" s="51" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E8" s="51" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F8" s="51" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G8" s="51" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H8" s="51">
         <v>5</v>
@@ -2029,38 +2114,41 @@
       <c r="M8" s="51">
         <v>3</v>
       </c>
-      <c r="N8" s="51" t="s">
-        <v>81</v>
-      </c>
-      <c r="O8" s="53" t="s">
-        <v>84</v>
-      </c>
-      <c r="P8" s="51" t="s">
+      <c r="N8" s="51">
+        <v>1</v>
+      </c>
+      <c r="O8" s="51" t="s">
         <v>85</v>
       </c>
-      <c r="Q8" s="51">
+      <c r="P8" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q8" s="51" t="s">
+        <v>89</v>
+      </c>
+      <c r="R8" s="51">
         <v>5</v>
       </c>
-      <c r="R8" s="51">
+      <c r="S8" s="51">
         <v>500</v>
       </c>
-      <c r="S8" s="51">
+      <c r="T8" s="51">
         <v>2</v>
       </c>
-      <c r="T8" s="51">
+      <c r="U8" s="51">
         <v>50</v>
       </c>
-      <c r="U8" s="51">
+      <c r="V8" s="51">
         <v>250</v>
       </c>
-      <c r="V8" s="51">
+      <c r="W8" s="51">
         <v>5</v>
       </c>
-      <c r="W8" s="51" t="s">
-        <v>86</v>
-      </c>
       <c r="X8" s="51" t="s">
-        <v>87</v>
+        <v>90</v>
+      </c>
+      <c r="Y8" s="49" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="9">
@@ -2074,16 +2162,16 @@
         <v>6</v>
       </c>
       <c r="D9" s="51" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E9" s="51" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F9" s="51" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G9" s="51" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H9" s="51">
         <v>6</v>
@@ -2103,38 +2191,41 @@
       <c r="M9" s="51">
         <v>3.5</v>
       </c>
-      <c r="N9" s="51" t="s">
-        <v>88</v>
+      <c r="N9" s="51">
+        <v>1</v>
       </c>
       <c r="O9" s="51" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="P9" s="51" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q9" s="51">
+        <v>93</v>
+      </c>
+      <c r="Q9" s="51" t="s">
+        <v>94</v>
+      </c>
+      <c r="R9" s="51">
         <v>6</v>
       </c>
-      <c r="R9" s="51">
+      <c r="S9" s="51">
         <v>600</v>
       </c>
-      <c r="S9" s="51">
+      <c r="T9" s="51">
         <v>3</v>
       </c>
-      <c r="T9" s="51">
+      <c r="U9" s="51">
         <v>60</v>
       </c>
-      <c r="U9" s="51">
+      <c r="V9" s="51">
         <v>300</v>
       </c>
-      <c r="V9" s="51">
+      <c r="W9" s="51">
         <v>6</v>
       </c>
-      <c r="W9" s="51" t="s">
-        <v>91</v>
-      </c>
       <c r="X9" s="51" t="s">
-        <v>92</v>
+        <v>95</v>
+      </c>
+      <c r="Y9" s="49" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="10">
@@ -2148,16 +2239,16 @@
         <v>7</v>
       </c>
       <c r="D10" s="51" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E10" s="51" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F10" s="51" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G10" s="51" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H10" s="51">
         <v>7</v>
@@ -2177,38 +2268,41 @@
       <c r="M10" s="51">
         <v>4</v>
       </c>
-      <c r="N10" s="51" t="s">
+      <c r="N10" s="51">
+        <v>1</v>
+      </c>
+      <c r="O10" s="51" t="s">
+        <v>97</v>
+      </c>
+      <c r="P10" s="51" t="s">
         <v>93</v>
       </c>
-      <c r="O10" s="51" t="s">
-        <v>89</v>
-      </c>
-      <c r="P10" s="51" t="s">
-        <v>94</v>
-      </c>
-      <c r="Q10" s="51">
+      <c r="Q10" s="51" t="s">
+        <v>98</v>
+      </c>
+      <c r="R10" s="51">
         <v>7</v>
       </c>
-      <c r="R10" s="51">
+      <c r="S10" s="51">
         <v>700</v>
       </c>
-      <c r="S10" s="51">
+      <c r="T10" s="51">
         <v>3</v>
       </c>
-      <c r="T10" s="51">
+      <c r="U10" s="51">
         <v>70</v>
       </c>
-      <c r="U10" s="51">
+      <c r="V10" s="51">
         <v>350</v>
       </c>
-      <c r="V10" s="51">
+      <c r="W10" s="51">
         <v>7</v>
       </c>
-      <c r="W10" s="51" t="s">
-        <v>95</v>
-      </c>
       <c r="X10" s="51" t="s">
-        <v>96</v>
+        <v>99</v>
+      </c>
+      <c r="Y10" s="49" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="11">
@@ -2222,16 +2316,16 @@
         <v>8</v>
       </c>
       <c r="D11" s="51" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E11" s="51" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F11" s="51" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G11" s="51" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H11" s="51">
         <v>8</v>
@@ -2251,38 +2345,41 @@
       <c r="M11" s="51">
         <v>4.5</v>
       </c>
-      <c r="N11" s="51" t="s">
-        <v>97</v>
+      <c r="N11" s="51">
+        <v>1</v>
       </c>
       <c r="O11" s="51" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="P11" s="51" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q11" s="51">
+        <v>93</v>
+      </c>
+      <c r="Q11" s="51" t="s">
+        <v>102</v>
+      </c>
+      <c r="R11" s="51">
         <v>8</v>
       </c>
-      <c r="R11" s="51">
+      <c r="S11" s="51">
         <v>800</v>
       </c>
-      <c r="S11" s="51">
+      <c r="T11" s="51">
         <v>3</v>
       </c>
-      <c r="T11" s="51">
+      <c r="U11" s="51">
         <v>80</v>
       </c>
-      <c r="U11" s="51">
+      <c r="V11" s="51">
         <v>400</v>
       </c>
-      <c r="V11" s="51">
+      <c r="W11" s="51">
         <v>8</v>
       </c>
-      <c r="W11" s="51" t="s">
-        <v>99</v>
-      </c>
       <c r="X11" s="51" t="s">
-        <v>100</v>
+        <v>103</v>
+      </c>
+      <c r="Y11" s="49" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="12">
@@ -2296,16 +2393,16 @@
         <v>9</v>
       </c>
       <c r="D12" s="51" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E12" s="51" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F12" s="51" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G12" s="51" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H12" s="51">
         <v>9</v>
@@ -2325,38 +2422,41 @@
       <c r="M12" s="51">
         <v>5</v>
       </c>
-      <c r="N12" s="51" t="s">
-        <v>101</v>
+      <c r="N12" s="51">
+        <v>1</v>
       </c>
       <c r="O12" s="51" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="P12" s="51" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q12" s="51">
+        <v>93</v>
+      </c>
+      <c r="Q12" s="51" t="s">
+        <v>106</v>
+      </c>
+      <c r="R12" s="51">
         <v>9</v>
       </c>
-      <c r="R12" s="51">
+      <c r="S12" s="51">
         <v>900</v>
       </c>
-      <c r="S12" s="51">
+      <c r="T12" s="51">
         <v>4</v>
       </c>
-      <c r="T12" s="51">
+      <c r="U12" s="51">
         <v>90</v>
       </c>
-      <c r="U12" s="51">
+      <c r="V12" s="51">
         <v>450</v>
       </c>
-      <c r="V12" s="51">
+      <c r="W12" s="51">
         <v>9</v>
       </c>
-      <c r="W12" s="51" t="s">
-        <v>103</v>
-      </c>
       <c r="X12" s="51" t="s">
-        <v>104</v>
+        <v>107</v>
+      </c>
+      <c r="Y12" s="49" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="13">
@@ -2370,16 +2470,16 @@
         <v>10</v>
       </c>
       <c r="D13" s="51" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E13" s="51" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F13" s="51" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G13" s="51" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H13" s="51">
         <v>10</v>
@@ -2399,38 +2499,41 @@
       <c r="M13" s="51">
         <v>5.5</v>
       </c>
-      <c r="N13" s="51" t="s">
-        <v>105</v>
+      <c r="N13" s="51">
+        <v>1</v>
       </c>
       <c r="O13" s="51" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="P13" s="51" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q13" s="51">
+        <v>93</v>
+      </c>
+      <c r="Q13" s="51" t="s">
+        <v>110</v>
+      </c>
+      <c r="R13" s="51">
         <v>10</v>
       </c>
-      <c r="R13" s="51">
+      <c r="S13" s="51">
         <v>1000</v>
       </c>
-      <c r="S13" s="51">
+      <c r="T13" s="51">
         <v>4</v>
       </c>
-      <c r="T13" s="51">
+      <c r="U13" s="51">
         <v>100</v>
       </c>
-      <c r="U13" s="51">
+      <c r="V13" s="51">
         <v>500</v>
       </c>
-      <c r="V13" s="51">
+      <c r="W13" s="51">
         <v>10</v>
       </c>
-      <c r="W13" s="51" t="s">
-        <v>107</v>
-      </c>
       <c r="X13" s="51" t="s">
-        <v>108</v>
+        <v>111</v>
+      </c>
+      <c r="Y13" s="49" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="51" customFormat="1"/>
@@ -2455,7 +2558,7 @@
     <row r="81" ht="12" customHeight="1" s="51" customFormat="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="112">
   <si>
     <t>id</t>
   </si>
@@ -193,9 +193,6 @@
   </si>
   <si>
     <t>60</t>
-  </si>
-  <si>
-    <t>7</t>
   </si>
   <si>
     <t>剑与魔法-难度1</t>
@@ -941,7 +938,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1087,6 +1084,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="32" applyFill="1" borderId="0" applyBorder="1" xfId="48" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
@@ -1517,1045 +1517,1045 @@
   <dimension ref="A1:Y13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="3" max="3" width="16" customWidth="1" style="51"/>
-    <col min="4" max="4" width="17.125" customWidth="1" style="51"/>
-    <col min="5" max="5" width="36.5" customWidth="1" style="51"/>
-    <col min="6" max="6" width="23.75" customWidth="1" style="51"/>
-    <col min="7" max="7" width="18.375" customWidth="1" style="51"/>
-    <col min="8" max="8" width="31.875" customWidth="1" style="51"/>
-    <col min="9" max="9" width="18.25" customWidth="1" style="51"/>
-    <col min="10" max="16" width="16" customWidth="1" style="51"/>
-    <col min="17" max="17" width="12.25" customWidth="1" style="51"/>
-    <col min="18" max="18" width="12.875" customWidth="1" style="51"/>
-    <col min="19" max="19" width="27.125" customWidth="1" style="51"/>
-    <col min="20" max="20" width="17.375" customWidth="1" style="51"/>
-    <col min="21" max="21" width="36.875" customWidth="1" style="51"/>
-    <col min="22" max="22" width="29.375" customWidth="1" style="51"/>
-    <col min="23" max="23" width="42.875" customWidth="1" style="51"/>
-    <col min="24" max="24" width="25.125" customWidth="1" style="51"/>
+    <col min="3" max="3" width="16" customWidth="1" style="52"/>
+    <col min="4" max="4" width="17.125" customWidth="1" style="52"/>
+    <col min="5" max="5" width="36.5" customWidth="1" style="52"/>
+    <col min="6" max="6" width="23.75" customWidth="1" style="52"/>
+    <col min="7" max="7" width="18.375" customWidth="1" style="52"/>
+    <col min="8" max="8" width="31.875" customWidth="1" style="52"/>
+    <col min="9" max="9" width="18.25" customWidth="1" style="52"/>
+    <col min="10" max="16" width="16" customWidth="1" style="52"/>
+    <col min="17" max="17" width="12.25" customWidth="1" style="52"/>
+    <col min="18" max="18" width="12.875" customWidth="1" style="52"/>
+    <col min="19" max="19" width="27.125" customWidth="1" style="52"/>
+    <col min="20" max="20" width="17.375" customWidth="1" style="52"/>
+    <col min="21" max="21" width="36.875" customWidth="1" style="52"/>
+    <col min="22" max="22" width="29.375" customWidth="1" style="52"/>
+    <col min="23" max="23" width="42.875" customWidth="1" style="52"/>
+    <col min="24" max="24" width="25.125" customWidth="1" style="52"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="51" t="s">
+      <c r="B1" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="51" t="s">
+      <c r="D1" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="51" t="s">
+      <c r="E1" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="51" t="s">
+      <c r="F1" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="51" t="s">
+      <c r="G1" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="51" t="s">
+      <c r="H1" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="51" t="s">
+      <c r="I1" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="51" t="s">
+      <c r="J1" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="51" t="s">
+      <c r="K1" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="51" t="s">
+      <c r="L1" s="52" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="51" t="s">
+      <c r="M1" s="52" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="51" t="s">
+      <c r="N1" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="51" t="s">
+      <c r="O1" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="51" t="s">
+      <c r="P1" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="51" t="s">
+      <c r="Q1" s="52" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="51" t="s">
+      <c r="R1" s="52" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="51" t="s">
+      <c r="S1" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="51" t="s">
+      <c r="T1" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="51" t="s">
+      <c r="U1" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="51" t="s">
+      <c r="V1" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="51" t="s">
+      <c r="W1" s="52" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="51" t="s">
+      <c r="X1" s="52" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="49" t="s">
+      <c r="Y1" s="50" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="51" t="s">
+      <c r="C2" s="52" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="51" t="s">
+      <c r="D2" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="51" t="s">
+      <c r="E2" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="F2" s="51" t="s">
+      <c r="F2" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="G2" s="51" t="s">
+      <c r="G2" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="51" t="s">
+      <c r="H2" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="51" t="s">
+      <c r="I2" s="52" t="s">
         <v>26</v>
       </c>
-      <c r="J2" s="51" t="s">
+      <c r="J2" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="K2" s="51" t="s">
+      <c r="K2" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="L2" s="51" t="s">
+      <c r="L2" s="52" t="s">
         <v>26</v>
       </c>
-      <c r="M2" s="51" t="s">
+      <c r="M2" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="N2" s="51" t="s">
+      <c r="N2" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="O2" s="51" t="s">
+      <c r="O2" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="P2" s="51" t="s">
+      <c r="P2" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="Q2" s="51" t="s">
+      <c r="Q2" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="R2" s="51" t="s">
+      <c r="R2" s="52" t="s">
         <v>26</v>
       </c>
-      <c r="S2" s="51" t="s">
+      <c r="S2" s="52" t="s">
         <v>26</v>
       </c>
-      <c r="T2" s="51" t="s">
+      <c r="T2" s="52" t="s">
         <v>26</v>
       </c>
-      <c r="U2" s="51" t="s">
+      <c r="U2" s="52" t="s">
         <v>26</v>
       </c>
-      <c r="V2" s="51" t="s">
+      <c r="V2" s="52" t="s">
         <v>26</v>
       </c>
-      <c r="W2" s="51" t="s">
+      <c r="W2" s="52" t="s">
         <v>26</v>
       </c>
-      <c r="X2" s="51" t="s">
+      <c r="X2" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="Y2" s="49" t="s">
+      <c r="Y2" s="50" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="50" t="s">
+      <c r="B3" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="51" t="s">
+      <c r="C3" s="52" t="s">
         <v>31</v>
       </c>
-      <c r="D3" s="51" t="s">
+      <c r="D3" s="52" t="s">
         <v>32</v>
       </c>
-      <c r="E3" s="51" t="s">
+      <c r="E3" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="51" t="s">
+      <c r="F3" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="G3" s="51" t="s">
+      <c r="G3" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="H3" s="51" t="s">
+      <c r="H3" s="52" t="s">
         <v>36</v>
       </c>
-      <c r="I3" s="51" t="s">
+      <c r="I3" s="52" t="s">
         <v>37</v>
       </c>
-      <c r="J3" s="51" t="s">
+      <c r="J3" s="52" t="s">
         <v>38</v>
       </c>
-      <c r="K3" s="51" t="s">
+      <c r="K3" s="52" t="s">
         <v>39</v>
       </c>
-      <c r="L3" s="51" t="s">
+      <c r="L3" s="52" t="s">
         <v>40</v>
       </c>
-      <c r="M3" s="51" t="s">
+      <c r="M3" s="52" t="s">
         <v>41</v>
       </c>
-      <c r="N3" s="51" t="s">
+      <c r="N3" s="52" t="s">
         <v>42</v>
       </c>
-      <c r="O3" s="51" t="s">
+      <c r="O3" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="P3" s="51" t="s">
+      <c r="P3" s="52" t="s">
         <v>44</v>
       </c>
-      <c r="Q3" s="51" t="s">
+      <c r="Q3" s="52" t="s">
         <v>45</v>
       </c>
-      <c r="R3" s="51" t="s">
+      <c r="R3" s="52" t="s">
         <v>46</v>
       </c>
-      <c r="S3" s="51" t="s">
+      <c r="S3" s="52" t="s">
         <v>47</v>
       </c>
-      <c r="T3" s="51" t="s">
+      <c r="T3" s="52" t="s">
         <v>48</v>
       </c>
-      <c r="U3" s="51" t="s">
+      <c r="U3" s="52" t="s">
         <v>49</v>
       </c>
-      <c r="V3" s="51" t="s">
+      <c r="V3" s="52" t="s">
         <v>50</v>
       </c>
-      <c r="W3" s="51" t="s">
+      <c r="W3" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="X3" s="51" t="s">
+      <c r="X3" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="Y3" s="49" t="s">
+      <c r="Y3" s="50" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="50">
+      <c r="A4" s="51">
         <v>1000001</v>
       </c>
-      <c r="B4" s="50">
-        <v>1</v>
-      </c>
-      <c r="C4" s="51">
-        <v>1</v>
-      </c>
-      <c r="D4" s="51" t="s">
+      <c r="B4" s="51">
+        <v>1</v>
+      </c>
+      <c r="C4" s="52">
+        <v>1</v>
+      </c>
+      <c r="D4" s="52" t="s">
         <v>54</v>
       </c>
-      <c r="E4" s="51" t="s">
+      <c r="E4" s="52" t="s">
         <v>55</v>
       </c>
-      <c r="F4" s="51" t="s">
+      <c r="F4" s="52" t="s">
         <v>56</v>
       </c>
-      <c r="G4" s="51" t="s">
+      <c r="G4" s="52" t="s">
         <v>57</v>
       </c>
-      <c r="H4" s="51" t="s">
+      <c r="H4" s="52" t="s">
         <v>54</v>
       </c>
-      <c r="I4" s="51" t="s">
+      <c r="I4" s="52" t="s">
         <v>58</v>
       </c>
-      <c r="J4" s="51" t="s">
+      <c r="J4" s="52" t="s">
         <v>59</v>
       </c>
-      <c r="K4" s="51">
-        <v>1</v>
-      </c>
-      <c r="L4" s="51" t="s">
+      <c r="K4" s="52">
+        <v>1</v>
+      </c>
+      <c r="L4" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="M4" s="52">
+        <v>1</v>
+      </c>
+      <c r="N4" s="52">
+        <v>1</v>
+      </c>
+      <c r="O4" s="52">
+        <v>5</v>
+      </c>
+      <c r="P4" s="52">
+        <v>2</v>
+      </c>
+      <c r="Q4" s="52">
+        <v>10</v>
+      </c>
+      <c r="R4" s="52">
+        <v>1</v>
+      </c>
+      <c r="S4" s="52">
+        <v>100</v>
+      </c>
+      <c r="T4" s="52">
+        <v>1</v>
+      </c>
+      <c r="U4" s="52">
+        <v>10</v>
+      </c>
+      <c r="V4" s="52">
+        <v>50</v>
+      </c>
+      <c r="W4" s="52">
+        <v>1</v>
+      </c>
+      <c r="X4" s="52" t="s">
         <v>60</v>
       </c>
-      <c r="M4" s="51">
-        <v>1</v>
-      </c>
-      <c r="N4" s="51">
-        <v>1</v>
-      </c>
-      <c r="O4" s="51">
-        <v>5</v>
-      </c>
-      <c r="P4" s="51">
-        <v>2</v>
-      </c>
-      <c r="Q4" s="51">
-        <v>10</v>
-      </c>
-      <c r="R4" s="51">
-        <v>1</v>
-      </c>
-      <c r="S4" s="51">
-        <v>100</v>
-      </c>
-      <c r="T4" s="51">
-        <v>1</v>
-      </c>
-      <c r="U4" s="51">
-        <v>10</v>
-      </c>
-      <c r="V4" s="51">
-        <v>50</v>
-      </c>
-      <c r="W4" s="51">
-        <v>1</v>
-      </c>
-      <c r="X4" s="51" t="s">
+      <c r="Y4" s="50" t="s">
         <v>61</v>
-      </c>
-      <c r="Y4" s="49" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="50">
+      <c r="A5" s="51">
         <v>1000002</v>
       </c>
-      <c r="B5" s="50">
-        <v>1</v>
-      </c>
-      <c r="C5" s="51">
+      <c r="B5" s="51">
+        <v>1</v>
+      </c>
+      <c r="C5" s="52">
         <v>2</v>
       </c>
-      <c r="D5" s="51" t="s">
+      <c r="D5" s="52" t="s">
+        <v>62</v>
+      </c>
+      <c r="E5" s="52" t="s">
+        <v>55</v>
+      </c>
+      <c r="F5" s="52" t="s">
         <v>63</v>
       </c>
-      <c r="E5" s="51" t="s">
-        <v>55</v>
-      </c>
-      <c r="F5" s="51" t="s">
+      <c r="G5" s="52" t="s">
         <v>64</v>
       </c>
-      <c r="G5" s="51" t="s">
+      <c r="H5" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="H5" s="51" t="s">
+      <c r="I5" s="52">
+        <v>20</v>
+      </c>
+      <c r="J5" s="52">
+        <v>60</v>
+      </c>
+      <c r="K5" s="52">
+        <v>1</v>
+      </c>
+      <c r="L5" s="52" t="s">
         <v>66</v>
       </c>
-      <c r="I5" s="51">
+      <c r="M5" s="52" t="s">
+        <v>67</v>
+      </c>
+      <c r="N5" s="52" t="s">
+        <v>68</v>
+      </c>
+      <c r="O5" s="52" t="s">
+        <v>69</v>
+      </c>
+      <c r="P5" s="52">
+        <v>3</v>
+      </c>
+      <c r="Q5" s="53" t="s">
+        <v>70</v>
+      </c>
+      <c r="R5" s="52">
+        <v>2</v>
+      </c>
+      <c r="S5" s="52">
+        <v>200</v>
+      </c>
+      <c r="T5" s="52">
+        <v>1</v>
+      </c>
+      <c r="U5" s="52">
         <v>20</v>
       </c>
-      <c r="J5" s="51">
-        <v>60</v>
-      </c>
-      <c r="K5" s="51">
-        <v>1</v>
-      </c>
-      <c r="L5" s="51" t="s">
-        <v>67</v>
-      </c>
-      <c r="M5" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="N5" s="51" t="s">
-        <v>69</v>
-      </c>
-      <c r="O5" s="51" t="s">
-        <v>70</v>
-      </c>
-      <c r="P5" s="51">
-        <v>3</v>
-      </c>
-      <c r="Q5" s="52" t="s">
+      <c r="V5" s="52">
+        <v>100</v>
+      </c>
+      <c r="W5" s="52">
+        <v>2</v>
+      </c>
+      <c r="X5" s="52" t="s">
         <v>71</v>
       </c>
-      <c r="R5" s="51">
-        <v>2</v>
-      </c>
-      <c r="S5" s="51">
-        <v>200</v>
-      </c>
-      <c r="T5" s="51">
-        <v>1</v>
-      </c>
-      <c r="U5" s="51">
-        <v>20</v>
-      </c>
-      <c r="V5" s="51">
-        <v>100</v>
-      </c>
-      <c r="W5" s="51">
-        <v>2</v>
-      </c>
-      <c r="X5" s="51" t="s">
+      <c r="Y5" s="50" t="s">
         <v>72</v>
-      </c>
-      <c r="Y5" s="49" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="50">
+      <c r="A6" s="51">
         <v>1000003</v>
       </c>
-      <c r="B6" s="50">
-        <v>1</v>
-      </c>
-      <c r="C6" s="51">
+      <c r="B6" s="51">
+        <v>1</v>
+      </c>
+      <c r="C6" s="52">
         <v>3</v>
       </c>
-      <c r="D6" s="51" t="s">
-        <v>63</v>
-      </c>
-      <c r="E6" s="51" t="s">
+      <c r="D6" s="52" t="s">
+        <v>62</v>
+      </c>
+      <c r="E6" s="52" t="s">
         <v>55</v>
       </c>
-      <c r="F6" s="51" t="s">
+      <c r="F6" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="G6" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="G6" s="51" t="s">
+      <c r="H6" s="52">
+        <v>3</v>
+      </c>
+      <c r="I6" s="52">
+        <v>30</v>
+      </c>
+      <c r="J6" s="52">
+        <v>60</v>
+      </c>
+      <c r="K6" s="52">
+        <v>1</v>
+      </c>
+      <c r="L6" s="52">
+        <v>15</v>
+      </c>
+      <c r="M6" s="52">
+        <v>2</v>
+      </c>
+      <c r="N6" s="52">
+        <v>1</v>
+      </c>
+      <c r="O6" s="52" t="s">
         <v>75</v>
       </c>
-      <c r="H6" s="51">
+      <c r="P6" s="54" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q6" s="52" t="s">
+        <v>77</v>
+      </c>
+      <c r="R6" s="52">
         <v>3</v>
       </c>
-      <c r="I6" s="51">
+      <c r="S6" s="52" t="s">
+        <v>78</v>
+      </c>
+      <c r="T6" s="52">
+        <v>2</v>
+      </c>
+      <c r="U6" s="52">
         <v>30</v>
       </c>
-      <c r="J6" s="51">
-        <v>60</v>
-      </c>
-      <c r="K6" s="51">
-        <v>1</v>
-      </c>
-      <c r="L6" s="51">
-        <v>15</v>
-      </c>
-      <c r="M6" s="51">
-        <v>2</v>
-      </c>
-      <c r="N6" s="51">
-        <v>1</v>
-      </c>
-      <c r="O6" s="51" t="s">
-        <v>76</v>
-      </c>
-      <c r="P6" s="53" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q6" s="51" t="s">
-        <v>78</v>
-      </c>
-      <c r="R6" s="51">
+      <c r="V6" s="52">
+        <v>150</v>
+      </c>
+      <c r="W6" s="52">
         <v>3</v>
       </c>
-      <c r="S6" s="51" t="s">
+      <c r="X6" s="52" t="s">
         <v>79</v>
       </c>
-      <c r="T6" s="51">
-        <v>2</v>
-      </c>
-      <c r="U6" s="51">
-        <v>30</v>
-      </c>
-      <c r="V6" s="51">
-        <v>150</v>
-      </c>
-      <c r="W6" s="51">
-        <v>3</v>
-      </c>
-      <c r="X6" s="51" t="s">
+      <c r="Y6" s="50" t="s">
         <v>80</v>
-      </c>
-      <c r="Y6" s="49" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="50">
+      <c r="A7" s="51">
         <v>1000004</v>
       </c>
-      <c r="B7" s="50">
-        <v>1</v>
-      </c>
-      <c r="C7" s="51">
+      <c r="B7" s="51">
+        <v>1</v>
+      </c>
+      <c r="C7" s="52">
         <v>4</v>
       </c>
-      <c r="D7" s="51" t="s">
-        <v>63</v>
-      </c>
-      <c r="E7" s="51" t="s">
+      <c r="D7" s="52" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" s="52" t="s">
         <v>55</v>
       </c>
-      <c r="F7" s="51" t="s">
+      <c r="F7" s="52" t="s">
+        <v>81</v>
+      </c>
+      <c r="G7" s="52" t="s">
+        <v>81</v>
+      </c>
+      <c r="H7" s="52">
+        <v>4</v>
+      </c>
+      <c r="I7" s="52">
+        <v>40</v>
+      </c>
+      <c r="J7" s="52">
+        <v>60</v>
+      </c>
+      <c r="K7" s="52">
+        <v>1</v>
+      </c>
+      <c r="L7" s="52">
+        <v>2</v>
+      </c>
+      <c r="M7" s="52">
+        <v>2.5</v>
+      </c>
+      <c r="N7" s="52">
+        <v>1</v>
+      </c>
+      <c r="O7" s="52" t="s">
         <v>82</v>
       </c>
-      <c r="G7" s="51" t="s">
-        <v>82</v>
-      </c>
-      <c r="H7" s="51">
+      <c r="P7" s="54" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q7" s="52" t="s">
+        <v>84</v>
+      </c>
+      <c r="R7" s="52">
         <v>4</v>
       </c>
-      <c r="I7" s="51">
+      <c r="S7" s="52">
+        <v>400</v>
+      </c>
+      <c r="T7" s="52">
+        <v>2</v>
+      </c>
+      <c r="U7" s="52">
         <v>40</v>
       </c>
-      <c r="J7" s="51">
-        <v>60</v>
-      </c>
-      <c r="K7" s="51">
-        <v>1</v>
-      </c>
-      <c r="L7" s="51">
-        <v>2</v>
-      </c>
-      <c r="M7" s="51">
-        <v>2.5</v>
-      </c>
-      <c r="N7" s="51">
-        <v>1</v>
-      </c>
-      <c r="O7" s="51" t="s">
-        <v>83</v>
-      </c>
-      <c r="P7" s="53" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q7" s="51" t="s">
+      <c r="V7" s="52">
+        <v>200</v>
+      </c>
+      <c r="W7" s="52">
+        <v>4</v>
+      </c>
+      <c r="X7" s="52" t="s">
         <v>85</v>
       </c>
-      <c r="R7" s="51">
-        <v>4</v>
-      </c>
-      <c r="S7" s="51">
-        <v>400</v>
-      </c>
-      <c r="T7" s="51">
-        <v>2</v>
-      </c>
-      <c r="U7" s="51">
-        <v>40</v>
-      </c>
-      <c r="V7" s="51">
-        <v>200</v>
-      </c>
-      <c r="W7" s="51">
-        <v>4</v>
-      </c>
-      <c r="X7" s="51" t="s">
+      <c r="Y7" s="50" t="s">
         <v>86</v>
-      </c>
-      <c r="Y7" s="49" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="50">
+      <c r="A8" s="51">
         <v>1000005</v>
       </c>
-      <c r="B8" s="50">
-        <v>1</v>
-      </c>
-      <c r="C8" s="51">
+      <c r="B8" s="51">
+        <v>1</v>
+      </c>
+      <c r="C8" s="52">
         <v>5</v>
       </c>
-      <c r="D8" s="51" t="s">
-        <v>63</v>
-      </c>
-      <c r="E8" s="51" t="s">
+      <c r="D8" s="52" t="s">
+        <v>62</v>
+      </c>
+      <c r="E8" s="52" t="s">
         <v>55</v>
       </c>
-      <c r="F8" s="51" t="s">
-        <v>82</v>
-      </c>
-      <c r="G8" s="51" t="s">
-        <v>82</v>
-      </c>
-      <c r="H8" s="51">
+      <c r="F8" s="52" t="s">
+        <v>81</v>
+      </c>
+      <c r="G8" s="52" t="s">
+        <v>81</v>
+      </c>
+      <c r="H8" s="52">
         <v>5</v>
       </c>
-      <c r="I8" s="51">
+      <c r="I8" s="52">
         <v>50</v>
       </c>
-      <c r="J8" s="51">
+      <c r="J8" s="52">
         <v>60</v>
       </c>
-      <c r="K8" s="51">
-        <v>1</v>
-      </c>
-      <c r="L8" s="51">
+      <c r="K8" s="52">
+        <v>1</v>
+      </c>
+      <c r="L8" s="52">
         <v>2</v>
       </c>
-      <c r="M8" s="51">
+      <c r="M8" s="52">
         <v>3</v>
       </c>
-      <c r="N8" s="51">
-        <v>1</v>
-      </c>
-      <c r="O8" s="51" t="s">
-        <v>85</v>
-      </c>
-      <c r="P8" s="53" t="s">
+      <c r="N8" s="52">
+        <v>1</v>
+      </c>
+      <c r="O8" s="52" t="s">
+        <v>84</v>
+      </c>
+      <c r="P8" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q8" s="52" t="s">
         <v>88</v>
       </c>
-      <c r="Q8" s="51" t="s">
+      <c r="R8" s="52">
+        <v>5</v>
+      </c>
+      <c r="S8" s="52">
+        <v>500</v>
+      </c>
+      <c r="T8" s="52">
+        <v>2</v>
+      </c>
+      <c r="U8" s="52">
+        <v>50</v>
+      </c>
+      <c r="V8" s="52">
+        <v>250</v>
+      </c>
+      <c r="W8" s="52">
+        <v>5</v>
+      </c>
+      <c r="X8" s="52" t="s">
         <v>89</v>
       </c>
-      <c r="R8" s="51">
-        <v>5</v>
-      </c>
-      <c r="S8" s="51">
-        <v>500</v>
-      </c>
-      <c r="T8" s="51">
-        <v>2</v>
-      </c>
-      <c r="U8" s="51">
-        <v>50</v>
-      </c>
-      <c r="V8" s="51">
-        <v>250</v>
-      </c>
-      <c r="W8" s="51">
-        <v>5</v>
-      </c>
-      <c r="X8" s="51" t="s">
+      <c r="Y8" s="50" t="s">
         <v>90</v>
-      </c>
-      <c r="Y8" s="49" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="50">
+      <c r="A9" s="51">
         <v>1000006</v>
       </c>
-      <c r="B9" s="50">
-        <v>1</v>
-      </c>
-      <c r="C9" s="51">
+      <c r="B9" s="51">
+        <v>1</v>
+      </c>
+      <c r="C9" s="52">
         <v>6</v>
       </c>
-      <c r="D9" s="51" t="s">
-        <v>63</v>
-      </c>
-      <c r="E9" s="51" t="s">
+      <c r="D9" s="52" t="s">
+        <v>62</v>
+      </c>
+      <c r="E9" s="52" t="s">
         <v>55</v>
       </c>
-      <c r="F9" s="51" t="s">
-        <v>82</v>
-      </c>
-      <c r="G9" s="51" t="s">
-        <v>82</v>
-      </c>
-      <c r="H9" s="51">
+      <c r="F9" s="52" t="s">
+        <v>81</v>
+      </c>
+      <c r="G9" s="52" t="s">
+        <v>81</v>
+      </c>
+      <c r="H9" s="52">
         <v>6</v>
       </c>
-      <c r="I9" s="51">
+      <c r="I9" s="52">
         <v>60</v>
       </c>
-      <c r="J9" s="51">
+      <c r="J9" s="52">
         <v>60</v>
       </c>
-      <c r="K9" s="51">
-        <v>1</v>
-      </c>
-      <c r="L9" s="51">
+      <c r="K9" s="52">
+        <v>1</v>
+      </c>
+      <c r="L9" s="52">
         <v>2</v>
       </c>
-      <c r="M9" s="51">
+      <c r="M9" s="52">
         <v>3.5</v>
       </c>
-      <c r="N9" s="51">
-        <v>1</v>
-      </c>
-      <c r="O9" s="51" t="s">
+      <c r="N9" s="52">
+        <v>1</v>
+      </c>
+      <c r="O9" s="52" t="s">
+        <v>91</v>
+      </c>
+      <c r="P9" s="52" t="s">
         <v>92</v>
       </c>
-      <c r="P9" s="51" t="s">
+      <c r="Q9" s="52" t="s">
         <v>93</v>
       </c>
-      <c r="Q9" s="51" t="s">
+      <c r="R9" s="52">
+        <v>6</v>
+      </c>
+      <c r="S9" s="52">
+        <v>600</v>
+      </c>
+      <c r="T9" s="52">
+        <v>3</v>
+      </c>
+      <c r="U9" s="52">
+        <v>60</v>
+      </c>
+      <c r="V9" s="52">
+        <v>300</v>
+      </c>
+      <c r="W9" s="52">
+        <v>6</v>
+      </c>
+      <c r="X9" s="52" t="s">
         <v>94</v>
       </c>
-      <c r="R9" s="51">
-        <v>6</v>
-      </c>
-      <c r="S9" s="51">
-        <v>600</v>
-      </c>
-      <c r="T9" s="51">
-        <v>3</v>
-      </c>
-      <c r="U9" s="51">
-        <v>60</v>
-      </c>
-      <c r="V9" s="51">
-        <v>300</v>
-      </c>
-      <c r="W9" s="51">
-        <v>6</v>
-      </c>
-      <c r="X9" s="51" t="s">
+      <c r="Y9" s="50" t="s">
         <v>95</v>
-      </c>
-      <c r="Y9" s="49" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="50">
+      <c r="A10" s="51">
         <v>1000007</v>
       </c>
-      <c r="B10" s="50">
-        <v>1</v>
-      </c>
-      <c r="C10" s="51">
+      <c r="B10" s="51">
+        <v>1</v>
+      </c>
+      <c r="C10" s="52">
         <v>7</v>
       </c>
-      <c r="D10" s="51" t="s">
-        <v>63</v>
-      </c>
-      <c r="E10" s="51" t="s">
+      <c r="D10" s="52" t="s">
+        <v>62</v>
+      </c>
+      <c r="E10" s="52" t="s">
         <v>55</v>
       </c>
-      <c r="F10" s="51" t="s">
-        <v>82</v>
-      </c>
-      <c r="G10" s="51" t="s">
-        <v>82</v>
-      </c>
-      <c r="H10" s="51">
+      <c r="F10" s="52" t="s">
+        <v>81</v>
+      </c>
+      <c r="G10" s="52" t="s">
+        <v>81</v>
+      </c>
+      <c r="H10" s="52">
         <v>7</v>
       </c>
-      <c r="I10" s="51">
+      <c r="I10" s="52">
         <v>70</v>
       </c>
-      <c r="J10" s="51">
+      <c r="J10" s="52">
         <v>60</v>
       </c>
-      <c r="K10" s="51">
-        <v>1</v>
-      </c>
-      <c r="L10" s="51">
+      <c r="K10" s="52">
+        <v>1</v>
+      </c>
+      <c r="L10" s="52">
         <v>2</v>
       </c>
-      <c r="M10" s="51">
+      <c r="M10" s="52">
         <v>4</v>
       </c>
-      <c r="N10" s="51">
-        <v>1</v>
-      </c>
-      <c r="O10" s="51" t="s">
+      <c r="N10" s="52">
+        <v>1</v>
+      </c>
+      <c r="O10" s="52" t="s">
+        <v>96</v>
+      </c>
+      <c r="P10" s="52" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q10" s="52" t="s">
         <v>97</v>
       </c>
-      <c r="P10" s="51" t="s">
-        <v>93</v>
-      </c>
-      <c r="Q10" s="51" t="s">
+      <c r="R10" s="52">
+        <v>7</v>
+      </c>
+      <c r="S10" s="52">
+        <v>700</v>
+      </c>
+      <c r="T10" s="52">
+        <v>3</v>
+      </c>
+      <c r="U10" s="52">
+        <v>70</v>
+      </c>
+      <c r="V10" s="52">
+        <v>350</v>
+      </c>
+      <c r="W10" s="52">
+        <v>7</v>
+      </c>
+      <c r="X10" s="52" t="s">
         <v>98</v>
       </c>
-      <c r="R10" s="51">
-        <v>7</v>
-      </c>
-      <c r="S10" s="51">
-        <v>700</v>
-      </c>
-      <c r="T10" s="51">
-        <v>3</v>
-      </c>
-      <c r="U10" s="51">
-        <v>70</v>
-      </c>
-      <c r="V10" s="51">
-        <v>350</v>
-      </c>
-      <c r="W10" s="51">
-        <v>7</v>
-      </c>
-      <c r="X10" s="51" t="s">
+      <c r="Y10" s="50" t="s">
         <v>99</v>
-      </c>
-      <c r="Y10" s="49" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="50">
+      <c r="A11" s="51">
         <v>1000008</v>
       </c>
-      <c r="B11" s="50">
-        <v>1</v>
-      </c>
-      <c r="C11" s="51">
+      <c r="B11" s="51">
+        <v>1</v>
+      </c>
+      <c r="C11" s="52">
         <v>8</v>
       </c>
-      <c r="D11" s="51" t="s">
-        <v>63</v>
-      </c>
-      <c r="E11" s="51" t="s">
+      <c r="D11" s="52" t="s">
+        <v>62</v>
+      </c>
+      <c r="E11" s="52" t="s">
         <v>55</v>
       </c>
-      <c r="F11" s="51" t="s">
-        <v>82</v>
-      </c>
-      <c r="G11" s="51" t="s">
-        <v>82</v>
-      </c>
-      <c r="H11" s="51">
+      <c r="F11" s="52" t="s">
+        <v>81</v>
+      </c>
+      <c r="G11" s="52" t="s">
+        <v>81</v>
+      </c>
+      <c r="H11" s="52">
         <v>8</v>
       </c>
-      <c r="I11" s="51">
+      <c r="I11" s="52">
         <v>80</v>
       </c>
-      <c r="J11" s="51">
+      <c r="J11" s="52">
         <v>60</v>
       </c>
-      <c r="K11" s="51">
-        <v>1</v>
-      </c>
-      <c r="L11" s="51">
+      <c r="K11" s="52">
+        <v>1</v>
+      </c>
+      <c r="L11" s="52">
         <v>2</v>
       </c>
-      <c r="M11" s="51">
+      <c r="M11" s="52">
         <v>4.5</v>
       </c>
-      <c r="N11" s="51">
-        <v>1</v>
-      </c>
-      <c r="O11" s="51" t="s">
+      <c r="N11" s="52">
+        <v>1</v>
+      </c>
+      <c r="O11" s="52" t="s">
+        <v>100</v>
+      </c>
+      <c r="P11" s="52" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q11" s="52" t="s">
         <v>101</v>
       </c>
-      <c r="P11" s="51" t="s">
-        <v>93</v>
-      </c>
-      <c r="Q11" s="51" t="s">
+      <c r="R11" s="52">
+        <v>8</v>
+      </c>
+      <c r="S11" s="52">
+        <v>800</v>
+      </c>
+      <c r="T11" s="52">
+        <v>3</v>
+      </c>
+      <c r="U11" s="52">
+        <v>80</v>
+      </c>
+      <c r="V11" s="52">
+        <v>400</v>
+      </c>
+      <c r="W11" s="52">
+        <v>8</v>
+      </c>
+      <c r="X11" s="52" t="s">
         <v>102</v>
       </c>
-      <c r="R11" s="51">
-        <v>8</v>
-      </c>
-      <c r="S11" s="51">
-        <v>800</v>
-      </c>
-      <c r="T11" s="51">
-        <v>3</v>
-      </c>
-      <c r="U11" s="51">
-        <v>80</v>
-      </c>
-      <c r="V11" s="51">
-        <v>400</v>
-      </c>
-      <c r="W11" s="51">
-        <v>8</v>
-      </c>
-      <c r="X11" s="51" t="s">
+      <c r="Y11" s="50" t="s">
         <v>103</v>
-      </c>
-      <c r="Y11" s="49" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="50">
+      <c r="A12" s="51">
         <v>1000009</v>
       </c>
-      <c r="B12" s="50">
-        <v>1</v>
-      </c>
-      <c r="C12" s="51">
+      <c r="B12" s="51">
+        <v>1</v>
+      </c>
+      <c r="C12" s="52">
         <v>9</v>
       </c>
-      <c r="D12" s="51" t="s">
-        <v>63</v>
-      </c>
-      <c r="E12" s="51" t="s">
+      <c r="D12" s="52" t="s">
+        <v>62</v>
+      </c>
+      <c r="E12" s="52" t="s">
         <v>55</v>
       </c>
-      <c r="F12" s="51" t="s">
-        <v>82</v>
-      </c>
-      <c r="G12" s="51" t="s">
-        <v>82</v>
-      </c>
-      <c r="H12" s="51">
+      <c r="F12" s="52" t="s">
+        <v>81</v>
+      </c>
+      <c r="G12" s="52" t="s">
+        <v>81</v>
+      </c>
+      <c r="H12" s="52">
         <v>9</v>
       </c>
-      <c r="I12" s="51">
+      <c r="I12" s="52">
         <v>90</v>
       </c>
-      <c r="J12" s="51">
+      <c r="J12" s="52">
         <v>60</v>
       </c>
-      <c r="K12" s="51">
-        <v>1</v>
-      </c>
-      <c r="L12" s="51">
+      <c r="K12" s="52">
+        <v>1</v>
+      </c>
+      <c r="L12" s="52">
         <v>2</v>
       </c>
-      <c r="M12" s="51">
+      <c r="M12" s="52">
         <v>5</v>
       </c>
-      <c r="N12" s="51">
-        <v>1</v>
-      </c>
-      <c r="O12" s="51" t="s">
+      <c r="N12" s="52">
+        <v>1</v>
+      </c>
+      <c r="O12" s="52" t="s">
+        <v>104</v>
+      </c>
+      <c r="P12" s="52" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q12" s="52" t="s">
         <v>105</v>
       </c>
-      <c r="P12" s="51" t="s">
-        <v>93</v>
-      </c>
-      <c r="Q12" s="51" t="s">
+      <c r="R12" s="52">
+        <v>9</v>
+      </c>
+      <c r="S12" s="52">
+        <v>900</v>
+      </c>
+      <c r="T12" s="52">
+        <v>4</v>
+      </c>
+      <c r="U12" s="52">
+        <v>90</v>
+      </c>
+      <c r="V12" s="52">
+        <v>450</v>
+      </c>
+      <c r="W12" s="52">
+        <v>9</v>
+      </c>
+      <c r="X12" s="52" t="s">
         <v>106</v>
       </c>
-      <c r="R12" s="51">
-        <v>9</v>
-      </c>
-      <c r="S12" s="51">
-        <v>900</v>
-      </c>
-      <c r="T12" s="51">
-        <v>4</v>
-      </c>
-      <c r="U12" s="51">
-        <v>90</v>
-      </c>
-      <c r="V12" s="51">
-        <v>450</v>
-      </c>
-      <c r="W12" s="51">
-        <v>9</v>
-      </c>
-      <c r="X12" s="51" t="s">
+      <c r="Y12" s="50" t="s">
         <v>107</v>
-      </c>
-      <c r="Y12" s="49" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="50">
+      <c r="A13" s="51">
         <v>1000010</v>
       </c>
-      <c r="B13" s="50">
-        <v>1</v>
-      </c>
-      <c r="C13" s="51">
+      <c r="B13" s="51">
+        <v>1</v>
+      </c>
+      <c r="C13" s="52">
         <v>10</v>
       </c>
-      <c r="D13" s="51" t="s">
-        <v>63</v>
-      </c>
-      <c r="E13" s="51" t="s">
+      <c r="D13" s="52" t="s">
+        <v>62</v>
+      </c>
+      <c r="E13" s="52" t="s">
         <v>55</v>
       </c>
-      <c r="F13" s="51" t="s">
-        <v>82</v>
-      </c>
-      <c r="G13" s="51" t="s">
-        <v>82</v>
-      </c>
-      <c r="H13" s="51">
+      <c r="F13" s="52" t="s">
+        <v>81</v>
+      </c>
+      <c r="G13" s="52" t="s">
+        <v>81</v>
+      </c>
+      <c r="H13" s="52">
         <v>10</v>
       </c>
-      <c r="I13" s="51">
+      <c r="I13" s="52">
         <v>100</v>
       </c>
-      <c r="J13" s="51">
+      <c r="J13" s="52">
         <v>60</v>
       </c>
-      <c r="K13" s="51">
-        <v>1</v>
-      </c>
-      <c r="L13" s="51">
+      <c r="K13" s="52">
+        <v>1</v>
+      </c>
+      <c r="L13" s="52">
         <v>2</v>
       </c>
-      <c r="M13" s="51">
+      <c r="M13" s="52">
         <v>5.5</v>
       </c>
-      <c r="N13" s="51">
-        <v>1</v>
-      </c>
-      <c r="O13" s="51" t="s">
+      <c r="N13" s="52">
+        <v>1</v>
+      </c>
+      <c r="O13" s="52" t="s">
+        <v>108</v>
+      </c>
+      <c r="P13" s="52" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q13" s="52" t="s">
         <v>109</v>
       </c>
-      <c r="P13" s="51" t="s">
-        <v>93</v>
-      </c>
-      <c r="Q13" s="51" t="s">
+      <c r="R13" s="52">
+        <v>10</v>
+      </c>
+      <c r="S13" s="52">
+        <v>1000</v>
+      </c>
+      <c r="T13" s="52">
+        <v>4</v>
+      </c>
+      <c r="U13" s="52">
+        <v>100</v>
+      </c>
+      <c r="V13" s="52">
+        <v>500</v>
+      </c>
+      <c r="W13" s="52">
+        <v>10</v>
+      </c>
+      <c r="X13" s="52" t="s">
         <v>110</v>
       </c>
-      <c r="R13" s="51">
-        <v>10</v>
-      </c>
-      <c r="S13" s="51">
-        <v>1000</v>
-      </c>
-      <c r="T13" s="51">
-        <v>4</v>
-      </c>
-      <c r="U13" s="51">
-        <v>100</v>
-      </c>
-      <c r="V13" s="51">
-        <v>500</v>
-      </c>
-      <c r="W13" s="51">
-        <v>10</v>
-      </c>
-      <c r="X13" s="51" t="s">
+      <c r="Y13" s="50" t="s">
         <v>111</v>
       </c>
-      <c r="Y13" s="49" t="s">
-        <v>112</v>
-      </c>
     </row>
-    <row r="31" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="32" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="33" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="34" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="35" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="36" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="37" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="38" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="39" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="40" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="41" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="73" ht="12" customHeight="1" s="51" customFormat="1"/>
-    <row r="74" ht="12" customHeight="1" s="51" customFormat="1"/>
-    <row r="75" ht="12" customHeight="1" s="51" customFormat="1"/>
-    <row r="76" ht="12" customHeight="1" s="51" customFormat="1"/>
-    <row r="77" ht="12" customHeight="1" s="51" customFormat="1"/>
-    <row r="78" ht="12" customHeight="1" s="51" customFormat="1"/>
-    <row r="79" ht="12" customHeight="1" s="51" customFormat="1"/>
-    <row r="80" ht="12" customHeight="1" s="51" customFormat="1"/>
-    <row r="81" ht="12" customHeight="1" s="51" customFormat="1"/>
+    <row r="31" ht="15" customHeight="1" s="52" customFormat="1"/>
+    <row r="32" ht="15" customHeight="1" s="52" customFormat="1"/>
+    <row r="33" ht="15" customHeight="1" s="52" customFormat="1"/>
+    <row r="34" ht="15" customHeight="1" s="52" customFormat="1"/>
+    <row r="35" ht="15" customHeight="1" s="52" customFormat="1"/>
+    <row r="36" ht="15" customHeight="1" s="52" customFormat="1"/>
+    <row r="37" ht="15" customHeight="1" s="52" customFormat="1"/>
+    <row r="38" ht="15" customHeight="1" s="52" customFormat="1"/>
+    <row r="39" ht="15" customHeight="1" s="52" customFormat="1"/>
+    <row r="40" ht="15" customHeight="1" s="52" customFormat="1"/>
+    <row r="41" ht="15" customHeight="1" s="52" customFormat="1"/>
+    <row r="73" ht="12" customHeight="1" s="52" customFormat="1"/>
+    <row r="74" ht="12" customHeight="1" s="52" customFormat="1"/>
+    <row r="75" ht="12" customHeight="1" s="52" customFormat="1"/>
+    <row r="76" ht="12" customHeight="1" s="52" customFormat="1"/>
+    <row r="77" ht="12" customHeight="1" s="52" customFormat="1"/>
+    <row r="78" ht="12" customHeight="1" s="52" customFormat="1"/>
+    <row r="79" ht="12" customHeight="1" s="52" customFormat="1"/>
+    <row r="80" ht="12" customHeight="1" s="52" customFormat="1"/>
+    <row r="81" ht="12" customHeight="1" s="52" customFormat="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
@@ -213,13 +213,13 @@
     <t>2</t>
   </si>
   <si>
-    <t>12</t>
+    <t>15</t>
   </si>
   <si>
     <t>1.1</t>
   </si>
   <si>
-    <t>1.5</t>
+    <t>1.25</t>
   </si>
   <si>
     <t>6</t>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="111">
   <si>
     <t>id</t>
   </si>
@@ -214,9 +214,6 @@
   </si>
   <si>
     <t>15</t>
-  </si>
-  <si>
-    <t>1.1</t>
   </si>
   <si>
     <t>1.25</t>
@@ -1881,19 +1878,19 @@
         <v>66</v>
       </c>
       <c r="M5" s="52" t="s">
+        <v>54</v>
+      </c>
+      <c r="N5" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="N5" s="52" t="s">
+      <c r="O5" s="52" t="s">
         <v>68</v>
-      </c>
-      <c r="O5" s="52" t="s">
-        <v>69</v>
       </c>
       <c r="P5" s="52">
         <v>3</v>
       </c>
       <c r="Q5" s="53" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R5" s="52">
         <v>2</v>
@@ -1914,10 +1911,10 @@
         <v>2</v>
       </c>
       <c r="X5" s="52" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y5" s="50" t="s">
         <v>71</v>
-      </c>
-      <c r="Y5" s="50" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="6">
@@ -1937,10 +1934,10 @@
         <v>55</v>
       </c>
       <c r="F6" s="52" t="s">
+        <v>72</v>
+      </c>
+      <c r="G6" s="52" t="s">
         <v>73</v>
-      </c>
-      <c r="G6" s="52" t="s">
-        <v>74</v>
       </c>
       <c r="H6" s="52">
         <v>3</v>
@@ -1964,19 +1961,19 @@
         <v>1</v>
       </c>
       <c r="O6" s="52" t="s">
+        <v>74</v>
+      </c>
+      <c r="P6" s="54" t="s">
         <v>75</v>
       </c>
-      <c r="P6" s="54" t="s">
+      <c r="Q6" s="52" t="s">
         <v>76</v>
-      </c>
-      <c r="Q6" s="52" t="s">
-        <v>77</v>
       </c>
       <c r="R6" s="52">
         <v>3</v>
       </c>
       <c r="S6" s="52" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T6" s="52">
         <v>2</v>
@@ -1991,10 +1988,10 @@
         <v>3</v>
       </c>
       <c r="X6" s="52" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y6" s="50" t="s">
         <v>79</v>
-      </c>
-      <c r="Y6" s="50" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="7">
@@ -2014,10 +2011,10 @@
         <v>55</v>
       </c>
       <c r="F7" s="52" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G7" s="52" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H7" s="52">
         <v>4</v>
@@ -2041,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="O7" s="52" t="s">
+        <v>81</v>
+      </c>
+      <c r="P7" s="54" t="s">
         <v>82</v>
       </c>
-      <c r="P7" s="54" t="s">
+      <c r="Q7" s="52" t="s">
         <v>83</v>
-      </c>
-      <c r="Q7" s="52" t="s">
-        <v>84</v>
       </c>
       <c r="R7" s="52">
         <v>4</v>
@@ -2068,10 +2065,10 @@
         <v>4</v>
       </c>
       <c r="X7" s="52" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y7" s="50" t="s">
         <v>85</v>
-      </c>
-      <c r="Y7" s="50" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="8">
@@ -2091,10 +2088,10 @@
         <v>55</v>
       </c>
       <c r="F8" s="52" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G8" s="52" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H8" s="52">
         <v>5</v>
@@ -2118,13 +2115,13 @@
         <v>1</v>
       </c>
       <c r="O8" s="52" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P8" s="54" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q8" s="52" t="s">
         <v>87</v>
-      </c>
-      <c r="Q8" s="52" t="s">
-        <v>88</v>
       </c>
       <c r="R8" s="52">
         <v>5</v>
@@ -2145,10 +2142,10 @@
         <v>5</v>
       </c>
       <c r="X8" s="52" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y8" s="50" t="s">
         <v>89</v>
-      </c>
-      <c r="Y8" s="50" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="9">
@@ -2168,10 +2165,10 @@
         <v>55</v>
       </c>
       <c r="F9" s="52" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G9" s="52" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H9" s="52">
         <v>6</v>
@@ -2195,13 +2192,13 @@
         <v>1</v>
       </c>
       <c r="O9" s="52" t="s">
+        <v>90</v>
+      </c>
+      <c r="P9" s="52" t="s">
         <v>91</v>
       </c>
-      <c r="P9" s="52" t="s">
+      <c r="Q9" s="52" t="s">
         <v>92</v>
-      </c>
-      <c r="Q9" s="52" t="s">
-        <v>93</v>
       </c>
       <c r="R9" s="52">
         <v>6</v>
@@ -2222,10 +2219,10 @@
         <v>6</v>
       </c>
       <c r="X9" s="52" t="s">
+        <v>93</v>
+      </c>
+      <c r="Y9" s="50" t="s">
         <v>94</v>
-      </c>
-      <c r="Y9" s="50" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="10">
@@ -2245,10 +2242,10 @@
         <v>55</v>
       </c>
       <c r="F10" s="52" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G10" s="52" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H10" s="52">
         <v>7</v>
@@ -2272,13 +2269,13 @@
         <v>1</v>
       </c>
       <c r="O10" s="52" t="s">
+        <v>95</v>
+      </c>
+      <c r="P10" s="52" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q10" s="52" t="s">
         <v>96</v>
-      </c>
-      <c r="P10" s="52" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q10" s="52" t="s">
-        <v>97</v>
       </c>
       <c r="R10" s="52">
         <v>7</v>
@@ -2299,10 +2296,10 @@
         <v>7</v>
       </c>
       <c r="X10" s="52" t="s">
+        <v>97</v>
+      </c>
+      <c r="Y10" s="50" t="s">
         <v>98</v>
-      </c>
-      <c r="Y10" s="50" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="11">
@@ -2322,10 +2319,10 @@
         <v>55</v>
       </c>
       <c r="F11" s="52" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G11" s="52" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H11" s="52">
         <v>8</v>
@@ -2349,13 +2346,13 @@
         <v>1</v>
       </c>
       <c r="O11" s="52" t="s">
+        <v>99</v>
+      </c>
+      <c r="P11" s="52" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q11" s="52" t="s">
         <v>100</v>
-      </c>
-      <c r="P11" s="52" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q11" s="52" t="s">
-        <v>101</v>
       </c>
       <c r="R11" s="52">
         <v>8</v>
@@ -2376,10 +2373,10 @@
         <v>8</v>
       </c>
       <c r="X11" s="52" t="s">
+        <v>101</v>
+      </c>
+      <c r="Y11" s="50" t="s">
         <v>102</v>
-      </c>
-      <c r="Y11" s="50" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="12">
@@ -2399,10 +2396,10 @@
         <v>55</v>
       </c>
       <c r="F12" s="52" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G12" s="52" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H12" s="52">
         <v>9</v>
@@ -2426,13 +2423,13 @@
         <v>1</v>
       </c>
       <c r="O12" s="52" t="s">
+        <v>103</v>
+      </c>
+      <c r="P12" s="52" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q12" s="52" t="s">
         <v>104</v>
-      </c>
-      <c r="P12" s="52" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q12" s="52" t="s">
-        <v>105</v>
       </c>
       <c r="R12" s="52">
         <v>9</v>
@@ -2453,10 +2450,10 @@
         <v>9</v>
       </c>
       <c r="X12" s="52" t="s">
+        <v>105</v>
+      </c>
+      <c r="Y12" s="50" t="s">
         <v>106</v>
-      </c>
-      <c r="Y12" s="50" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="13">
@@ -2476,10 +2473,10 @@
         <v>55</v>
       </c>
       <c r="F13" s="52" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G13" s="52" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H13" s="52">
         <v>10</v>
@@ -2503,13 +2500,13 @@
         <v>1</v>
       </c>
       <c r="O13" s="52" t="s">
+        <v>107</v>
+      </c>
+      <c r="P13" s="52" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q13" s="52" t="s">
         <v>108</v>
-      </c>
-      <c r="P13" s="52" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q13" s="52" t="s">
-        <v>109</v>
       </c>
       <c r="R13" s="52">
         <v>10</v>
@@ -2530,10 +2527,10 @@
         <v>10</v>
       </c>
       <c r="X13" s="52" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y13" s="50" t="s">
         <v>110</v>
-      </c>
-      <c r="Y13" s="50" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="52" customFormat="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
@@ -1,19 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Unity\DemonLordRoguelike\Demon Lord Roguelike\Assets\Data\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="FightTypeConquerInfo" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="123">
   <si>
     <t>id</t>
   </si>
@@ -198,6 +217,9 @@
     <t>60</t>
   </si>
   <si>
+    <t>100-150</t>
+  </si>
+  <si>
     <t>剑与魔法-难度1</t>
   </si>
   <si>
@@ -228,6 +250,9 @@
     <t>9-10</t>
   </si>
   <si>
+    <t>200-250</t>
+  </si>
+  <si>
     <t>剑与魔法-难度2</t>
   </si>
   <si>
@@ -255,7 +280,7 @@
     <t>8-10</t>
   </si>
   <si>
-    <t>400</t>
+    <t>300-350</t>
   </si>
   <si>
     <t>剑与魔法-难度3</t>
@@ -276,6 +301,9 @@
     <t>7-10</t>
   </si>
   <si>
+    <t>400-450</t>
+  </si>
+  <si>
     <t>剑与魔法-难度4</t>
   </si>
   <si>
@@ -288,6 +316,9 @@
     <t>6-10</t>
   </si>
   <si>
+    <t>500-550</t>
+  </si>
+  <si>
     <t>剑与魔法-难度5</t>
   </si>
   <si>
@@ -303,6 +334,9 @@
     <t>5-10</t>
   </si>
   <si>
+    <t>600-650</t>
+  </si>
+  <si>
     <t>剑与魔法-难度6</t>
   </si>
   <si>
@@ -315,6 +349,9 @@
     <t>4-10</t>
   </si>
   <si>
+    <t>700-750</t>
+  </si>
+  <si>
     <t>剑与魔法-难度7</t>
   </si>
   <si>
@@ -327,6 +364,9 @@
     <t>3-10</t>
   </si>
   <si>
+    <t>800-850</t>
+  </si>
+  <si>
     <t>剑与魔法-难度8</t>
   </si>
   <si>
@@ -339,6 +379,9 @@
     <t>2-10</t>
   </si>
   <si>
+    <t>900-950</t>
+  </si>
+  <si>
     <t>剑与魔法-难度9</t>
   </si>
   <si>
@@ -349,6 +392,9 @@
   </si>
   <si>
     <t>1-10</t>
+  </si>
+  <si>
+    <t>1000-1200</t>
   </si>
   <si>
     <t>剑与魔法-难度10</t>
@@ -360,13 +406,19 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
   <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -374,6 +426,7 @@
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -381,12 +434,14 @@
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -394,6 +449,7 @@
       <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -401,6 +457,7 @@
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -408,6 +465,7 @@
       <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -415,6 +473,7 @@
       <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -422,12 +481,14 @@
       <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -435,6 +496,7 @@
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -442,6 +504,7 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -449,12 +512,14 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -462,30 +527,35 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -939,163 +1009,16 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="54">
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="2" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="3" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="4" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="5" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="7" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" xfId="8" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="9" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="4" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="10" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="11" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="6" applyFont="1" fillId="0" applyFill="1" borderId="2" applyBorder="1" xfId="12" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="7" applyFont="1" fillId="0" applyFill="1" borderId="2" applyBorder="1" xfId="13" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="8" applyFont="1" fillId="0" applyFill="1" borderId="3" applyBorder="1" xfId="14" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="8" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="15" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="9" applyFont="1" fillId="3" applyFill="1" borderId="4" applyBorder="1" xfId="16" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="10" applyFont="1" fillId="4" applyFill="1" borderId="5" applyBorder="1" xfId="17" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="11" applyFont="1" fillId="4" applyFill="1" borderId="4" applyBorder="1" xfId="18" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="12" applyFont="1" fillId="5" applyFill="1" borderId="6" applyBorder="1" xfId="19" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="13" applyFont="1" fillId="0" applyFill="1" borderId="7" applyBorder="1" xfId="20" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="14" applyFont="1" fillId="0" applyFill="1" borderId="8" applyBorder="1" xfId="21" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="15" applyFont="1" fillId="6" applyFill="1" borderId="0" applyBorder="1" xfId="22" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="16" applyFont="1" fillId="7" applyFill="1" borderId="0" applyBorder="1" xfId="23" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="17" applyFont="1" fillId="8" applyFill="1" borderId="0" applyBorder="1" xfId="24" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="9" applyFill="1" borderId="0" applyBorder="1" xfId="25" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="1" xfId="26" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="11" applyFill="1" borderId="0" applyBorder="1" xfId="27" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="12" applyFill="1" borderId="0" applyBorder="1" xfId="28" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="13" applyFill="1" borderId="0" applyBorder="1" xfId="29" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="14" applyFill="1" borderId="0" applyBorder="1" xfId="30" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="15" applyFill="1" borderId="0" applyBorder="1" xfId="31" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="16" applyFill="1" borderId="0" applyBorder="1" xfId="32" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="17" applyFill="1" borderId="0" applyBorder="1" xfId="33" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="18" applyFill="1" borderId="0" applyBorder="1" xfId="34" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="19" applyFill="1" borderId="0" applyBorder="1" xfId="35" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="20" applyFill="1" borderId="0" applyBorder="1" xfId="36" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="21" applyFill="1" borderId="0" applyBorder="1" xfId="37" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="22" applyFill="1" borderId="0" applyBorder="1" xfId="38" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="23" applyFill="1" borderId="0" applyBorder="1" xfId="39" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="24" applyFill="1" borderId="0" applyBorder="1" xfId="40" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="25" applyFill="1" borderId="0" applyBorder="1" xfId="41" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="26" applyFill="1" borderId="0" applyBorder="1" xfId="42" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="27" applyFill="1" borderId="0" applyBorder="1" xfId="43" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="28" applyFill="1" borderId="0" applyBorder="1" xfId="44" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="29" applyFill="1" borderId="0" applyBorder="1" xfId="45" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="30" applyFill="1" borderId="0" applyBorder="1" xfId="46" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="31" applyFill="1" borderId="0" applyBorder="1" xfId="47" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="32" applyFill="1" borderId="0" applyBorder="1" xfId="48" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1151,74 +1074,11 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1507,1056 +1367,1053 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Y13"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:Y81"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="3" max="3" width="16" customWidth="1" style="51"/>
-    <col min="4" max="4" width="17.125" customWidth="1" style="51"/>
-    <col min="5" max="5" width="36.5" customWidth="1" style="51"/>
-    <col min="6" max="6" width="23.75" customWidth="1" style="51"/>
-    <col min="7" max="7" width="18.375" customWidth="1" style="51"/>
-    <col min="8" max="8" width="31.875" customWidth="1" style="51"/>
-    <col min="9" max="9" width="18.25" customWidth="1" style="51"/>
-    <col min="10" max="16" width="16" customWidth="1" style="51"/>
-    <col min="17" max="17" width="12.25" customWidth="1" style="51"/>
-    <col min="18" max="18" width="12.875" customWidth="1" style="51"/>
-    <col min="19" max="19" width="27.125" customWidth="1" style="51"/>
-    <col min="20" max="20" width="17.375" customWidth="1" style="51"/>
-    <col min="21" max="21" width="36.875" customWidth="1" style="51"/>
-    <col min="22" max="22" width="29.375" customWidth="1" style="51"/>
-    <col min="23" max="23" width="42.875" customWidth="1" style="51"/>
-    <col min="24" max="24" width="25.125" customWidth="1" style="51"/>
+    <col min="3" max="3" width="16" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="36.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="23.75" style="1" customWidth="1"/>
+    <col min="7" max="7" width="18.375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="31.875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.25" style="1" customWidth="1"/>
+    <col min="10" max="16" width="16" style="1" customWidth="1"/>
+    <col min="17" max="17" width="12.25" style="1" customWidth="1"/>
+    <col min="18" max="18" width="12.875" style="1" customWidth="1"/>
+    <col min="19" max="19" width="27.125" style="1" customWidth="1"/>
+    <col min="20" max="20" width="17.375" style="1" customWidth="1"/>
+    <col min="21" max="21" width="36.875" style="1" customWidth="1"/>
+    <col min="22" max="22" width="29.375" style="1" customWidth="1"/>
+    <col min="23" max="23" width="42.875" style="1" customWidth="1"/>
+    <col min="24" max="24" width="25.125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="50" t="s">
+    <row r="1" spans="1:25">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="51" t="s">
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="51" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="51" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="51" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="51" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="51" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="51" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="51" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="51" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="51" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="51" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="51" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="51" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="51" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="51" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="51" t="s">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="51" t="s">
+      <c r="S1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="51" t="s">
+      <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="51" t="s">
+      <c r="U1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="51" t="s">
+      <c r="V1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="51" t="s">
+      <c r="W1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="51" t="s">
+      <c r="X1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="50" t="s">
+      <c r="Y1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="50" t="s">
+    <row r="2" spans="1:25">
+      <c r="A2" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="50" t="s">
+      <c r="B2" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="51" t="s">
+      <c r="C2" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="51" t="s">
+      <c r="D2" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="51" t="s">
+      <c r="E2" t="s">
         <v>27</v>
       </c>
-      <c r="F2" s="51" t="s">
+      <c r="F2" t="s">
         <v>27</v>
       </c>
-      <c r="G2" s="51" t="s">
+      <c r="G2" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="51" t="s">
+      <c r="H2" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="51" t="s">
+      <c r="I2" t="s">
         <v>26</v>
       </c>
-      <c r="J2" s="51" t="s">
+      <c r="J2" t="s">
         <v>28</v>
       </c>
-      <c r="K2" s="51" t="s">
+      <c r="K2" t="s">
         <v>28</v>
       </c>
-      <c r="L2" s="51" t="s">
+      <c r="L2" t="s">
         <v>26</v>
       </c>
-      <c r="M2" s="51" t="s">
+      <c r="M2" t="s">
         <v>28</v>
       </c>
-      <c r="N2" s="51" t="s">
+      <c r="N2" t="s">
         <v>28</v>
       </c>
-      <c r="O2" s="51" t="s">
+      <c r="O2" t="s">
         <v>27</v>
       </c>
-      <c r="P2" s="51" t="s">
+      <c r="P2" t="s">
         <v>27</v>
       </c>
-      <c r="Q2" s="51" t="s">
+      <c r="Q2" t="s">
         <v>27</v>
       </c>
-      <c r="R2" s="51" t="s">
+      <c r="R2" t="s">
         <v>26</v>
       </c>
-      <c r="S2" s="51" t="s">
+      <c r="S2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T2" t="s">
         <v>26</v>
       </c>
-      <c r="T2" s="51" t="s">
+      <c r="U2" t="s">
         <v>26</v>
       </c>
-      <c r="U2" s="51" t="s">
+      <c r="V2" t="s">
         <v>26</v>
       </c>
-      <c r="V2" s="51" t="s">
+      <c r="W2" t="s">
         <v>26</v>
       </c>
-      <c r="W2" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="X2" s="51" t="s">
+      <c r="X2" t="s">
         <v>27</v>
       </c>
-      <c r="Y2" s="50" t="s">
+      <c r="Y2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="50" t="s">
+    <row r="3" spans="1:25">
+      <c r="A3" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="50" t="s">
+      <c r="B3" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="51" t="s">
+      <c r="C3" t="s">
         <v>31</v>
       </c>
-      <c r="D3" s="51" t="s">
+      <c r="D3" t="s">
         <v>32</v>
       </c>
-      <c r="E3" s="51" t="s">
+      <c r="E3" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="51" t="s">
+      <c r="F3" t="s">
         <v>34</v>
       </c>
-      <c r="G3" s="51" t="s">
+      <c r="G3" t="s">
         <v>35</v>
       </c>
-      <c r="H3" s="51" t="s">
+      <c r="H3" t="s">
         <v>36</v>
       </c>
-      <c r="I3" s="51" t="s">
+      <c r="I3" t="s">
         <v>37</v>
       </c>
-      <c r="J3" s="51" t="s">
+      <c r="J3" t="s">
         <v>38</v>
       </c>
-      <c r="K3" s="51" t="s">
+      <c r="K3" t="s">
         <v>39</v>
       </c>
-      <c r="L3" s="51" t="s">
+      <c r="L3" t="s">
         <v>40</v>
       </c>
-      <c r="M3" s="51" t="s">
+      <c r="M3" t="s">
         <v>41</v>
       </c>
-      <c r="N3" s="51" t="s">
+      <c r="N3" t="s">
         <v>42</v>
       </c>
-      <c r="O3" s="51" t="s">
+      <c r="O3" t="s">
         <v>43</v>
       </c>
-      <c r="P3" s="51" t="s">
+      <c r="P3" t="s">
         <v>44</v>
       </c>
-      <c r="Q3" s="51" t="s">
+      <c r="Q3" t="s">
         <v>45</v>
       </c>
-      <c r="R3" s="51" t="s">
+      <c r="R3" t="s">
         <v>46</v>
       </c>
-      <c r="S3" s="51" t="s">
+      <c r="S3" t="s">
         <v>47</v>
       </c>
-      <c r="T3" s="51" t="s">
+      <c r="T3" t="s">
         <v>48</v>
       </c>
-      <c r="U3" s="51" t="s">
+      <c r="U3" t="s">
         <v>49</v>
       </c>
-      <c r="V3" s="51" t="s">
+      <c r="V3" t="s">
         <v>50</v>
       </c>
-      <c r="W3" s="51" t="s">
+      <c r="W3" t="s">
         <v>51</v>
       </c>
-      <c r="X3" s="51" t="s">
+      <c r="X3" t="s">
         <v>52</v>
       </c>
-      <c r="Y3" s="50" t="s">
+      <c r="Y3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="50">
+    <row r="4" spans="1:25">
+      <c r="A4">
         <v>1000001</v>
       </c>
-      <c r="B4" s="50">
-        <v>1</v>
-      </c>
-      <c r="C4" s="51">
-        <v>1</v>
-      </c>
-      <c r="D4" s="51" t="s">
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
         <v>54</v>
       </c>
-      <c r="E4" s="51" t="s">
+      <c r="E4" t="s">
         <v>55</v>
       </c>
-      <c r="F4" s="51" t="s">
+      <c r="F4" t="s">
         <v>56</v>
       </c>
-      <c r="G4" s="51" t="s">
+      <c r="G4" t="s">
         <v>57</v>
       </c>
-      <c r="H4" s="51" t="s">
+      <c r="H4" t="s">
         <v>58</v>
       </c>
-      <c r="I4" s="51" t="s">
+      <c r="I4" t="s">
         <v>59</v>
       </c>
-      <c r="J4" s="51" t="s">
+      <c r="J4" t="s">
         <v>60</v>
       </c>
-      <c r="K4" s="51">
-        <v>1</v>
-      </c>
-      <c r="L4" s="51" t="s">
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4" t="s">
         <v>59</v>
       </c>
-      <c r="M4" s="51">
-        <v>1</v>
-      </c>
-      <c r="N4" s="51">
-        <v>1</v>
-      </c>
-      <c r="O4" s="51">
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="O4">
         <v>5</v>
       </c>
-      <c r="P4" s="51">
+      <c r="P4">
         <v>2</v>
       </c>
-      <c r="Q4" s="51">
+      <c r="Q4">
         <v>10</v>
       </c>
-      <c r="R4" s="51">
-        <v>1</v>
-      </c>
-      <c r="S4" s="51">
+      <c r="R4">
+        <v>1</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="T4">
+        <v>1</v>
+      </c>
+      <c r="U4">
+        <v>10</v>
+      </c>
+      <c r="V4">
+        <v>50</v>
+      </c>
+      <c r="W4">
+        <v>1</v>
+      </c>
+      <c r="X4" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25">
+      <c r="A5">
+        <v>1000002</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F5" t="s">
+        <v>65</v>
+      </c>
+      <c r="G5" t="s">
+        <v>66</v>
+      </c>
+      <c r="H5" t="s">
+        <v>67</v>
+      </c>
+      <c r="I5">
+        <v>20</v>
+      </c>
+      <c r="J5">
+        <v>60</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5" t="s">
+        <v>68</v>
+      </c>
+      <c r="M5" t="s">
+        <v>58</v>
+      </c>
+      <c r="N5" t="s">
+        <v>69</v>
+      </c>
+      <c r="O5" t="s">
+        <v>70</v>
+      </c>
+      <c r="P5">
+        <v>3</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="R5">
+        <v>2</v>
+      </c>
+      <c r="S5" t="s">
+        <v>72</v>
+      </c>
+      <c r="T5">
+        <v>1</v>
+      </c>
+      <c r="U5">
+        <v>20</v>
+      </c>
+      <c r="V5">
         <v>100</v>
       </c>
-      <c r="T4" s="51">
-        <v>1</v>
-      </c>
-      <c r="U4" s="51">
+      <c r="W5">
+        <v>2</v>
+      </c>
+      <c r="X5" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25">
+      <c r="A6">
+        <v>1000003</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G6" t="s">
+        <v>76</v>
+      </c>
+      <c r="H6">
+        <v>3</v>
+      </c>
+      <c r="I6">
+        <v>30</v>
+      </c>
+      <c r="J6">
+        <v>60</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6" t="s">
+        <v>77</v>
+      </c>
+      <c r="M6" t="s">
+        <v>58</v>
+      </c>
+      <c r="N6" t="s">
+        <v>78</v>
+      </c>
+      <c r="O6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P6" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>81</v>
+      </c>
+      <c r="R6">
+        <v>3</v>
+      </c>
+      <c r="S6" t="s">
+        <v>82</v>
+      </c>
+      <c r="T6">
+        <v>2</v>
+      </c>
+      <c r="U6">
+        <v>30</v>
+      </c>
+      <c r="V6">
+        <v>150</v>
+      </c>
+      <c r="W6">
+        <v>3</v>
+      </c>
+      <c r="X6" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25">
+      <c r="A7">
+        <v>1000004</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>4</v>
+      </c>
+      <c r="D7" t="s">
+        <v>64</v>
+      </c>
+      <c r="E7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F7" t="s">
+        <v>85</v>
+      </c>
+      <c r="G7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H7">
+        <v>4</v>
+      </c>
+      <c r="I7">
+        <v>40</v>
+      </c>
+      <c r="J7">
+        <v>60</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>2</v>
+      </c>
+      <c r="M7">
+        <v>2.5</v>
+      </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="O7" t="s">
+        <v>86</v>
+      </c>
+      <c r="P7" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>88</v>
+      </c>
+      <c r="R7">
+        <v>4</v>
+      </c>
+      <c r="S7" t="s">
+        <v>89</v>
+      </c>
+      <c r="T7">
+        <v>2</v>
+      </c>
+      <c r="U7">
+        <v>40</v>
+      </c>
+      <c r="V7">
+        <v>200</v>
+      </c>
+      <c r="W7">
+        <v>4</v>
+      </c>
+      <c r="X7" t="s">
+        <v>90</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25">
+      <c r="A8">
+        <v>1000005</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+      <c r="D8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G8" t="s">
+        <v>85</v>
+      </c>
+      <c r="H8">
+        <v>5</v>
+      </c>
+      <c r="I8">
+        <v>50</v>
+      </c>
+      <c r="J8">
+        <v>60</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>2</v>
+      </c>
+      <c r="M8">
+        <v>3</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8" t="s">
+        <v>88</v>
+      </c>
+      <c r="P8" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>93</v>
+      </c>
+      <c r="R8">
+        <v>5</v>
+      </c>
+      <c r="S8" t="s">
+        <v>94</v>
+      </c>
+      <c r="T8">
+        <v>2</v>
+      </c>
+      <c r="U8">
+        <v>50</v>
+      </c>
+      <c r="V8">
+        <v>250</v>
+      </c>
+      <c r="W8">
+        <v>5</v>
+      </c>
+      <c r="X8" t="s">
+        <v>95</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25">
+      <c r="A9">
+        <v>1000006</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>6</v>
+      </c>
+      <c r="D9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" t="s">
+        <v>85</v>
+      </c>
+      <c r="G9" t="s">
+        <v>85</v>
+      </c>
+      <c r="H9">
+        <v>6</v>
+      </c>
+      <c r="I9">
+        <v>60</v>
+      </c>
+      <c r="J9">
+        <v>60</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>2</v>
+      </c>
+      <c r="M9">
+        <v>3.5</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="O9" t="s">
+        <v>97</v>
+      </c>
+      <c r="P9" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>99</v>
+      </c>
+      <c r="R9">
+        <v>6</v>
+      </c>
+      <c r="S9" t="s">
+        <v>100</v>
+      </c>
+      <c r="T9">
+        <v>3</v>
+      </c>
+      <c r="U9">
+        <v>60</v>
+      </c>
+      <c r="V9">
+        <v>300</v>
+      </c>
+      <c r="W9">
+        <v>6</v>
+      </c>
+      <c r="X9" t="s">
+        <v>101</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25">
+      <c r="A10">
+        <v>1000007</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>7</v>
+      </c>
+      <c r="D10" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" t="s">
+        <v>85</v>
+      </c>
+      <c r="G10" t="s">
+        <v>85</v>
+      </c>
+      <c r="H10">
+        <v>7</v>
+      </c>
+      <c r="I10">
+        <v>70</v>
+      </c>
+      <c r="J10">
+        <v>60</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>2</v>
+      </c>
+      <c r="M10">
+        <v>4</v>
+      </c>
+      <c r="N10">
+        <v>1</v>
+      </c>
+      <c r="O10" t="s">
+        <v>103</v>
+      </c>
+      <c r="P10" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>104</v>
+      </c>
+      <c r="R10">
+        <v>7</v>
+      </c>
+      <c r="S10" t="s">
+        <v>105</v>
+      </c>
+      <c r="T10">
+        <v>3</v>
+      </c>
+      <c r="U10">
+        <v>70</v>
+      </c>
+      <c r="V10">
+        <v>350</v>
+      </c>
+      <c r="W10">
+        <v>7</v>
+      </c>
+      <c r="X10" t="s">
+        <v>106</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25">
+      <c r="A11">
+        <v>1000008</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>8</v>
+      </c>
+      <c r="D11" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" t="s">
+        <v>55</v>
+      </c>
+      <c r="F11" t="s">
+        <v>85</v>
+      </c>
+      <c r="G11" t="s">
+        <v>85</v>
+      </c>
+      <c r="H11">
+        <v>8</v>
+      </c>
+      <c r="I11">
+        <v>80</v>
+      </c>
+      <c r="J11">
+        <v>60</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>2</v>
+      </c>
+      <c r="M11">
+        <v>4.5</v>
+      </c>
+      <c r="N11">
+        <v>1</v>
+      </c>
+      <c r="O11" t="s">
+        <v>108</v>
+      </c>
+      <c r="P11" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>109</v>
+      </c>
+      <c r="R11">
+        <v>8</v>
+      </c>
+      <c r="S11" t="s">
+        <v>110</v>
+      </c>
+      <c r="T11">
+        <v>3</v>
+      </c>
+      <c r="U11">
+        <v>80</v>
+      </c>
+      <c r="V11">
+        <v>400</v>
+      </c>
+      <c r="W11">
+        <v>8</v>
+      </c>
+      <c r="X11" t="s">
+        <v>111</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25">
+      <c r="A12">
+        <v>1000009</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>9</v>
+      </c>
+      <c r="D12" t="s">
+        <v>64</v>
+      </c>
+      <c r="E12" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12" t="s">
+        <v>85</v>
+      </c>
+      <c r="G12" t="s">
+        <v>85</v>
+      </c>
+      <c r="H12">
+        <v>9</v>
+      </c>
+      <c r="I12">
+        <v>90</v>
+      </c>
+      <c r="J12">
+        <v>60</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>2</v>
+      </c>
+      <c r="M12">
+        <v>5</v>
+      </c>
+      <c r="N12">
+        <v>1</v>
+      </c>
+      <c r="O12" t="s">
+        <v>113</v>
+      </c>
+      <c r="P12" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>114</v>
+      </c>
+      <c r="R12">
+        <v>9</v>
+      </c>
+      <c r="S12" t="s">
+        <v>115</v>
+      </c>
+      <c r="T12">
+        <v>4</v>
+      </c>
+      <c r="U12">
+        <v>90</v>
+      </c>
+      <c r="V12">
+        <v>450</v>
+      </c>
+      <c r="W12">
+        <v>9</v>
+      </c>
+      <c r="X12" t="s">
+        <v>116</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25">
+      <c r="A13">
+        <v>1000010</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
         <v>10</v>
       </c>
-      <c r="V4" s="51">
-        <v>50</v>
-      </c>
-      <c r="W4" s="51">
-        <v>1</v>
-      </c>
-      <c r="X4" s="51" t="s">
-        <v>61</v>
-      </c>
-      <c r="Y4" s="50" t="s">
-        <v>62</v>
+      <c r="D13" t="s">
+        <v>64</v>
+      </c>
+      <c r="E13" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" t="s">
+        <v>85</v>
+      </c>
+      <c r="G13" t="s">
+        <v>85</v>
+      </c>
+      <c r="H13">
+        <v>10</v>
+      </c>
+      <c r="I13">
+        <v>100</v>
+      </c>
+      <c r="J13">
+        <v>60</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>2</v>
+      </c>
+      <c r="M13">
+        <v>5.5</v>
+      </c>
+      <c r="N13">
+        <v>1</v>
+      </c>
+      <c r="O13" t="s">
+        <v>118</v>
+      </c>
+      <c r="P13" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>119</v>
+      </c>
+      <c r="R13">
+        <v>10</v>
+      </c>
+      <c r="S13" t="s">
+        <v>120</v>
+      </c>
+      <c r="T13">
+        <v>4</v>
+      </c>
+      <c r="U13">
+        <v>100</v>
+      </c>
+      <c r="V13">
+        <v>500</v>
+      </c>
+      <c r="W13">
+        <v>10</v>
+      </c>
+      <c r="X13" t="s">
+        <v>121</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>122</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="50">
-        <v>1000002</v>
-      </c>
-      <c r="B5" s="50">
-        <v>1</v>
-      </c>
-      <c r="C5" s="51">
-        <v>2</v>
-      </c>
-      <c r="D5" s="51" t="s">
-        <v>63</v>
-      </c>
-      <c r="E5" s="51" t="s">
-        <v>55</v>
-      </c>
-      <c r="F5" s="51" t="s">
-        <v>64</v>
-      </c>
-      <c r="G5" s="51" t="s">
-        <v>65</v>
-      </c>
-      <c r="H5" s="51" t="s">
-        <v>66</v>
-      </c>
-      <c r="I5" s="51">
-        <v>20</v>
-      </c>
-      <c r="J5" s="51">
-        <v>60</v>
-      </c>
-      <c r="K5" s="51">
-        <v>1</v>
-      </c>
-      <c r="L5" s="51" t="s">
-        <v>67</v>
-      </c>
-      <c r="M5" s="51" t="s">
-        <v>58</v>
-      </c>
-      <c r="N5" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="O5" s="51" t="s">
-        <v>69</v>
-      </c>
-      <c r="P5" s="51">
-        <v>3</v>
-      </c>
-      <c r="Q5" s="52" t="s">
-        <v>70</v>
-      </c>
-      <c r="R5" s="51">
-        <v>2</v>
-      </c>
-      <c r="S5" s="51">
-        <v>200</v>
-      </c>
-      <c r="T5" s="51">
-        <v>1</v>
-      </c>
-      <c r="U5" s="51">
-        <v>20</v>
-      </c>
-      <c r="V5" s="51">
-        <v>100</v>
-      </c>
-      <c r="W5" s="51">
-        <v>2</v>
-      </c>
-      <c r="X5" s="51" t="s">
-        <v>71</v>
-      </c>
-      <c r="Y5" s="50" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="50">
-        <v>1000003</v>
-      </c>
-      <c r="B6" s="50">
-        <v>1</v>
-      </c>
-      <c r="C6" s="51">
-        <v>3</v>
-      </c>
-      <c r="D6" s="51" t="s">
-        <v>63</v>
-      </c>
-      <c r="E6" s="51" t="s">
-        <v>55</v>
-      </c>
-      <c r="F6" s="51" t="s">
-        <v>73</v>
-      </c>
-      <c r="G6" s="51" t="s">
-        <v>74</v>
-      </c>
-      <c r="H6" s="51">
-        <v>3</v>
-      </c>
-      <c r="I6" s="51">
-        <v>30</v>
-      </c>
-      <c r="J6" s="51">
-        <v>60</v>
-      </c>
-      <c r="K6" s="51">
-        <v>1</v>
-      </c>
-      <c r="L6" s="51" t="s">
-        <v>75</v>
-      </c>
-      <c r="M6" s="51" t="s">
-        <v>58</v>
-      </c>
-      <c r="N6" s="51" t="s">
-        <v>76</v>
-      </c>
-      <c r="O6" s="51" t="s">
-        <v>77</v>
-      </c>
-      <c r="P6" s="53" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q6" s="51" t="s">
-        <v>79</v>
-      </c>
-      <c r="R6" s="51">
-        <v>3</v>
-      </c>
-      <c r="S6" s="51" t="s">
-        <v>80</v>
-      </c>
-      <c r="T6" s="51">
-        <v>2</v>
-      </c>
-      <c r="U6" s="51">
-        <v>30</v>
-      </c>
-      <c r="V6" s="51">
-        <v>150</v>
-      </c>
-      <c r="W6" s="51">
-        <v>3</v>
-      </c>
-      <c r="X6" s="51" t="s">
-        <v>81</v>
-      </c>
-      <c r="Y6" s="50" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="50">
-        <v>1000004</v>
-      </c>
-      <c r="B7" s="50">
-        <v>1</v>
-      </c>
-      <c r="C7" s="51">
-        <v>4</v>
-      </c>
-      <c r="D7" s="51" t="s">
-        <v>63</v>
-      </c>
-      <c r="E7" s="51" t="s">
-        <v>55</v>
-      </c>
-      <c r="F7" s="51" t="s">
-        <v>83</v>
-      </c>
-      <c r="G7" s="51" t="s">
-        <v>83</v>
-      </c>
-      <c r="H7" s="51">
-        <v>4</v>
-      </c>
-      <c r="I7" s="51">
-        <v>40</v>
-      </c>
-      <c r="J7" s="51">
-        <v>60</v>
-      </c>
-      <c r="K7" s="51">
-        <v>1</v>
-      </c>
-      <c r="L7" s="51">
-        <v>2</v>
-      </c>
-      <c r="M7" s="51">
-        <v>2.5</v>
-      </c>
-      <c r="N7" s="51">
-        <v>1</v>
-      </c>
-      <c r="O7" s="51" t="s">
-        <v>84</v>
-      </c>
-      <c r="P7" s="53" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q7" s="51" t="s">
-        <v>86</v>
-      </c>
-      <c r="R7" s="51">
-        <v>4</v>
-      </c>
-      <c r="S7" s="51">
-        <v>400</v>
-      </c>
-      <c r="T7" s="51">
-        <v>2</v>
-      </c>
-      <c r="U7" s="51">
-        <v>40</v>
-      </c>
-      <c r="V7" s="51">
-        <v>200</v>
-      </c>
-      <c r="W7" s="51">
-        <v>4</v>
-      </c>
-      <c r="X7" s="51" t="s">
-        <v>87</v>
-      </c>
-      <c r="Y7" s="50" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="50">
-        <v>1000005</v>
-      </c>
-      <c r="B8" s="50">
-        <v>1</v>
-      </c>
-      <c r="C8" s="51">
-        <v>5</v>
-      </c>
-      <c r="D8" s="51" t="s">
-        <v>63</v>
-      </c>
-      <c r="E8" s="51" t="s">
-        <v>55</v>
-      </c>
-      <c r="F8" s="51" t="s">
-        <v>83</v>
-      </c>
-      <c r="G8" s="51" t="s">
-        <v>83</v>
-      </c>
-      <c r="H8" s="51">
-        <v>5</v>
-      </c>
-      <c r="I8" s="51">
-        <v>50</v>
-      </c>
-      <c r="J8" s="51">
-        <v>60</v>
-      </c>
-      <c r="K8" s="51">
-        <v>1</v>
-      </c>
-      <c r="L8" s="51">
-        <v>2</v>
-      </c>
-      <c r="M8" s="51">
-        <v>3</v>
-      </c>
-      <c r="N8" s="51">
-        <v>1</v>
-      </c>
-      <c r="O8" s="51" t="s">
-        <v>86</v>
-      </c>
-      <c r="P8" s="53" t="s">
-        <v>89</v>
-      </c>
-      <c r="Q8" s="51" t="s">
-        <v>90</v>
-      </c>
-      <c r="R8" s="51">
-        <v>5</v>
-      </c>
-      <c r="S8" s="51">
-        <v>500</v>
-      </c>
-      <c r="T8" s="51">
-        <v>2</v>
-      </c>
-      <c r="U8" s="51">
-        <v>50</v>
-      </c>
-      <c r="V8" s="51">
-        <v>250</v>
-      </c>
-      <c r="W8" s="51">
-        <v>5</v>
-      </c>
-      <c r="X8" s="51" t="s">
-        <v>91</v>
-      </c>
-      <c r="Y8" s="50" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="50">
-        <v>1000006</v>
-      </c>
-      <c r="B9" s="50">
-        <v>1</v>
-      </c>
-      <c r="C9" s="51">
-        <v>6</v>
-      </c>
-      <c r="D9" s="51" t="s">
-        <v>63</v>
-      </c>
-      <c r="E9" s="51" t="s">
-        <v>55</v>
-      </c>
-      <c r="F9" s="51" t="s">
-        <v>83</v>
-      </c>
-      <c r="G9" s="51" t="s">
-        <v>83</v>
-      </c>
-      <c r="H9" s="51">
-        <v>6</v>
-      </c>
-      <c r="I9" s="51">
-        <v>60</v>
-      </c>
-      <c r="J9" s="51">
-        <v>60</v>
-      </c>
-      <c r="K9" s="51">
-        <v>1</v>
-      </c>
-      <c r="L9" s="51">
-        <v>2</v>
-      </c>
-      <c r="M9" s="51">
-        <v>3.5</v>
-      </c>
-      <c r="N9" s="51">
-        <v>1</v>
-      </c>
-      <c r="O9" s="51" t="s">
-        <v>93</v>
-      </c>
-      <c r="P9" s="51" t="s">
-        <v>94</v>
-      </c>
-      <c r="Q9" s="51" t="s">
-        <v>95</v>
-      </c>
-      <c r="R9" s="51">
-        <v>6</v>
-      </c>
-      <c r="S9" s="51">
-        <v>600</v>
-      </c>
-      <c r="T9" s="51">
-        <v>3</v>
-      </c>
-      <c r="U9" s="51">
-        <v>60</v>
-      </c>
-      <c r="V9" s="51">
-        <v>300</v>
-      </c>
-      <c r="W9" s="51">
-        <v>6</v>
-      </c>
-      <c r="X9" s="51" t="s">
-        <v>96</v>
-      </c>
-      <c r="Y9" s="50" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="50">
-        <v>1000007</v>
-      </c>
-      <c r="B10" s="50">
-        <v>1</v>
-      </c>
-      <c r="C10" s="51">
-        <v>7</v>
-      </c>
-      <c r="D10" s="51" t="s">
-        <v>63</v>
-      </c>
-      <c r="E10" s="51" t="s">
-        <v>55</v>
-      </c>
-      <c r="F10" s="51" t="s">
-        <v>83</v>
-      </c>
-      <c r="G10" s="51" t="s">
-        <v>83</v>
-      </c>
-      <c r="H10" s="51">
-        <v>7</v>
-      </c>
-      <c r="I10" s="51">
-        <v>70</v>
-      </c>
-      <c r="J10" s="51">
-        <v>60</v>
-      </c>
-      <c r="K10" s="51">
-        <v>1</v>
-      </c>
-      <c r="L10" s="51">
-        <v>2</v>
-      </c>
-      <c r="M10" s="51">
-        <v>4</v>
-      </c>
-      <c r="N10" s="51">
-        <v>1</v>
-      </c>
-      <c r="O10" s="51" t="s">
-        <v>98</v>
-      </c>
-      <c r="P10" s="51" t="s">
-        <v>94</v>
-      </c>
-      <c r="Q10" s="51" t="s">
-        <v>99</v>
-      </c>
-      <c r="R10" s="51">
-        <v>7</v>
-      </c>
-      <c r="S10" s="51">
-        <v>700</v>
-      </c>
-      <c r="T10" s="51">
-        <v>3</v>
-      </c>
-      <c r="U10" s="51">
-        <v>70</v>
-      </c>
-      <c r="V10" s="51">
-        <v>350</v>
-      </c>
-      <c r="W10" s="51">
-        <v>7</v>
-      </c>
-      <c r="X10" s="51" t="s">
-        <v>100</v>
-      </c>
-      <c r="Y10" s="50" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="50">
-        <v>1000008</v>
-      </c>
-      <c r="B11" s="50">
-        <v>1</v>
-      </c>
-      <c r="C11" s="51">
-        <v>8</v>
-      </c>
-      <c r="D11" s="51" t="s">
-        <v>63</v>
-      </c>
-      <c r="E11" s="51" t="s">
-        <v>55</v>
-      </c>
-      <c r="F11" s="51" t="s">
-        <v>83</v>
-      </c>
-      <c r="G11" s="51" t="s">
-        <v>83</v>
-      </c>
-      <c r="H11" s="51">
-        <v>8</v>
-      </c>
-      <c r="I11" s="51">
-        <v>80</v>
-      </c>
-      <c r="J11" s="51">
-        <v>60</v>
-      </c>
-      <c r="K11" s="51">
-        <v>1</v>
-      </c>
-      <c r="L11" s="51">
-        <v>2</v>
-      </c>
-      <c r="M11" s="51">
-        <v>4.5</v>
-      </c>
-      <c r="N11" s="51">
-        <v>1</v>
-      </c>
-      <c r="O11" s="51" t="s">
-        <v>102</v>
-      </c>
-      <c r="P11" s="51" t="s">
-        <v>94</v>
-      </c>
-      <c r="Q11" s="51" t="s">
-        <v>103</v>
-      </c>
-      <c r="R11" s="51">
-        <v>8</v>
-      </c>
-      <c r="S11" s="51">
-        <v>800</v>
-      </c>
-      <c r="T11" s="51">
-        <v>3</v>
-      </c>
-      <c r="U11" s="51">
-        <v>80</v>
-      </c>
-      <c r="V11" s="51">
-        <v>400</v>
-      </c>
-      <c r="W11" s="51">
-        <v>8</v>
-      </c>
-      <c r="X11" s="51" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y11" s="50" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="50">
-        <v>1000009</v>
-      </c>
-      <c r="B12" s="50">
-        <v>1</v>
-      </c>
-      <c r="C12" s="51">
-        <v>9</v>
-      </c>
-      <c r="D12" s="51" t="s">
-        <v>63</v>
-      </c>
-      <c r="E12" s="51" t="s">
-        <v>55</v>
-      </c>
-      <c r="F12" s="51" t="s">
-        <v>83</v>
-      </c>
-      <c r="G12" s="51" t="s">
-        <v>83</v>
-      </c>
-      <c r="H12" s="51">
-        <v>9</v>
-      </c>
-      <c r="I12" s="51">
-        <v>90</v>
-      </c>
-      <c r="J12" s="51">
-        <v>60</v>
-      </c>
-      <c r="K12" s="51">
-        <v>1</v>
-      </c>
-      <c r="L12" s="51">
-        <v>2</v>
-      </c>
-      <c r="M12" s="51">
-        <v>5</v>
-      </c>
-      <c r="N12" s="51">
-        <v>1</v>
-      </c>
-      <c r="O12" s="51" t="s">
-        <v>106</v>
-      </c>
-      <c r="P12" s="51" t="s">
-        <v>94</v>
-      </c>
-      <c r="Q12" s="51" t="s">
-        <v>107</v>
-      </c>
-      <c r="R12" s="51">
-        <v>9</v>
-      </c>
-      <c r="S12" s="51">
-        <v>900</v>
-      </c>
-      <c r="T12" s="51">
-        <v>4</v>
-      </c>
-      <c r="U12" s="51">
-        <v>90</v>
-      </c>
-      <c r="V12" s="51">
-        <v>450</v>
-      </c>
-      <c r="W12" s="51">
-        <v>9</v>
-      </c>
-      <c r="X12" s="51" t="s">
-        <v>108</v>
-      </c>
-      <c r="Y12" s="50" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="50">
-        <v>1000010</v>
-      </c>
-      <c r="B13" s="50">
-        <v>1</v>
-      </c>
-      <c r="C13" s="51">
-        <v>10</v>
-      </c>
-      <c r="D13" s="51" t="s">
-        <v>63</v>
-      </c>
-      <c r="E13" s="51" t="s">
-        <v>55</v>
-      </c>
-      <c r="F13" s="51" t="s">
-        <v>83</v>
-      </c>
-      <c r="G13" s="51" t="s">
-        <v>83</v>
-      </c>
-      <c r="H13" s="51">
-        <v>10</v>
-      </c>
-      <c r="I13" s="51">
-        <v>100</v>
-      </c>
-      <c r="J13" s="51">
-        <v>60</v>
-      </c>
-      <c r="K13" s="51">
-        <v>1</v>
-      </c>
-      <c r="L13" s="51">
-        <v>2</v>
-      </c>
-      <c r="M13" s="51">
-        <v>5.5</v>
-      </c>
-      <c r="N13" s="51">
-        <v>1</v>
-      </c>
-      <c r="O13" s="51" t="s">
-        <v>110</v>
-      </c>
-      <c r="P13" s="51" t="s">
-        <v>94</v>
-      </c>
-      <c r="Q13" s="51" t="s">
-        <v>111</v>
-      </c>
-      <c r="R13" s="51">
-        <v>10</v>
-      </c>
-      <c r="S13" s="51">
-        <v>1000</v>
-      </c>
-      <c r="T13" s="51">
-        <v>4</v>
-      </c>
-      <c r="U13" s="51">
-        <v>100</v>
-      </c>
-      <c r="V13" s="51">
-        <v>500</v>
-      </c>
-      <c r="W13" s="51">
-        <v>10</v>
-      </c>
-      <c r="X13" s="51" t="s">
-        <v>112</v>
-      </c>
-      <c r="Y13" s="50" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="32" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="33" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="34" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="35" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="36" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="37" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="38" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="39" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="40" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="41" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="73" ht="12" customHeight="1" s="51" customFormat="1"/>
-    <row r="74" ht="12" customHeight="1" s="51" customFormat="1"/>
-    <row r="75" ht="12" customHeight="1" s="51" customFormat="1"/>
-    <row r="76" ht="12" customHeight="1" s="51" customFormat="1"/>
-    <row r="77" ht="12" customHeight="1" s="51" customFormat="1"/>
-    <row r="78" ht="12" customHeight="1" s="51" customFormat="1"/>
-    <row r="79" ht="12" customHeight="1" s="51" customFormat="1"/>
-    <row r="80" ht="12" customHeight="1" s="51" customFormat="1"/>
-    <row r="81" ht="12" customHeight="1" s="51" customFormat="1"/>
+    <row r="31" ht="15" customHeight="1"/>
+    <row r="32" ht="15" customHeight="1"/>
+    <row r="33" ht="15" customHeight="1"/>
+    <row r="34" ht="15" customHeight="1"/>
+    <row r="35" ht="15" customHeight="1"/>
+    <row r="36" ht="15" customHeight="1"/>
+    <row r="37" ht="15" customHeight="1"/>
+    <row r="38" ht="15" customHeight="1"/>
+    <row r="39" ht="15" customHeight="1"/>
+    <row r="40" ht="15" customHeight="1"/>
+    <row r="41" ht="15" customHeight="1"/>
+    <row r="73" ht="12" customHeight="1"/>
+    <row r="74" ht="12" customHeight="1"/>
+    <row r="75" ht="12" customHeight="1"/>
+    <row r="76" ht="12" customHeight="1"/>
+    <row r="77" ht="12" customHeight="1"/>
+    <row r="78" ht="12" customHeight="1"/>
+    <row r="79" ht="12" customHeight="1"/>
+    <row r="80" ht="12" customHeight="1"/>
+    <row r="81" ht="12" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
@@ -14,7 +14,7 @@
   <sheets>
     <sheet name="FightTypeConquerInfo" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="124">
   <si>
     <t>id</t>
   </si>
@@ -263,6 +263,9 @@
   </si>
   <si>
     <t>1020020001&amp;1020030001&amp;1031010001&amp;1031020001</t>
+  </si>
+  <si>
+    <t>40</t>
   </si>
   <si>
     <t>20</t>
@@ -418,7 +421,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -426,7 +428,6 @@
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -434,14 +435,12 @@
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -449,7 +448,6 @@
       <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -457,7 +455,6 @@
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -465,7 +462,6 @@
       <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -473,7 +469,6 @@
       <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -481,14 +476,12 @@
       <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -496,7 +489,6 @@
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -504,7 +496,6 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -512,14 +503,12 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -527,35 +516,30 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1009,16 +993,163 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+  <cellXfs count="54">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="2" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="3" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="4" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="5" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="7" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" xfId="8" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="9" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="4" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="10" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="11" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="6" applyFont="1" fillId="0" applyFill="1" borderId="2" applyBorder="1" xfId="12" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="7" applyFont="1" fillId="0" applyFill="1" borderId="2" applyBorder="1" xfId="13" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="8" applyFont="1" fillId="0" applyFill="1" borderId="3" applyBorder="1" xfId="14" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="8" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="15" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="9" applyFont="1" fillId="3" applyFill="1" borderId="4" applyBorder="1" xfId="16" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="10" applyFont="1" fillId="4" applyFill="1" borderId="5" applyBorder="1" xfId="17" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="11" applyFont="1" fillId="4" applyFill="1" borderId="4" applyBorder="1" xfId="18" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="12" applyFont="1" fillId="5" applyFill="1" borderId="6" applyBorder="1" xfId="19" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="13" applyFont="1" fillId="0" applyFill="1" borderId="7" applyBorder="1" xfId="20" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="14" applyFont="1" fillId="0" applyFill="1" borderId="8" applyBorder="1" xfId="21" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="15" applyFont="1" fillId="6" applyFill="1" borderId="0" applyBorder="1" xfId="22" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="16" applyFont="1" fillId="7" applyFill="1" borderId="0" applyBorder="1" xfId="23" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="17" applyFont="1" fillId="8" applyFill="1" borderId="0" applyBorder="1" xfId="24" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="9" applyFill="1" borderId="0" applyBorder="1" xfId="25" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="1" xfId="26" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="11" applyFill="1" borderId="0" applyBorder="1" xfId="27" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="12" applyFill="1" borderId="0" applyBorder="1" xfId="28" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="13" applyFill="1" borderId="0" applyBorder="1" xfId="29" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="14" applyFill="1" borderId="0" applyBorder="1" xfId="30" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="15" applyFill="1" borderId="0" applyBorder="1" xfId="31" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="16" applyFill="1" borderId="0" applyBorder="1" xfId="32" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="17" applyFill="1" borderId="0" applyBorder="1" xfId="33" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="18" applyFill="1" borderId="0" applyBorder="1" xfId="34" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="19" applyFill="1" borderId="0" applyBorder="1" xfId="35" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="20" applyFill="1" borderId="0" applyBorder="1" xfId="36" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="21" applyFill="1" borderId="0" applyBorder="1" xfId="37" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="22" applyFill="1" borderId="0" applyBorder="1" xfId="38" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="23" applyFill="1" borderId="0" applyBorder="1" xfId="39" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="24" applyFill="1" borderId="0" applyBorder="1" xfId="40" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="25" applyFill="1" borderId="0" applyBorder="1" xfId="41" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="26" applyFill="1" borderId="0" applyBorder="1" xfId="42" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="27" applyFill="1" borderId="0" applyBorder="1" xfId="43" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="28" applyFill="1" borderId="0" applyBorder="1" xfId="44" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="29" applyFill="1" borderId="0" applyBorder="1" xfId="45" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="30" applyFill="1" borderId="0" applyBorder="1" xfId="46" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="31" applyFill="1" borderId="0" applyBorder="1" xfId="47" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="32" applyFill="1" borderId="0" applyBorder="1" xfId="48" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="3" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="49" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1369,1026 +1500,1026 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Y81"/>
+  <dimension ref="A1:Y13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="3" max="3" width="16" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="36.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="23.75" style="1" customWidth="1"/>
-    <col min="7" max="7" width="18.375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="31.875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="18.25" style="1" customWidth="1"/>
-    <col min="10" max="16" width="16" style="1" customWidth="1"/>
-    <col min="17" max="17" width="12.25" style="1" customWidth="1"/>
-    <col min="18" max="18" width="12.875" style="1" customWidth="1"/>
-    <col min="19" max="19" width="27.125" style="1" customWidth="1"/>
-    <col min="20" max="20" width="17.375" style="1" customWidth="1"/>
-    <col min="21" max="21" width="36.875" style="1" customWidth="1"/>
-    <col min="22" max="22" width="29.375" style="1" customWidth="1"/>
-    <col min="23" max="23" width="42.875" style="1" customWidth="1"/>
-    <col min="24" max="24" width="25.125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1" style="50"/>
+    <col min="4" max="4" width="17.125" customWidth="1" style="50"/>
+    <col min="5" max="5" width="36.5" customWidth="1" style="50"/>
+    <col min="6" max="6" width="23.75" customWidth="1" style="50"/>
+    <col min="7" max="7" width="18.375" customWidth="1" style="50"/>
+    <col min="8" max="8" width="31.875" customWidth="1" style="50"/>
+    <col min="9" max="9" width="18.25" customWidth="1" style="50"/>
+    <col min="10" max="16" width="16" customWidth="1" style="50"/>
+    <col min="17" max="17" width="12.25" customWidth="1" style="50"/>
+    <col min="18" max="18" width="12.875" customWidth="1" style="50"/>
+    <col min="19" max="19" width="27.125" customWidth="1" style="50"/>
+    <col min="20" max="20" width="17.375" customWidth="1" style="50"/>
+    <col min="21" max="21" width="36.875" customWidth="1" style="50"/>
+    <col min="22" max="22" width="29.375" customWidth="1" style="50"/>
+    <col min="23" max="23" width="42.875" customWidth="1" style="50"/>
+    <col min="24" max="24" width="25.125" customWidth="1" style="50"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="B1" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" s="50" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+      <c r="W1" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="X1" t="s">
+      <c r="X1" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Y1" s="49" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25">
-      <c r="A2" t="s">
+    <row r="2">
+      <c r="A2" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="O2" t="s">
+      <c r="O2" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="P2" t="s">
+      <c r="P2" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="Q2" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="R2" t="s">
+      <c r="R2" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="S2" t="s">
+      <c r="S2" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="T2" t="s">
+      <c r="T2" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="U2" t="s">
+      <c r="U2" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="V2" t="s">
+      <c r="V2" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="W2" t="s">
+      <c r="W2" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="X2" t="s">
+      <c r="X2" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Y2" s="49" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:25">
-      <c r="A3" t="s">
+    <row r="3">
+      <c r="A3" s="49" t="s">
         <v>29</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="50" t="s">
         <v>31</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="50" t="s">
         <v>35</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="50" t="s">
         <v>38</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" s="50" t="s">
         <v>40</v>
       </c>
-      <c r="M3" t="s">
+      <c r="M3" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="N3" t="s">
+      <c r="N3" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="O3" t="s">
+      <c r="O3" s="50" t="s">
         <v>43</v>
       </c>
-      <c r="P3" t="s">
+      <c r="P3" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="Q3" s="50" t="s">
         <v>45</v>
       </c>
-      <c r="R3" t="s">
+      <c r="R3" s="50" t="s">
         <v>46</v>
       </c>
-      <c r="S3" t="s">
+      <c r="S3" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="T3" t="s">
+      <c r="T3" s="50" t="s">
         <v>48</v>
       </c>
-      <c r="U3" t="s">
+      <c r="U3" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="V3" t="s">
+      <c r="V3" s="50" t="s">
         <v>50</v>
       </c>
-      <c r="W3" t="s">
+      <c r="W3" s="50" t="s">
         <v>51</v>
       </c>
-      <c r="X3" t="s">
+      <c r="X3" s="50" t="s">
         <v>52</v>
       </c>
-      <c r="Y3" t="s">
+      <c r="Y3" s="49" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:25">
-      <c r="A4">
+    <row r="4">
+      <c r="A4" s="49">
         <v>1000001</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="B4" s="49">
+        <v>1</v>
+      </c>
+      <c r="C4" s="50">
+        <v>1</v>
+      </c>
+      <c r="D4" s="50" t="s">
         <v>54</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="50" t="s">
         <v>56</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="50" t="s">
         <v>57</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="50" t="s">
         <v>58</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="50" t="s">
         <v>59</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4" t="s">
+      <c r="K4" s="50">
+        <v>1</v>
+      </c>
+      <c r="L4" s="50" t="s">
         <v>59</v>
       </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-      <c r="N4">
-        <v>1</v>
-      </c>
-      <c r="O4">
+      <c r="M4" s="50">
+        <v>1</v>
+      </c>
+      <c r="N4" s="50">
+        <v>1</v>
+      </c>
+      <c r="O4" s="50">
         <v>5</v>
       </c>
-      <c r="P4">
+      <c r="P4" s="50">
         <v>2</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="50">
         <v>10</v>
       </c>
-      <c r="R4">
-        <v>1</v>
-      </c>
-      <c r="S4" s="2" t="s">
+      <c r="R4" s="50">
+        <v>1</v>
+      </c>
+      <c r="S4" s="51" t="s">
         <v>61</v>
       </c>
-      <c r="T4">
-        <v>1</v>
-      </c>
-      <c r="U4">
+      <c r="T4" s="50">
+        <v>1</v>
+      </c>
+      <c r="U4" s="50">
         <v>10</v>
       </c>
-      <c r="V4">
+      <c r="V4" s="50">
         <v>50</v>
       </c>
-      <c r="W4">
-        <v>1</v>
-      </c>
-      <c r="X4" t="s">
+      <c r="W4" s="50">
+        <v>1</v>
+      </c>
+      <c r="X4" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="Y4" s="49" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:25">
-      <c r="A5">
+    <row r="5">
+      <c r="A5" s="49">
         <v>1000002</v>
       </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
+      <c r="B5" s="49">
+        <v>1</v>
+      </c>
+      <c r="C5" s="50">
         <v>2</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="50" t="s">
         <v>65</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="50" t="s">
         <v>66</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="50">
         <v>20</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="50">
         <v>60</v>
       </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5" t="s">
+      <c r="K5" s="50">
+        <v>1</v>
+      </c>
+      <c r="L5" s="50" t="s">
         <v>68</v>
       </c>
-      <c r="M5" t="s">
+      <c r="M5" s="50" t="s">
         <v>58</v>
       </c>
-      <c r="N5" t="s">
+      <c r="N5" s="50" t="s">
         <v>69</v>
       </c>
-      <c r="O5" t="s">
+      <c r="O5" s="50" t="s">
         <v>70</v>
       </c>
-      <c r="P5">
+      <c r="P5" s="50">
         <v>3</v>
       </c>
-      <c r="Q5" s="3" t="s">
+      <c r="Q5" s="52" t="s">
         <v>71</v>
       </c>
-      <c r="R5">
+      <c r="R5" s="50">
         <v>2</v>
       </c>
-      <c r="S5" t="s">
+      <c r="S5" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="T5">
-        <v>1</v>
-      </c>
-      <c r="U5">
+      <c r="T5" s="50">
+        <v>1</v>
+      </c>
+      <c r="U5" s="50">
         <v>20</v>
       </c>
-      <c r="V5">
+      <c r="V5" s="50">
         <v>100</v>
       </c>
-      <c r="W5">
+      <c r="W5" s="50">
         <v>2</v>
       </c>
-      <c r="X5" t="s">
+      <c r="X5" s="50" t="s">
         <v>73</v>
       </c>
-      <c r="Y5" t="s">
+      <c r="Y5" s="49" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
-      <c r="A6">
+    <row r="6">
+      <c r="A6" s="49">
         <v>1000003</v>
       </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
+      <c r="B6" s="49">
+        <v>1</v>
+      </c>
+      <c r="C6" s="50">
         <v>3</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="50" t="s">
         <v>75</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="50" t="s">
         <v>76</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="50">
         <v>3</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="50" t="s">
+        <v>77</v>
+      </c>
+      <c r="J6" s="50">
+        <v>60</v>
+      </c>
+      <c r="K6" s="50">
+        <v>1</v>
+      </c>
+      <c r="L6" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="M6" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="N6" s="50" t="s">
+        <v>79</v>
+      </c>
+      <c r="O6" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="P6" s="53" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q6" s="50" t="s">
+        <v>82</v>
+      </c>
+      <c r="R6" s="50">
+        <v>3</v>
+      </c>
+      <c r="S6" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="T6" s="50">
+        <v>2</v>
+      </c>
+      <c r="U6" s="50">
         <v>30</v>
       </c>
-      <c r="J6">
+      <c r="V6" s="50">
+        <v>150</v>
+      </c>
+      <c r="W6" s="50">
+        <v>3</v>
+      </c>
+      <c r="X6" s="50" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y6" s="49" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="49">
+        <v>1000004</v>
+      </c>
+      <c r="B7" s="49">
+        <v>1</v>
+      </c>
+      <c r="C7" s="50">
+        <v>4</v>
+      </c>
+      <c r="D7" s="50" t="s">
+        <v>64</v>
+      </c>
+      <c r="E7" s="50" t="s">
+        <v>55</v>
+      </c>
+      <c r="F7" s="50" t="s">
+        <v>86</v>
+      </c>
+      <c r="G7" s="50" t="s">
+        <v>86</v>
+      </c>
+      <c r="H7" s="50">
+        <v>4</v>
+      </c>
+      <c r="I7" s="50">
+        <v>40</v>
+      </c>
+      <c r="J7" s="50">
         <v>60</v>
       </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="L6" t="s">
-        <v>77</v>
-      </c>
-      <c r="M6" t="s">
-        <v>58</v>
-      </c>
-      <c r="N6" t="s">
-        <v>78</v>
-      </c>
-      <c r="O6" t="s">
-        <v>79</v>
-      </c>
-      <c r="P6" s="4" t="s">
+      <c r="K7" s="50">
+        <v>1</v>
+      </c>
+      <c r="L7" s="50">
+        <v>2</v>
+      </c>
+      <c r="M7" s="50">
+        <v>2.5</v>
+      </c>
+      <c r="N7" s="50">
+        <v>1</v>
+      </c>
+      <c r="O7" s="50" t="s">
+        <v>87</v>
+      </c>
+      <c r="P7" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q7" s="50" t="s">
+        <v>89</v>
+      </c>
+      <c r="R7" s="50">
+        <v>4</v>
+      </c>
+      <c r="S7" s="50" t="s">
+        <v>90</v>
+      </c>
+      <c r="T7" s="50">
+        <v>2</v>
+      </c>
+      <c r="U7" s="50">
+        <v>40</v>
+      </c>
+      <c r="V7" s="50">
+        <v>200</v>
+      </c>
+      <c r="W7" s="50">
+        <v>4</v>
+      </c>
+      <c r="X7" s="50" t="s">
+        <v>91</v>
+      </c>
+      <c r="Y7" s="49" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="49">
+        <v>1000005</v>
+      </c>
+      <c r="B8" s="49">
+        <v>1</v>
+      </c>
+      <c r="C8" s="50">
+        <v>5</v>
+      </c>
+      <c r="D8" s="50" t="s">
+        <v>64</v>
+      </c>
+      <c r="E8" s="50" t="s">
+        <v>55</v>
+      </c>
+      <c r="F8" s="50" t="s">
+        <v>86</v>
+      </c>
+      <c r="G8" s="50" t="s">
+        <v>86</v>
+      </c>
+      <c r="H8" s="50">
+        <v>5</v>
+      </c>
+      <c r="I8" s="50">
+        <v>50</v>
+      </c>
+      <c r="J8" s="50">
+        <v>60</v>
+      </c>
+      <c r="K8" s="50">
+        <v>1</v>
+      </c>
+      <c r="L8" s="50">
+        <v>2</v>
+      </c>
+      <c r="M8" s="50">
+        <v>3</v>
+      </c>
+      <c r="N8" s="50">
+        <v>1</v>
+      </c>
+      <c r="O8" s="50" t="s">
+        <v>89</v>
+      </c>
+      <c r="P8" s="53" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q8" s="50" t="s">
+        <v>94</v>
+      </c>
+      <c r="R8" s="50">
+        <v>5</v>
+      </c>
+      <c r="S8" s="50" t="s">
+        <v>95</v>
+      </c>
+      <c r="T8" s="50">
+        <v>2</v>
+      </c>
+      <c r="U8" s="50">
+        <v>50</v>
+      </c>
+      <c r="V8" s="50">
+        <v>250</v>
+      </c>
+      <c r="W8" s="50">
+        <v>5</v>
+      </c>
+      <c r="X8" s="50" t="s">
+        <v>96</v>
+      </c>
+      <c r="Y8" s="49" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="49">
+        <v>1000006</v>
+      </c>
+      <c r="B9" s="49">
+        <v>1</v>
+      </c>
+      <c r="C9" s="50">
+        <v>6</v>
+      </c>
+      <c r="D9" s="50" t="s">
+        <v>64</v>
+      </c>
+      <c r="E9" s="50" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" s="50" t="s">
+        <v>86</v>
+      </c>
+      <c r="G9" s="50" t="s">
+        <v>86</v>
+      </c>
+      <c r="H9" s="50">
+        <v>6</v>
+      </c>
+      <c r="I9" s="50">
+        <v>60</v>
+      </c>
+      <c r="J9" s="50">
+        <v>60</v>
+      </c>
+      <c r="K9" s="50">
+        <v>1</v>
+      </c>
+      <c r="L9" s="50">
+        <v>2</v>
+      </c>
+      <c r="M9" s="50">
+        <v>3.5</v>
+      </c>
+      <c r="N9" s="50">
+        <v>1</v>
+      </c>
+      <c r="O9" s="50" t="s">
+        <v>98</v>
+      </c>
+      <c r="P9" s="50" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q9" s="50" t="s">
+        <v>100</v>
+      </c>
+      <c r="R9" s="50">
+        <v>6</v>
+      </c>
+      <c r="S9" s="50" t="s">
+        <v>101</v>
+      </c>
+      <c r="T9" s="50">
+        <v>3</v>
+      </c>
+      <c r="U9" s="50">
+        <v>60</v>
+      </c>
+      <c r="V9" s="50">
+        <v>300</v>
+      </c>
+      <c r="W9" s="50">
+        <v>6</v>
+      </c>
+      <c r="X9" s="50" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y9" s="49" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="49">
+        <v>1000007</v>
+      </c>
+      <c r="B10" s="49">
+        <v>1</v>
+      </c>
+      <c r="C10" s="50">
+        <v>7</v>
+      </c>
+      <c r="D10" s="50" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" s="50" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="50" t="s">
+        <v>86</v>
+      </c>
+      <c r="G10" s="50" t="s">
+        <v>86</v>
+      </c>
+      <c r="H10" s="50">
+        <v>7</v>
+      </c>
+      <c r="I10" s="50">
+        <v>70</v>
+      </c>
+      <c r="J10" s="50">
+        <v>60</v>
+      </c>
+      <c r="K10" s="50">
+        <v>1</v>
+      </c>
+      <c r="L10" s="50">
+        <v>2</v>
+      </c>
+      <c r="M10" s="50">
+        <v>4</v>
+      </c>
+      <c r="N10" s="50">
+        <v>1</v>
+      </c>
+      <c r="O10" s="50" t="s">
+        <v>104</v>
+      </c>
+      <c r="P10" s="50" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q10" s="50" t="s">
+        <v>105</v>
+      </c>
+      <c r="R10" s="50">
+        <v>7</v>
+      </c>
+      <c r="S10" s="50" t="s">
+        <v>106</v>
+      </c>
+      <c r="T10" s="50">
+        <v>3</v>
+      </c>
+      <c r="U10" s="50">
+        <v>70</v>
+      </c>
+      <c r="V10" s="50">
+        <v>350</v>
+      </c>
+      <c r="W10" s="50">
+        <v>7</v>
+      </c>
+      <c r="X10" s="50" t="s">
+        <v>107</v>
+      </c>
+      <c r="Y10" s="49" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="49">
+        <v>1000008</v>
+      </c>
+      <c r="B11" s="49">
+        <v>1</v>
+      </c>
+      <c r="C11" s="50">
+        <v>8</v>
+      </c>
+      <c r="D11" s="50" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" s="50" t="s">
+        <v>55</v>
+      </c>
+      <c r="F11" s="50" t="s">
+        <v>86</v>
+      </c>
+      <c r="G11" s="50" t="s">
+        <v>86</v>
+      </c>
+      <c r="H11" s="50">
+        <v>8</v>
+      </c>
+      <c r="I11" s="50">
         <v>80</v>
       </c>
-      <c r="Q6" t="s">
-        <v>81</v>
-      </c>
-      <c r="R6">
+      <c r="J11" s="50">
+        <v>60</v>
+      </c>
+      <c r="K11" s="50">
+        <v>1</v>
+      </c>
+      <c r="L11" s="50">
+        <v>2</v>
+      </c>
+      <c r="M11" s="50">
+        <v>4.5</v>
+      </c>
+      <c r="N11" s="50">
+        <v>1</v>
+      </c>
+      <c r="O11" s="50" t="s">
+        <v>109</v>
+      </c>
+      <c r="P11" s="50" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q11" s="50" t="s">
+        <v>110</v>
+      </c>
+      <c r="R11" s="50">
+        <v>8</v>
+      </c>
+      <c r="S11" s="50" t="s">
+        <v>111</v>
+      </c>
+      <c r="T11" s="50">
         <v>3</v>
       </c>
-      <c r="S6" t="s">
-        <v>82</v>
-      </c>
-      <c r="T6">
+      <c r="U11" s="50">
+        <v>80</v>
+      </c>
+      <c r="V11" s="50">
+        <v>400</v>
+      </c>
+      <c r="W11" s="50">
+        <v>8</v>
+      </c>
+      <c r="X11" s="50" t="s">
+        <v>112</v>
+      </c>
+      <c r="Y11" s="49" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="49">
+        <v>1000009</v>
+      </c>
+      <c r="B12" s="49">
+        <v>1</v>
+      </c>
+      <c r="C12" s="50">
+        <v>9</v>
+      </c>
+      <c r="D12" s="50" t="s">
+        <v>64</v>
+      </c>
+      <c r="E12" s="50" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12" s="50" t="s">
+        <v>86</v>
+      </c>
+      <c r="G12" s="50" t="s">
+        <v>86</v>
+      </c>
+      <c r="H12" s="50">
+        <v>9</v>
+      </c>
+      <c r="I12" s="50">
+        <v>90</v>
+      </c>
+      <c r="J12" s="50">
+        <v>60</v>
+      </c>
+      <c r="K12" s="50">
+        <v>1</v>
+      </c>
+      <c r="L12" s="50">
         <v>2</v>
       </c>
-      <c r="U6">
-        <v>30</v>
-      </c>
-      <c r="V6">
-        <v>150</v>
-      </c>
-      <c r="W6">
-        <v>3</v>
-      </c>
-      <c r="X6" t="s">
-        <v>83</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>84</v>
+      <c r="M12" s="50">
+        <v>5</v>
+      </c>
+      <c r="N12" s="50">
+        <v>1</v>
+      </c>
+      <c r="O12" s="50" t="s">
+        <v>114</v>
+      </c>
+      <c r="P12" s="50" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q12" s="50" t="s">
+        <v>115</v>
+      </c>
+      <c r="R12" s="50">
+        <v>9</v>
+      </c>
+      <c r="S12" s="50" t="s">
+        <v>116</v>
+      </c>
+      <c r="T12" s="50">
+        <v>4</v>
+      </c>
+      <c r="U12" s="50">
+        <v>90</v>
+      </c>
+      <c r="V12" s="50">
+        <v>450</v>
+      </c>
+      <c r="W12" s="50">
+        <v>9</v>
+      </c>
+      <c r="X12" s="50" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y12" s="49" t="s">
+        <v>118</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
-      <c r="A7">
-        <v>1000004</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
+    <row r="13">
+      <c r="A13" s="49">
+        <v>1000010</v>
+      </c>
+      <c r="B13" s="49">
+        <v>1</v>
+      </c>
+      <c r="C13" s="50">
+        <v>10</v>
+      </c>
+      <c r="D13" s="50" t="s">
+        <v>64</v>
+      </c>
+      <c r="E13" s="50" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" s="50" t="s">
+        <v>86</v>
+      </c>
+      <c r="G13" s="50" t="s">
+        <v>86</v>
+      </c>
+      <c r="H13" s="50">
+        <v>10</v>
+      </c>
+      <c r="I13" s="50">
+        <v>100</v>
+      </c>
+      <c r="J13" s="50">
+        <v>60</v>
+      </c>
+      <c r="K13" s="50">
+        <v>1</v>
+      </c>
+      <c r="L13" s="50">
+        <v>2</v>
+      </c>
+      <c r="M13" s="50">
+        <v>5.5</v>
+      </c>
+      <c r="N13" s="50">
+        <v>1</v>
+      </c>
+      <c r="O13" s="50" t="s">
+        <v>119</v>
+      </c>
+      <c r="P13" s="50" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q13" s="50" t="s">
+        <v>120</v>
+      </c>
+      <c r="R13" s="50">
+        <v>10</v>
+      </c>
+      <c r="S13" s="50" t="s">
+        <v>121</v>
+      </c>
+      <c r="T13" s="50">
         <v>4</v>
       </c>
-      <c r="D7" t="s">
-        <v>64</v>
-      </c>
-      <c r="E7" t="s">
-        <v>55</v>
-      </c>
-      <c r="F7" t="s">
-        <v>85</v>
-      </c>
-      <c r="G7" t="s">
-        <v>85</v>
-      </c>
-      <c r="H7">
-        <v>4</v>
-      </c>
-      <c r="I7">
-        <v>40</v>
-      </c>
-      <c r="J7">
-        <v>60</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
-      </c>
-      <c r="L7">
-        <v>2</v>
-      </c>
-      <c r="M7">
-        <v>2.5</v>
-      </c>
-      <c r="N7">
-        <v>1</v>
-      </c>
-      <c r="O7" t="s">
-        <v>86</v>
-      </c>
-      <c r="P7" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>88</v>
-      </c>
-      <c r="R7">
-        <v>4</v>
-      </c>
-      <c r="S7" t="s">
-        <v>89</v>
-      </c>
-      <c r="T7">
-        <v>2</v>
-      </c>
-      <c r="U7">
-        <v>40</v>
-      </c>
-      <c r="V7">
-        <v>200</v>
-      </c>
-      <c r="W7">
-        <v>4</v>
-      </c>
-      <c r="X7" t="s">
-        <v>90</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25">
-      <c r="A8">
-        <v>1000005</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8">
-        <v>5</v>
-      </c>
-      <c r="D8" t="s">
-        <v>64</v>
-      </c>
-      <c r="E8" t="s">
-        <v>55</v>
-      </c>
-      <c r="F8" t="s">
-        <v>85</v>
-      </c>
-      <c r="G8" t="s">
-        <v>85</v>
-      </c>
-      <c r="H8">
-        <v>5</v>
-      </c>
-      <c r="I8">
-        <v>50</v>
-      </c>
-      <c r="J8">
-        <v>60</v>
-      </c>
-      <c r="K8">
-        <v>1</v>
-      </c>
-      <c r="L8">
-        <v>2</v>
-      </c>
-      <c r="M8">
-        <v>3</v>
-      </c>
-      <c r="N8">
-        <v>1</v>
-      </c>
-      <c r="O8" t="s">
-        <v>88</v>
-      </c>
-      <c r="P8" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>93</v>
-      </c>
-      <c r="R8">
-        <v>5</v>
-      </c>
-      <c r="S8" t="s">
-        <v>94</v>
-      </c>
-      <c r="T8">
-        <v>2</v>
-      </c>
-      <c r="U8">
-        <v>50</v>
-      </c>
-      <c r="V8">
-        <v>250</v>
-      </c>
-      <c r="W8">
-        <v>5</v>
-      </c>
-      <c r="X8" t="s">
-        <v>95</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25">
-      <c r="A9">
-        <v>1000006</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9">
-        <v>6</v>
-      </c>
-      <c r="D9" t="s">
-        <v>64</v>
-      </c>
-      <c r="E9" t="s">
-        <v>55</v>
-      </c>
-      <c r="F9" t="s">
-        <v>85</v>
-      </c>
-      <c r="G9" t="s">
-        <v>85</v>
-      </c>
-      <c r="H9">
-        <v>6</v>
-      </c>
-      <c r="I9">
-        <v>60</v>
-      </c>
-      <c r="J9">
-        <v>60</v>
-      </c>
-      <c r="K9">
-        <v>1</v>
-      </c>
-      <c r="L9">
-        <v>2</v>
-      </c>
-      <c r="M9">
-        <v>3.5</v>
-      </c>
-      <c r="N9">
-        <v>1</v>
-      </c>
-      <c r="O9" t="s">
-        <v>97</v>
-      </c>
-      <c r="P9" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>99</v>
-      </c>
-      <c r="R9">
-        <v>6</v>
-      </c>
-      <c r="S9" t="s">
+      <c r="U13" s="50">
         <v>100</v>
       </c>
-      <c r="T9">
-        <v>3</v>
-      </c>
-      <c r="U9">
-        <v>60</v>
-      </c>
-      <c r="V9">
-        <v>300</v>
-      </c>
-      <c r="W9">
-        <v>6</v>
-      </c>
-      <c r="X9" t="s">
-        <v>101</v>
-      </c>
-      <c r="Y9" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25">
-      <c r="A10">
-        <v>1000007</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10">
-        <v>7</v>
-      </c>
-      <c r="D10" t="s">
-        <v>64</v>
-      </c>
-      <c r="E10" t="s">
-        <v>55</v>
-      </c>
-      <c r="F10" t="s">
-        <v>85</v>
-      </c>
-      <c r="G10" t="s">
-        <v>85</v>
-      </c>
-      <c r="H10">
-        <v>7</v>
-      </c>
-      <c r="I10">
-        <v>70</v>
-      </c>
-      <c r="J10">
-        <v>60</v>
-      </c>
-      <c r="K10">
-        <v>1</v>
-      </c>
-      <c r="L10">
-        <v>2</v>
-      </c>
-      <c r="M10">
-        <v>4</v>
-      </c>
-      <c r="N10">
-        <v>1</v>
-      </c>
-      <c r="O10" t="s">
-        <v>103</v>
-      </c>
-      <c r="P10" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>104</v>
-      </c>
-      <c r="R10">
-        <v>7</v>
-      </c>
-      <c r="S10" t="s">
-        <v>105</v>
-      </c>
-      <c r="T10">
-        <v>3</v>
-      </c>
-      <c r="U10">
-        <v>70</v>
-      </c>
-      <c r="V10">
-        <v>350</v>
-      </c>
-      <c r="W10">
-        <v>7</v>
-      </c>
-      <c r="X10" t="s">
-        <v>106</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25">
-      <c r="A11">
-        <v>1000008</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11">
-        <v>8</v>
-      </c>
-      <c r="D11" t="s">
-        <v>64</v>
-      </c>
-      <c r="E11" t="s">
-        <v>55</v>
-      </c>
-      <c r="F11" t="s">
-        <v>85</v>
-      </c>
-      <c r="G11" t="s">
-        <v>85</v>
-      </c>
-      <c r="H11">
-        <v>8</v>
-      </c>
-      <c r="I11">
-        <v>80</v>
-      </c>
-      <c r="J11">
-        <v>60</v>
-      </c>
-      <c r="K11">
-        <v>1</v>
-      </c>
-      <c r="L11">
-        <v>2</v>
-      </c>
-      <c r="M11">
-        <v>4.5</v>
-      </c>
-      <c r="N11">
-        <v>1</v>
-      </c>
-      <c r="O11" t="s">
-        <v>108</v>
-      </c>
-      <c r="P11" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>109</v>
-      </c>
-      <c r="R11">
-        <v>8</v>
-      </c>
-      <c r="S11" t="s">
-        <v>110</v>
-      </c>
-      <c r="T11">
-        <v>3</v>
-      </c>
-      <c r="U11">
-        <v>80</v>
-      </c>
-      <c r="V11">
-        <v>400</v>
-      </c>
-      <c r="W11">
-        <v>8</v>
-      </c>
-      <c r="X11" t="s">
-        <v>111</v>
-      </c>
-      <c r="Y11" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25">
-      <c r="A12">
-        <v>1000009</v>
-      </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12">
-        <v>9</v>
-      </c>
-      <c r="D12" t="s">
-        <v>64</v>
-      </c>
-      <c r="E12" t="s">
-        <v>55</v>
-      </c>
-      <c r="F12" t="s">
-        <v>85</v>
-      </c>
-      <c r="G12" t="s">
-        <v>85</v>
-      </c>
-      <c r="H12">
-        <v>9</v>
-      </c>
-      <c r="I12">
-        <v>90</v>
-      </c>
-      <c r="J12">
-        <v>60</v>
-      </c>
-      <c r="K12">
-        <v>1</v>
-      </c>
-      <c r="L12">
-        <v>2</v>
-      </c>
-      <c r="M12">
-        <v>5</v>
-      </c>
-      <c r="N12">
-        <v>1</v>
-      </c>
-      <c r="O12" t="s">
-        <v>113</v>
-      </c>
-      <c r="P12" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>114</v>
-      </c>
-      <c r="R12">
-        <v>9</v>
-      </c>
-      <c r="S12" t="s">
-        <v>115</v>
-      </c>
-      <c r="T12">
-        <v>4</v>
-      </c>
-      <c r="U12">
-        <v>90</v>
-      </c>
-      <c r="V12">
-        <v>450</v>
-      </c>
-      <c r="W12">
-        <v>9</v>
-      </c>
-      <c r="X12" t="s">
-        <v>116</v>
-      </c>
-      <c r="Y12" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25">
-      <c r="A13">
-        <v>1000010</v>
-      </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13">
+      <c r="V13" s="50">
+        <v>500</v>
+      </c>
+      <c r="W13" s="50">
         <v>10</v>
       </c>
-      <c r="D13" t="s">
-        <v>64</v>
-      </c>
-      <c r="E13" t="s">
-        <v>55</v>
-      </c>
-      <c r="F13" t="s">
-        <v>85</v>
-      </c>
-      <c r="G13" t="s">
-        <v>85</v>
-      </c>
-      <c r="H13">
-        <v>10</v>
-      </c>
-      <c r="I13">
-        <v>100</v>
-      </c>
-      <c r="J13">
-        <v>60</v>
-      </c>
-      <c r="K13">
-        <v>1</v>
-      </c>
-      <c r="L13">
-        <v>2</v>
-      </c>
-      <c r="M13">
-        <v>5.5</v>
-      </c>
-      <c r="N13">
-        <v>1</v>
-      </c>
-      <c r="O13" t="s">
-        <v>118</v>
-      </c>
-      <c r="P13" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>119</v>
-      </c>
-      <c r="R13">
-        <v>10</v>
-      </c>
-      <c r="S13" t="s">
-        <v>120</v>
-      </c>
-      <c r="T13">
-        <v>4</v>
-      </c>
-      <c r="U13">
-        <v>100</v>
-      </c>
-      <c r="V13">
-        <v>500</v>
-      </c>
-      <c r="W13">
-        <v>10</v>
-      </c>
-      <c r="X13" t="s">
-        <v>121</v>
-      </c>
-      <c r="Y13" t="s">
+      <c r="X13" s="50" t="s">
         <v>122</v>
+      </c>
+      <c r="Y13" s="49" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="127">
   <si>
     <t>id</t>
   </si>
@@ -295,10 +295,19 @@
     <t>1010010001&amp;1010010001</t>
   </si>
   <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>1.75</t>
+  </si>
+  <si>
     <t>6-9</t>
   </si>
   <si>
-    <t>4-5</t>
+    <t>5</t>
   </si>
   <si>
     <t>7-10</t>
@@ -993,7 +1002,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1139,6 +1148,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="32" applyFill="1" borderId="0" applyBorder="1" xfId="48" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
@@ -1503,1023 +1515,1023 @@
   <dimension ref="A1:Y13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="3" max="3" width="16" customWidth="1" style="50"/>
-    <col min="4" max="4" width="17.125" customWidth="1" style="50"/>
-    <col min="5" max="5" width="36.5" customWidth="1" style="50"/>
-    <col min="6" max="6" width="23.75" customWidth="1" style="50"/>
-    <col min="7" max="7" width="18.375" customWidth="1" style="50"/>
-    <col min="8" max="8" width="31.875" customWidth="1" style="50"/>
-    <col min="9" max="9" width="18.25" customWidth="1" style="50"/>
-    <col min="10" max="16" width="16" customWidth="1" style="50"/>
-    <col min="17" max="17" width="12.25" customWidth="1" style="50"/>
-    <col min="18" max="18" width="12.875" customWidth="1" style="50"/>
-    <col min="19" max="19" width="27.125" customWidth="1" style="50"/>
-    <col min="20" max="20" width="17.375" customWidth="1" style="50"/>
-    <col min="21" max="21" width="36.875" customWidth="1" style="50"/>
-    <col min="22" max="22" width="29.375" customWidth="1" style="50"/>
-    <col min="23" max="23" width="42.875" customWidth="1" style="50"/>
-    <col min="24" max="24" width="25.125" customWidth="1" style="50"/>
+    <col min="3" max="3" width="16" customWidth="1" style="51"/>
+    <col min="4" max="4" width="17.125" customWidth="1" style="51"/>
+    <col min="5" max="5" width="36.5" customWidth="1" style="51"/>
+    <col min="6" max="6" width="23.75" customWidth="1" style="51"/>
+    <col min="7" max="7" width="18.375" customWidth="1" style="51"/>
+    <col min="8" max="8" width="31.875" customWidth="1" style="51"/>
+    <col min="9" max="9" width="18.25" customWidth="1" style="51"/>
+    <col min="10" max="16" width="16" customWidth="1" style="51"/>
+    <col min="17" max="17" width="12.25" customWidth="1" style="51"/>
+    <col min="18" max="18" width="12.875" customWidth="1" style="51"/>
+    <col min="19" max="19" width="27.125" customWidth="1" style="51"/>
+    <col min="20" max="20" width="17.375" customWidth="1" style="51"/>
+    <col min="21" max="21" width="36.875" customWidth="1" style="51"/>
+    <col min="22" max="22" width="29.375" customWidth="1" style="51"/>
+    <col min="23" max="23" width="42.875" customWidth="1" style="51"/>
+    <col min="24" max="24" width="25.125" customWidth="1" style="51"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="50" t="s">
+      <c r="B1" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="50" t="s">
+      <c r="D1" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="50" t="s">
+      <c r="E1" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="50" t="s">
+      <c r="F1" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="50" t="s">
+      <c r="G1" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="50" t="s">
+      <c r="H1" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="50" t="s">
+      <c r="I1" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="50" t="s">
+      <c r="J1" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="50" t="s">
+      <c r="K1" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="50" t="s">
+      <c r="L1" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="50" t="s">
+      <c r="M1" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="50" t="s">
+      <c r="N1" s="51" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="50" t="s">
+      <c r="O1" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="50" t="s">
+      <c r="P1" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="50" t="s">
+      <c r="Q1" s="51" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="50" t="s">
+      <c r="R1" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="50" t="s">
+      <c r="S1" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="50" t="s">
+      <c r="T1" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="50" t="s">
+      <c r="U1" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="50" t="s">
+      <c r="V1" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="50" t="s">
+      <c r="W1" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="50" t="s">
+      <c r="X1" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="49" t="s">
+      <c r="Y1" s="50" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="50" t="s">
+      <c r="C2" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="50" t="s">
+      <c r="D2" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="50" t="s">
+      <c r="E2" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="F2" s="50" t="s">
+      <c r="F2" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="G2" s="50" t="s">
+      <c r="G2" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="50" t="s">
+      <c r="H2" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="50" t="s">
+      <c r="I2" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="J2" s="50" t="s">
+      <c r="J2" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="K2" s="50" t="s">
+      <c r="K2" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="L2" s="50" t="s">
+      <c r="L2" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="M2" s="50" t="s">
+      <c r="M2" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="N2" s="50" t="s">
+      <c r="N2" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="O2" s="50" t="s">
+      <c r="O2" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="P2" s="50" t="s">
+      <c r="P2" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="Q2" s="50" t="s">
+      <c r="Q2" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="R2" s="50" t="s">
+      <c r="R2" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="S2" s="50" t="s">
+      <c r="S2" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="T2" s="50" t="s">
+      <c r="T2" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="U2" s="50" t="s">
+      <c r="U2" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="V2" s="50" t="s">
+      <c r="V2" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="W2" s="50" t="s">
+      <c r="W2" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="X2" s="50" t="s">
+      <c r="X2" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="Y2" s="49" t="s">
+      <c r="Y2" s="50" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="49" t="s">
+      <c r="B3" s="50" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="50" t="s">
+      <c r="C3" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="D3" s="50" t="s">
+      <c r="D3" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="E3" s="50" t="s">
+      <c r="E3" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="50" t="s">
+      <c r="F3" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="G3" s="50" t="s">
+      <c r="G3" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="H3" s="50" t="s">
+      <c r="H3" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="I3" s="50" t="s">
+      <c r="I3" s="51" t="s">
         <v>37</v>
       </c>
-      <c r="J3" s="50" t="s">
+      <c r="J3" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="K3" s="50" t="s">
+      <c r="K3" s="51" t="s">
         <v>39</v>
       </c>
-      <c r="L3" s="50" t="s">
+      <c r="L3" s="51" t="s">
         <v>40</v>
       </c>
-      <c r="M3" s="50" t="s">
+      <c r="M3" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="N3" s="50" t="s">
+      <c r="N3" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="O3" s="50" t="s">
+      <c r="O3" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="P3" s="50" t="s">
+      <c r="P3" s="51" t="s">
         <v>44</v>
       </c>
-      <c r="Q3" s="50" t="s">
+      <c r="Q3" s="51" t="s">
         <v>45</v>
       </c>
-      <c r="R3" s="50" t="s">
+      <c r="R3" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="S3" s="50" t="s">
+      <c r="S3" s="51" t="s">
         <v>47</v>
       </c>
-      <c r="T3" s="50" t="s">
+      <c r="T3" s="51" t="s">
         <v>48</v>
       </c>
-      <c r="U3" s="50" t="s">
+      <c r="U3" s="51" t="s">
         <v>49</v>
       </c>
-      <c r="V3" s="50" t="s">
+      <c r="V3" s="51" t="s">
         <v>50</v>
       </c>
-      <c r="W3" s="50" t="s">
+      <c r="W3" s="51" t="s">
         <v>51</v>
       </c>
-      <c r="X3" s="50" t="s">
+      <c r="X3" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="Y3" s="49" t="s">
+      <c r="Y3" s="50" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="49">
+      <c r="A4" s="50">
         <v>1000001</v>
       </c>
-      <c r="B4" s="49">
-        <v>1</v>
-      </c>
-      <c r="C4" s="50">
-        <v>1</v>
-      </c>
-      <c r="D4" s="50" t="s">
+      <c r="B4" s="50">
+        <v>1</v>
+      </c>
+      <c r="C4" s="51">
+        <v>1</v>
+      </c>
+      <c r="D4" s="51" t="s">
         <v>54</v>
       </c>
-      <c r="E4" s="50" t="s">
+      <c r="E4" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="F4" s="50" t="s">
+      <c r="F4" s="51" t="s">
         <v>56</v>
       </c>
-      <c r="G4" s="50" t="s">
+      <c r="G4" s="51" t="s">
         <v>57</v>
       </c>
-      <c r="H4" s="50" t="s">
+      <c r="H4" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="I4" s="50" t="s">
+      <c r="I4" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="J4" s="50" t="s">
+      <c r="J4" s="51" t="s">
         <v>60</v>
       </c>
-      <c r="K4" s="50">
-        <v>1</v>
-      </c>
-      <c r="L4" s="50" t="s">
+      <c r="K4" s="51">
+        <v>1</v>
+      </c>
+      <c r="L4" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="M4" s="50">
-        <v>1</v>
-      </c>
-      <c r="N4" s="50">
-        <v>1</v>
-      </c>
-      <c r="O4" s="50">
+      <c r="M4" s="51">
+        <v>1</v>
+      </c>
+      <c r="N4" s="51">
+        <v>1</v>
+      </c>
+      <c r="O4" s="51">
         <v>5</v>
       </c>
-      <c r="P4" s="50">
+      <c r="P4" s="51">
         <v>2</v>
       </c>
-      <c r="Q4" s="50">
+      <c r="Q4" s="51">
         <v>10</v>
       </c>
-      <c r="R4" s="50">
-        <v>1</v>
-      </c>
-      <c r="S4" s="51" t="s">
+      <c r="R4" s="51">
+        <v>1</v>
+      </c>
+      <c r="S4" s="52" t="s">
         <v>61</v>
       </c>
-      <c r="T4" s="50">
-        <v>1</v>
-      </c>
-      <c r="U4" s="50">
+      <c r="T4" s="51">
+        <v>1</v>
+      </c>
+      <c r="U4" s="51">
         <v>10</v>
       </c>
-      <c r="V4" s="50">
+      <c r="V4" s="51">
         <v>50</v>
       </c>
-      <c r="W4" s="50">
-        <v>1</v>
-      </c>
-      <c r="X4" s="50" t="s">
+      <c r="W4" s="51">
+        <v>1</v>
+      </c>
+      <c r="X4" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="Y4" s="49" t="s">
+      <c r="Y4" s="50" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="49">
+      <c r="A5" s="50">
         <v>1000002</v>
       </c>
-      <c r="B5" s="49">
-        <v>1</v>
-      </c>
-      <c r="C5" s="50">
+      <c r="B5" s="50">
+        <v>1</v>
+      </c>
+      <c r="C5" s="51">
         <v>2</v>
       </c>
-      <c r="D5" s="50" t="s">
+      <c r="D5" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="E5" s="50" t="s">
+      <c r="E5" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="F5" s="50" t="s">
+      <c r="F5" s="51" t="s">
         <v>65</v>
       </c>
-      <c r="G5" s="50" t="s">
+      <c r="G5" s="51" t="s">
         <v>66</v>
       </c>
-      <c r="H5" s="50" t="s">
+      <c r="H5" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="I5" s="50">
+      <c r="I5" s="51">
         <v>20</v>
       </c>
-      <c r="J5" s="50">
+      <c r="J5" s="51">
         <v>60</v>
       </c>
-      <c r="K5" s="50">
-        <v>1</v>
-      </c>
-      <c r="L5" s="50" t="s">
+      <c r="K5" s="51">
+        <v>1</v>
+      </c>
+      <c r="L5" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="M5" s="50" t="s">
+      <c r="M5" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="N5" s="50" t="s">
+      <c r="N5" s="51" t="s">
         <v>69</v>
       </c>
-      <c r="O5" s="50" t="s">
+      <c r="O5" s="51" t="s">
         <v>70</v>
       </c>
-      <c r="P5" s="50">
+      <c r="P5" s="51">
         <v>3</v>
       </c>
-      <c r="Q5" s="52" t="s">
+      <c r="Q5" s="53" t="s">
         <v>71</v>
       </c>
-      <c r="R5" s="50">
+      <c r="R5" s="51">
         <v>2</v>
       </c>
-      <c r="S5" s="50" t="s">
+      <c r="S5" s="51" t="s">
         <v>72</v>
       </c>
-      <c r="T5" s="50">
-        <v>1</v>
-      </c>
-      <c r="U5" s="50">
+      <c r="T5" s="51">
+        <v>1</v>
+      </c>
+      <c r="U5" s="51">
         <v>20</v>
       </c>
-      <c r="V5" s="50">
+      <c r="V5" s="51">
         <v>100</v>
       </c>
-      <c r="W5" s="50">
+      <c r="W5" s="51">
         <v>2</v>
       </c>
-      <c r="X5" s="50" t="s">
+      <c r="X5" s="51" t="s">
         <v>73</v>
       </c>
-      <c r="Y5" s="49" t="s">
+      <c r="Y5" s="50" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="49">
+      <c r="A6" s="50">
         <v>1000003</v>
       </c>
-      <c r="B6" s="49">
-        <v>1</v>
-      </c>
-      <c r="C6" s="50">
+      <c r="B6" s="50">
+        <v>1</v>
+      </c>
+      <c r="C6" s="51">
         <v>3</v>
       </c>
-      <c r="D6" s="50" t="s">
+      <c r="D6" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="E6" s="50" t="s">
+      <c r="E6" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="F6" s="50" t="s">
+      <c r="F6" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="G6" s="50" t="s">
+      <c r="G6" s="51" t="s">
         <v>76</v>
       </c>
-      <c r="H6" s="50">
+      <c r="H6" s="51">
         <v>3</v>
       </c>
-      <c r="I6" s="50" t="s">
+      <c r="I6" s="51" t="s">
         <v>77</v>
       </c>
-      <c r="J6" s="50">
+      <c r="J6" s="51">
         <v>60</v>
       </c>
-      <c r="K6" s="50">
-        <v>1</v>
-      </c>
-      <c r="L6" s="50" t="s">
+      <c r="K6" s="51">
+        <v>1</v>
+      </c>
+      <c r="L6" s="51" t="s">
         <v>78</v>
       </c>
-      <c r="M6" s="50" t="s">
+      <c r="M6" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="N6" s="50" t="s">
+      <c r="N6" s="51" t="s">
         <v>79</v>
       </c>
-      <c r="O6" s="50" t="s">
+      <c r="O6" s="51" t="s">
         <v>80</v>
       </c>
-      <c r="P6" s="53" t="s">
+      <c r="P6" s="54" t="s">
         <v>81</v>
       </c>
-      <c r="Q6" s="50" t="s">
+      <c r="Q6" s="51" t="s">
         <v>82</v>
       </c>
-      <c r="R6" s="50">
+      <c r="R6" s="51">
         <v>3</v>
       </c>
-      <c r="S6" s="50" t="s">
+      <c r="S6" s="51" t="s">
         <v>83</v>
       </c>
-      <c r="T6" s="50">
+      <c r="T6" s="51">
         <v>2</v>
       </c>
-      <c r="U6" s="50">
+      <c r="U6" s="51">
         <v>30</v>
       </c>
-      <c r="V6" s="50">
+      <c r="V6" s="51">
         <v>150</v>
       </c>
-      <c r="W6" s="50">
+      <c r="W6" s="51">
         <v>3</v>
       </c>
-      <c r="X6" s="50" t="s">
+      <c r="X6" s="51" t="s">
         <v>84</v>
       </c>
-      <c r="Y6" s="49" t="s">
+      <c r="Y6" s="50" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="49">
+      <c r="A7" s="50">
         <v>1000004</v>
       </c>
-      <c r="B7" s="49">
-        <v>1</v>
-      </c>
-      <c r="C7" s="50">
+      <c r="B7" s="50">
+        <v>1</v>
+      </c>
+      <c r="C7" s="51">
         <v>4</v>
       </c>
-      <c r="D7" s="50" t="s">
+      <c r="D7" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="E7" s="50" t="s">
+      <c r="E7" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="F7" s="50" t="s">
+      <c r="F7" s="51" t="s">
         <v>86</v>
       </c>
-      <c r="G7" s="50" t="s">
+      <c r="G7" s="51" t="s">
         <v>86</v>
       </c>
-      <c r="H7" s="50">
+      <c r="H7" s="51">
         <v>4</v>
       </c>
-      <c r="I7" s="50">
+      <c r="I7" s="51" t="s">
+        <v>87</v>
+      </c>
+      <c r="J7" s="51">
+        <v>60</v>
+      </c>
+      <c r="K7" s="51">
+        <v>1</v>
+      </c>
+      <c r="L7" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="M7" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="N7" s="51" t="s">
+        <v>89</v>
+      </c>
+      <c r="O7" s="51" t="s">
+        <v>90</v>
+      </c>
+      <c r="P7" s="54" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q7" s="51" t="s">
+        <v>92</v>
+      </c>
+      <c r="R7" s="51">
+        <v>4</v>
+      </c>
+      <c r="S7" s="51" t="s">
+        <v>93</v>
+      </c>
+      <c r="T7" s="51">
+        <v>2</v>
+      </c>
+      <c r="U7" s="51">
         <v>40</v>
       </c>
-      <c r="J7" s="50">
-        <v>60</v>
-      </c>
-      <c r="K7" s="50">
-        <v>1</v>
-      </c>
-      <c r="L7" s="50">
-        <v>2</v>
-      </c>
-      <c r="M7" s="50">
-        <v>2.5</v>
-      </c>
-      <c r="N7" s="50">
-        <v>1</v>
-      </c>
-      <c r="O7" s="50" t="s">
-        <v>87</v>
-      </c>
-      <c r="P7" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q7" s="50" t="s">
-        <v>89</v>
-      </c>
-      <c r="R7" s="50">
+      <c r="V7" s="51">
+        <v>200</v>
+      </c>
+      <c r="W7" s="51">
         <v>4</v>
       </c>
-      <c r="S7" s="50" t="s">
-        <v>90</v>
-      </c>
-      <c r="T7" s="50">
-        <v>2</v>
-      </c>
-      <c r="U7" s="50">
-        <v>40</v>
-      </c>
-      <c r="V7" s="50">
-        <v>200</v>
-      </c>
-      <c r="W7" s="50">
-        <v>4</v>
-      </c>
-      <c r="X7" s="50" t="s">
-        <v>91</v>
-      </c>
-      <c r="Y7" s="49" t="s">
-        <v>92</v>
+      <c r="X7" s="51" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y7" s="50" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="49">
+      <c r="A8" s="50">
         <v>1000005</v>
       </c>
-      <c r="B8" s="49">
-        <v>1</v>
-      </c>
-      <c r="C8" s="50">
+      <c r="B8" s="50">
+        <v>1</v>
+      </c>
+      <c r="C8" s="51">
         <v>5</v>
       </c>
-      <c r="D8" s="50" t="s">
+      <c r="D8" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="E8" s="50" t="s">
+      <c r="E8" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="F8" s="50" t="s">
+      <c r="F8" s="51" t="s">
         <v>86</v>
       </c>
-      <c r="G8" s="50" t="s">
+      <c r="G8" s="51" t="s">
         <v>86</v>
       </c>
-      <c r="H8" s="50">
+      <c r="H8" s="51">
         <v>5</v>
       </c>
-      <c r="I8" s="50">
+      <c r="I8" s="51">
         <v>50</v>
       </c>
-      <c r="J8" s="50">
+      <c r="J8" s="51">
         <v>60</v>
       </c>
-      <c r="K8" s="50">
-        <v>1</v>
-      </c>
-      <c r="L8" s="50">
+      <c r="K8" s="51">
+        <v>1</v>
+      </c>
+      <c r="L8" s="51">
         <v>2</v>
       </c>
-      <c r="M8" s="50">
+      <c r="M8" s="51">
         <v>3</v>
       </c>
-      <c r="N8" s="50">
-        <v>1</v>
-      </c>
-      <c r="O8" s="50" t="s">
-        <v>89</v>
-      </c>
-      <c r="P8" s="53" t="s">
-        <v>93</v>
-      </c>
-      <c r="Q8" s="50" t="s">
-        <v>94</v>
-      </c>
-      <c r="R8" s="50">
+      <c r="N8" s="51">
+        <v>1</v>
+      </c>
+      <c r="O8" s="51" t="s">
+        <v>92</v>
+      </c>
+      <c r="P8" s="54" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q8" s="51" t="s">
+        <v>97</v>
+      </c>
+      <c r="R8" s="51">
         <v>5</v>
       </c>
-      <c r="S8" s="50" t="s">
-        <v>95</v>
-      </c>
-      <c r="T8" s="50">
+      <c r="S8" s="51" t="s">
+        <v>98</v>
+      </c>
+      <c r="T8" s="51">
         <v>2</v>
       </c>
-      <c r="U8" s="50">
+      <c r="U8" s="51">
         <v>50</v>
       </c>
-      <c r="V8" s="50">
+      <c r="V8" s="51">
         <v>250</v>
       </c>
-      <c r="W8" s="50">
+      <c r="W8" s="51">
         <v>5</v>
       </c>
-      <c r="X8" s="50" t="s">
-        <v>96</v>
-      </c>
-      <c r="Y8" s="49" t="s">
-        <v>97</v>
+      <c r="X8" s="51" t="s">
+        <v>99</v>
+      </c>
+      <c r="Y8" s="50" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="49">
+      <c r="A9" s="50">
         <v>1000006</v>
       </c>
-      <c r="B9" s="49">
-        <v>1</v>
-      </c>
-      <c r="C9" s="50">
+      <c r="B9" s="50">
+        <v>1</v>
+      </c>
+      <c r="C9" s="51">
         <v>6</v>
       </c>
-      <c r="D9" s="50" t="s">
+      <c r="D9" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="E9" s="50" t="s">
+      <c r="E9" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="F9" s="50" t="s">
+      <c r="F9" s="51" t="s">
         <v>86</v>
       </c>
-      <c r="G9" s="50" t="s">
+      <c r="G9" s="51" t="s">
         <v>86</v>
       </c>
-      <c r="H9" s="50">
+      <c r="H9" s="51">
         <v>6</v>
       </c>
-      <c r="I9" s="50">
+      <c r="I9" s="51">
         <v>60</v>
       </c>
-      <c r="J9" s="50">
+      <c r="J9" s="51">
         <v>60</v>
       </c>
-      <c r="K9" s="50">
-        <v>1</v>
-      </c>
-      <c r="L9" s="50">
+      <c r="K9" s="51">
+        <v>1</v>
+      </c>
+      <c r="L9" s="51">
         <v>2</v>
       </c>
-      <c r="M9" s="50">
+      <c r="M9" s="51">
         <v>3.5</v>
       </c>
-      <c r="N9" s="50">
-        <v>1</v>
-      </c>
-      <c r="O9" s="50" t="s">
-        <v>98</v>
-      </c>
-      <c r="P9" s="50" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q9" s="50" t="s">
-        <v>100</v>
-      </c>
-      <c r="R9" s="50">
+      <c r="N9" s="51">
+        <v>1</v>
+      </c>
+      <c r="O9" s="51" t="s">
+        <v>101</v>
+      </c>
+      <c r="P9" s="51" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q9" s="51" t="s">
+        <v>103</v>
+      </c>
+      <c r="R9" s="51">
         <v>6</v>
       </c>
-      <c r="S9" s="50" t="s">
-        <v>101</v>
-      </c>
-      <c r="T9" s="50">
+      <c r="S9" s="51" t="s">
+        <v>104</v>
+      </c>
+      <c r="T9" s="51">
         <v>3</v>
       </c>
-      <c r="U9" s="50">
+      <c r="U9" s="51">
         <v>60</v>
       </c>
-      <c r="V9" s="50">
+      <c r="V9" s="51">
         <v>300</v>
       </c>
-      <c r="W9" s="50">
+      <c r="W9" s="51">
         <v>6</v>
       </c>
-      <c r="X9" s="50" t="s">
-        <v>102</v>
-      </c>
-      <c r="Y9" s="49" t="s">
-        <v>103</v>
+      <c r="X9" s="51" t="s">
+        <v>105</v>
+      </c>
+      <c r="Y9" s="50" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="49">
+      <c r="A10" s="50">
         <v>1000007</v>
       </c>
-      <c r="B10" s="49">
-        <v>1</v>
-      </c>
-      <c r="C10" s="50">
+      <c r="B10" s="50">
+        <v>1</v>
+      </c>
+      <c r="C10" s="51">
         <v>7</v>
       </c>
-      <c r="D10" s="50" t="s">
+      <c r="D10" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="E10" s="50" t="s">
+      <c r="E10" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="F10" s="50" t="s">
+      <c r="F10" s="51" t="s">
         <v>86</v>
       </c>
-      <c r="G10" s="50" t="s">
+      <c r="G10" s="51" t="s">
         <v>86</v>
       </c>
-      <c r="H10" s="50">
+      <c r="H10" s="51">
         <v>7</v>
       </c>
-      <c r="I10" s="50">
+      <c r="I10" s="51">
         <v>70</v>
       </c>
-      <c r="J10" s="50">
+      <c r="J10" s="51">
         <v>60</v>
       </c>
-      <c r="K10" s="50">
-        <v>1</v>
-      </c>
-      <c r="L10" s="50">
+      <c r="K10" s="51">
+        <v>1</v>
+      </c>
+      <c r="L10" s="51">
         <v>2</v>
       </c>
-      <c r="M10" s="50">
+      <c r="M10" s="51">
         <v>4</v>
       </c>
-      <c r="N10" s="50">
-        <v>1</v>
-      </c>
-      <c r="O10" s="50" t="s">
-        <v>104</v>
-      </c>
-      <c r="P10" s="50" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q10" s="50" t="s">
-        <v>105</v>
-      </c>
-      <c r="R10" s="50">
+      <c r="N10" s="51">
+        <v>1</v>
+      </c>
+      <c r="O10" s="51" t="s">
+        <v>107</v>
+      </c>
+      <c r="P10" s="51" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q10" s="51" t="s">
+        <v>108</v>
+      </c>
+      <c r="R10" s="51">
         <v>7</v>
       </c>
-      <c r="S10" s="50" t="s">
-        <v>106</v>
-      </c>
-      <c r="T10" s="50">
+      <c r="S10" s="51" t="s">
+        <v>109</v>
+      </c>
+      <c r="T10" s="51">
         <v>3</v>
       </c>
-      <c r="U10" s="50">
+      <c r="U10" s="51">
         <v>70</v>
       </c>
-      <c r="V10" s="50">
+      <c r="V10" s="51">
         <v>350</v>
       </c>
-      <c r="W10" s="50">
+      <c r="W10" s="51">
         <v>7</v>
       </c>
-      <c r="X10" s="50" t="s">
-        <v>107</v>
-      </c>
-      <c r="Y10" s="49" t="s">
-        <v>108</v>
+      <c r="X10" s="51" t="s">
+        <v>110</v>
+      </c>
+      <c r="Y10" s="50" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="49">
+      <c r="A11" s="50">
         <v>1000008</v>
       </c>
-      <c r="B11" s="49">
-        <v>1</v>
-      </c>
-      <c r="C11" s="50">
+      <c r="B11" s="50">
+        <v>1</v>
+      </c>
+      <c r="C11" s="51">
         <v>8</v>
       </c>
-      <c r="D11" s="50" t="s">
+      <c r="D11" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="E11" s="50" t="s">
+      <c r="E11" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="F11" s="50" t="s">
+      <c r="F11" s="51" t="s">
         <v>86</v>
       </c>
-      <c r="G11" s="50" t="s">
+      <c r="G11" s="51" t="s">
         <v>86</v>
       </c>
-      <c r="H11" s="50">
+      <c r="H11" s="51">
         <v>8</v>
       </c>
-      <c r="I11" s="50">
+      <c r="I11" s="51">
         <v>80</v>
       </c>
-      <c r="J11" s="50">
+      <c r="J11" s="51">
         <v>60</v>
       </c>
-      <c r="K11" s="50">
-        <v>1</v>
-      </c>
-      <c r="L11" s="50">
+      <c r="K11" s="51">
+        <v>1</v>
+      </c>
+      <c r="L11" s="51">
         <v>2</v>
       </c>
-      <c r="M11" s="50">
+      <c r="M11" s="51">
         <v>4.5</v>
       </c>
-      <c r="N11" s="50">
-        <v>1</v>
-      </c>
-      <c r="O11" s="50" t="s">
-        <v>109</v>
-      </c>
-      <c r="P11" s="50" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q11" s="50" t="s">
-        <v>110</v>
-      </c>
-      <c r="R11" s="50">
+      <c r="N11" s="51">
+        <v>1</v>
+      </c>
+      <c r="O11" s="51" t="s">
+        <v>112</v>
+      </c>
+      <c r="P11" s="51" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q11" s="51" t="s">
+        <v>113</v>
+      </c>
+      <c r="R11" s="51">
         <v>8</v>
       </c>
-      <c r="S11" s="50" t="s">
-        <v>111</v>
-      </c>
-      <c r="T11" s="50">
+      <c r="S11" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="T11" s="51">
         <v>3</v>
       </c>
-      <c r="U11" s="50">
+      <c r="U11" s="51">
         <v>80</v>
       </c>
-      <c r="V11" s="50">
+      <c r="V11" s="51">
         <v>400</v>
       </c>
-      <c r="W11" s="50">
+      <c r="W11" s="51">
         <v>8</v>
       </c>
-      <c r="X11" s="50" t="s">
-        <v>112</v>
-      </c>
-      <c r="Y11" s="49" t="s">
-        <v>113</v>
+      <c r="X11" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="Y11" s="50" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="49">
+      <c r="A12" s="50">
         <v>1000009</v>
       </c>
-      <c r="B12" s="49">
-        <v>1</v>
-      </c>
-      <c r="C12" s="50">
+      <c r="B12" s="50">
+        <v>1</v>
+      </c>
+      <c r="C12" s="51">
         <v>9</v>
       </c>
-      <c r="D12" s="50" t="s">
+      <c r="D12" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="E12" s="50" t="s">
+      <c r="E12" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="F12" s="50" t="s">
+      <c r="F12" s="51" t="s">
         <v>86</v>
       </c>
-      <c r="G12" s="50" t="s">
+      <c r="G12" s="51" t="s">
         <v>86</v>
       </c>
-      <c r="H12" s="50">
+      <c r="H12" s="51">
         <v>9</v>
       </c>
-      <c r="I12" s="50">
+      <c r="I12" s="51">
         <v>90</v>
       </c>
-      <c r="J12" s="50">
+      <c r="J12" s="51">
         <v>60</v>
       </c>
-      <c r="K12" s="50">
-        <v>1</v>
-      </c>
-      <c r="L12" s="50">
+      <c r="K12" s="51">
+        <v>1</v>
+      </c>
+      <c r="L12" s="51">
         <v>2</v>
       </c>
-      <c r="M12" s="50">
+      <c r="M12" s="51">
         <v>5</v>
       </c>
-      <c r="N12" s="50">
-        <v>1</v>
-      </c>
-      <c r="O12" s="50" t="s">
-        <v>114</v>
-      </c>
-      <c r="P12" s="50" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q12" s="50" t="s">
-        <v>115</v>
-      </c>
-      <c r="R12" s="50">
+      <c r="N12" s="51">
+        <v>1</v>
+      </c>
+      <c r="O12" s="51" t="s">
+        <v>117</v>
+      </c>
+      <c r="P12" s="51" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q12" s="51" t="s">
+        <v>118</v>
+      </c>
+      <c r="R12" s="51">
         <v>9</v>
       </c>
-      <c r="S12" s="50" t="s">
-        <v>116</v>
-      </c>
-      <c r="T12" s="50">
+      <c r="S12" s="51" t="s">
+        <v>119</v>
+      </c>
+      <c r="T12" s="51">
         <v>4</v>
       </c>
-      <c r="U12" s="50">
+      <c r="U12" s="51">
         <v>90</v>
       </c>
-      <c r="V12" s="50">
+      <c r="V12" s="51">
         <v>450</v>
       </c>
-      <c r="W12" s="50">
+      <c r="W12" s="51">
         <v>9</v>
       </c>
-      <c r="X12" s="50" t="s">
-        <v>117</v>
-      </c>
-      <c r="Y12" s="49" t="s">
-        <v>118</v>
+      <c r="X12" s="51" t="s">
+        <v>120</v>
+      </c>
+      <c r="Y12" s="50" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="49">
+      <c r="A13" s="50">
         <v>1000010</v>
       </c>
-      <c r="B13" s="49">
-        <v>1</v>
-      </c>
-      <c r="C13" s="50">
+      <c r="B13" s="50">
+        <v>1</v>
+      </c>
+      <c r="C13" s="51">
         <v>10</v>
       </c>
-      <c r="D13" s="50" t="s">
+      <c r="D13" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="E13" s="50" t="s">
+      <c r="E13" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="F13" s="50" t="s">
+      <c r="F13" s="51" t="s">
         <v>86</v>
       </c>
-      <c r="G13" s="50" t="s">
+      <c r="G13" s="51" t="s">
         <v>86</v>
       </c>
-      <c r="H13" s="50">
+      <c r="H13" s="51">
         <v>10</v>
       </c>
-      <c r="I13" s="50">
+      <c r="I13" s="51">
         <v>100</v>
       </c>
-      <c r="J13" s="50">
+      <c r="J13" s="51">
         <v>60</v>
       </c>
-      <c r="K13" s="50">
-        <v>1</v>
-      </c>
-      <c r="L13" s="50">
+      <c r="K13" s="51">
+        <v>1</v>
+      </c>
+      <c r="L13" s="51">
         <v>2</v>
       </c>
-      <c r="M13" s="50">
+      <c r="M13" s="51">
         <v>5.5</v>
       </c>
-      <c r="N13" s="50">
-        <v>1</v>
-      </c>
-      <c r="O13" s="50" t="s">
-        <v>119</v>
-      </c>
-      <c r="P13" s="50" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q13" s="50" t="s">
-        <v>120</v>
-      </c>
-      <c r="R13" s="50">
+      <c r="N13" s="51">
+        <v>1</v>
+      </c>
+      <c r="O13" s="51" t="s">
+        <v>122</v>
+      </c>
+      <c r="P13" s="51" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q13" s="51" t="s">
+        <v>123</v>
+      </c>
+      <c r="R13" s="51">
         <v>10</v>
       </c>
-      <c r="S13" s="50" t="s">
-        <v>121</v>
-      </c>
-      <c r="T13" s="50">
+      <c r="S13" s="51" t="s">
+        <v>124</v>
+      </c>
+      <c r="T13" s="51">
         <v>4</v>
       </c>
-      <c r="U13" s="50">
+      <c r="U13" s="51">
         <v>100</v>
       </c>
-      <c r="V13" s="50">
+      <c r="V13" s="51">
         <v>500</v>
       </c>
-      <c r="W13" s="50">
+      <c r="W13" s="51">
         <v>10</v>
       </c>
-      <c r="X13" s="50" t="s">
-        <v>122</v>
-      </c>
-      <c r="Y13" s="49" t="s">
-        <v>123</v>
+      <c r="X13" s="51" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y13" s="50" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
@@ -1,38 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Unity\DemonLordRoguelike\Demon Lord Roguelike\Assets\Data\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12255" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="FightTypeConquerInfo" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="129">
   <si>
     <t>id</t>
   </si>
@@ -292,34 +273,40 @@
     <t>#C0CA33</t>
   </si>
   <si>
+    <t>1040010001&amp;1040020001&amp;1020010001&amp;1030010001&amp;1030020001</t>
+  </si>
+  <si>
+    <t>1041010001&amp;1041020001&amp;1031010001&amp;1031020001&amp;1020020001&amp;1020030001</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>1.75</t>
+  </si>
+  <si>
+    <t>6-9</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>7-10</t>
+  </si>
+  <si>
+    <t>400-450</t>
+  </si>
+  <si>
+    <t>剑与魔法-难度4</t>
+  </si>
+  <si>
+    <t>#FBC02D</t>
+  </si>
+  <si>
     <t>1010010001&amp;1010010001</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>1.75</t>
-  </si>
-  <si>
-    <t>6-9</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>7-10</t>
-  </si>
-  <si>
-    <t>400-450</t>
-  </si>
-  <si>
-    <t>剑与魔法-难度4</t>
-  </si>
-  <si>
-    <t>#FBC02D</t>
   </si>
   <si>
     <t>5-6</t>
@@ -418,12 +405,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="166" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="167" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="19">
     <font>
@@ -1217,11 +1204,74 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1510,10 +1560,13 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:Y13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="3" max="3" width="16" customWidth="1" style="51"/>
     <col min="4" max="4" width="17.125" customWidth="1" style="51"/>
@@ -2015,13 +2068,13 @@
         <v>86</v>
       </c>
       <c r="G7" s="51" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H7" s="51">
         <v>4</v>
       </c>
       <c r="I7" s="51" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J7" s="51">
         <v>60</v>
@@ -2030,28 +2083,28 @@
         <v>1</v>
       </c>
       <c r="L7" s="51" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M7" s="51" t="s">
         <v>58</v>
       </c>
       <c r="N7" s="51" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O7" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P7" s="54" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q7" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R7" s="51">
         <v>4</v>
       </c>
       <c r="S7" s="51" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="T7" s="51">
         <v>2</v>
@@ -2066,10 +2119,10 @@
         <v>4</v>
       </c>
       <c r="X7" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Y7" s="50" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8">
@@ -2089,10 +2142,10 @@
         <v>55</v>
       </c>
       <c r="F8" s="51" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="G8" s="51" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="H8" s="51">
         <v>5</v>
@@ -2116,19 +2169,19 @@
         <v>1</v>
       </c>
       <c r="O8" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P8" s="54" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q8" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="R8" s="51">
         <v>5</v>
       </c>
       <c r="S8" s="51" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="T8" s="51">
         <v>2</v>
@@ -2143,10 +2196,10 @@
         <v>5</v>
       </c>
       <c r="X8" s="51" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="Y8" s="50" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9">
@@ -2166,10 +2219,10 @@
         <v>55</v>
       </c>
       <c r="F9" s="51" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="G9" s="51" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="H9" s="51">
         <v>6</v>
@@ -2193,19 +2246,19 @@
         <v>1</v>
       </c>
       <c r="O9" s="51" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="P9" s="51" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="Q9" s="51" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="R9" s="51">
         <v>6</v>
       </c>
       <c r="S9" s="51" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="T9" s="51">
         <v>3</v>
@@ -2220,10 +2273,10 @@
         <v>6</v>
       </c>
       <c r="X9" s="51" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="Y9" s="50" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10">
@@ -2243,10 +2296,10 @@
         <v>55</v>
       </c>
       <c r="F10" s="51" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="G10" s="51" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="H10" s="51">
         <v>7</v>
@@ -2270,19 +2323,19 @@
         <v>1</v>
       </c>
       <c r="O10" s="51" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="P10" s="51" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="Q10" s="51" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="R10" s="51">
         <v>7</v>
       </c>
       <c r="S10" s="51" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="T10" s="51">
         <v>3</v>
@@ -2297,10 +2350,10 @@
         <v>7</v>
       </c>
       <c r="X10" s="51" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="Y10" s="50" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11">
@@ -2320,10 +2373,10 @@
         <v>55</v>
       </c>
       <c r="F11" s="51" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="G11" s="51" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="H11" s="51">
         <v>8</v>
@@ -2347,19 +2400,19 @@
         <v>1</v>
       </c>
       <c r="O11" s="51" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="P11" s="51" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="Q11" s="51" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="R11" s="51">
         <v>8</v>
       </c>
       <c r="S11" s="51" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="T11" s="51">
         <v>3</v>
@@ -2374,10 +2427,10 @@
         <v>8</v>
       </c>
       <c r="X11" s="51" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="Y11" s="50" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="12">
@@ -2397,10 +2450,10 @@
         <v>55</v>
       </c>
       <c r="F12" s="51" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="G12" s="51" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="H12" s="51">
         <v>9</v>
@@ -2424,19 +2477,19 @@
         <v>1</v>
       </c>
       <c r="O12" s="51" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="P12" s="51" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="Q12" s="51" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="R12" s="51">
         <v>9</v>
       </c>
       <c r="S12" s="51" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="T12" s="51">
         <v>4</v>
@@ -2451,10 +2504,10 @@
         <v>9</v>
       </c>
       <c r="X12" s="51" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="Y12" s="50" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13">
@@ -2474,10 +2527,10 @@
         <v>55</v>
       </c>
       <c r="F13" s="51" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="G13" s="51" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="H13" s="51">
         <v>10</v>
@@ -2501,19 +2554,19 @@
         <v>1</v>
       </c>
       <c r="O13" s="51" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="P13" s="51" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="Q13" s="51" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="R13" s="51">
         <v>10</v>
       </c>
       <c r="S13" s="51" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="T13" s="51">
         <v>4</v>
@@ -2528,35 +2581,35 @@
         <v>10</v>
       </c>
       <c r="X13" s="51" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="Y13" s="50" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1"/>
-    <row r="32" ht="15" customHeight="1"/>
-    <row r="33" ht="15" customHeight="1"/>
-    <row r="34" ht="15" customHeight="1"/>
-    <row r="35" ht="15" customHeight="1"/>
-    <row r="36" ht="15" customHeight="1"/>
-    <row r="37" ht="15" customHeight="1"/>
-    <row r="38" ht="15" customHeight="1"/>
-    <row r="39" ht="15" customHeight="1"/>
-    <row r="40" ht="15" customHeight="1"/>
-    <row r="41" ht="15" customHeight="1"/>
-    <row r="73" ht="12" customHeight="1"/>
-    <row r="74" ht="12" customHeight="1"/>
-    <row r="75" ht="12" customHeight="1"/>
-    <row r="76" ht="12" customHeight="1"/>
-    <row r="77" ht="12" customHeight="1"/>
-    <row r="78" ht="12" customHeight="1"/>
-    <row r="79" ht="12" customHeight="1"/>
-    <row r="80" ht="12" customHeight="1"/>
-    <row r="81" ht="12" customHeight="1"/>
+    <row r="31" ht="15" customHeight="1" s="51" customFormat="1"/>
+    <row r="32" ht="15" customHeight="1" s="51" customFormat="1"/>
+    <row r="33" ht="15" customHeight="1" s="51" customFormat="1"/>
+    <row r="34" ht="15" customHeight="1" s="51" customFormat="1"/>
+    <row r="35" ht="15" customHeight="1" s="51" customFormat="1"/>
+    <row r="36" ht="15" customHeight="1" s="51" customFormat="1"/>
+    <row r="37" ht="15" customHeight="1" s="51" customFormat="1"/>
+    <row r="38" ht="15" customHeight="1" s="51" customFormat="1"/>
+    <row r="39" ht="15" customHeight="1" s="51" customFormat="1"/>
+    <row r="40" ht="15" customHeight="1" s="51" customFormat="1"/>
+    <row r="41" ht="15" customHeight="1" s="51" customFormat="1"/>
+    <row r="73" ht="12" customHeight="1" s="51" customFormat="1"/>
+    <row r="74" ht="12" customHeight="1" s="51" customFormat="1"/>
+    <row r="75" ht="12" customHeight="1" s="51" customFormat="1"/>
+    <row r="76" ht="12" customHeight="1" s="51" customFormat="1"/>
+    <row r="77" ht="12" customHeight="1" s="51" customFormat="1"/>
+    <row r="78" ht="12" customHeight="1" s="51" customFormat="1"/>
+    <row r="79" ht="12" customHeight="1" s="51" customFormat="1"/>
+    <row r="80" ht="12" customHeight="1" s="51" customFormat="1"/>
+    <row r="81" ht="12" customHeight="1" s="51" customFormat="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
   <headerFooter/>
 </worksheet>
 </file>